--- a/Financial Analysis/SNOW.xlsx
+++ b/Financial Analysis/SNOW.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C07BE18-3617-4C20-8F4C-AA27DB5FC170}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6DEF5EF-3C8B-4753-A296-8A0ADAB558F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{BC02690B-70EA-46CB-8D56-DD95DADEB9E1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{BC02690B-70EA-46CB-8D56-DD95DADEB9E1}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -316,9 +316,6 @@
     <t>NPV (FCF)</t>
   </si>
   <si>
-    <t>Q425 8K</t>
-  </si>
-  <si>
     <t>Q126</t>
   </si>
   <si>
@@ -338,6 +335,9 @@
   </si>
   <si>
     <t>CapEx y/y</t>
+  </si>
+  <si>
+    <t>Q126 8K</t>
   </si>
 </sst>
 </file>
@@ -872,17 +872,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="5">
-        <v>138.38999999999999</v>
+        <v>205.72</v>
       </c>
       <c r="E3" s="4">
-        <v>45751</v>
+        <v>45805</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45751</v>
+        <v>45805</v>
       </c>
       <c r="G3" s="4">
-        <v>45798</v>
+        <v>45889</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -890,11 +890,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="6">
-        <f>331.4</f>
-        <v>331.4</v>
+        <f>332.7</f>
+        <v>332.7</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -903,7 +903,7 @@
       </c>
       <c r="D5" s="6">
         <f>D3*D4</f>
-        <v>45862.445999999989</v>
+        <v>68443.043999999994</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -911,11 +911,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="6">
-        <f>2628.8+2008.9+656.5</f>
-        <v>5294.2000000000007</v>
+        <f>2243.1+1667.6+956.1</f>
+        <v>4866.8</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>61</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -923,10 +923,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="6">
-        <v>2269.5</v>
+        <f>2273.6</f>
+        <v>2273.6</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>61</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -935,7 +936,7 @@
       </c>
       <c r="D8" s="6">
         <f>D6-D7</f>
-        <v>3024.7000000000007</v>
+        <v>2593.2000000000003</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -944,7 +945,7 @@
       </c>
       <c r="D9" s="6">
         <f>D5-D8</f>
-        <v>42837.745999999985</v>
+        <v>65849.843999999997</v>
       </c>
     </row>
   </sheetData>
@@ -1167,16 +1168,16 @@
         <v>61</v>
       </c>
       <c r="Y2" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z2" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="Z2" s="7" t="s">
+      <c r="AA2" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="AA2" s="7" t="s">
+      <c r="AB2" s="7" t="s">
         <v>99</v>
-      </c>
-      <c r="AB2" s="7" t="s">
-        <v>100</v>
       </c>
       <c r="AD2">
         <v>2019</v>
@@ -1305,8 +1306,7 @@
         <v>986.8</v>
       </c>
       <c r="Y3" s="9">
-        <f>U3*1.2</f>
-        <v>994.44</v>
+        <v>1042.0999999999999</v>
       </c>
       <c r="Z3" s="9">
         <f>V3*1.2</f>
@@ -1347,47 +1347,47 @@
       </c>
       <c r="AK3" s="9">
         <f>SUM(Y3:AB3)</f>
-        <v>4351.68</v>
+        <v>4399.34</v>
       </c>
       <c r="AL3" s="9">
         <f>AK3*1.24</f>
-        <v>5396.0832</v>
+        <v>5455.1815999999999</v>
       </c>
       <c r="AM3" s="9">
         <f>AL3*1.2</f>
-        <v>6475.2998399999997</v>
+        <v>6546.21792</v>
       </c>
       <c r="AN3" s="9">
         <f>AM3*1.14</f>
-        <v>7381.8418175999986</v>
+        <v>7462.6884287999992</v>
       </c>
       <c r="AO3" s="9">
         <f>AN3*1.11</f>
-        <v>8193.844417536</v>
+        <v>8283.5841559679993</v>
       </c>
       <c r="AP3" s="9">
         <f>AO3*1.09</f>
-        <v>8931.2904151142411</v>
+        <v>9029.10673000512</v>
       </c>
       <c r="AQ3" s="9">
         <f>AP3*1.07</f>
-        <v>9556.4807441722387</v>
+        <v>9661.1442011054787</v>
       </c>
       <c r="AR3" s="9">
         <f>AQ3*1.05</f>
-        <v>10034.304781380852</v>
+        <v>10144.201411160753</v>
       </c>
       <c r="AS3" s="9">
         <f t="shared" ref="AS3:AU3" si="1">AR3*1.05</f>
-        <v>10536.020020449894</v>
+        <v>10651.411481718791</v>
       </c>
       <c r="AT3" s="9">
         <f t="shared" si="1"/>
-        <v>11062.821021472389</v>
+        <v>11183.98205580473</v>
       </c>
       <c r="AU3" s="9">
         <f t="shared" si="1"/>
-        <v>11615.96207254601</v>
+        <v>11743.181158594967</v>
       </c>
       <c r="AV3" s="9"/>
     </row>
@@ -1458,8 +1458,7 @@
         <v>333.2</v>
       </c>
       <c r="Y4" s="6">
-        <f>Y3-Y5</f>
-        <v>328.16520000000003</v>
+        <v>348.8</v>
       </c>
       <c r="Z4" s="6">
         <f t="shared" ref="Z4:AB4" si="2">Z3-Z5</f>
@@ -1500,47 +1499,47 @@
       </c>
       <c r="AK4" s="6">
         <f>SUM(Y4:AB4)</f>
-        <v>1436.0543999999998</v>
+        <v>1456.6891999999998</v>
       </c>
       <c r="AL4" s="6">
         <f t="shared" ref="AL4:AQ4" si="3">AL3-AL5</f>
-        <v>1780.7074559999996</v>
+        <v>1800.2099279999998</v>
       </c>
       <c r="AM4" s="6">
         <f t="shared" si="3"/>
-        <v>2072.0959487999999</v>
+        <v>2094.7897343999994</v>
       </c>
       <c r="AN4" s="6">
         <f t="shared" si="3"/>
-        <v>2288.370963456</v>
+        <v>2313.4334129280005</v>
       </c>
       <c r="AO4" s="6">
         <f t="shared" si="3"/>
-        <v>2458.1533252608006</v>
+        <v>2485.0752467904003</v>
       </c>
       <c r="AP4" s="6">
         <f t="shared" si="3"/>
-        <v>2679.3871245342725</v>
+        <v>2708.7320190015362</v>
       </c>
       <c r="AQ4" s="6">
         <f t="shared" si="3"/>
-        <v>2866.9442232516722</v>
+        <v>2898.3432603316442</v>
       </c>
       <c r="AR4" s="6">
         <f t="shared" ref="AR4:AU4" si="4">AR3-AR5</f>
-        <v>3010.2914344142555</v>
+        <v>3043.2604233482261</v>
       </c>
       <c r="AS4" s="6">
         <f t="shared" si="4"/>
-        <v>3160.8060061349688</v>
+        <v>3195.423444515638</v>
       </c>
       <c r="AT4" s="6">
         <f t="shared" si="4"/>
-        <v>3318.8463064417174</v>
+        <v>3355.1946167414198</v>
       </c>
       <c r="AU4" s="6">
         <f t="shared" si="4"/>
-        <v>3484.7886217638033</v>
+        <v>3522.9543475784903</v>
       </c>
     </row>
     <row r="5" spans="2:160" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1558,7 +1557,7 @@
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
       <c r="G5" s="9">
-        <f t="shared" ref="G5:X5" si="5">G3-G4</f>
+        <f t="shared" ref="G5:Y5" si="5">G3-G4</f>
         <v>92.899999999999991</v>
       </c>
       <c r="H5" s="9">
@@ -1630,8 +1629,8 @@
         <v>653.59999999999991</v>
       </c>
       <c r="Y5" s="9">
-        <f>Y3*0.67</f>
-        <v>666.27480000000003</v>
+        <f t="shared" si="5"/>
+        <v>693.3</v>
       </c>
       <c r="Z5" s="9">
         <f t="shared" ref="Z5:AB5" si="6">Z3*0.67</f>
@@ -1675,47 +1674,47 @@
       </c>
       <c r="AK5" s="9">
         <f>AK3*0.66</f>
-        <v>2872.1088000000004</v>
+        <v>2903.5644000000002</v>
       </c>
       <c r="AL5" s="9">
         <f>AL3*0.67</f>
-        <v>3615.3757440000004</v>
+        <v>3654.9716720000001</v>
       </c>
       <c r="AM5" s="9">
         <f>AM3*0.68</f>
-        <v>4403.2038911999998</v>
+        <v>4451.4281856000007</v>
       </c>
       <c r="AN5" s="9">
         <f>AN3*0.69</f>
-        <v>5093.4708541439986</v>
+        <v>5149.2550158719987</v>
       </c>
       <c r="AO5" s="9">
         <f>AO3*0.7</f>
-        <v>5735.6910922751995</v>
+        <v>5798.508909177599</v>
       </c>
       <c r="AP5" s="9">
         <f t="shared" ref="AP5:AU5" si="8">AP3*0.7</f>
-        <v>6251.9032905799686</v>
+        <v>6320.3747110035838</v>
       </c>
       <c r="AQ5" s="9">
         <f t="shared" si="8"/>
-        <v>6689.5365209205665</v>
+        <v>6762.8009407738346</v>
       </c>
       <c r="AR5" s="9">
         <f t="shared" si="8"/>
-        <v>7024.0133469665961</v>
+        <v>7100.9409878125271</v>
       </c>
       <c r="AS5" s="9">
         <f t="shared" si="8"/>
-        <v>7375.2140143149254</v>
+        <v>7455.988037203153</v>
       </c>
       <c r="AT5" s="9">
         <f t="shared" si="8"/>
-        <v>7743.9747150306721</v>
+        <v>7828.7874390633106</v>
       </c>
       <c r="AU5" s="9">
         <f t="shared" si="8"/>
-        <v>8131.1734507822066</v>
+        <v>8220.2268110164769</v>
       </c>
     </row>
     <row r="6" spans="2:160" x14ac:dyDescent="0.3">
@@ -1785,12 +1784,11 @@
         <v>432.7</v>
       </c>
       <c r="Y6" s="6">
-        <f>Y3*0.43</f>
-        <v>427.60920000000004</v>
+        <v>458.6</v>
       </c>
       <c r="Z6" s="6">
-        <f>Z3*0.41</f>
-        <v>427.44959999999998</v>
+        <f>Z3*0.44</f>
+        <v>458.72639999999996</v>
       </c>
       <c r="AA6" s="6">
         <f>AA3*0.41</f>
@@ -1827,47 +1825,47 @@
       </c>
       <c r="AK6" s="6">
         <f>SUM(Y6:AB6)</f>
-        <v>1792.2360000000001</v>
+        <v>1854.5035999999998</v>
       </c>
       <c r="AL6" s="6">
         <f>AL3*0.35</f>
-        <v>1888.6291199999998</v>
+        <v>1909.3135599999998</v>
       </c>
       <c r="AM6" s="6">
         <f>AM3*0.31</f>
-        <v>2007.3429503999998</v>
+        <v>2029.3275552</v>
       </c>
       <c r="AN6" s="6">
         <f>AN3*0.28</f>
-        <v>2066.9157089279997</v>
+        <v>2089.5527600639998</v>
       </c>
       <c r="AO6" s="6">
         <f>AO3*0.26</f>
-        <v>2130.39954855936</v>
+        <v>2153.7318805516798</v>
       </c>
       <c r="AP6" s="6">
         <f>AP3*0.25</f>
-        <v>2232.8226037785603</v>
+        <v>2257.27668250128</v>
       </c>
       <c r="AQ6" s="6">
         <f>AQ3*0.24</f>
-        <v>2293.555378601337</v>
+        <v>2318.6746082653149</v>
       </c>
       <c r="AR6" s="6">
         <f>AR3*0.23</f>
-        <v>2307.8900997175961</v>
+        <v>2333.1663245669733</v>
       </c>
       <c r="AS6" s="6">
         <f t="shared" ref="AS6:AU6" si="9">AS3*0.23</f>
-        <v>2423.2846047034759</v>
+        <v>2449.824640795322</v>
       </c>
       <c r="AT6" s="6">
         <f t="shared" si="9"/>
-        <v>2544.4488349386497</v>
+        <v>2572.3158728350882</v>
       </c>
       <c r="AU6" s="6">
         <f t="shared" si="9"/>
-        <v>2671.6712766855826</v>
+        <v>2700.9316664768426</v>
       </c>
     </row>
     <row r="7" spans="2:160" x14ac:dyDescent="0.3">
@@ -1937,20 +1935,19 @@
         <v>492.5</v>
       </c>
       <c r="Y7" s="6">
-        <f>U7*1.3</f>
-        <v>534.04000000000008</v>
+        <v>472.4</v>
       </c>
       <c r="Z7" s="6">
-        <f>V7*1.25</f>
-        <v>547.125</v>
+        <f>V7*1.15</f>
+        <v>503.35499999999996</v>
       </c>
       <c r="AA7" s="6">
-        <f t="shared" ref="AA7" si="10">W7*1.25</f>
-        <v>553</v>
+        <f>W7*1.17</f>
+        <v>517.60799999999995</v>
       </c>
       <c r="AB7" s="6">
-        <f>X7*1.2</f>
-        <v>591</v>
+        <f>X7*1.15</f>
+        <v>566.375</v>
       </c>
       <c r="AD7" s="6">
         <v>68.7</v>
@@ -1979,47 +1976,47 @@
       </c>
       <c r="AK7" s="6">
         <f>SUM(Y7:AB7)</f>
-        <v>2225.165</v>
+        <v>2059.7379999999998</v>
       </c>
       <c r="AL7" s="6">
-        <f>AK7*1.15</f>
-        <v>2558.9397499999995</v>
+        <f>AK7*1.07</f>
+        <v>2203.91966</v>
       </c>
       <c r="AM7" s="6">
-        <f>AL7*1.08</f>
-        <v>2763.6549299999997</v>
+        <f>AL7*1.04</f>
+        <v>2292.0764463999999</v>
       </c>
       <c r="AN7" s="6">
-        <f>AM7*1.04</f>
-        <v>2874.2011272</v>
+        <f>AM7*1.03</f>
+        <v>2360.8387397920001</v>
       </c>
       <c r="AO7" s="6">
-        <f>AN7*1.03</f>
-        <v>2960.4271610159999</v>
+        <f>AN7*1.02</f>
+        <v>2408.0555145878402</v>
       </c>
       <c r="AP7" s="6">
-        <f>AO7*1.02</f>
-        <v>3019.6357042363197</v>
+        <f t="shared" ref="AP7:AU7" si="10">AO7*1.02</f>
+        <v>2456.216624879597</v>
       </c>
       <c r="AQ7" s="6">
-        <f>AP7*1.02</f>
-        <v>3080.028418321046</v>
+        <f t="shared" si="10"/>
+        <v>2505.3409573771892</v>
       </c>
       <c r="AR7" s="6">
-        <f t="shared" ref="AR7:AU7" si="11">AQ7*1.02</f>
-        <v>3141.6289866874672</v>
+        <f t="shared" si="10"/>
+        <v>2555.4477765247329</v>
       </c>
       <c r="AS7" s="6">
-        <f t="shared" si="11"/>
-        <v>3204.4615664212165</v>
+        <f t="shared" si="10"/>
+        <v>2606.5567320552277</v>
       </c>
       <c r="AT7" s="6">
-        <f t="shared" si="11"/>
-        <v>3268.5507977496409</v>
+        <f t="shared" si="10"/>
+        <v>2658.6878666963321</v>
       </c>
       <c r="AU7" s="6">
-        <f t="shared" si="11"/>
-        <v>3333.9218137046337</v>
+        <f t="shared" si="10"/>
+        <v>2711.861624030259</v>
       </c>
     </row>
     <row r="8" spans="2:160" x14ac:dyDescent="0.3">
@@ -2089,20 +2086,19 @@
         <v>115.1</v>
       </c>
       <c r="Y8" s="6">
-        <f>U8*1.4</f>
-        <v>130.33999999999997</v>
+        <v>209.6</v>
       </c>
       <c r="Z8" s="6">
-        <f>V8*1.35</f>
-        <v>132.03</v>
+        <f>V8*2.17</f>
+        <v>212.226</v>
       </c>
       <c r="AA8" s="6">
-        <f>W8*1.25</f>
-        <v>132.875</v>
+        <f>W8*2</f>
+        <v>212.6</v>
       </c>
       <c r="AB8" s="6">
-        <f>X8*1.2</f>
-        <v>138.11999999999998</v>
+        <f>X8*2</f>
+        <v>230.2</v>
       </c>
       <c r="AD8" s="6">
         <v>36.1</v>
@@ -2131,47 +2127,47 @@
       </c>
       <c r="AK8" s="6">
         <f>SUM(Y8:AB8)</f>
-        <v>533.36500000000001</v>
+        <v>864.62599999999998</v>
       </c>
       <c r="AL8" s="6">
         <f>AK8*1.1</f>
-        <v>586.70150000000001</v>
+        <v>951.08860000000004</v>
       </c>
       <c r="AM8" s="6">
         <f>AL8*1.05</f>
-        <v>616.03657500000008</v>
+        <v>998.64303000000007</v>
       </c>
       <c r="AN8" s="6">
         <f>AM8*1.04</f>
-        <v>640.67803800000013</v>
+        <v>1038.5887512000002</v>
       </c>
       <c r="AO8" s="6">
         <f>AN8*1.03</f>
-        <v>659.8983791400002</v>
+        <v>1069.7464137360002</v>
       </c>
       <c r="AP8" s="6">
         <f>AO8*1.02</f>
-        <v>673.09634672280026</v>
+        <v>1091.1413420107203</v>
       </c>
       <c r="AQ8" s="6">
         <f>AP8*1.02</f>
-        <v>686.55827365725634</v>
+        <v>1112.9641688509348</v>
       </c>
       <c r="AR8" s="6">
-        <f t="shared" ref="AR8:AU8" si="12">AQ8*1.02</f>
-        <v>700.28943913040143</v>
+        <f t="shared" ref="AR8:AU8" si="11">AQ8*1.02</f>
+        <v>1135.2234522279534</v>
       </c>
       <c r="AS8" s="6">
-        <f t="shared" si="12"/>
-        <v>714.29522791300951</v>
+        <f t="shared" si="11"/>
+        <v>1157.9279212725125</v>
       </c>
       <c r="AT8" s="6">
-        <f t="shared" si="12"/>
-        <v>728.58113247126971</v>
+        <f t="shared" si="11"/>
+        <v>1181.0864796979629</v>
       </c>
       <c r="AU8" s="6">
-        <f t="shared" si="12"/>
-        <v>743.15275512069513</v>
+        <f t="shared" si="11"/>
+        <v>1204.7082092919222</v>
       </c>
     </row>
     <row r="9" spans="2:160" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2189,92 +2185,92 @@
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
       <c r="G9" s="9">
-        <f t="shared" ref="G9:AB9" si="13">G5-G6-G7-G8</f>
+        <f t="shared" ref="G9:AB9" si="12">G5-G6-G7-G8</f>
         <v>-169.39999999999998</v>
       </c>
       <c r="H9" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>-200.4</v>
       </c>
       <c r="I9" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>-205.6</v>
       </c>
       <c r="J9" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>-200.10000000000002</v>
       </c>
       <c r="K9" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>-157.40000000000003</v>
       </c>
       <c r="L9" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>-152</v>
       </c>
       <c r="M9" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>-188.70000000000002</v>
       </c>
       <c r="N9" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>-207.70000000000002</v>
       </c>
       <c r="O9" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>-206.1</v>
       </c>
       <c r="P9" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>-239.79999999999998</v>
       </c>
       <c r="Q9" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>-273.29999999999995</v>
       </c>
       <c r="R9" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>-285.39999999999998</v>
       </c>
       <c r="S9" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>-260.59999999999997</v>
       </c>
       <c r="T9" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>-275.49999999999989</v>
       </c>
       <c r="U9" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>-348.5</v>
       </c>
       <c r="V9" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>-355.40000000000009</v>
       </c>
       <c r="W9" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>-365.49999999999994</v>
       </c>
       <c r="X9" s="9">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>-386.70000000000005</v>
       </c>
       <c r="Y9" s="9">
-        <f t="shared" si="13"/>
-        <v>-425.71440000000007</v>
+        <f t="shared" si="12"/>
+        <v>-447.30000000000007</v>
       </c>
       <c r="Z9" s="9">
-        <f t="shared" si="13"/>
-        <v>-408.08939999999996</v>
+        <f t="shared" si="12"/>
+        <v>-475.79219999999987</v>
       </c>
       <c r="AA9" s="9">
-        <f t="shared" si="13"/>
-        <v>-391.93979999999999</v>
+        <f t="shared" si="12"/>
+        <v>-436.27279999999996</v>
       </c>
       <c r="AB9" s="9">
-        <f t="shared" si="13"/>
-        <v>-409.3968000000001</v>
+        <f t="shared" si="12"/>
+        <v>-476.85180000000008</v>
       </c>
       <c r="AD9" s="9">
         <f>AD5-AD6-AD7-AD8</f>
@@ -2289,64 +2285,64 @@
         <v>-543.90000000000009</v>
       </c>
       <c r="AG9" s="9">
-        <f t="shared" ref="AG9" si="14">AG5-AG6-AG7-AG8</f>
+        <f t="shared" ref="AG9" si="13">AG5-AG6-AG7-AG8</f>
         <v>-715.1</v>
       </c>
       <c r="AH9" s="9">
-        <f t="shared" ref="AH9" si="15">AH5-AH6-AH7-AH8</f>
+        <f t="shared" ref="AH9" si="14">AH5-AH6-AH7-AH8</f>
         <v>-842.30000000000007</v>
       </c>
       <c r="AI9" s="9">
-        <f t="shared" ref="AI9" si="16">AI5-AI6-AI7-AI8</f>
+        <f t="shared" ref="AI9" si="15">AI5-AI6-AI7-AI8</f>
         <v>-1094.8</v>
       </c>
       <c r="AJ9" s="9">
-        <f t="shared" ref="AJ9" si="17">AJ5-AJ6-AJ7-AJ8</f>
+        <f t="shared" ref="AJ9" si="16">AJ5-AJ6-AJ7-AJ8</f>
         <v>-1456.1000000000004</v>
       </c>
       <c r="AK9" s="9">
-        <f t="shared" ref="AK9" si="18">AK5-AK6-AK7-AK8</f>
-        <v>-1678.6571999999996</v>
+        <f t="shared" ref="AK9" si="17">AK5-AK6-AK7-AK8</f>
+        <v>-1875.3031999999994</v>
       </c>
       <c r="AL9" s="9">
-        <f t="shared" ref="AL9" si="19">AL5-AL6-AL7-AL8</f>
-        <v>-1418.8946259999989</v>
+        <f t="shared" ref="AL9" si="18">AL5-AL6-AL7-AL8</f>
+        <v>-1409.3501479999998</v>
       </c>
       <c r="AM9" s="9">
-        <f t="shared" ref="AM9" si="20">AM5-AM6-AM7-AM8</f>
-        <v>-983.83056419999957</v>
+        <f t="shared" ref="AM9" si="19">AM5-AM6-AM7-AM8</f>
+        <v>-868.61884599999928</v>
       </c>
       <c r="AN9" s="9">
-        <f t="shared" ref="AN9" si="21">AN5-AN6-AN7-AN8</f>
-        <v>-488.32401998400121</v>
+        <f t="shared" ref="AN9" si="20">AN5-AN6-AN7-AN8</f>
+        <v>-339.72523518400135</v>
       </c>
       <c r="AO9" s="9">
-        <f t="shared" ref="AO9" si="22">AO5-AO6-AO7-AO8</f>
-        <v>-15.033996440160649</v>
+        <f t="shared" ref="AO9" si="21">AO5-AO6-AO7-AO8</f>
+        <v>166.97510030207877</v>
       </c>
       <c r="AP9" s="9">
-        <f t="shared" ref="AP9" si="23">AP5-AP6-AP7-AP8</f>
-        <v>326.34863584228833</v>
+        <f t="shared" ref="AP9" si="22">AP5-AP6-AP7-AP8</f>
+        <v>515.74006161198645</v>
       </c>
       <c r="AQ9" s="9">
-        <f t="shared" ref="AQ9:AU9" si="24">AQ5-AQ6-AQ7-AQ8</f>
-        <v>629.39445034092716</v>
+        <f t="shared" ref="AQ9:AU9" si="23">AQ5-AQ6-AQ7-AQ8</f>
+        <v>825.82120628039615</v>
       </c>
       <c r="AR9" s="9">
-        <f t="shared" si="24"/>
-        <v>874.20482143113145</v>
+        <f t="shared" si="23"/>
+        <v>1077.1034344928673</v>
       </c>
       <c r="AS9" s="9">
-        <f t="shared" si="24"/>
-        <v>1033.1726152772239</v>
+        <f t="shared" si="23"/>
+        <v>1241.6787430800907</v>
       </c>
       <c r="AT9" s="9">
-        <f t="shared" si="24"/>
-        <v>1202.3939498711113</v>
+        <f t="shared" si="23"/>
+        <v>1416.6972198339274</v>
       </c>
       <c r="AU9" s="9">
-        <f t="shared" si="24"/>
-        <v>1382.4276052712953</v>
+        <f t="shared" si="23"/>
+        <v>1602.7253112174526</v>
       </c>
     </row>
     <row r="10" spans="2:160" x14ac:dyDescent="0.3">
@@ -2416,19 +2412,18 @@
         <v>-56.3</v>
       </c>
       <c r="Y10" s="6">
-        <f>U10*1.05</f>
-        <v>-57.54</v>
+        <v>-53.2</v>
       </c>
       <c r="Z10" s="6">
-        <f t="shared" ref="Z10:AB10" si="25">V10*1.05</f>
+        <f t="shared" ref="Z10:AB10" si="24">V10*1.05</f>
         <v>-51.765000000000001</v>
       </c>
       <c r="AA10" s="6">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>-51.135000000000005</v>
       </c>
       <c r="AB10" s="6">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>-59.115000000000002</v>
       </c>
       <c r="AD10" s="6">
@@ -2458,47 +2453,47 @@
       </c>
       <c r="AK10" s="6">
         <f>SUM(Y10:AB10)</f>
-        <v>-219.55500000000001</v>
+        <v>-215.21500000000003</v>
       </c>
       <c r="AL10" s="6">
-        <f t="shared" ref="AL10" si="26">AK10*1.02</f>
-        <v>-223.9461</v>
+        <f t="shared" ref="AL10" si="25">AK10*1.02</f>
+        <v>-219.51930000000004</v>
       </c>
       <c r="AM10" s="6">
-        <f t="shared" ref="AM10" si="27">AL10*1.02</f>
-        <v>-228.42502200000001</v>
+        <f t="shared" ref="AM10" si="26">AL10*1.02</f>
+        <v>-223.90968600000005</v>
       </c>
       <c r="AN10" s="6">
-        <f t="shared" ref="AN10" si="28">AM10*1.02</f>
-        <v>-232.99352244000002</v>
+        <f t="shared" ref="AN10" si="27">AM10*1.02</f>
+        <v>-228.38787972000006</v>
       </c>
       <c r="AO10" s="6">
-        <f t="shared" ref="AO10" si="29">AN10*1.02</f>
-        <v>-237.65339288880003</v>
+        <f t="shared" ref="AO10" si="28">AN10*1.02</f>
+        <v>-232.95563731440006</v>
       </c>
       <c r="AP10" s="6">
-        <f t="shared" ref="AP10" si="30">AO10*1.02</f>
-        <v>-242.40646074657604</v>
+        <f t="shared" ref="AP10" si="29">AO10*1.02</f>
+        <v>-237.61475006068807</v>
       </c>
       <c r="AQ10" s="6">
-        <f t="shared" ref="AQ10" si="31">AP10*1.02</f>
-        <v>-247.25458996150758</v>
+        <f t="shared" ref="AQ10" si="30">AP10*1.02</f>
+        <v>-242.36704506190182</v>
       </c>
       <c r="AR10" s="6">
-        <f t="shared" ref="AR10" si="32">AQ10*1.02</f>
-        <v>-252.19968176073775</v>
+        <f t="shared" ref="AR10" si="31">AQ10*1.02</f>
+        <v>-247.21438596313985</v>
       </c>
       <c r="AS10" s="6">
-        <f t="shared" ref="AS10" si="33">AR10*1.02</f>
-        <v>-257.24367539595249</v>
+        <f t="shared" ref="AS10" si="32">AR10*1.02</f>
+        <v>-252.15867368240265</v>
       </c>
       <c r="AT10" s="6">
-        <f t="shared" ref="AT10" si="34">AS10*1.02</f>
-        <v>-262.38854890387154</v>
+        <f t="shared" ref="AT10" si="33">AS10*1.02</f>
+        <v>-257.20184715605069</v>
       </c>
       <c r="AU10" s="6">
-        <f t="shared" ref="AU10" si="35">AT10*1.02</f>
-        <v>-267.63631988194896</v>
+        <f t="shared" ref="AU10" si="34">AT10*1.02</f>
+        <v>-262.34588409917171</v>
       </c>
     </row>
     <row r="11" spans="2:160" x14ac:dyDescent="0.3">
@@ -2560,7 +2555,7 @@
         <v>2.1</v>
       </c>
       <c r="Y11" s="6">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z11" s="6">
         <v>0</v>
@@ -2586,7 +2581,7 @@
       </c>
       <c r="AK11" s="6">
         <f>SUM(Y11:AB11)</f>
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL11" s="6"/>
       <c r="AM11" s="6"/>
@@ -2666,7 +2661,7 @@
         <v>-2.4</v>
       </c>
       <c r="Y12" s="6">
-        <v>0</v>
+        <v>28.1</v>
       </c>
       <c r="Z12" s="6">
         <v>0</v>
@@ -2704,7 +2699,7 @@
       </c>
       <c r="AK12" s="6">
         <f>SUM(Y12:AB12)</f>
-        <v>0</v>
+        <v>28.1</v>
       </c>
       <c r="AL12" s="6">
         <v>0</v>
@@ -2760,156 +2755,156 @@
         <v>-197.5</v>
       </c>
       <c r="I13" s="9">
-        <f t="shared" ref="I13:AB13" si="36">I9-SUM(I10:I12)</f>
+        <f t="shared" ref="I13:AB13" si="35">I9-SUM(I10:I12)</f>
         <v>-203.5</v>
       </c>
       <c r="J13" s="9">
+        <f t="shared" si="35"/>
+        <v>-189.20000000000002</v>
+      </c>
+      <c r="K13" s="9">
+        <f t="shared" si="35"/>
+        <v>-153.80000000000004</v>
+      </c>
+      <c r="L13" s="9">
+        <f t="shared" si="35"/>
+        <v>-130.6</v>
+      </c>
+      <c r="M13" s="9">
+        <f t="shared" si="35"/>
+        <v>-192.4</v>
+      </c>
+      <c r="N13" s="9">
+        <f t="shared" si="35"/>
+        <v>-218.9</v>
+      </c>
+      <c r="O13" s="9">
+        <f t="shared" si="35"/>
+        <v>-197.5</v>
+      </c>
+      <c r="P13" s="9">
+        <f t="shared" si="35"/>
+        <v>-207.2</v>
+      </c>
+      <c r="Q13" s="9">
+        <f t="shared" si="35"/>
+        <v>-232.79999999999995</v>
+      </c>
+      <c r="R13" s="9">
+        <f t="shared" si="35"/>
+        <v>-230.99999999999997</v>
+      </c>
+      <c r="S13" s="9">
+        <f t="shared" si="35"/>
+        <v>-211.29999999999995</v>
+      </c>
+      <c r="T13" s="9">
+        <f t="shared" si="35"/>
+        <v>-174.19999999999987</v>
+      </c>
+      <c r="U13" s="9">
+        <f t="shared" si="35"/>
+        <v>-315</v>
+      </c>
+      <c r="V13" s="9">
+        <f t="shared" si="35"/>
+        <v>-314.00000000000011</v>
+      </c>
+      <c r="W13" s="9">
+        <f t="shared" si="35"/>
+        <v>-325.99999999999994</v>
+      </c>
+      <c r="X13" s="9">
+        <f t="shared" si="35"/>
+        <v>-330.1</v>
+      </c>
+      <c r="Y13" s="9">
+        <f t="shared" si="35"/>
+        <v>-424.30000000000007</v>
+      </c>
+      <c r="Z13" s="9">
+        <f t="shared" si="35"/>
+        <v>-424.02719999999988</v>
+      </c>
+      <c r="AA13" s="9">
+        <f t="shared" si="35"/>
+        <v>-385.13779999999997</v>
+      </c>
+      <c r="AB13" s="9">
+        <f t="shared" si="35"/>
+        <v>-417.73680000000007</v>
+      </c>
+      <c r="AD13" s="9">
+        <f t="shared" ref="AD13:AQ13" si="36">AD9-SUM(AD10:AD12)</f>
+        <v>-177.1</v>
+      </c>
+      <c r="AE13" s="9">
         <f t="shared" si="36"/>
-        <v>-189.20000000000002</v>
-      </c>
-      <c r="K13" s="9">
+        <v>-347.5</v>
+      </c>
+      <c r="AF13" s="9">
         <f t="shared" si="36"/>
-        <v>-153.80000000000004</v>
-      </c>
-      <c r="L13" s="9">
+        <v>-537.00000000000011</v>
+      </c>
+      <c r="AG13" s="9">
         <f t="shared" si="36"/>
-        <v>-130.6</v>
-      </c>
-      <c r="M13" s="9">
+        <v>-677.1</v>
+      </c>
+      <c r="AH13" s="9">
         <f t="shared" si="36"/>
-        <v>-192.4</v>
-      </c>
-      <c r="N13" s="9">
+        <v>-816.00000000000011</v>
+      </c>
+      <c r="AI13" s="9">
         <f t="shared" si="36"/>
-        <v>-218.9</v>
-      </c>
-      <c r="O13" s="9">
+        <v>-849.3</v>
+      </c>
+      <c r="AJ13" s="9">
         <f t="shared" si="36"/>
-        <v>-197.5</v>
-      </c>
-      <c r="P13" s="9">
+        <v>-1285.1000000000004</v>
+      </c>
+      <c r="AK13" s="9">
         <f t="shared" si="36"/>
-        <v>-207.2</v>
-      </c>
-      <c r="Q13" s="9">
+        <v>-1690.2881999999993</v>
+      </c>
+      <c r="AL13" s="9">
         <f t="shared" si="36"/>
-        <v>-232.79999999999995</v>
-      </c>
-      <c r="R13" s="9">
+        <v>-1189.8308479999996</v>
+      </c>
+      <c r="AM13" s="9">
         <f t="shared" si="36"/>
-        <v>-230.99999999999997</v>
-      </c>
-      <c r="S13" s="9">
+        <v>-644.7091599999992</v>
+      </c>
+      <c r="AN13" s="9">
         <f t="shared" si="36"/>
-        <v>-211.29999999999995</v>
-      </c>
-      <c r="T13" s="9">
+        <v>-111.33735546400129</v>
+      </c>
+      <c r="AO13" s="9">
         <f t="shared" si="36"/>
-        <v>-174.19999999999987</v>
-      </c>
-      <c r="U13" s="9">
+        <v>399.93073761647884</v>
+      </c>
+      <c r="AP13" s="9">
         <f t="shared" si="36"/>
-        <v>-315</v>
-      </c>
-      <c r="V13" s="9">
+        <v>753.35481167267449</v>
+      </c>
+      <c r="AQ13" s="9">
         <f t="shared" si="36"/>
-        <v>-314.00000000000011</v>
-      </c>
-      <c r="W13" s="9">
-        <f t="shared" si="36"/>
-        <v>-325.99999999999994</v>
-      </c>
-      <c r="X13" s="9">
-        <f t="shared" si="36"/>
-        <v>-330.1</v>
-      </c>
-      <c r="Y13" s="9">
-        <f t="shared" si="36"/>
-        <v>-368.17440000000005</v>
-      </c>
-      <c r="Z13" s="9">
-        <f t="shared" si="36"/>
-        <v>-356.32439999999997</v>
-      </c>
-      <c r="AA13" s="9">
-        <f t="shared" si="36"/>
-        <v>-340.8048</v>
-      </c>
-      <c r="AB13" s="9">
-        <f t="shared" si="36"/>
-        <v>-350.28180000000009</v>
-      </c>
-      <c r="AD13" s="9">
-        <f t="shared" ref="AD13:AQ13" si="37">AD9-SUM(AD10:AD12)</f>
-        <v>-177.1</v>
-      </c>
-      <c r="AE13" s="9">
-        <f t="shared" si="37"/>
-        <v>-347.5</v>
-      </c>
-      <c r="AF13" s="9">
-        <f t="shared" si="37"/>
-        <v>-537.00000000000011</v>
-      </c>
-      <c r="AG13" s="9">
-        <f t="shared" si="37"/>
-        <v>-677.1</v>
-      </c>
-      <c r="AH13" s="9">
-        <f t="shared" si="37"/>
-        <v>-816.00000000000011</v>
-      </c>
-      <c r="AI13" s="9">
-        <f t="shared" si="37"/>
-        <v>-849.3</v>
-      </c>
-      <c r="AJ13" s="9">
-        <f t="shared" si="37"/>
-        <v>-1285.1000000000004</v>
-      </c>
-      <c r="AK13" s="9">
-        <f t="shared" si="37"/>
-        <v>-1459.1021999999996</v>
-      </c>
-      <c r="AL13" s="9">
-        <f t="shared" si="37"/>
-        <v>-1194.9485259999988</v>
-      </c>
-      <c r="AM13" s="9">
-        <f t="shared" si="37"/>
-        <v>-755.40554219999956</v>
-      </c>
-      <c r="AN13" s="9">
-        <f t="shared" si="37"/>
-        <v>-255.33049754400119</v>
-      </c>
-      <c r="AO13" s="9">
-        <f t="shared" si="37"/>
-        <v>222.61939644863938</v>
-      </c>
-      <c r="AP13" s="9">
-        <f t="shared" si="37"/>
-        <v>568.75509658886438</v>
-      </c>
-      <c r="AQ13" s="9">
-        <f t="shared" si="37"/>
-        <v>876.64904030243474</v>
+        <v>1068.1882513422979</v>
       </c>
       <c r="AR13" s="9">
-        <f t="shared" ref="AR13" si="38">AR9-SUM(AR10:AR12)</f>
-        <v>1126.4045031918693</v>
+        <f t="shared" ref="AR13" si="37">AR9-SUM(AR10:AR12)</f>
+        <v>1324.3178204560072</v>
       </c>
       <c r="AS13" s="9">
-        <f t="shared" ref="AS13" si="39">AS9-SUM(AS10:AS12)</f>
-        <v>1290.4162906731765</v>
+        <f t="shared" ref="AS13" si="38">AS9-SUM(AS10:AS12)</f>
+        <v>1493.8374167624934</v>
       </c>
       <c r="AT13" s="9">
-        <f t="shared" ref="AT13" si="40">AT9-SUM(AT10:AT12)</f>
-        <v>1464.7824987749827</v>
+        <f t="shared" ref="AT13" si="39">AT9-SUM(AT10:AT12)</f>
+        <v>1673.8990669899781</v>
       </c>
       <c r="AU13" s="9">
-        <f t="shared" ref="AU13" si="41">AU9-SUM(AU10:AU12)</f>
-        <v>1650.0639251532443</v>
+        <f t="shared" ref="AU13" si="40">AU9-SUM(AU10:AU12)</f>
+        <v>1865.0711953166242</v>
       </c>
     </row>
     <row r="14" spans="2:160" x14ac:dyDescent="0.3">
@@ -2979,7 +2974,7 @@
         <v>-4.3</v>
       </c>
       <c r="Y14" s="6">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="Z14" s="6">
         <v>0</v>
@@ -3017,46 +3012,46 @@
       </c>
       <c r="AK14" s="6">
         <f>SUM(Y14:AB14)</f>
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AL14" s="6">
         <v>0</v>
       </c>
       <c r="AM14" s="6">
         <f>AM13*0.05</f>
-        <v>-37.770277109999981</v>
+        <v>-32.235457999999959</v>
       </c>
       <c r="AN14" s="6">
         <f>AN13*0.05</f>
-        <v>-12.766524877200061</v>
+        <v>-5.5668677732000651</v>
       </c>
       <c r="AO14" s="6">
         <f>AO13*0.1</f>
-        <v>22.26193964486394</v>
+        <v>39.993073761647885</v>
       </c>
       <c r="AP14" s="6">
         <f>AP13*0.1</f>
-        <v>56.875509658886443</v>
+        <v>75.335481167267446</v>
       </c>
       <c r="AQ14" s="6">
         <f>AQ13*0.11</f>
-        <v>96.431394433267826</v>
+        <v>117.50070764765277</v>
       </c>
       <c r="AR14" s="6">
-        <f t="shared" ref="AR14:AU14" si="42">AR13*0.15</f>
-        <v>168.96067547878039</v>
+        <f t="shared" ref="AR14:AU14" si="41">AR13*0.15</f>
+        <v>198.64767306840108</v>
       </c>
       <c r="AS14" s="6">
-        <f t="shared" si="42"/>
-        <v>193.56244360097648</v>
+        <f t="shared" si="41"/>
+        <v>224.075612514374</v>
       </c>
       <c r="AT14" s="6">
-        <f t="shared" si="42"/>
-        <v>219.7173748162474</v>
+        <f t="shared" si="41"/>
+        <v>251.08486004849669</v>
       </c>
       <c r="AU14" s="6">
-        <f t="shared" si="42"/>
-        <v>247.50958877298663</v>
+        <f t="shared" si="41"/>
+        <v>279.7606792974936</v>
       </c>
     </row>
     <row r="15" spans="2:160" x14ac:dyDescent="0.3">
@@ -3118,20 +3113,19 @@
         <v>1.8</v>
       </c>
       <c r="Y15" s="6">
-        <f>Y13*0.005</f>
-        <v>-1.8408720000000003</v>
+        <v>0.1</v>
       </c>
       <c r="Z15" s="6">
-        <f t="shared" ref="Z15:AB15" si="43">Z13*0.005</f>
-        <v>-1.7816219999999998</v>
+        <f t="shared" ref="Z15:AB15" si="42">Z13*0.005</f>
+        <v>-2.1201359999999996</v>
       </c>
       <c r="AA15" s="6">
-        <f t="shared" si="43"/>
-        <v>-1.704024</v>
+        <f t="shared" si="42"/>
+        <v>-1.925689</v>
       </c>
       <c r="AB15" s="6">
-        <f t="shared" si="43"/>
-        <v>-1.7514090000000004</v>
+        <f t="shared" si="42"/>
+        <v>-2.0886840000000002</v>
       </c>
       <c r="AD15" s="6"/>
       <c r="AE15" s="6"/>
@@ -3151,47 +3145,47 @@
       </c>
       <c r="AK15" s="6">
         <f>SUM(Y15:AB15)</f>
-        <v>-7.0779270000000007</v>
+        <v>-6.0345089999999999</v>
       </c>
       <c r="AL15" s="6">
-        <f t="shared" ref="AL15:AU15" si="44">AL13*0.01</f>
-        <v>-11.949485259999989</v>
+        <f t="shared" ref="AL15:AU15" si="43">AL13*0.01</f>
+        <v>-11.898308479999995</v>
       </c>
       <c r="AM15" s="6">
-        <f t="shared" si="44"/>
-        <v>-7.5540554219999958</v>
+        <f t="shared" si="43"/>
+        <v>-6.4470915999999923</v>
       </c>
       <c r="AN15" s="6">
-        <f t="shared" si="44"/>
-        <v>-2.5533049754400121</v>
+        <f t="shared" si="43"/>
+        <v>-1.113373554640013</v>
       </c>
       <c r="AO15" s="6">
-        <f t="shared" si="44"/>
-        <v>2.2261939644863937</v>
+        <f t="shared" si="43"/>
+        <v>3.9993073761647886</v>
       </c>
       <c r="AP15" s="6">
-        <f t="shared" si="44"/>
-        <v>5.6875509658886436</v>
+        <f t="shared" si="43"/>
+        <v>7.5335481167267453</v>
       </c>
       <c r="AQ15" s="6">
-        <f t="shared" si="44"/>
-        <v>8.7664904030243473</v>
+        <f t="shared" si="43"/>
+        <v>10.681882513422979</v>
       </c>
       <c r="AR15" s="6">
-        <f t="shared" si="44"/>
-        <v>11.264045031918693</v>
+        <f t="shared" si="43"/>
+        <v>13.243178204560072</v>
       </c>
       <c r="AS15" s="6">
-        <f t="shared" si="44"/>
-        <v>12.904162906731765</v>
+        <f t="shared" si="43"/>
+        <v>14.938374167624934</v>
       </c>
       <c r="AT15" s="6">
-        <f t="shared" si="44"/>
-        <v>14.647824987749829</v>
+        <f t="shared" si="43"/>
+        <v>16.738990669899781</v>
       </c>
       <c r="AU15" s="6">
-        <f t="shared" si="44"/>
-        <v>16.500639251532444</v>
+        <f t="shared" si="43"/>
+        <v>18.650711953166244</v>
       </c>
     </row>
     <row r="16" spans="2:160" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3217,608 +3211,608 @@
         <v>-198.8</v>
       </c>
       <c r="I16" s="9">
-        <f t="shared" ref="I16:X16" si="45">I13-I14-I15</f>
+        <f t="shared" ref="I16:X16" si="44">I13-I14-I15</f>
         <v>-203.2</v>
       </c>
       <c r="J16" s="9">
+        <f t="shared" si="44"/>
+        <v>-189.70000000000002</v>
+      </c>
+      <c r="K16" s="9">
+        <f t="shared" si="44"/>
+        <v>-155.00000000000003</v>
+      </c>
+      <c r="L16" s="9">
+        <f t="shared" si="44"/>
+        <v>-132.1</v>
+      </c>
+      <c r="M16" s="9">
+        <f t="shared" si="44"/>
+        <v>-165.70000000000002</v>
+      </c>
+      <c r="N16" s="9">
+        <f t="shared" si="44"/>
+        <v>-222.70000000000002</v>
+      </c>
+      <c r="O16" s="9">
+        <f t="shared" si="44"/>
+        <v>-201</v>
+      </c>
+      <c r="P16" s="9">
+        <f t="shared" si="44"/>
+        <v>-207.29999999999998</v>
+      </c>
+      <c r="Q16" s="9">
+        <f t="shared" si="44"/>
+        <v>-225.79999999999995</v>
+      </c>
+      <c r="R16" s="9">
+        <f t="shared" si="44"/>
+        <v>-226.79999999999998</v>
+      </c>
+      <c r="S16" s="9">
+        <f t="shared" si="44"/>
+        <v>-214.29999999999995</v>
+      </c>
+      <c r="T16" s="9">
+        <f t="shared" si="44"/>
+        <v>-169.29999999999987</v>
+      </c>
+      <c r="U16" s="9">
+        <f t="shared" si="44"/>
+        <v>-316.89999999999998</v>
+      </c>
+      <c r="V16" s="9">
+        <f t="shared" si="44"/>
+        <v>-316.90000000000015</v>
+      </c>
+      <c r="W16" s="9">
+        <f t="shared" si="44"/>
+        <v>-324.2999999999999</v>
+      </c>
+      <c r="X16" s="9">
+        <f t="shared" si="44"/>
+        <v>-327.60000000000002</v>
+      </c>
+      <c r="Y16" s="9">
+        <f t="shared" ref="Y16:AB16" si="45">Y13-Y14-Y15</f>
+        <v>-430.10000000000008</v>
+      </c>
+      <c r="Z16" s="9">
         <f t="shared" si="45"/>
-        <v>-189.70000000000002</v>
-      </c>
-      <c r="K16" s="9">
+        <v>-421.90706399999988</v>
+      </c>
+      <c r="AA16" s="9">
         <f t="shared" si="45"/>
-        <v>-155.00000000000003</v>
-      </c>
-      <c r="L16" s="9">
+        <v>-383.21211099999999</v>
+      </c>
+      <c r="AB16" s="9">
         <f t="shared" si="45"/>
-        <v>-132.1</v>
-      </c>
-      <c r="M16" s="9">
-        <f t="shared" si="45"/>
-        <v>-165.70000000000002</v>
-      </c>
-      <c r="N16" s="9">
-        <f t="shared" si="45"/>
-        <v>-222.70000000000002</v>
-      </c>
-      <c r="O16" s="9">
-        <f t="shared" si="45"/>
-        <v>-201</v>
-      </c>
-      <c r="P16" s="9">
-        <f t="shared" si="45"/>
-        <v>-207.29999999999998</v>
-      </c>
-      <c r="Q16" s="9">
-        <f t="shared" si="45"/>
-        <v>-225.79999999999995</v>
-      </c>
-      <c r="R16" s="9">
-        <f t="shared" si="45"/>
-        <v>-226.79999999999998</v>
-      </c>
-      <c r="S16" s="9">
-        <f t="shared" si="45"/>
-        <v>-214.29999999999995</v>
-      </c>
-      <c r="T16" s="9">
-        <f t="shared" si="45"/>
-        <v>-169.29999999999987</v>
-      </c>
-      <c r="U16" s="9">
-        <f t="shared" si="45"/>
-        <v>-316.89999999999998</v>
-      </c>
-      <c r="V16" s="9">
-        <f t="shared" si="45"/>
-        <v>-316.90000000000015</v>
-      </c>
-      <c r="W16" s="9">
-        <f t="shared" si="45"/>
-        <v>-324.2999999999999</v>
-      </c>
-      <c r="X16" s="9">
-        <f t="shared" si="45"/>
-        <v>-327.60000000000002</v>
-      </c>
-      <c r="Y16" s="9">
-        <f t="shared" ref="Y16:AB16" si="46">Y13-Y14-Y15</f>
-        <v>-366.33352800000006</v>
-      </c>
-      <c r="Z16" s="9">
+        <v>-415.64811600000007</v>
+      </c>
+      <c r="AD16" s="9">
+        <f t="shared" ref="AD16:AQ16" si="46">AD13-AD14-AD15</f>
+        <v>-177.9</v>
+      </c>
+      <c r="AE16" s="9">
         <f t="shared" si="46"/>
-        <v>-354.54277799999994</v>
-      </c>
-      <c r="AA16" s="9">
+        <v>-348.5</v>
+      </c>
+      <c r="AF16" s="9">
         <f t="shared" si="46"/>
-        <v>-339.100776</v>
-      </c>
-      <c r="AB16" s="9">
+        <v>-539.10000000000014</v>
+      </c>
+      <c r="AG16" s="9">
         <f t="shared" si="46"/>
-        <v>-348.53039100000007</v>
-      </c>
-      <c r="AD16" s="9">
-        <f t="shared" ref="AD16:AQ16" si="47">AD13-AD14-AD15</f>
-        <v>-177.9</v>
-      </c>
-      <c r="AE16" s="9">
-        <f t="shared" si="47"/>
-        <v>-348.5</v>
-      </c>
-      <c r="AF16" s="9">
-        <f t="shared" si="47"/>
-        <v>-539.10000000000014</v>
-      </c>
-      <c r="AG16" s="9">
-        <f t="shared" si="47"/>
         <v>-680</v>
       </c>
       <c r="AH16" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="46"/>
         <v>-796.70000000000016</v>
       </c>
       <c r="AI16" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="46"/>
         <v>-836.19999999999993</v>
       </c>
       <c r="AJ16" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="46"/>
         <v>-1285.7000000000003</v>
       </c>
       <c r="AK16" s="9">
-        <f t="shared" si="47"/>
-        <v>-1452.0242729999995</v>
+        <f t="shared" si="46"/>
+        <v>-1689.9536909999993</v>
       </c>
       <c r="AL16" s="9">
-        <f t="shared" si="47"/>
-        <v>-1182.9990407399987</v>
+        <f t="shared" si="46"/>
+        <v>-1177.9325395199996</v>
       </c>
       <c r="AM16" s="9">
-        <f t="shared" si="47"/>
-        <v>-710.08120966799959</v>
+        <f t="shared" si="46"/>
+        <v>-606.02661039999919</v>
       </c>
       <c r="AN16" s="9">
-        <f t="shared" si="47"/>
-        <v>-240.01066769136114</v>
+        <f t="shared" si="46"/>
+        <v>-104.65711413616123</v>
       </c>
       <c r="AO16" s="9">
-        <f t="shared" si="47"/>
-        <v>198.13126283928906</v>
+        <f t="shared" si="46"/>
+        <v>355.93835647866615</v>
       </c>
       <c r="AP16" s="9">
-        <f t="shared" si="47"/>
-        <v>506.19203596408926</v>
+        <f t="shared" si="46"/>
+        <v>670.48578238868038</v>
       </c>
       <c r="AQ16" s="9">
-        <f t="shared" si="47"/>
-        <v>771.45115546614261</v>
+        <f t="shared" si="46"/>
+        <v>940.00566118122208</v>
       </c>
       <c r="AR16" s="9">
-        <f t="shared" ref="AR16" si="48">AR13-AR14-AR15</f>
-        <v>946.1797826811702</v>
+        <f t="shared" ref="AR16" si="47">AR13-AR14-AR15</f>
+        <v>1112.4269691830461</v>
       </c>
       <c r="AS16" s="9">
-        <f t="shared" ref="AS16" si="49">AS13-AS14-AS15</f>
-        <v>1083.9496841654684</v>
+        <f t="shared" ref="AS16" si="48">AS13-AS14-AS15</f>
+        <v>1254.8234300804945</v>
       </c>
       <c r="AT16" s="9">
-        <f t="shared" ref="AT16" si="50">AT13-AT14-AT15</f>
-        <v>1230.4172989709855</v>
+        <f t="shared" ref="AT16" si="49">AT13-AT14-AT15</f>
+        <v>1406.0752162715817</v>
       </c>
       <c r="AU16" s="9">
-        <f t="shared" ref="AU16" si="51">AU13-AU14-AU15</f>
-        <v>1386.0536971287252</v>
+        <f t="shared" ref="AU16" si="50">AU13-AU14-AU15</f>
+        <v>1566.6598040659644</v>
       </c>
       <c r="AV16" s="1">
         <f>AU16*(1+$AX$22)</f>
-        <v>1372.1931601574379</v>
+        <v>1550.9932060253047</v>
       </c>
       <c r="AW16" s="1">
-        <f t="shared" ref="AW16:DH16" si="52">AV16*(1+$AX$22)</f>
-        <v>1358.4712285558635</v>
+        <f t="shared" ref="AW16:DH16" si="51">AV16*(1+$AX$22)</f>
+        <v>1535.4832739650517</v>
       </c>
       <c r="AX16" s="1">
+        <f t="shared" si="51"/>
+        <v>1520.1284412254013</v>
+      </c>
+      <c r="AY16" s="1">
+        <f t="shared" si="51"/>
+        <v>1504.9271568131473</v>
+      </c>
+      <c r="AZ16" s="1">
+        <f t="shared" si="51"/>
+        <v>1489.8778852450159</v>
+      </c>
+      <c r="BA16" s="1">
+        <f t="shared" si="51"/>
+        <v>1474.9791063925657</v>
+      </c>
+      <c r="BB16" s="1">
+        <f t="shared" si="51"/>
+        <v>1460.22931532864</v>
+      </c>
+      <c r="BC16" s="1">
+        <f t="shared" si="51"/>
+        <v>1445.6270221753537</v>
+      </c>
+      <c r="BD16" s="1">
+        <f t="shared" si="51"/>
+        <v>1431.1707519536001</v>
+      </c>
+      <c r="BE16" s="1">
+        <f t="shared" si="51"/>
+        <v>1416.8590444340641</v>
+      </c>
+      <c r="BF16" s="1">
+        <f t="shared" si="51"/>
+        <v>1402.6904539897234</v>
+      </c>
+      <c r="BG16" s="1">
+        <f t="shared" si="51"/>
+        <v>1388.6635494498262</v>
+      </c>
+      <c r="BH16" s="1">
+        <f t="shared" si="51"/>
+        <v>1374.7769139553279</v>
+      </c>
+      <c r="BI16" s="1">
+        <f t="shared" si="51"/>
+        <v>1361.0291448157745</v>
+      </c>
+      <c r="BJ16" s="1">
+        <f t="shared" si="51"/>
+        <v>1347.4188533676167</v>
+      </c>
+      <c r="BK16" s="1">
+        <f t="shared" si="51"/>
+        <v>1333.9446648339406</v>
+      </c>
+      <c r="BL16" s="1">
+        <f t="shared" si="51"/>
+        <v>1320.6052181856012</v>
+      </c>
+      <c r="BM16" s="1">
+        <f t="shared" si="51"/>
+        <v>1307.3991660037452</v>
+      </c>
+      <c r="BN16" s="1">
+        <f t="shared" si="51"/>
+        <v>1294.3251743437077</v>
+      </c>
+      <c r="BO16" s="1">
+        <f t="shared" si="51"/>
+        <v>1281.3819226002706</v>
+      </c>
+      <c r="BP16" s="1">
+        <f t="shared" si="51"/>
+        <v>1268.5681033742678</v>
+      </c>
+      <c r="BQ16" s="1">
+        <f t="shared" si="51"/>
+        <v>1255.8824223405252</v>
+      </c>
+      <c r="BR16" s="1">
+        <f t="shared" si="51"/>
+        <v>1243.3235981171199</v>
+      </c>
+      <c r="BS16" s="1">
+        <f t="shared" si="51"/>
+        <v>1230.8903621359486</v>
+      </c>
+      <c r="BT16" s="1">
+        <f t="shared" si="51"/>
+        <v>1218.581458514589</v>
+      </c>
+      <c r="BU16" s="1">
+        <f t="shared" si="51"/>
+        <v>1206.3956439294432</v>
+      </c>
+      <c r="BV16" s="1">
+        <f t="shared" si="51"/>
+        <v>1194.3316874901486</v>
+      </c>
+      <c r="BW16" s="1">
+        <f t="shared" si="51"/>
+        <v>1182.3883706152471</v>
+      </c>
+      <c r="BX16" s="1">
+        <f t="shared" si="51"/>
+        <v>1170.5644869090947</v>
+      </c>
+      <c r="BY16" s="1">
+        <f t="shared" si="51"/>
+        <v>1158.8588420400038</v>
+      </c>
+      <c r="BZ16" s="1">
+        <f t="shared" si="51"/>
+        <v>1147.2702536196036</v>
+      </c>
+      <c r="CA16" s="1">
+        <f t="shared" si="51"/>
+        <v>1135.7975510834076</v>
+      </c>
+      <c r="CB16" s="1">
+        <f t="shared" si="51"/>
+        <v>1124.4395755725734</v>
+      </c>
+      <c r="CC16" s="1">
+        <f t="shared" si="51"/>
+        <v>1113.1951798168477</v>
+      </c>
+      <c r="CD16" s="1">
+        <f t="shared" si="51"/>
+        <v>1102.0632280186792</v>
+      </c>
+      <c r="CE16" s="1">
+        <f t="shared" si="51"/>
+        <v>1091.0425957384923</v>
+      </c>
+      <c r="CF16" s="1">
+        <f t="shared" si="51"/>
+        <v>1080.1321697811075</v>
+      </c>
+      <c r="CG16" s="1">
+        <f t="shared" si="51"/>
+        <v>1069.3308480832964</v>
+      </c>
+      <c r="CH16" s="1">
+        <f t="shared" si="51"/>
+        <v>1058.6375396024634</v>
+      </c>
+      <c r="CI16" s="1">
+        <f t="shared" si="51"/>
+        <v>1048.0511642064389</v>
+      </c>
+      <c r="CJ16" s="1">
+        <f t="shared" si="51"/>
+        <v>1037.5706525643745</v>
+      </c>
+      <c r="CK16" s="1">
+        <f t="shared" si="51"/>
+        <v>1027.1949460387307</v>
+      </c>
+      <c r="CL16" s="1">
+        <f t="shared" si="51"/>
+        <v>1016.9229965783434</v>
+      </c>
+      <c r="CM16" s="1">
+        <f t="shared" si="51"/>
+        <v>1006.75376661256</v>
+      </c>
+      <c r="CN16" s="1">
+        <f t="shared" si="51"/>
+        <v>996.68622894643431</v>
+      </c>
+      <c r="CO16" s="1">
+        <f t="shared" si="51"/>
+        <v>986.71936665697001</v>
+      </c>
+      <c r="CP16" s="1">
+        <f t="shared" si="51"/>
+        <v>976.85217299040028</v>
+      </c>
+      <c r="CQ16" s="1">
+        <f t="shared" si="51"/>
+        <v>967.08365126049625</v>
+      </c>
+      <c r="CR16" s="1">
+        <f t="shared" si="51"/>
+        <v>957.41281474789128</v>
+      </c>
+      <c r="CS16" s="1">
+        <f t="shared" si="51"/>
+        <v>947.8386866004123</v>
+      </c>
+      <c r="CT16" s="1">
+        <f t="shared" si="51"/>
+        <v>938.36029973440816</v>
+      </c>
+      <c r="CU16" s="1">
+        <f t="shared" si="51"/>
+        <v>928.97669673706412</v>
+      </c>
+      <c r="CV16" s="1">
+        <f t="shared" si="51"/>
+        <v>919.68692976969351</v>
+      </c>
+      <c r="CW16" s="1">
+        <f t="shared" si="51"/>
+        <v>910.49006047199657</v>
+      </c>
+      <c r="CX16" s="1">
+        <f t="shared" si="51"/>
+        <v>901.38515986727657</v>
+      </c>
+      <c r="CY16" s="1">
+        <f t="shared" si="51"/>
+        <v>892.3713082686038</v>
+      </c>
+      <c r="CZ16" s="1">
+        <f t="shared" si="51"/>
+        <v>883.44759518591775</v>
+      </c>
+      <c r="DA16" s="1">
+        <f t="shared" si="51"/>
+        <v>874.61311923405856</v>
+      </c>
+      <c r="DB16" s="1">
+        <f t="shared" si="51"/>
+        <v>865.86698804171795</v>
+      </c>
+      <c r="DC16" s="1">
+        <f t="shared" si="51"/>
+        <v>857.20831816130078</v>
+      </c>
+      <c r="DD16" s="1">
+        <f t="shared" si="51"/>
+        <v>848.63623497968774</v>
+      </c>
+      <c r="DE16" s="1">
+        <f t="shared" si="51"/>
+        <v>840.14987262989087</v>
+      </c>
+      <c r="DF16" s="1">
+        <f t="shared" si="51"/>
+        <v>831.74837390359198</v>
+      </c>
+      <c r="DG16" s="1">
+        <f t="shared" si="51"/>
+        <v>823.4308901645561</v>
+      </c>
+      <c r="DH16" s="1">
+        <f t="shared" si="51"/>
+        <v>815.19658126291051</v>
+      </c>
+      <c r="DI16" s="1">
+        <f t="shared" ref="DI16:FD16" si="52">DH16*(1+$AX$22)</f>
+        <v>807.04461545028141</v>
+      </c>
+      <c r="DJ16" s="1">
         <f t="shared" si="52"/>
-        <v>1344.8865162703048</v>
-      </c>
-      <c r="AY16" s="1">
+        <v>798.97416929577855</v>
+      </c>
+      <c r="DK16" s="1">
         <f t="shared" si="52"/>
-        <v>1331.4376511076018</v>
-      </c>
-      <c r="AZ16" s="1">
+        <v>790.9844276028208</v>
+      </c>
+      <c r="DL16" s="1">
         <f t="shared" si="52"/>
-        <v>1318.1232745965258</v>
-      </c>
-      <c r="BA16" s="1">
+        <v>783.07458332679255</v>
+      </c>
+      <c r="DM16" s="1">
         <f t="shared" si="52"/>
-        <v>1304.9420418505606</v>
-      </c>
-      <c r="BB16" s="1">
+        <v>775.24383749352467</v>
+      </c>
+      <c r="DN16" s="1">
         <f t="shared" si="52"/>
-        <v>1291.892621432055</v>
-      </c>
-      <c r="BC16" s="1">
+        <v>767.49139911858936</v>
+      </c>
+      <c r="DO16" s="1">
         <f t="shared" si="52"/>
-        <v>1278.9736952177343</v>
-      </c>
-      <c r="BD16" s="1">
+        <v>759.81648512740344</v>
+      </c>
+      <c r="DP16" s="1">
         <f t="shared" si="52"/>
-        <v>1266.1839582655568</v>
-      </c>
-      <c r="BE16" s="1">
+        <v>752.21832027612936</v>
+      </c>
+      <c r="DQ16" s="1">
         <f t="shared" si="52"/>
-        <v>1253.5221186829012</v>
-      </c>
-      <c r="BF16" s="1">
+        <v>744.69613707336805</v>
+      </c>
+      <c r="DR16" s="1">
         <f t="shared" si="52"/>
-        <v>1240.9868974960723</v>
-      </c>
-      <c r="BG16" s="1">
+        <v>737.24917570263437</v>
+      </c>
+      <c r="DS16" s="1">
         <f t="shared" si="52"/>
-        <v>1228.5770285211115</v>
-      </c>
-      <c r="BH16" s="1">
+        <v>729.87668394560808</v>
+      </c>
+      <c r="DT16" s="1">
         <f t="shared" si="52"/>
-        <v>1216.2912582359004</v>
-      </c>
-      <c r="BI16" s="1">
+        <v>722.57791710615197</v>
+      </c>
+      <c r="DU16" s="1">
         <f t="shared" si="52"/>
-        <v>1204.1283456535414</v>
-      </c>
-      <c r="BJ16" s="1">
+        <v>715.35213793509047</v>
+      </c>
+      <c r="DV16" s="1">
         <f t="shared" si="52"/>
-        <v>1192.0870621970059</v>
-      </c>
-      <c r="BK16" s="1">
+        <v>708.19861655573959</v>
+      </c>
+      <c r="DW16" s="1">
         <f t="shared" si="52"/>
-        <v>1180.1661915750358</v>
-      </c>
-      <c r="BL16" s="1">
+        <v>701.11663039018219</v>
+      </c>
+      <c r="DX16" s="1">
         <f t="shared" si="52"/>
-        <v>1168.3645296592854</v>
-      </c>
-      <c r="BM16" s="1">
+        <v>694.10546408628034</v>
+      </c>
+      <c r="DY16" s="1">
         <f t="shared" si="52"/>
-        <v>1156.6808843626925</v>
-      </c>
-      <c r="BN16" s="1">
+        <v>687.1644094454175</v>
+      </c>
+      <c r="DZ16" s="1">
         <f t="shared" si="52"/>
-        <v>1145.1140755190656</v>
-      </c>
-      <c r="BO16" s="1">
+        <v>680.29276535096335</v>
+      </c>
+      <c r="EA16" s="1">
         <f t="shared" si="52"/>
-        <v>1133.662934763875</v>
-      </c>
-      <c r="BP16" s="1">
+        <v>673.48983769745371</v>
+      </c>
+      <c r="EB16" s="1">
         <f t="shared" si="52"/>
-        <v>1122.3263054162362</v>
-      </c>
-      <c r="BQ16" s="1">
+        <v>666.75493932047914</v>
+      </c>
+      <c r="EC16" s="1">
         <f t="shared" si="52"/>
-        <v>1111.1030423620739</v>
-      </c>
-      <c r="BR16" s="1">
+        <v>660.08738992727433</v>
+      </c>
+      <c r="ED16" s="1">
         <f t="shared" si="52"/>
-        <v>1099.9920119384531</v>
-      </c>
-      <c r="BS16" s="1">
+        <v>653.48651602800157</v>
+      </c>
+      <c r="EE16" s="1">
         <f t="shared" si="52"/>
-        <v>1088.9920918190685</v>
-      </c>
-      <c r="BT16" s="1">
+        <v>646.95165086772158</v>
+      </c>
+      <c r="EF16" s="1">
         <f t="shared" si="52"/>
-        <v>1078.1021709008778</v>
-      </c>
-      <c r="BU16" s="1">
+        <v>640.48213435904438</v>
+      </c>
+      <c r="EG16" s="1">
         <f t="shared" si="52"/>
-        <v>1067.3211491918689</v>
-      </c>
-      <c r="BV16" s="1">
+        <v>634.07731301545391</v>
+      </c>
+      <c r="EH16" s="1">
         <f t="shared" si="52"/>
-        <v>1056.6479376999503</v>
-      </c>
-      <c r="BW16" s="1">
+        <v>627.73653988529941</v>
+      </c>
+      <c r="EI16" s="1">
         <f t="shared" si="52"/>
-        <v>1046.0814583229508</v>
-      </c>
-      <c r="BX16" s="1">
+        <v>621.45917448644639</v>
+      </c>
+      <c r="EJ16" s="1">
         <f t="shared" si="52"/>
-        <v>1035.6206437397213</v>
-      </c>
-      <c r="BY16" s="1">
+        <v>615.24458274158189</v>
+      </c>
+      <c r="EK16" s="1">
         <f t="shared" si="52"/>
-        <v>1025.264437302324</v>
-      </c>
-      <c r="BZ16" s="1">
+        <v>609.09213691416608</v>
+      </c>
+      <c r="EL16" s="1">
         <f t="shared" si="52"/>
-        <v>1015.0117929293008</v>
-      </c>
-      <c r="CA16" s="1">
+        <v>603.00121554502437</v>
+      </c>
+      <c r="EM16" s="1">
         <f t="shared" si="52"/>
-        <v>1004.8616750000077</v>
-      </c>
-      <c r="CB16" s="1">
+        <v>596.97120338957416</v>
+      </c>
+      <c r="EN16" s="1">
         <f t="shared" si="52"/>
-        <v>994.81305825000766</v>
-      </c>
-      <c r="CC16" s="1">
+        <v>591.00149135567835</v>
+      </c>
+      <c r="EO16" s="1">
         <f t="shared" si="52"/>
-        <v>984.86492766750757</v>
-      </c>
-      <c r="CD16" s="1">
+        <v>585.09147644212158</v>
+      </c>
+      <c r="EP16" s="1">
         <f t="shared" si="52"/>
-        <v>975.01627839083244</v>
-      </c>
-      <c r="CE16" s="1">
+        <v>579.24056167770038</v>
+      </c>
+      <c r="EQ16" s="1">
         <f t="shared" si="52"/>
-        <v>965.26611560692413</v>
-      </c>
-      <c r="CF16" s="1">
+        <v>573.44815606092334</v>
+      </c>
+      <c r="ER16" s="1">
         <f t="shared" si="52"/>
-        <v>955.61345445085487</v>
-      </c>
-      <c r="CG16" s="1">
+        <v>567.71367450031414</v>
+      </c>
+      <c r="ES16" s="1">
         <f t="shared" si="52"/>
-        <v>946.05731990634627</v>
-      </c>
-      <c r="CH16" s="1">
+        <v>562.03653775531097</v>
+      </c>
+      <c r="ET16" s="1">
         <f t="shared" si="52"/>
-        <v>936.59674670728282</v>
-      </c>
-      <c r="CI16" s="1">
+        <v>556.4161723777579</v>
+      </c>
+      <c r="EU16" s="1">
         <f t="shared" si="52"/>
-        <v>927.23077924020993</v>
-      </c>
-      <c r="CJ16" s="1">
+        <v>550.8520106539803</v>
+      </c>
+      <c r="EV16" s="1">
         <f t="shared" si="52"/>
-        <v>917.95847144780782</v>
-      </c>
-      <c r="CK16" s="1">
+        <v>545.34349054744052</v>
+      </c>
+      <c r="EW16" s="1">
         <f t="shared" si="52"/>
-        <v>908.77888673332973</v>
-      </c>
-      <c r="CL16" s="1">
+        <v>539.89005564196611</v>
+      </c>
+      <c r="EX16" s="1">
         <f t="shared" si="52"/>
-        <v>899.69109786599643</v>
-      </c>
-      <c r="CM16" s="1">
+        <v>534.49115508554644</v>
+      </c>
+      <c r="EY16" s="1">
         <f t="shared" si="52"/>
-        <v>890.6941868873364</v>
-      </c>
-      <c r="CN16" s="1">
+        <v>529.14624353469094</v>
+      </c>
+      <c r="EZ16" s="1">
         <f t="shared" si="52"/>
-        <v>881.78724501846307</v>
-      </c>
-      <c r="CO16" s="1">
+        <v>523.854781099344</v>
+      </c>
+      <c r="FA16" s="1">
         <f t="shared" si="52"/>
-        <v>872.96937256827846</v>
-      </c>
-      <c r="CP16" s="1">
+        <v>518.6162332883506</v>
+      </c>
+      <c r="FB16" s="1">
         <f t="shared" si="52"/>
-        <v>864.23967884259571</v>
-      </c>
-      <c r="CQ16" s="1">
+        <v>513.43007095546704</v>
+      </c>
+      <c r="FC16" s="1">
         <f t="shared" si="52"/>
-        <v>855.5972820541698</v>
-      </c>
-      <c r="CR16" s="1">
+        <v>508.29577024591237</v>
+      </c>
+      <c r="FD16" s="1">
         <f t="shared" si="52"/>
-        <v>847.04130923362811</v>
-      </c>
-      <c r="CS16" s="1">
-        <f t="shared" si="52"/>
-        <v>838.57089614129177</v>
-      </c>
-      <c r="CT16" s="1">
-        <f t="shared" si="52"/>
-        <v>830.18518717987888</v>
-      </c>
-      <c r="CU16" s="1">
-        <f t="shared" si="52"/>
-        <v>821.88333530808006</v>
-      </c>
-      <c r="CV16" s="1">
-        <f t="shared" si="52"/>
-        <v>813.66450195499931</v>
-      </c>
-      <c r="CW16" s="1">
-        <f t="shared" si="52"/>
-        <v>805.52785693544934</v>
-      </c>
-      <c r="CX16" s="1">
-        <f t="shared" si="52"/>
-        <v>797.47257836609481</v>
-      </c>
-      <c r="CY16" s="1">
-        <f t="shared" si="52"/>
-        <v>789.49785258243389</v>
-      </c>
-      <c r="CZ16" s="1">
-        <f t="shared" si="52"/>
-        <v>781.60287405660949</v>
-      </c>
-      <c r="DA16" s="1">
-        <f t="shared" si="52"/>
-        <v>773.78684531604335</v>
-      </c>
-      <c r="DB16" s="1">
-        <f t="shared" si="52"/>
-        <v>766.04897686288291</v>
-      </c>
-      <c r="DC16" s="1">
-        <f t="shared" si="52"/>
-        <v>758.38848709425406</v>
-      </c>
-      <c r="DD16" s="1">
-        <f t="shared" si="52"/>
-        <v>750.80460222331146</v>
-      </c>
-      <c r="DE16" s="1">
-        <f t="shared" si="52"/>
-        <v>743.29655620107837</v>
-      </c>
-      <c r="DF16" s="1">
-        <f t="shared" si="52"/>
-        <v>735.86359063906764</v>
-      </c>
-      <c r="DG16" s="1">
-        <f t="shared" si="52"/>
-        <v>728.50495473267699</v>
-      </c>
-      <c r="DH16" s="1">
-        <f t="shared" si="52"/>
-        <v>721.21990518535017</v>
-      </c>
-      <c r="DI16" s="1">
-        <f t="shared" ref="DI16:FD16" si="53">DH16*(1+$AX$22)</f>
-        <v>714.00770613349664</v>
-      </c>
-      <c r="DJ16" s="1">
-        <f t="shared" si="53"/>
-        <v>706.86762907216166</v>
-      </c>
-      <c r="DK16" s="1">
-        <f t="shared" si="53"/>
-        <v>699.79895278143999</v>
-      </c>
-      <c r="DL16" s="1">
-        <f t="shared" si="53"/>
-        <v>692.80096325362558</v>
-      </c>
-      <c r="DM16" s="1">
-        <f t="shared" si="53"/>
-        <v>685.87295362108932</v>
-      </c>
-      <c r="DN16" s="1">
-        <f t="shared" si="53"/>
-        <v>679.01422408487838</v>
-      </c>
-      <c r="DO16" s="1">
-        <f t="shared" si="53"/>
-        <v>672.22408184402957</v>
-      </c>
-      <c r="DP16" s="1">
-        <f t="shared" si="53"/>
-        <v>665.50184102558921</v>
-      </c>
-      <c r="DQ16" s="1">
-        <f t="shared" si="53"/>
-        <v>658.84682261533328</v>
-      </c>
-      <c r="DR16" s="1">
-        <f t="shared" si="53"/>
-        <v>652.25835438917989</v>
-      </c>
-      <c r="DS16" s="1">
-        <f t="shared" si="53"/>
-        <v>645.73577084528813</v>
-      </c>
-      <c r="DT16" s="1">
-        <f t="shared" si="53"/>
-        <v>639.2784131368353</v>
-      </c>
-      <c r="DU16" s="1">
-        <f t="shared" si="53"/>
-        <v>632.88562900546697</v>
-      </c>
-      <c r="DV16" s="1">
-        <f t="shared" si="53"/>
-        <v>626.55677271541231</v>
-      </c>
-      <c r="DW16" s="1">
-        <f t="shared" si="53"/>
-        <v>620.29120498825819</v>
-      </c>
-      <c r="DX16" s="1">
-        <f t="shared" si="53"/>
-        <v>614.08829293837562</v>
-      </c>
-      <c r="DY16" s="1">
-        <f t="shared" si="53"/>
-        <v>607.94741000899182</v>
-      </c>
-      <c r="DZ16" s="1">
-        <f t="shared" si="53"/>
-        <v>601.86793590890193</v>
-      </c>
-      <c r="EA16" s="1">
-        <f t="shared" si="53"/>
-        <v>595.84925654981294</v>
-      </c>
-      <c r="EB16" s="1">
-        <f t="shared" si="53"/>
-        <v>589.89076398431484</v>
-      </c>
-      <c r="EC16" s="1">
-        <f t="shared" si="53"/>
-        <v>583.99185634447167</v>
-      </c>
-      <c r="ED16" s="1">
-        <f t="shared" si="53"/>
-        <v>578.15193778102696</v>
-      </c>
-      <c r="EE16" s="1">
-        <f t="shared" si="53"/>
-        <v>572.37041840321672</v>
-      </c>
-      <c r="EF16" s="1">
-        <f t="shared" si="53"/>
-        <v>566.64671421918456</v>
-      </c>
-      <c r="EG16" s="1">
-        <f t="shared" si="53"/>
-        <v>560.98024707699267</v>
-      </c>
-      <c r="EH16" s="1">
-        <f t="shared" si="53"/>
-        <v>555.37044460622269</v>
-      </c>
-      <c r="EI16" s="1">
-        <f t="shared" si="53"/>
-        <v>549.81674016016041</v>
-      </c>
-      <c r="EJ16" s="1">
-        <f t="shared" si="53"/>
-        <v>544.31857275855884</v>
-      </c>
-      <c r="EK16" s="1">
-        <f t="shared" si="53"/>
-        <v>538.87538703097323</v>
-      </c>
-      <c r="EL16" s="1">
-        <f t="shared" si="53"/>
-        <v>533.48663316066347</v>
-      </c>
-      <c r="EM16" s="1">
-        <f t="shared" si="53"/>
-        <v>528.15176682905678</v>
-      </c>
-      <c r="EN16" s="1">
-        <f t="shared" si="53"/>
-        <v>522.87024916076621</v>
-      </c>
-      <c r="EO16" s="1">
-        <f t="shared" si="53"/>
-        <v>517.64154666915852</v>
-      </c>
-      <c r="EP16" s="1">
-        <f t="shared" si="53"/>
-        <v>512.46513120246698</v>
-      </c>
-      <c r="EQ16" s="1">
-        <f t="shared" si="53"/>
-        <v>507.34047989044228</v>
-      </c>
-      <c r="ER16" s="1">
-        <f t="shared" si="53"/>
-        <v>502.26707509153783</v>
-      </c>
-      <c r="ES16" s="1">
-        <f t="shared" si="53"/>
-        <v>497.24440434062245</v>
-      </c>
-      <c r="ET16" s="1">
-        <f t="shared" si="53"/>
-        <v>492.2719602972162</v>
-      </c>
-      <c r="EU16" s="1">
-        <f t="shared" si="53"/>
-        <v>487.34924069424403</v>
-      </c>
-      <c r="EV16" s="1">
-        <f t="shared" si="53"/>
-        <v>482.4757482873016</v>
-      </c>
-      <c r="EW16" s="1">
-        <f t="shared" si="53"/>
-        <v>477.6509908044286</v>
-      </c>
-      <c r="EX16" s="1">
-        <f t="shared" si="53"/>
-        <v>472.87448089638428</v>
-      </c>
-      <c r="EY16" s="1">
-        <f t="shared" si="53"/>
-        <v>468.14573608742046</v>
-      </c>
-      <c r="EZ16" s="1">
-        <f t="shared" si="53"/>
-        <v>463.46427872654624</v>
-      </c>
-      <c r="FA16" s="1">
-        <f t="shared" si="53"/>
-        <v>458.82963593928076</v>
-      </c>
-      <c r="FB16" s="1">
-        <f t="shared" si="53"/>
-        <v>454.24133957988795</v>
-      </c>
-      <c r="FC16" s="1">
-        <f t="shared" si="53"/>
-        <v>449.69892618408909</v>
-      </c>
-      <c r="FD16" s="1">
-        <f t="shared" si="53"/>
-        <v>445.20193692224819</v>
+        <v>503.21281254345325</v>
       </c>
     </row>
     <row r="17" spans="2:50" x14ac:dyDescent="0.3">
@@ -3890,20 +3884,20 @@
         <v>331.4</v>
       </c>
       <c r="Y17" s="6">
-        <f t="shared" ref="Y17:AB17" si="54">331.4</f>
-        <v>331.4</v>
+        <f>332.7</f>
+        <v>332.7</v>
       </c>
       <c r="Z17" s="6">
-        <f t="shared" si="54"/>
-        <v>331.4</v>
+        <f>332.7</f>
+        <v>332.7</v>
       </c>
       <c r="AA17" s="6">
-        <f t="shared" si="54"/>
-        <v>331.4</v>
+        <f>332.7</f>
+        <v>332.7</v>
       </c>
       <c r="AB17" s="6">
-        <f t="shared" si="54"/>
-        <v>331.4</v>
+        <f>332.7</f>
+        <v>332.7</v>
       </c>
       <c r="AD17" s="6">
         <v>284.10000000000002</v>
@@ -3924,52 +3918,52 @@
         <v>289</v>
       </c>
       <c r="AJ17" s="6">
-        <f t="shared" ref="AJ17:AU17" si="55">331.4</f>
+        <f t="shared" ref="AJ17:AU17" si="53">331.4</f>
         <v>331.4</v>
       </c>
       <c r="AK17" s="6">
-        <f t="shared" si="55"/>
-        <v>331.4</v>
+        <f>332.7</f>
+        <v>332.7</v>
       </c>
       <c r="AL17" s="6">
-        <f t="shared" si="55"/>
-        <v>331.4</v>
+        <f>332.7</f>
+        <v>332.7</v>
       </c>
       <c r="AM17" s="6">
-        <f t="shared" si="55"/>
-        <v>331.4</v>
+        <f>332.7</f>
+        <v>332.7</v>
       </c>
       <c r="AN17" s="6">
-        <f t="shared" si="55"/>
-        <v>331.4</v>
+        <f>332.7</f>
+        <v>332.7</v>
       </c>
       <c r="AO17" s="6">
-        <f t="shared" si="55"/>
-        <v>331.4</v>
+        <f>332.7</f>
+        <v>332.7</v>
       </c>
       <c r="AP17" s="6">
-        <f t="shared" si="55"/>
-        <v>331.4</v>
+        <f>332.7</f>
+        <v>332.7</v>
       </c>
       <c r="AQ17" s="6">
-        <f t="shared" si="55"/>
-        <v>331.4</v>
+        <f>332.7</f>
+        <v>332.7</v>
       </c>
       <c r="AR17" s="6">
-        <f t="shared" si="55"/>
-        <v>331.4</v>
+        <f>332.7</f>
+        <v>332.7</v>
       </c>
       <c r="AS17" s="6">
-        <f t="shared" si="55"/>
-        <v>331.4</v>
+        <f>332.7</f>
+        <v>332.7</v>
       </c>
       <c r="AT17" s="6">
-        <f t="shared" si="55"/>
-        <v>331.4</v>
+        <f>332.7</f>
+        <v>332.7</v>
       </c>
       <c r="AU17" s="6">
-        <f t="shared" si="55"/>
-        <v>331.4</v>
+        <f>332.7</f>
+        <v>332.7</v>
       </c>
     </row>
     <row r="18" spans="2:50" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3985,92 +3979,92 @@
         <v>-0.29074269623372051</v>
       </c>
       <c r="G18" s="8">
-        <f t="shared" ref="G18:X18" si="56">G16/G17</f>
+        <f t="shared" ref="G18:X18" si="54">G16/G17</f>
         <v>-0.59415698697641661</v>
       </c>
       <c r="H18" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>-0.69975360788454766</v>
       </c>
       <c r="I18" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>-0.71524111228440679</v>
       </c>
       <c r="J18" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>-0.66772263287574796</v>
       </c>
       <c r="K18" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>-0.54558254135867656</v>
       </c>
       <c r="L18" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>-0.46497712073213654</v>
       </c>
       <c r="M18" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>-0.58324533614924323</v>
       </c>
       <c r="N18" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>-0.78387891587469205</v>
       </c>
       <c r="O18" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>-0.70749736008447728</v>
       </c>
       <c r="P18" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>-0.7296726504751847</v>
       </c>
       <c r="Q18" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>-0.79479056670186532</v>
       </c>
       <c r="R18" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>-0.79831045406546974</v>
       </c>
       <c r="S18" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>-0.75431186202041511</v>
       </c>
       <c r="T18" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>-0.59591693065821838</v>
       </c>
       <c r="U18" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>-1.1154523055262231</v>
       </c>
       <c r="V18" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>-1.1154523055262235</v>
       </c>
       <c r="W18" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>-0.98242956679793969</v>
       </c>
       <c r="X18" s="8">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>-0.9885334942667473</v>
       </c>
       <c r="Y18" s="8">
-        <f t="shared" ref="Y18:AB18" si="57">Y16/Y17</f>
-        <v>-1.1054119734459871</v>
+        <f t="shared" ref="Y18:AB18" si="55">Y16/Y17</f>
+        <v>-1.2927562368500154</v>
       </c>
       <c r="Z18" s="8">
-        <f t="shared" si="57"/>
-        <v>-1.0698333675316836</v>
+        <f t="shared" si="55"/>
+        <v>-1.2681306402164108</v>
       </c>
       <c r="AA18" s="8">
-        <f t="shared" si="57"/>
-        <v>-1.0232371031985517</v>
+        <f t="shared" si="55"/>
+        <v>-1.1518248001202285</v>
       </c>
       <c r="AB18" s="8">
-        <f t="shared" si="57"/>
-        <v>-1.0516909806879906</v>
+        <f t="shared" si="55"/>
+        <v>-1.249318052299369</v>
       </c>
       <c r="AD18" s="8">
         <f>AD16/AD17</f>
@@ -4089,60 +4083,60 @@
         <v>-2.3529411764705883</v>
       </c>
       <c r="AH18" s="8">
-        <f t="shared" ref="AH18:AQ18" si="58">AH16/AH17</f>
+        <f t="shared" ref="AH18:AQ18" si="56">AH16/AH17</f>
         <v>-2.7567474048442913</v>
       </c>
       <c r="AI18" s="8">
-        <f t="shared" si="58"/>
+        <f t="shared" si="56"/>
         <v>-2.8934256055363319</v>
       </c>
       <c r="AJ18" s="8">
-        <f t="shared" si="58"/>
+        <f t="shared" si="56"/>
         <v>-3.8796016898008459</v>
       </c>
       <c r="AK18" s="8">
-        <f t="shared" si="58"/>
-        <v>-4.3814854345202159</v>
+        <f t="shared" si="56"/>
+        <v>-5.079512146077545</v>
       </c>
       <c r="AL18" s="8">
-        <f t="shared" si="58"/>
-        <v>-3.5697013902836416</v>
+        <f t="shared" si="56"/>
+        <v>-3.5405246153291245</v>
       </c>
       <c r="AM18" s="8">
-        <f t="shared" si="58"/>
-        <v>-2.1426711215087497</v>
+        <f t="shared" si="56"/>
+        <v>-1.8215407586414163</v>
       </c>
       <c r="AN18" s="8">
-        <f t="shared" si="58"/>
-        <v>-0.72423255187495816</v>
+        <f t="shared" si="56"/>
+        <v>-0.31456902355323485</v>
       </c>
       <c r="AO18" s="8">
-        <f t="shared" si="58"/>
-        <v>0.59786138454824711</v>
+        <f t="shared" si="56"/>
+        <v>1.0698477802184134</v>
       </c>
       <c r="AP18" s="8">
-        <f t="shared" si="58"/>
-        <v>1.5274352322392555</v>
+        <f t="shared" si="56"/>
+        <v>2.0152863913095294</v>
       </c>
       <c r="AQ18" s="8">
-        <f t="shared" si="58"/>
-        <v>2.3278550255465982</v>
+        <f t="shared" si="56"/>
+        <v>2.8253852154530272</v>
       </c>
       <c r="AR18" s="8">
-        <f t="shared" ref="AR18:AU18" si="59">AR16/AR17</f>
-        <v>2.8550989217898923</v>
+        <f t="shared" ref="AR18:AU18" si="57">AR16/AR17</f>
+        <v>3.3436338117915425</v>
       </c>
       <c r="AS18" s="8">
-        <f t="shared" si="59"/>
-        <v>3.2708198073792047</v>
+        <f t="shared" si="57"/>
+        <v>3.7716363994003443</v>
       </c>
       <c r="AT18" s="8">
-        <f t="shared" si="59"/>
-        <v>3.7127860560379768</v>
+        <f t="shared" si="57"/>
+        <v>4.2262555343299724</v>
       </c>
       <c r="AU18" s="8">
-        <f t="shared" si="59"/>
-        <v>4.1824191222954896</v>
+        <f t="shared" si="57"/>
+        <v>4.7089263723052737</v>
       </c>
     </row>
     <row r="20" spans="2:50" x14ac:dyDescent="0.3">
@@ -4150,160 +4144,160 @@
         <v>30</v>
       </c>
       <c r="G20" s="10">
-        <f t="shared" ref="G20:L20" si="60">G3/C3-1</f>
+        <f t="shared" ref="G20:L20" si="58">G3/C3-1</f>
         <v>1.1863013698630138</v>
       </c>
       <c r="H20" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>1.1721778791334092</v>
       </c>
       <c r="I20" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>1.1392523364485982</v>
       </c>
       <c r="J20" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>1.0177909562638989</v>
       </c>
       <c r="K20" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>1.0952380952380953</v>
       </c>
       <c r="L20" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>1.0146981627296587</v>
       </c>
       <c r="M20" s="10">
-        <f t="shared" ref="M20:X20" si="61">M3/I3-1</f>
+        <f t="shared" ref="M20:X20" si="59">M3/I3-1</f>
         <v>0.84534731323722134</v>
       </c>
       <c r="N20" s="10">
-        <f t="shared" si="61"/>
+        <f t="shared" si="59"/>
         <v>0.82659808963997072</v>
       </c>
       <c r="O20" s="10">
-        <f t="shared" si="61"/>
+        <f t="shared" si="59"/>
         <v>0.66566985645933019</v>
       </c>
       <c r="P20" s="10">
-        <f t="shared" si="61"/>
+        <f t="shared" si="59"/>
         <v>0.53465346534653468</v>
       </c>
       <c r="Q20" s="10">
-        <f t="shared" si="61"/>
+        <f t="shared" si="59"/>
         <v>0.47632575757575779</v>
       </c>
       <c r="R20" s="10">
-        <f t="shared" si="61"/>
+        <f t="shared" si="59"/>
         <v>0.35559131134352384</v>
       </c>
       <c r="S20" s="10">
-        <f t="shared" si="61"/>
+        <f t="shared" si="59"/>
         <v>0.31813285457809704</v>
       </c>
       <c r="T20" s="10">
-        <f t="shared" si="61"/>
+        <f t="shared" si="59"/>
         <v>0.31528013582342962</v>
       </c>
       <c r="U20" s="10">
-        <f t="shared" si="61"/>
+        <f t="shared" si="59"/>
         <v>0.32889672867222575</v>
       </c>
       <c r="V20" s="10">
-        <f t="shared" si="61"/>
+        <f t="shared" si="59"/>
         <v>0.28902077151335304</v>
       </c>
       <c r="W20" s="10">
-        <f t="shared" si="61"/>
+        <f t="shared" si="59"/>
         <v>0.28316535004086085</v>
       </c>
       <c r="X20" s="10">
-        <f t="shared" si="61"/>
+        <f t="shared" si="59"/>
         <v>0.27378340002581636</v>
       </c>
       <c r="Y20" s="10">
-        <f t="shared" ref="Y20" si="62">Y3/U3-1</f>
+        <f t="shared" ref="Y20" si="60">Y3/U3-1</f>
+        <v>0.25751176541571108</v>
+      </c>
+      <c r="Z20" s="10">
+        <f t="shared" ref="Z20" si="61">Z3/V3-1</f>
         <v>0.19999999999999996</v>
       </c>
-      <c r="Z20" s="10">
-        <f t="shared" ref="Z20" si="63">Z3/V3-1</f>
+      <c r="AA20" s="10">
+        <f t="shared" ref="AA20" si="62">AA3/W3-1</f>
         <v>0.19999999999999996</v>
       </c>
-      <c r="AA20" s="10">
-        <f t="shared" ref="AA20" si="64">AA3/W3-1</f>
-        <v>0.19999999999999996</v>
-      </c>
       <c r="AB20" s="10">
-        <f t="shared" ref="AB20" si="65">AB3/X3-1</f>
+        <f t="shared" ref="AB20" si="63">AB3/X3-1</f>
         <v>0.19999999999999996</v>
       </c>
       <c r="AD20" s="10"/>
       <c r="AE20" s="10">
-        <f t="shared" ref="AE20:AQ20" si="66">AE3/AD3-1</f>
+        <f t="shared" ref="AE20:AQ20" si="64">AE3/AD3-1</f>
         <v>1.7383660806618408</v>
       </c>
       <c r="AF20" s="10">
-        <f t="shared" si="66"/>
+        <f t="shared" si="64"/>
         <v>1.2356495468277946</v>
       </c>
       <c r="AG20" s="10">
-        <f t="shared" si="66"/>
+        <f t="shared" si="64"/>
         <v>1.0596283783783784</v>
       </c>
       <c r="AH20" s="10">
-        <f t="shared" si="66"/>
+        <f t="shared" si="64"/>
         <v>0.69408677109817107</v>
       </c>
       <c r="AI20" s="10">
-        <f t="shared" si="66"/>
+        <f t="shared" si="64"/>
         <v>0.35868512780790085</v>
       </c>
       <c r="AJ20" s="10">
-        <f t="shared" si="66"/>
+        <f t="shared" si="64"/>
         <v>0.29214323890967386</v>
       </c>
       <c r="AK20" s="10">
-        <f t="shared" si="66"/>
-        <v>0.20000000000000018</v>
+        <f t="shared" si="64"/>
+        <v>0.21314251047871191</v>
       </c>
       <c r="AL20" s="10">
-        <f t="shared" si="66"/>
+        <f t="shared" si="64"/>
         <v>0.24</v>
       </c>
       <c r="AM20" s="10">
-        <f t="shared" si="66"/>
+        <f t="shared" si="64"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="AN20" s="10">
-        <f t="shared" si="66"/>
+        <f t="shared" si="64"/>
         <v>0.1399999999999999</v>
       </c>
       <c r="AO20" s="10">
-        <f t="shared" si="66"/>
+        <f t="shared" si="64"/>
         <v>0.1100000000000001</v>
       </c>
       <c r="AP20" s="10">
-        <f t="shared" si="66"/>
+        <f t="shared" si="64"/>
         <v>9.000000000000008E-2</v>
       </c>
       <c r="AQ20" s="10">
-        <f t="shared" si="66"/>
+        <f t="shared" si="64"/>
         <v>7.0000000000000062E-2</v>
       </c>
       <c r="AR20" s="10">
-        <f t="shared" ref="AR20:AU20" si="67">AR3/AQ3-1</f>
+        <f t="shared" ref="AR20:AU20" si="65">AR3/AQ3-1</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AS20" s="10">
-        <f t="shared" si="67"/>
+        <f t="shared" si="65"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AT20" s="10">
-        <f t="shared" si="67"/>
+        <f t="shared" si="65"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AU20" s="10">
-        <f t="shared" si="67"/>
+        <f t="shared" si="65"/>
         <v>5.0000000000000044E-2</v>
       </c>
     </row>
@@ -4320,163 +4314,163 @@
         <v>0.60661345496009123</v>
       </c>
       <c r="G21" s="10">
-        <f t="shared" ref="G21:L21" si="68">G5/G3</f>
+        <f t="shared" ref="G21:L21" si="66">G5/G3</f>
         <v>0.58208020050125309</v>
       </c>
       <c r="H21" s="10">
+        <f t="shared" si="66"/>
+        <v>0.56482939632545925</v>
+      </c>
+      <c r="I21" s="10">
+        <f t="shared" si="66"/>
+        <v>0.57492354740061169</v>
+      </c>
+      <c r="J21" s="10">
+        <f t="shared" si="66"/>
+        <v>0.61021307861866281</v>
+      </c>
+      <c r="K21" s="10">
+        <f t="shared" si="66"/>
+        <v>0.63875598086124397</v>
+      </c>
+      <c r="L21" s="10">
+        <f t="shared" si="66"/>
+        <v>0.65033871808233457</v>
+      </c>
+      <c r="M21" s="10">
+        <f t="shared" ref="M21:X21" si="67">M5/M3</f>
+        <v>0.64985795454545459</v>
+      </c>
+      <c r="N21" s="10">
+        <f t="shared" si="67"/>
+        <v>0.65164923572003219</v>
+      </c>
+      <c r="O21" s="10">
+        <f t="shared" si="67"/>
+        <v>0.65763016157989229</v>
+      </c>
+      <c r="P21" s="10">
+        <f t="shared" si="67"/>
+        <v>0.65076400679117152</v>
+      </c>
+      <c r="Q21" s="10">
+        <f t="shared" si="67"/>
+        <v>0.66420782552918545</v>
+      </c>
+      <c r="R21" s="10">
+        <f t="shared" si="67"/>
+        <v>0.67596439169139466</v>
+      </c>
+      <c r="S21" s="10">
+        <f t="shared" si="67"/>
+        <v>0.6882320893489513</v>
+      </c>
+      <c r="T21" s="10">
+        <f t="shared" si="67"/>
+        <v>0.68787917903704665</v>
+      </c>
+      <c r="U21" s="10">
+        <f t="shared" si="67"/>
+        <v>0.67117171473392057</v>
+      </c>
+      <c r="V21" s="10">
+        <f t="shared" si="67"/>
+        <v>0.66839318600368325</v>
+      </c>
+      <c r="W21" s="10">
+        <f t="shared" si="67"/>
+        <v>0.65937798535187353</v>
+      </c>
+      <c r="X21" s="10">
+        <f t="shared" si="67"/>
+        <v>0.66234292663153627</v>
+      </c>
+      <c r="Y21" s="10">
+        <f t="shared" ref="Y21:AB21" si="68">Y5/Y3</f>
+        <v>0.6652912388446407</v>
+      </c>
+      <c r="Z21" s="10">
         <f t="shared" si="68"/>
-        <v>0.56482939632545925</v>
-      </c>
-      <c r="I21" s="10">
+        <v>0.67</v>
+      </c>
+      <c r="AA21" s="10">
         <f t="shared" si="68"/>
-        <v>0.57492354740061169</v>
-      </c>
-      <c r="J21" s="10">
+        <v>0.67</v>
+      </c>
+      <c r="AB21" s="10">
         <f t="shared" si="68"/>
-        <v>0.61021307861866281</v>
-      </c>
-      <c r="K21" s="10">
-        <f t="shared" si="68"/>
-        <v>0.63875598086124397</v>
-      </c>
-      <c r="L21" s="10">
-        <f t="shared" si="68"/>
-        <v>0.65033871808233457</v>
-      </c>
-      <c r="M21" s="10">
-        <f t="shared" ref="M21:X21" si="69">M5/M3</f>
-        <v>0.64985795454545459</v>
-      </c>
-      <c r="N21" s="10">
+        <v>0.67</v>
+      </c>
+      <c r="AD21" s="10">
+        <f t="shared" ref="AD21:AQ21" si="69">AD5/AD3</f>
+        <v>0.46535677352637023</v>
+      </c>
+      <c r="AE21" s="10">
         <f t="shared" si="69"/>
-        <v>0.65164923572003219</v>
-      </c>
-      <c r="O21" s="10">
+        <v>0.55966767371601212</v>
+      </c>
+      <c r="AF21" s="10">
         <f t="shared" si="69"/>
-        <v>0.65763016157989229</v>
-      </c>
-      <c r="P21" s="10">
+        <v>0.5902027027027027</v>
+      </c>
+      <c r="AG21" s="10">
         <f t="shared" si="69"/>
-        <v>0.65076400679117152</v>
-      </c>
-      <c r="Q21" s="10">
+        <v>0.62404658410563441</v>
+      </c>
+      <c r="AH21" s="10">
         <f t="shared" si="69"/>
-        <v>0.66420782552918545</v>
-      </c>
-      <c r="R21" s="10">
+        <v>0.65264329976762203</v>
+      </c>
+      <c r="AI21" s="10">
         <f t="shared" si="69"/>
-        <v>0.67596439169139466</v>
-      </c>
-      <c r="S21" s="10">
+        <v>0.67985034740780337</v>
+      </c>
+      <c r="AJ21" s="10">
         <f t="shared" si="69"/>
-        <v>0.6882320893489513</v>
-      </c>
-      <c r="T21" s="10">
+        <v>0.66503970880211782</v>
+      </c>
+      <c r="AK21" s="10">
         <f t="shared" si="69"/>
-        <v>0.68787917903704665</v>
-      </c>
-      <c r="U21" s="10">
+        <v>0.66</v>
+      </c>
+      <c r="AL21" s="10">
         <f t="shared" si="69"/>
-        <v>0.67117171473392057</v>
-      </c>
-      <c r="V21" s="10">
+        <v>0.67</v>
+      </c>
+      <c r="AM21" s="10">
         <f t="shared" si="69"/>
-        <v>0.66839318600368325</v>
-      </c>
-      <c r="W21" s="10">
+        <v>0.68</v>
+      </c>
+      <c r="AN21" s="10">
         <f t="shared" si="69"/>
-        <v>0.65937798535187353</v>
-      </c>
-      <c r="X21" s="10">
+        <v>0.69</v>
+      </c>
+      <c r="AO21" s="10">
         <f t="shared" si="69"/>
-        <v>0.66234292663153627</v>
-      </c>
-      <c r="Y21" s="10">
-        <f t="shared" ref="Y21:AB21" si="70">Y5/Y3</f>
-        <v>0.67</v>
-      </c>
-      <c r="Z21" s="10">
+        <v>0.7</v>
+      </c>
+      <c r="AP21" s="10">
+        <f t="shared" si="69"/>
+        <v>0.7</v>
+      </c>
+      <c r="AQ21" s="10">
+        <f t="shared" si="69"/>
+        <v>0.7</v>
+      </c>
+      <c r="AR21" s="10">
+        <f t="shared" ref="AR21:AU21" si="70">AR5/AR3</f>
+        <v>0.7</v>
+      </c>
+      <c r="AS21" s="10">
         <f t="shared" si="70"/>
-        <v>0.67</v>
-      </c>
-      <c r="AA21" s="10">
+        <v>0.7</v>
+      </c>
+      <c r="AT21" s="10">
         <f t="shared" si="70"/>
-        <v>0.67</v>
-      </c>
-      <c r="AB21" s="10">
+        <v>0.7</v>
+      </c>
+      <c r="AU21" s="10">
         <f t="shared" si="70"/>
-        <v>0.67</v>
-      </c>
-      <c r="AD21" s="10">
-        <f t="shared" ref="AD21:AQ21" si="71">AD5/AD3</f>
-        <v>0.46535677352637023</v>
-      </c>
-      <c r="AE21" s="10">
-        <f t="shared" si="71"/>
-        <v>0.55966767371601212</v>
-      </c>
-      <c r="AF21" s="10">
-        <f t="shared" si="71"/>
-        <v>0.5902027027027027</v>
-      </c>
-      <c r="AG21" s="10">
-        <f t="shared" si="71"/>
-        <v>0.62404658410563441</v>
-      </c>
-      <c r="AH21" s="10">
-        <f t="shared" si="71"/>
-        <v>0.65264329976762203</v>
-      </c>
-      <c r="AI21" s="10">
-        <f t="shared" si="71"/>
-        <v>0.67985034740780337</v>
-      </c>
-      <c r="AJ21" s="10">
-        <f t="shared" si="71"/>
-        <v>0.66503970880211782</v>
-      </c>
-      <c r="AK21" s="10">
-        <f t="shared" si="71"/>
-        <v>0.66</v>
-      </c>
-      <c r="AL21" s="10">
-        <f t="shared" si="71"/>
-        <v>0.67</v>
-      </c>
-      <c r="AM21" s="10">
-        <f t="shared" si="71"/>
-        <v>0.68</v>
-      </c>
-      <c r="AN21" s="10">
-        <f t="shared" si="71"/>
-        <v>0.69</v>
-      </c>
-      <c r="AO21" s="10">
-        <f t="shared" si="71"/>
-        <v>0.7</v>
-      </c>
-      <c r="AP21" s="10">
-        <f t="shared" si="71"/>
-        <v>0.7</v>
-      </c>
-      <c r="AQ21" s="10">
-        <f t="shared" si="71"/>
-        <v>0.7</v>
-      </c>
-      <c r="AR21" s="10">
-        <f t="shared" ref="AR21:AU21" si="72">AR5/AR3</f>
-        <v>0.7</v>
-      </c>
-      <c r="AS21" s="10">
-        <f t="shared" si="72"/>
-        <v>0.7</v>
-      </c>
-      <c r="AT21" s="10">
-        <f t="shared" si="72"/>
-        <v>0.7</v>
-      </c>
-      <c r="AU21" s="10">
-        <f t="shared" si="72"/>
         <v>0.7</v>
       </c>
     </row>
@@ -4493,164 +4487,164 @@
         <v>-0.96921322690992018</v>
       </c>
       <c r="G22" s="10">
-        <f t="shared" ref="G22:L22" si="73">G9/G3</f>
+        <f t="shared" ref="G22:L22" si="71">G9/G3</f>
         <v>-1.0614035087719298</v>
       </c>
       <c r="H22" s="10">
+        <f t="shared" si="71"/>
+        <v>-1.0519685039370079</v>
+      </c>
+      <c r="I22" s="10">
+        <f t="shared" si="71"/>
+        <v>-0.8982088248143294</v>
+      </c>
+      <c r="J22" s="10">
+        <f t="shared" si="71"/>
+        <v>-0.73512123438648069</v>
+      </c>
+      <c r="K22" s="10">
+        <f t="shared" si="71"/>
+        <v>-0.47069377990430633</v>
+      </c>
+      <c r="L22" s="10">
+        <f t="shared" si="71"/>
+        <v>-0.396039603960396</v>
+      </c>
+      <c r="M22" s="10">
+        <f t="shared" ref="M22:X22" si="72">M9/M3</f>
+        <v>-0.44673295454545459</v>
+      </c>
+      <c r="N22" s="10">
+        <f t="shared" si="72"/>
+        <v>-0.41773934030571203</v>
+      </c>
+      <c r="O22" s="10">
+        <f t="shared" si="72"/>
+        <v>-0.37001795332136445</v>
+      </c>
+      <c r="P22" s="10">
+        <f t="shared" si="72"/>
+        <v>-0.40713073005093375</v>
+      </c>
+      <c r="Q22" s="10">
+        <f t="shared" si="72"/>
+        <v>-0.43826170622193705</v>
+      </c>
+      <c r="R22" s="10">
+        <f t="shared" si="72"/>
+        <v>-0.42344213649851631</v>
+      </c>
+      <c r="S22" s="10">
+        <f t="shared" si="72"/>
+        <v>-0.35494415690547526</v>
+      </c>
+      <c r="T22" s="10">
+        <f t="shared" si="72"/>
+        <v>-0.35562153091519283</v>
+      </c>
+      <c r="U22" s="10">
+        <f t="shared" si="72"/>
+        <v>-0.42053819234946299</v>
+      </c>
+      <c r="V22" s="10">
+        <f t="shared" si="72"/>
+        <v>-0.40906998158379387</v>
+      </c>
+      <c r="W22" s="10">
+        <f t="shared" si="72"/>
+        <v>-0.38796306124615215</v>
+      </c>
+      <c r="X22" s="10">
+        <f t="shared" si="72"/>
+        <v>-0.39187271990271594</v>
+      </c>
+      <c r="Y22" s="10">
+        <f t="shared" ref="Y22:AB22" si="73">Y9/Y3</f>
+        <v>-0.42922944055273016</v>
+      </c>
+      <c r="Z22" s="10">
         <f t="shared" si="73"/>
-        <v>-1.0519685039370079</v>
-      </c>
-      <c r="I22" s="10">
+        <v>-0.45636912983425404</v>
+      </c>
+      <c r="AA22" s="10">
         <f t="shared" si="73"/>
-        <v>-0.8982088248143294</v>
-      </c>
-      <c r="J22" s="10">
+        <v>-0.38590453950394504</v>
+      </c>
+      <c r="AB22" s="10">
         <f t="shared" si="73"/>
-        <v>-0.73512123438648069</v>
-      </c>
-      <c r="K22" s="10">
-        <f t="shared" si="73"/>
-        <v>-0.47069377990430633</v>
-      </c>
-      <c r="L22" s="10">
-        <f t="shared" si="73"/>
-        <v>-0.396039603960396</v>
-      </c>
-      <c r="M22" s="10">
-        <f t="shared" ref="M22:X22" si="74">M9/M3</f>
-        <v>-0.44673295454545459</v>
-      </c>
-      <c r="N22" s="10">
+        <v>-0.40269203486015415</v>
+      </c>
+      <c r="AD22" s="10">
+        <f t="shared" ref="AD22:AQ22" si="74">AD9/AD3</f>
+        <v>-1.9172699069286454</v>
+      </c>
+      <c r="AE22" s="10">
         <f t="shared" si="74"/>
-        <v>-0.41773934030571203</v>
-      </c>
-      <c r="O22" s="10">
+        <v>-1.3523413897280967</v>
+      </c>
+      <c r="AF22" s="10">
         <f t="shared" si="74"/>
-        <v>-0.37001795332136445</v>
-      </c>
-      <c r="P22" s="10">
+        <v>-0.91875000000000018</v>
+      </c>
+      <c r="AG22" s="10">
         <f t="shared" si="74"/>
-        <v>-0.40713073005093375</v>
-      </c>
-      <c r="Q22" s="10">
+        <v>-0.58648404822439104</v>
+      </c>
+      <c r="AH22" s="10">
         <f t="shared" si="74"/>
-        <v>-0.43826170622193705</v>
-      </c>
-      <c r="R22" s="10">
+        <v>-0.4077749806351666</v>
+      </c>
+      <c r="AI22" s="10">
         <f t="shared" si="74"/>
-        <v>-0.42344213649851631</v>
-      </c>
-      <c r="S22" s="10">
+        <v>-0.3900944236593622</v>
+      </c>
+      <c r="AJ22" s="10">
         <f t="shared" si="74"/>
-        <v>-0.35494415690547526</v>
-      </c>
-      <c r="T22" s="10">
+        <v>-0.40152768585925452</v>
+      </c>
+      <c r="AK22" s="10">
         <f t="shared" si="74"/>
-        <v>-0.35562153091519283</v>
-      </c>
-      <c r="U22" s="10">
+        <v>-0.42626921310923893</v>
+      </c>
+      <c r="AL22" s="10">
         <f t="shared" si="74"/>
-        <v>-0.42053819234946299</v>
-      </c>
-      <c r="V22" s="10">
+        <v>-0.25835072988220958</v>
+      </c>
+      <c r="AM22" s="10">
         <f t="shared" si="74"/>
-        <v>-0.40906998158379387</v>
-      </c>
-      <c r="W22" s="10">
+        <v>-0.13269018181417327</v>
+      </c>
+      <c r="AN22" s="10">
         <f t="shared" si="74"/>
-        <v>-0.38796306124615215</v>
-      </c>
-      <c r="X22" s="10">
+        <v>-4.5523170158482576E-2</v>
+      </c>
+      <c r="AO22" s="10">
         <f t="shared" si="74"/>
-        <v>-0.39187271990271594</v>
-      </c>
-      <c r="Y22" s="10">
-        <f t="shared" ref="Y22:AB22" si="75">Y9/Y3</f>
-        <v>-0.4280946060094124</v>
-      </c>
-      <c r="Z22" s="10">
+        <v>2.0157349422445323E-2</v>
+      </c>
+      <c r="AP22" s="10">
+        <f t="shared" si="74"/>
+        <v>5.7119721477884668E-2</v>
+      </c>
+      <c r="AQ22" s="10">
+        <f t="shared" si="74"/>
+        <v>8.5478612997609685E-2</v>
+      </c>
+      <c r="AR22" s="10">
+        <f t="shared" ref="AR22:AU22" si="75">AR9/AR3</f>
+        <v>0.10617922405482084</v>
+      </c>
+      <c r="AS22" s="10">
         <f t="shared" si="75"/>
-        <v>-0.39143013351749539</v>
-      </c>
-      <c r="AA22" s="10">
+        <v>0.11657410336754019</v>
+      </c>
+      <c r="AT22" s="10">
         <f t="shared" si="75"/>
-        <v>-0.34668984184269186</v>
-      </c>
-      <c r="AB22" s="10">
+        <v>0.12667198612846761</v>
+      </c>
+      <c r="AU22" s="10">
         <f t="shared" si="75"/>
-        <v>-0.34572760437778693</v>
-      </c>
-      <c r="AD22" s="10">
-        <f t="shared" ref="AD22:AQ22" si="76">AD9/AD3</f>
-        <v>-1.9172699069286454</v>
-      </c>
-      <c r="AE22" s="10">
-        <f t="shared" si="76"/>
-        <v>-1.3523413897280967</v>
-      </c>
-      <c r="AF22" s="10">
-        <f t="shared" si="76"/>
-        <v>-0.91875000000000018</v>
-      </c>
-      <c r="AG22" s="10">
-        <f t="shared" si="76"/>
-        <v>-0.58648404822439104</v>
-      </c>
-      <c r="AH22" s="10">
-        <f t="shared" si="76"/>
-        <v>-0.4077749806351666</v>
-      </c>
-      <c r="AI22" s="10">
-        <f t="shared" si="76"/>
-        <v>-0.3900944236593622</v>
-      </c>
-      <c r="AJ22" s="10">
-        <f t="shared" si="76"/>
-        <v>-0.40152768585925452</v>
-      </c>
-      <c r="AK22" s="10">
-        <f t="shared" si="76"/>
-        <v>-0.38574922788440313</v>
-      </c>
-      <c r="AL22" s="10">
-        <f t="shared" si="76"/>
-        <v>-0.26294898974129954</v>
-      </c>
-      <c r="AM22" s="10">
-        <f t="shared" si="76"/>
-        <v>-0.15193590853083949</v>
-      </c>
-      <c r="AN22" s="10">
-        <f t="shared" si="76"/>
-        <v>-6.6152056905327494E-2</v>
-      </c>
-      <c r="AO22" s="10">
-        <f t="shared" si="76"/>
-        <v>-1.8347915427812792E-3</v>
-      </c>
-      <c r="AP22" s="10">
-        <f t="shared" si="76"/>
-        <v>3.6539919840700194E-2</v>
-      </c>
-      <c r="AQ22" s="10">
-        <f t="shared" si="76"/>
-        <v>6.5860484334125446E-2</v>
-      </c>
-      <c r="AR22" s="10">
-        <f t="shared" ref="AR22:AU22" si="77">AR9/AR3</f>
-        <v>8.7121613353150454E-2</v>
-      </c>
-      <c r="AS22" s="10">
-        <f t="shared" si="77"/>
-        <v>9.8060995828774714E-2</v>
-      </c>
-      <c r="AT22" s="10">
-        <f t="shared" si="77"/>
-        <v>0.10868782451938108</v>
-      </c>
-      <c r="AU22" s="10">
-        <f t="shared" si="77"/>
-        <v>0.11901102953311314</v>
+        <v>0.13648135795336852</v>
       </c>
       <c r="AW22" t="s">
         <v>40</v>
@@ -4672,164 +4666,164 @@
         <v>0.91676168757126575</v>
       </c>
       <c r="G23" s="10">
-        <f t="shared" ref="G23:L23" si="78">G6/G3</f>
+        <f t="shared" ref="G23:L23" si="76">G6/G3</f>
         <v>0.84398496240601495</v>
       </c>
       <c r="H23" s="10">
+        <f t="shared" si="76"/>
+        <v>0.80892388451443564</v>
+      </c>
+      <c r="I23" s="10">
+        <f t="shared" si="76"/>
+        <v>0.72870249017038013</v>
+      </c>
+      <c r="J23" s="10">
+        <f t="shared" si="76"/>
+        <v>0.67193240264511389</v>
+      </c>
+      <c r="K23" s="10">
+        <f t="shared" si="76"/>
+        <v>0.57117224880382778</v>
+      </c>
+      <c r="L23" s="10">
+        <f t="shared" si="76"/>
+        <v>0.52970297029702973</v>
+      </c>
+      <c r="M23" s="10">
+        <f t="shared" ref="M23:X23" si="77">M6/M3</f>
+        <v>0.57741477272727282</v>
+      </c>
+      <c r="N23" s="10">
+        <f t="shared" si="77"/>
+        <v>0.55229283990345945</v>
+      </c>
+      <c r="O23" s="10">
+        <f t="shared" si="77"/>
+        <v>0.51077199281867147</v>
+      </c>
+      <c r="P23" s="10">
+        <f t="shared" si="77"/>
+        <v>0.51528013582342957</v>
+      </c>
+      <c r="Q23" s="10">
+        <f t="shared" si="77"/>
+        <v>0.53175112251443235</v>
+      </c>
+      <c r="R23" s="10">
+        <f t="shared" si="77"/>
+        <v>0.50934718100890208</v>
+      </c>
+      <c r="S23" s="10">
+        <f t="shared" si="77"/>
+        <v>0.48365567965132117</v>
+      </c>
+      <c r="T23" s="10">
+        <f t="shared" si="77"/>
+        <v>0.467019491416032</v>
+      </c>
+      <c r="U23" s="10">
+        <f t="shared" si="77"/>
+        <v>0.48364908893447567</v>
+      </c>
+      <c r="V23" s="10">
+        <f t="shared" si="77"/>
+        <v>0.46109576427255988</v>
+      </c>
+      <c r="W23" s="10">
+        <f t="shared" si="77"/>
+        <v>0.46491879842904149</v>
+      </c>
+      <c r="X23" s="10">
+        <f t="shared" si="77"/>
+        <v>0.43848804215646536</v>
+      </c>
+      <c r="Y23" s="10">
+        <f t="shared" ref="Y23:AB23" si="78">Y6/Y3</f>
+        <v>0.44007292966126099</v>
+      </c>
+      <c r="Z23" s="10">
         <f t="shared" si="78"/>
-        <v>0.80892388451443564</v>
-      </c>
-      <c r="I23" s="10">
+        <v>0.44</v>
+      </c>
+      <c r="AA23" s="10">
         <f t="shared" si="78"/>
-        <v>0.72870249017038013</v>
-      </c>
-      <c r="J23" s="10">
+        <v>0.41</v>
+      </c>
+      <c r="AB23" s="10">
         <f t="shared" si="78"/>
-        <v>0.67193240264511389</v>
-      </c>
-      <c r="K23" s="10">
-        <f t="shared" si="78"/>
-        <v>0.57117224880382778</v>
-      </c>
-      <c r="L23" s="10">
-        <f t="shared" si="78"/>
-        <v>0.52970297029702973</v>
-      </c>
-      <c r="M23" s="10">
-        <f t="shared" ref="M23:X23" si="79">M6/M3</f>
-        <v>0.57741477272727282</v>
-      </c>
-      <c r="N23" s="10">
+        <v>0.4</v>
+      </c>
+      <c r="AD23" s="10">
+        <f t="shared" ref="AD23:AQ23" si="79">AD6/AD3</f>
+        <v>1.2988624612202688</v>
+      </c>
+      <c r="AE23" s="10">
         <f t="shared" si="79"/>
-        <v>0.55229283990345945</v>
-      </c>
-      <c r="O23" s="10">
+        <v>1.1087613293051359</v>
+      </c>
+      <c r="AF23" s="10">
         <f t="shared" si="79"/>
-        <v>0.51077199281867147</v>
-      </c>
-      <c r="P23" s="10">
+        <v>0.80962837837837842</v>
+      </c>
+      <c r="AG23" s="10">
         <f t="shared" si="79"/>
-        <v>0.51528013582342957</v>
-      </c>
-      <c r="Q23" s="10">
+        <v>0.61018617239399653</v>
+      </c>
+      <c r="AH23" s="10">
         <f t="shared" si="79"/>
-        <v>0.53175112251443235</v>
-      </c>
-      <c r="R23" s="10">
+        <v>0.53567970565453138</v>
+      </c>
+      <c r="AI23" s="10">
         <f t="shared" si="79"/>
-        <v>0.50934718100890208</v>
-      </c>
-      <c r="S23" s="10">
+        <v>0.49592018528416176</v>
+      </c>
+      <c r="AJ23" s="10">
         <f t="shared" si="79"/>
-        <v>0.48365567965132117</v>
-      </c>
-      <c r="T23" s="10">
+        <v>0.46109088903595863</v>
+      </c>
+      <c r="AK23" s="10">
         <f t="shared" si="79"/>
-        <v>0.467019491416032</v>
-      </c>
-      <c r="U23" s="10">
+        <v>0.42154132210740697</v>
+      </c>
+      <c r="AL23" s="10">
         <f t="shared" si="79"/>
-        <v>0.48364908893447567</v>
-      </c>
-      <c r="V23" s="10">
+        <v>0.35</v>
+      </c>
+      <c r="AM23" s="10">
         <f t="shared" si="79"/>
-        <v>0.46109576427255988</v>
-      </c>
-      <c r="W23" s="10">
+        <v>0.31</v>
+      </c>
+      <c r="AN23" s="10">
         <f t="shared" si="79"/>
-        <v>0.46491879842904149</v>
-      </c>
-      <c r="X23" s="10">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="AO23" s="10">
         <f t="shared" si="79"/>
-        <v>0.43848804215646536</v>
-      </c>
-      <c r="Y23" s="10">
-        <f t="shared" ref="Y23:AB23" si="80">Y6/Y3</f>
-        <v>0.43</v>
-      </c>
-      <c r="Z23" s="10">
+        <v>0.26</v>
+      </c>
+      <c r="AP23" s="10">
+        <f t="shared" si="79"/>
+        <v>0.25</v>
+      </c>
+      <c r="AQ23" s="10">
+        <f t="shared" si="79"/>
+        <v>0.24</v>
+      </c>
+      <c r="AR23" s="10">
+        <f t="shared" ref="AR23:AU23" si="80">AR6/AR3</f>
+        <v>0.23</v>
+      </c>
+      <c r="AS23" s="10">
         <f t="shared" si="80"/>
-        <v>0.41</v>
-      </c>
-      <c r="AA23" s="10">
+        <v>0.23</v>
+      </c>
+      <c r="AT23" s="10">
         <f t="shared" si="80"/>
-        <v>0.41</v>
-      </c>
-      <c r="AB23" s="10">
+        <v>0.23</v>
+      </c>
+      <c r="AU23" s="10">
         <f t="shared" si="80"/>
-        <v>0.4</v>
-      </c>
-      <c r="AD23" s="10">
-        <f t="shared" ref="AD23:AQ23" si="81">AD6/AD3</f>
-        <v>1.2988624612202688</v>
-      </c>
-      <c r="AE23" s="10">
-        <f t="shared" si="81"/>
-        <v>1.1087613293051359</v>
-      </c>
-      <c r="AF23" s="10">
-        <f t="shared" si="81"/>
-        <v>0.80962837837837842</v>
-      </c>
-      <c r="AG23" s="10">
-        <f t="shared" si="81"/>
-        <v>0.61018617239399653</v>
-      </c>
-      <c r="AH23" s="10">
-        <f t="shared" si="81"/>
-        <v>0.53567970565453138</v>
-      </c>
-      <c r="AI23" s="10">
-        <f t="shared" si="81"/>
-        <v>0.49592018528416176</v>
-      </c>
-      <c r="AJ23" s="10">
-        <f t="shared" si="81"/>
-        <v>0.46109088903595863</v>
-      </c>
-      <c r="AK23" s="10">
-        <f t="shared" si="81"/>
-        <v>0.41184921685418047</v>
-      </c>
-      <c r="AL23" s="10">
-        <f t="shared" si="81"/>
-        <v>0.35</v>
-      </c>
-      <c r="AM23" s="10">
-        <f t="shared" si="81"/>
-        <v>0.31</v>
-      </c>
-      <c r="AN23" s="10">
-        <f t="shared" si="81"/>
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="AO23" s="10">
-        <f t="shared" si="81"/>
-        <v>0.26</v>
-      </c>
-      <c r="AP23" s="10">
-        <f t="shared" si="81"/>
-        <v>0.25</v>
-      </c>
-      <c r="AQ23" s="10">
-        <f t="shared" si="81"/>
-        <v>0.23999999999999996</v>
-      </c>
-      <c r="AR23" s="10">
-        <f t="shared" ref="AR23:AU23" si="82">AR6/AR3</f>
         <v>0.23</v>
-      </c>
-      <c r="AS23" s="10">
-        <f t="shared" si="82"/>
-        <v>0.23</v>
-      </c>
-      <c r="AT23" s="10">
-        <f t="shared" si="82"/>
-        <v>0.23</v>
-      </c>
-      <c r="AU23" s="10">
-        <f t="shared" si="82"/>
-        <v>0.23000000000000004</v>
       </c>
       <c r="AW23" t="s">
         <v>41</v>
@@ -4845,160 +4839,160 @@
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
       <c r="G24" s="10">
-        <f t="shared" ref="G24:L25" si="83">G7/C7-1</f>
+        <f t="shared" ref="G24:L25" si="81">G7/C7-1</f>
         <v>1.6750902527075811</v>
       </c>
       <c r="H24" s="10">
-        <f t="shared" si="83"/>
+        <f t="shared" si="81"/>
         <v>2.1649831649831652</v>
       </c>
       <c r="I24" s="10" t="e">
-        <f t="shared" si="83"/>
+        <f t="shared" si="81"/>
         <v>#DIV/0!</v>
       </c>
       <c r="J24" s="10" t="e">
-        <f t="shared" si="83"/>
+        <f t="shared" si="81"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K24" s="10">
-        <f t="shared" si="83"/>
+        <f t="shared" si="81"/>
         <v>0.56410256410256432</v>
       </c>
       <c r="L24" s="10">
-        <f t="shared" si="83"/>
+        <f t="shared" si="81"/>
         <v>0.30957446808510625</v>
       </c>
       <c r="M24" s="10">
-        <f t="shared" ref="M24:X24" si="84">M7/I7-1</f>
+        <f t="shared" ref="M24:X24" si="82">M7/I7-1</f>
         <v>0.37340619307832434</v>
       </c>
       <c r="N24" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="82"/>
         <v>0.55546147332768836</v>
       </c>
       <c r="O24" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="82"/>
         <v>0.82398619499568593</v>
       </c>
       <c r="P24" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="82"/>
         <v>0.966693744922827</v>
       </c>
       <c r="Q24" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="82"/>
         <v>0.83952254641909785</v>
       </c>
       <c r="R24" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="82"/>
         <v>0.70930865541644006</v>
       </c>
       <c r="S24" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="82"/>
         <v>0.57095553453169345</v>
       </c>
       <c r="T24" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="82"/>
         <v>0.50557620817843874</v>
       </c>
       <c r="U24" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="82"/>
         <v>0.48089401586157199</v>
       </c>
       <c r="V24" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="82"/>
         <v>0.39394904458598723</v>
       </c>
       <c r="W24" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="82"/>
         <v>0.33212887684432379</v>
       </c>
       <c r="X24" s="10">
-        <f t="shared" si="84"/>
+        <f t="shared" si="82"/>
         <v>0.35116598079561046</v>
       </c>
       <c r="Y24" s="10">
-        <f t="shared" ref="Y24:Y25" si="85">Y7/U7-1</f>
-        <v>0.30000000000000004</v>
+        <f t="shared" ref="Y24:Y25" si="83">Y7/U7-1</f>
+        <v>0.14995131450827648</v>
       </c>
       <c r="Z24" s="10">
-        <f t="shared" ref="Z24:Z25" si="86">Z7/V7-1</f>
-        <v>0.25</v>
+        <f t="shared" ref="Z24:Z25" si="84">Z7/V7-1</f>
+        <v>0.14999999999999991</v>
       </c>
       <c r="AA24" s="10">
-        <f t="shared" ref="AA24:AA25" si="87">AA7/W7-1</f>
-        <v>0.25</v>
+        <f t="shared" ref="AA24:AA25" si="85">AA7/W7-1</f>
+        <v>0.16999999999999993</v>
       </c>
       <c r="AB24" s="10">
-        <f t="shared" ref="AB24:AB25" si="88">AB7/X7-1</f>
-        <v>0.19999999999999996</v>
+        <f t="shared" ref="AB24:AB25" si="86">AB7/X7-1</f>
+        <v>0.14999999999999991</v>
       </c>
       <c r="AD24" s="10"/>
       <c r="AE24" s="10">
-        <f t="shared" ref="AE24:AQ24" si="89">AE7/AD7-1</f>
+        <f t="shared" ref="AE24:AQ24" si="87">AE7/AD7-1</f>
         <v>0.53129548762736523</v>
       </c>
       <c r="AF24" s="10">
-        <f t="shared" si="89"/>
+        <f t="shared" si="87"/>
         <v>1.2614068441064639</v>
       </c>
       <c r="AG24" s="10">
-        <f t="shared" si="89"/>
+        <f t="shared" si="87"/>
         <v>0.96258932324506086</v>
       </c>
       <c r="AH24" s="10">
-        <f t="shared" si="89"/>
+        <f t="shared" si="87"/>
         <v>0.68772756478903418</v>
       </c>
       <c r="AI24" s="10">
-        <f t="shared" si="89"/>
+        <f t="shared" si="87"/>
         <v>0.63451776649746194</v>
       </c>
       <c r="AJ24" s="10">
-        <f t="shared" si="89"/>
+        <f t="shared" si="87"/>
         <v>0.38462732919254661</v>
       </c>
       <c r="AK24" s="10">
-        <f t="shared" si="89"/>
-        <v>0.24770943142312429</v>
+        <f t="shared" si="87"/>
+        <v>0.15495009532353921</v>
       </c>
       <c r="AL24" s="10">
-        <f t="shared" si="89"/>
-        <v>0.14999999999999991</v>
+        <f t="shared" si="87"/>
+        <v>7.0000000000000062E-2</v>
       </c>
       <c r="AM24" s="10">
-        <f t="shared" si="89"/>
-        <v>8.0000000000000071E-2</v>
+        <f t="shared" si="87"/>
+        <v>4.0000000000000036E-2</v>
       </c>
       <c r="AN24" s="10">
-        <f t="shared" si="89"/>
-        <v>4.0000000000000036E-2</v>
+        <f t="shared" si="87"/>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AO24" s="10">
-        <f t="shared" si="89"/>
-        <v>3.0000000000000027E-2</v>
+        <f t="shared" si="87"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AP24" s="10">
-        <f t="shared" si="89"/>
+        <f t="shared" si="87"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AQ24" s="10">
-        <f t="shared" si="89"/>
+        <f t="shared" si="87"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AR24" s="10">
-        <f t="shared" ref="AR24:AU24" si="90">AR7/AQ7-1</f>
+        <f t="shared" ref="AR24:AU24" si="88">AR7/AQ7-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AS24" s="10">
-        <f t="shared" si="90"/>
+        <f t="shared" si="88"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AT24" s="10">
-        <f t="shared" si="90"/>
+        <f t="shared" si="88"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AU24" s="10">
-        <f t="shared" si="90"/>
+        <f t="shared" si="88"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AW24" t="s">
@@ -5006,7 +5000,7 @@
       </c>
       <c r="AX24" s="6">
         <f>NPV(AX23,AJ16:FD16)</f>
-        <v>4885.1205470761852</v>
+        <v>6238.3937200405708</v>
       </c>
     </row>
     <row r="25" spans="2:50" x14ac:dyDescent="0.3">
@@ -5016,160 +5010,160 @@
       <c r="C25" s="10"/>
       <c r="D25" s="10"/>
       <c r="G25" s="10">
+        <f t="shared" si="81"/>
+        <v>0.76567656765676562</v>
+      </c>
+      <c r="H25" s="10">
+        <f t="shared" si="81"/>
+        <v>1.1316725978647684</v>
+      </c>
+      <c r="I25" s="10" t="e">
+        <f t="shared" si="81"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J25" s="10" t="e">
+        <f t="shared" si="81"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K25" s="10">
+        <f t="shared" si="81"/>
+        <v>0.19813084112149526</v>
+      </c>
+      <c r="L25" s="10">
+        <f t="shared" si="81"/>
+        <v>0.25542570951585986</v>
+      </c>
+      <c r="M25" s="10">
+        <f t="shared" ref="M25:X25" si="89">M8/I8-1</f>
+        <v>0.13036303630363033</v>
+      </c>
+      <c r="N25" s="10">
+        <f t="shared" si="89"/>
+        <v>0.12576687116564411</v>
+      </c>
+      <c r="O25" s="10">
+        <f t="shared" si="89"/>
+        <v>0.19344773790951653</v>
+      </c>
+      <c r="P25" s="10">
+        <f t="shared" si="89"/>
+        <v>3.0585106382978733E-2</v>
+      </c>
+      <c r="Q25" s="10">
+        <f t="shared" si="89"/>
+        <v>0.14598540145985406</v>
+      </c>
+      <c r="R25" s="10">
+        <f t="shared" si="89"/>
+        <v>0.14032697547683926</v>
+      </c>
+      <c r="S25" s="10">
+        <f t="shared" si="89"/>
+        <v>2.8758169934640643E-2</v>
+      </c>
+      <c r="T25" s="10">
+        <f t="shared" si="89"/>
+        <v>5.9354838709677393E-2</v>
+      </c>
+      <c r="U25" s="10">
+        <f t="shared" si="89"/>
+        <v>0.18598726114649677</v>
+      </c>
+      <c r="V25" s="10">
+        <f t="shared" si="89"/>
+        <v>0.16845878136200709</v>
+      </c>
+      <c r="W25" s="10">
+        <f t="shared" si="89"/>
+        <v>0.35069885641677256</v>
+      </c>
+      <c r="X25" s="10">
+        <f t="shared" si="89"/>
+        <v>0.40194884287454324</v>
+      </c>
+      <c r="Y25" s="10">
         <f t="shared" si="83"/>
-        <v>0.76567656765676562</v>
-      </c>
-      <c r="H25" s="10">
-        <f t="shared" si="83"/>
-        <v>1.1316725978647684</v>
-      </c>
-      <c r="I25" s="10" t="e">
-        <f t="shared" si="83"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J25" s="10" t="e">
-        <f t="shared" si="83"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K25" s="10">
-        <f t="shared" si="83"/>
-        <v>0.19813084112149526</v>
-      </c>
-      <c r="L25" s="10">
-        <f t="shared" si="83"/>
-        <v>0.25542570951585986</v>
-      </c>
-      <c r="M25" s="10">
-        <f t="shared" ref="M25:X25" si="91">M8/I8-1</f>
-        <v>0.13036303630363033</v>
-      </c>
-      <c r="N25" s="10">
-        <f t="shared" si="91"/>
-        <v>0.12576687116564411</v>
-      </c>
-      <c r="O25" s="10">
-        <f t="shared" si="91"/>
-        <v>0.19344773790951653</v>
-      </c>
-      <c r="P25" s="10">
-        <f t="shared" si="91"/>
-        <v>3.0585106382978733E-2</v>
-      </c>
-      <c r="Q25" s="10">
-        <f t="shared" si="91"/>
-        <v>0.14598540145985406</v>
-      </c>
-      <c r="R25" s="10">
-        <f t="shared" si="91"/>
-        <v>0.14032697547683926</v>
-      </c>
-      <c r="S25" s="10">
-        <f t="shared" si="91"/>
-        <v>2.8758169934640643E-2</v>
-      </c>
-      <c r="T25" s="10">
-        <f t="shared" si="91"/>
-        <v>5.9354838709677393E-2</v>
-      </c>
-      <c r="U25" s="10">
-        <f t="shared" si="91"/>
-        <v>0.18598726114649677</v>
-      </c>
-      <c r="V25" s="10">
-        <f t="shared" si="91"/>
-        <v>0.16845878136200709</v>
-      </c>
-      <c r="W25" s="10">
-        <f t="shared" si="91"/>
-        <v>0.35069885641677256</v>
-      </c>
-      <c r="X25" s="10">
-        <f t="shared" si="91"/>
-        <v>0.40194884287454324</v>
-      </c>
-      <c r="Y25" s="10">
+        <v>1.2513426423200862</v>
+      </c>
+      <c r="Z25" s="10">
+        <f t="shared" si="84"/>
+        <v>1.17</v>
+      </c>
+      <c r="AA25" s="10">
         <f t="shared" si="85"/>
-        <v>0.39999999999999991</v>
-      </c>
-      <c r="Z25" s="10">
+        <v>1</v>
+      </c>
+      <c r="AB25" s="10">
         <f t="shared" si="86"/>
-        <v>0.35000000000000009</v>
-      </c>
-      <c r="AA25" s="10">
-        <f t="shared" si="87"/>
-        <v>0.25</v>
-      </c>
-      <c r="AB25" s="10">
-        <f t="shared" si="88"/>
-        <v>0.19999999999999996</v>
+        <v>1</v>
       </c>
       <c r="AD25" s="10"/>
       <c r="AE25" s="10">
-        <f t="shared" ref="AE25:AQ25" si="92">AE8/AD8-1</f>
+        <f t="shared" ref="AE25:AQ25" si="90">AE8/AD8-1</f>
         <v>1.9778393351800552</v>
       </c>
       <c r="AF25" s="10">
-        <f t="shared" si="92"/>
+        <f t="shared" si="90"/>
         <v>0.63813953488372088</v>
       </c>
       <c r="AG25" s="10">
-        <f t="shared" si="92"/>
+        <f t="shared" si="90"/>
         <v>0.50539466212379347</v>
       </c>
       <c r="AH25" s="10">
-        <f t="shared" si="92"/>
+        <f t="shared" si="90"/>
         <v>0.11618257261410769</v>
       </c>
       <c r="AI25" s="10">
-        <f t="shared" si="92"/>
+        <f t="shared" si="90"/>
         <v>9.1584994930719921E-2</v>
       </c>
       <c r="AJ25" s="10">
-        <f t="shared" si="92"/>
+        <f t="shared" si="90"/>
         <v>0.27647058823529402</v>
       </c>
       <c r="AK25" s="10">
-        <f t="shared" si="92"/>
-        <v>0.29363327674023787</v>
+        <f t="shared" si="90"/>
+        <v>1.0970797962648557</v>
       </c>
       <c r="AL25" s="10">
-        <f t="shared" si="92"/>
+        <f t="shared" si="90"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AM25" s="10">
-        <f t="shared" si="92"/>
+        <f t="shared" si="90"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AN25" s="10">
-        <f t="shared" si="92"/>
+        <f t="shared" si="90"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AO25" s="10">
-        <f t="shared" si="92"/>
+        <f t="shared" si="90"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AP25" s="10">
-        <f t="shared" si="92"/>
+        <f t="shared" si="90"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AQ25" s="10">
-        <f t="shared" si="92"/>
+        <f t="shared" si="90"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AR25" s="10">
-        <f t="shared" ref="AR25:AU25" si="93">AR8/AQ8-1</f>
+        <f t="shared" ref="AR25:AU25" si="91">AR8/AQ8-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AS25" s="10">
-        <f t="shared" si="93"/>
+        <f t="shared" si="91"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AT25" s="10">
-        <f t="shared" si="93"/>
+        <f t="shared" si="91"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AU25" s="10">
-        <f t="shared" si="93"/>
+        <f t="shared" si="91"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AW25" t="s">
@@ -5177,7 +5171,7 @@
       </c>
       <c r="AX25" s="6">
         <f>Main!D8</f>
-        <v>3024.7000000000007</v>
+        <v>2593.2000000000003</v>
       </c>
     </row>
     <row r="26" spans="2:50" x14ac:dyDescent="0.3">
@@ -5189,7 +5183,7 @@
         <v>-4.5610034207525657E-3</v>
       </c>
       <c r="D26" s="10">
-        <f t="shared" ref="D26" si="94">D14/D13</f>
+        <f t="shared" ref="D26" si="92">D14/D13</f>
         <v>3.6188178528347402E-3</v>
       </c>
       <c r="G26" s="10">
@@ -5197,159 +5191,159 @@
         <v>-2.3752969121140148E-3</v>
       </c>
       <c r="H26" s="10">
-        <f t="shared" ref="H26:L26" si="95">H14/H13</f>
+        <f t="shared" ref="H26:L26" si="93">H14/H13</f>
         <v>-6.5822784810126581E-3</v>
       </c>
       <c r="I26" s="10">
+        <f t="shared" si="93"/>
+        <v>1.4742014742014742E-3</v>
+      </c>
+      <c r="J26" s="10">
+        <f t="shared" si="93"/>
+        <v>-2.6427061310782237E-3</v>
+      </c>
+      <c r="K26" s="10">
+        <f t="shared" si="93"/>
+        <v>-7.8023407022106608E-3</v>
+      </c>
+      <c r="L26" s="10">
+        <f t="shared" si="93"/>
+        <v>-1.1485451761102604E-2</v>
+      </c>
+      <c r="M26" s="10">
+        <f t="shared" ref="M26:X26" si="94">M14/M13</f>
+        <v>0.13877338877338877</v>
+      </c>
+      <c r="N26" s="10">
+        <f t="shared" si="94"/>
+        <v>-1.735952489721334E-2</v>
+      </c>
+      <c r="O26" s="10">
+        <f t="shared" si="94"/>
+        <v>-2.0253164556962026E-2</v>
+      </c>
+      <c r="P26" s="10">
+        <f t="shared" si="94"/>
+        <v>-1.9305019305019308E-3</v>
+      </c>
+      <c r="Q26" s="10">
+        <f t="shared" si="94"/>
+        <v>2.8350515463917529E-2</v>
+      </c>
+      <c r="R26" s="10">
+        <f t="shared" si="94"/>
+        <v>1.601731601731602E-2</v>
+      </c>
+      <c r="S26" s="10">
+        <f t="shared" si="94"/>
+        <v>-1.6090866067203034E-2</v>
+      </c>
+      <c r="T26" s="10">
+        <f t="shared" si="94"/>
+        <v>2.4684270952927686E-2</v>
+      </c>
+      <c r="U26" s="10">
+        <f t="shared" si="94"/>
+        <v>-8.5714285714285719E-3</v>
+      </c>
+      <c r="V26" s="10">
+        <f t="shared" si="94"/>
+        <v>-1.2101910828025473E-2</v>
+      </c>
+      <c r="W26" s="10">
+        <f t="shared" si="94"/>
+        <v>-5.8282208588957066E-3</v>
+      </c>
+      <c r="X26" s="10">
+        <f t="shared" si="94"/>
+        <v>1.3026355649803088E-2</v>
+      </c>
+      <c r="Y26" s="10">
+        <f t="shared" ref="Y26:AB26" si="95">Y14/Y13</f>
+        <v>-1.3433891114777278E-2</v>
+      </c>
+      <c r="Z26" s="10">
         <f t="shared" si="95"/>
-        <v>1.4742014742014742E-3</v>
-      </c>
-      <c r="J26" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="10">
         <f t="shared" si="95"/>
-        <v>-2.6427061310782237E-3</v>
-      </c>
-      <c r="K26" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB26" s="10">
         <f t="shared" si="95"/>
-        <v>-7.8023407022106608E-3</v>
-      </c>
-      <c r="L26" s="10">
-        <f t="shared" si="95"/>
-        <v>-1.1485451761102604E-2</v>
-      </c>
-      <c r="M26" s="10">
-        <f t="shared" ref="M26:X26" si="96">M14/M13</f>
-        <v>0.13877338877338877</v>
-      </c>
-      <c r="N26" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD26" s="10">
+        <f t="shared" ref="AD26:AQ26" si="96">AD14/AD13</f>
+        <v>-4.5172219085262569E-3</v>
+      </c>
+      <c r="AE26" s="10">
         <f t="shared" si="96"/>
-        <v>-1.735952489721334E-2</v>
-      </c>
-      <c r="O26" s="10">
+        <v>-2.8776978417266188E-3</v>
+      </c>
+      <c r="AF26" s="10">
         <f t="shared" si="96"/>
-        <v>-2.0253164556962026E-2</v>
-      </c>
-      <c r="P26" s="10">
+        <v>-3.9106145251396641E-3</v>
+      </c>
+      <c r="AG26" s="10">
         <f t="shared" si="96"/>
-        <v>-1.9305019305019308E-3</v>
-      </c>
-      <c r="Q26" s="10">
+        <v>-4.2829714960862502E-3</v>
+      </c>
+      <c r="AH26" s="10">
         <f t="shared" si="96"/>
-        <v>2.8350515463917529E-2</v>
-      </c>
-      <c r="R26" s="10">
+        <v>2.2671568627450976E-2</v>
+      </c>
+      <c r="AI26" s="10">
         <f t="shared" si="96"/>
-        <v>1.601731601731602E-2</v>
-      </c>
-      <c r="S26" s="10">
+        <v>1.3187330742964794E-2</v>
+      </c>
+      <c r="AJ26" s="10">
         <f t="shared" si="96"/>
-        <v>-1.6090866067203034E-2</v>
-      </c>
-      <c r="T26" s="10">
+        <v>-3.1904131974165428E-3</v>
+      </c>
+      <c r="AK26" s="10">
         <f t="shared" si="96"/>
-        <v>2.4684270952927686E-2</v>
-      </c>
-      <c r="U26" s="10">
+        <v>-3.3722059942203953E-3</v>
+      </c>
+      <c r="AL26" s="10">
         <f t="shared" si="96"/>
-        <v>-8.5714285714285719E-3</v>
-      </c>
-      <c r="V26" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM26" s="10">
         <f t="shared" si="96"/>
-        <v>-1.2101910828025473E-2</v>
-      </c>
-      <c r="W26" s="10">
+        <v>4.9999999999999996E-2</v>
+      </c>
+      <c r="AN26" s="10">
         <f t="shared" si="96"/>
-        <v>-5.8282208588957066E-3</v>
-      </c>
-      <c r="X26" s="10">
+        <v>0.05</v>
+      </c>
+      <c r="AO26" s="10">
         <f t="shared" si="96"/>
-        <v>1.3026355649803088E-2</v>
-      </c>
-      <c r="Y26" s="10">
-        <f t="shared" ref="Y26:AB26" si="97">Y14/Y13</f>
-        <v>0</v>
-      </c>
-      <c r="Z26" s="10">
+        <v>0.1</v>
+      </c>
+      <c r="AP26" s="10">
+        <f t="shared" si="96"/>
+        <v>9.9999999999999992E-2</v>
+      </c>
+      <c r="AQ26" s="10">
+        <f t="shared" si="96"/>
+        <v>0.11</v>
+      </c>
+      <c r="AR26" s="10">
+        <f t="shared" ref="AR26:AU26" si="97">AR14/AR13</f>
+        <v>0.15</v>
+      </c>
+      <c r="AS26" s="10">
         <f t="shared" si="97"/>
-        <v>0</v>
-      </c>
-      <c r="AA26" s="10">
+        <v>0.15</v>
+      </c>
+      <c r="AT26" s="10">
         <f t="shared" si="97"/>
-        <v>0</v>
-      </c>
-      <c r="AB26" s="10">
+        <v>0.15</v>
+      </c>
+      <c r="AU26" s="10">
         <f t="shared" si="97"/>
-        <v>0</v>
-      </c>
-      <c r="AD26" s="10">
-        <f t="shared" ref="AD26:AQ26" si="98">AD14/AD13</f>
-        <v>-4.5172219085262569E-3</v>
-      </c>
-      <c r="AE26" s="10">
-        <f t="shared" si="98"/>
-        <v>-2.8776978417266188E-3</v>
-      </c>
-      <c r="AF26" s="10">
-        <f t="shared" si="98"/>
-        <v>-3.9106145251396641E-3</v>
-      </c>
-      <c r="AG26" s="10">
-        <f t="shared" si="98"/>
-        <v>-4.2829714960862502E-3</v>
-      </c>
-      <c r="AH26" s="10">
-        <f t="shared" si="98"/>
-        <v>2.2671568627450976E-2</v>
-      </c>
-      <c r="AI26" s="10">
-        <f t="shared" si="98"/>
-        <v>1.3187330742964794E-2</v>
-      </c>
-      <c r="AJ26" s="10">
-        <f t="shared" si="98"/>
-        <v>-3.1904131974165428E-3</v>
-      </c>
-      <c r="AK26" s="10">
-        <f t="shared" si="98"/>
-        <v>0</v>
-      </c>
-      <c r="AL26" s="10">
-        <f t="shared" si="98"/>
-        <v>0</v>
-      </c>
-      <c r="AM26" s="10">
-        <f t="shared" si="98"/>
-        <v>0.05</v>
-      </c>
-      <c r="AN26" s="10">
-        <f t="shared" si="98"/>
-        <v>0.05</v>
-      </c>
-      <c r="AO26" s="10">
-        <f t="shared" si="98"/>
-        <v>0.1</v>
-      </c>
-      <c r="AP26" s="10">
-        <f t="shared" si="98"/>
-        <v>0.1</v>
-      </c>
-      <c r="AQ26" s="10">
-        <f t="shared" si="98"/>
-        <v>0.11</v>
-      </c>
-      <c r="AR26" s="10">
-        <f t="shared" ref="AR26:AU26" si="99">AR14/AR13</f>
-        <v>0.15</v>
-      </c>
-      <c r="AS26" s="10">
-        <f t="shared" si="99"/>
-        <v>0.15</v>
-      </c>
-      <c r="AT26" s="10">
-        <f t="shared" si="99"/>
-        <v>0.15</v>
-      </c>
-      <c r="AU26" s="10">
-        <f t="shared" si="99"/>
         <v>0.15</v>
       </c>
       <c r="AW26" t="s">
@@ -5357,7 +5351,7 @@
       </c>
       <c r="AX26" s="6">
         <f>AX24+AX25</f>
-        <v>7909.8205470761859</v>
+        <v>8831.5937200405715</v>
       </c>
     </row>
     <row r="27" spans="2:50" x14ac:dyDescent="0.3">
@@ -5373,171 +5367,171 @@
         <v>-0.94184720638540487</v>
       </c>
       <c r="G27" s="10">
-        <f t="shared" ref="G27:X27" si="100">G16/G3</f>
+        <f t="shared" ref="G27:X27" si="98">G16/G3</f>
         <v>-1.0576441102756891</v>
       </c>
       <c r="H27" s="10">
+        <f t="shared" si="98"/>
+        <v>-1.0435695538057743</v>
+      </c>
+      <c r="I27" s="10">
+        <f t="shared" si="98"/>
+        <v>-0.88772389689820874</v>
+      </c>
+      <c r="J27" s="10">
+        <f t="shared" si="98"/>
+        <v>-0.69691403379867756</v>
+      </c>
+      <c r="K27" s="10">
+        <f t="shared" si="98"/>
+        <v>-0.46351674641148338</v>
+      </c>
+      <c r="L27" s="10">
+        <f t="shared" si="98"/>
+        <v>-0.34418968212610734</v>
+      </c>
+      <c r="M27" s="10">
+        <f t="shared" si="98"/>
+        <v>-0.39228219696969702</v>
+      </c>
+      <c r="N27" s="10">
+        <f t="shared" si="98"/>
+        <v>-0.44790828640386166</v>
+      </c>
+      <c r="O27" s="10">
+        <f t="shared" si="98"/>
+        <v>-0.3608617594254937</v>
+      </c>
+      <c r="P27" s="10">
+        <f t="shared" si="98"/>
+        <v>-0.35195246179966039</v>
+      </c>
+      <c r="Q27" s="10">
+        <f t="shared" si="98"/>
+        <v>-0.36209108402822315</v>
+      </c>
+      <c r="R27" s="10">
+        <f t="shared" si="98"/>
+        <v>-0.33649851632047473</v>
+      </c>
+      <c r="S27" s="10">
+        <f t="shared" si="98"/>
+        <v>-0.29188232089348942</v>
+      </c>
+      <c r="T27" s="10">
+        <f t="shared" si="98"/>
+        <v>-0.21853620756421824</v>
+      </c>
+      <c r="U27" s="10">
+        <f t="shared" si="98"/>
+        <v>-0.38240617835163504</v>
+      </c>
+      <c r="V27" s="10">
+        <f t="shared" si="98"/>
+        <v>-0.36475598526703518</v>
+      </c>
+      <c r="W27" s="10">
+        <f t="shared" si="98"/>
+        <v>-0.34423097335739294</v>
+      </c>
+      <c r="X27" s="10">
+        <f t="shared" si="98"/>
+        <v>-0.33198216457235513</v>
+      </c>
+      <c r="Y27" s="10">
+        <f t="shared" ref="Y27:AB27" si="99">Y16/Y3</f>
+        <v>-0.41272430668841775</v>
+      </c>
+      <c r="Z27" s="10">
+        <f t="shared" si="99"/>
+        <v>-0.40468372467771629</v>
+      </c>
+      <c r="AA27" s="10">
+        <f t="shared" si="99"/>
+        <v>-0.33896977585535859</v>
+      </c>
+      <c r="AB27" s="10">
+        <f t="shared" si="99"/>
+        <v>-0.35100671868666405</v>
+      </c>
+      <c r="AD27" s="10">
+        <f t="shared" ref="AD27:AU27" si="100">AD16/AD3</f>
+        <v>-1.8397104446742503</v>
+      </c>
+      <c r="AE27" s="10">
         <f t="shared" si="100"/>
-        <v>-1.0435695538057743</v>
-      </c>
-      <c r="I27" s="10">
+        <v>-1.3160876132930512</v>
+      </c>
+      <c r="AF27" s="10">
         <f t="shared" si="100"/>
-        <v>-0.88772389689820874</v>
-      </c>
-      <c r="J27" s="10">
+        <v>-0.91064189189189215</v>
+      </c>
+      <c r="AG27" s="10">
         <f t="shared" si="100"/>
-        <v>-0.69691403379867756</v>
-      </c>
-      <c r="K27" s="10">
+        <v>-0.55769703928483561</v>
+      </c>
+      <c r="AH27" s="10">
         <f t="shared" si="100"/>
-        <v>-0.46351674641148338</v>
-      </c>
-      <c r="L27" s="10">
+        <v>-0.3856990704879939</v>
+      </c>
+      <c r="AI27" s="10">
         <f t="shared" si="100"/>
-        <v>-0.34418968212610734</v>
-      </c>
-      <c r="M27" s="10">
+        <v>-0.29795118474968818</v>
+      </c>
+      <c r="AJ27" s="10">
         <f t="shared" si="100"/>
-        <v>-0.39228219696969702</v>
-      </c>
-      <c r="N27" s="10">
+        <v>-0.3545389366865212</v>
+      </c>
+      <c r="AK27" s="10">
         <f t="shared" si="100"/>
-        <v>-0.44790828640386166</v>
-      </c>
-      <c r="O27" s="10">
+        <v>-0.38413800501893447</v>
+      </c>
+      <c r="AL27" s="10">
         <f t="shared" si="100"/>
-        <v>-0.3608617594254937</v>
-      </c>
-      <c r="P27" s="10">
+        <v>-0.21592911581898569</v>
+      </c>
+      <c r="AM27" s="10">
         <f t="shared" si="100"/>
-        <v>-0.35195246179966039</v>
-      </c>
-      <c r="Q27" s="10">
+        <v>-9.2576601910618825E-2</v>
+      </c>
+      <c r="AN27" s="10">
         <f t="shared" si="100"/>
-        <v>-0.36209108402822315</v>
-      </c>
-      <c r="R27" s="10">
+        <v>-1.4024049795817364E-2</v>
+      </c>
+      <c r="AO27" s="10">
         <f t="shared" si="100"/>
-        <v>-0.33649851632047473</v>
-      </c>
-      <c r="S27" s="10">
+        <v>4.2969124207210045E-2</v>
+      </c>
+      <c r="AP27" s="10">
         <f t="shared" si="100"/>
-        <v>-0.29188232089348942</v>
-      </c>
-      <c r="T27" s="10">
+        <v>7.4258263019591111E-2</v>
+      </c>
+      <c r="AQ27" s="10">
         <f t="shared" si="100"/>
-        <v>-0.21853620756421824</v>
-      </c>
-      <c r="U27" s="10">
+        <v>9.7297550022456103E-2</v>
+      </c>
+      <c r="AR27" s="10">
         <f t="shared" si="100"/>
-        <v>-0.38240617835163504</v>
-      </c>
-      <c r="V27" s="10">
+        <v>0.10966136456627751</v>
+      </c>
+      <c r="AS27" s="10">
         <f t="shared" si="100"/>
-        <v>-0.36475598526703518</v>
-      </c>
-      <c r="W27" s="10">
+        <v>0.11780818272152667</v>
+      </c>
+      <c r="AT27" s="10">
         <f t="shared" si="100"/>
-        <v>-0.34423097335739294</v>
-      </c>
-      <c r="X27" s="10">
+        <v>0.12572223464376878</v>
+      </c>
+      <c r="AU27" s="10">
         <f t="shared" si="100"/>
-        <v>-0.33198216457235513</v>
-      </c>
-      <c r="Y27" s="10">
-        <f t="shared" ref="Y27:AB27" si="101">Y16/Y3</f>
-        <v>-0.36838173042114158</v>
-      </c>
-      <c r="Z27" s="10">
-        <f t="shared" si="101"/>
-        <v>-0.34006942334254142</v>
-      </c>
-      <c r="AA27" s="10">
-        <f t="shared" si="101"/>
-        <v>-0.29995115168241165</v>
-      </c>
-      <c r="AB27" s="10">
-        <f t="shared" si="101"/>
-        <v>-0.29432711035670867</v>
-      </c>
-      <c r="AD27" s="10">
-        <f t="shared" ref="AD27:AU27" si="102">AD16/AD3</f>
-        <v>-1.8397104446742503</v>
-      </c>
-      <c r="AE27" s="10">
-        <f t="shared" si="102"/>
-        <v>-1.3160876132930512</v>
-      </c>
-      <c r="AF27" s="10">
-        <f t="shared" si="102"/>
-        <v>-0.91064189189189215</v>
-      </c>
-      <c r="AG27" s="10">
-        <f t="shared" si="102"/>
-        <v>-0.55769703928483561</v>
-      </c>
-      <c r="AH27" s="10">
-        <f t="shared" si="102"/>
-        <v>-0.3856990704879939</v>
-      </c>
-      <c r="AI27" s="10">
-        <f t="shared" si="102"/>
-        <v>-0.29795118474968818</v>
-      </c>
-      <c r="AJ27" s="10">
-        <f t="shared" si="102"/>
-        <v>-0.3545389366865212</v>
-      </c>
-      <c r="AK27" s="10">
-        <f t="shared" si="102"/>
-        <v>-0.33366981786344574</v>
-      </c>
-      <c r="AL27" s="10">
-        <f t="shared" si="102"/>
-        <v>-0.21923291337316642</v>
-      </c>
-      <c r="AM27" s="10">
-        <f t="shared" si="102"/>
-        <v>-0.10965997362494331</v>
-      </c>
-      <c r="AN27" s="10">
-        <f t="shared" si="102"/>
-        <v>-3.2513656296335264E-2</v>
-      </c>
-      <c r="AO27" s="10">
-        <f t="shared" si="102"/>
-        <v>2.4180500964267736E-2</v>
-      </c>
-      <c r="AP27" s="10">
-        <f t="shared" si="102"/>
-        <v>5.6676248608764392E-2</v>
-      </c>
-      <c r="AQ27" s="10">
-        <f t="shared" si="102"/>
-        <v>8.072544445156668E-2</v>
-      </c>
-      <c r="AR27" s="10">
-        <f t="shared" si="102"/>
-        <v>9.4294503036907298E-2</v>
-      </c>
-      <c r="AS27" s="10">
-        <f t="shared" si="102"/>
-        <v>0.10288037437870995</v>
-      </c>
-      <c r="AT27" s="10">
-        <f t="shared" si="102"/>
-        <v>0.11122093511074672</v>
-      </c>
-      <c r="AU27" s="10">
-        <f t="shared" si="102"/>
-        <v>0.11932319410758262</v>
+        <v>0.13341017079680392</v>
       </c>
       <c r="AW27" t="s">
         <v>45</v>
       </c>
       <c r="AX27" s="5">
         <f>AX26/AQ17</f>
-        <v>23.86789543475011</v>
+        <v>26.545217072559577</v>
       </c>
     </row>
     <row r="28" spans="2:50" x14ac:dyDescent="0.3">
@@ -5546,7 +5540,7 @@
       </c>
       <c r="AX28" s="5">
         <f>Main!D3</f>
-        <v>138.38999999999999</v>
+        <v>205.72</v>
       </c>
     </row>
     <row r="29" spans="2:50" x14ac:dyDescent="0.3">
@@ -5555,7 +5549,7 @@
       </c>
       <c r="AX29" s="11">
         <f>AX27/AX28-1</f>
-        <v>-0.82753164654418587</v>
+        <v>-0.8709643346657614</v>
       </c>
     </row>
     <row r="30" spans="2:50" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -5986,7 +5980,7 @@
         <v>8223.2999999999993</v>
       </c>
       <c r="W58" s="12">
-        <f t="shared" ref="W58" si="103">W50+W55+W56+W57</f>
+        <f t="shared" ref="W58" si="101">W50+W55+W56+W57</f>
         <v>8202.2999999999993</v>
       </c>
       <c r="X58" s="12">
@@ -5999,56 +5993,56 @@
         <v>85</v>
       </c>
       <c r="P60" s="9">
-        <f t="shared" ref="P60:AB60" si="104">P16</f>
+        <f t="shared" ref="P60:AB60" si="102">P16</f>
         <v>-207.29999999999998</v>
       </c>
       <c r="Q60" s="9">
-        <f t="shared" si="104"/>
+        <f t="shared" si="102"/>
         <v>-225.79999999999995</v>
       </c>
       <c r="R60" s="9">
-        <f t="shared" si="104"/>
+        <f t="shared" si="102"/>
         <v>-226.79999999999998</v>
       </c>
       <c r="S60" s="9">
-        <f t="shared" si="104"/>
+        <f t="shared" si="102"/>
         <v>-214.29999999999995</v>
       </c>
       <c r="T60" s="9">
-        <f t="shared" si="104"/>
+        <f t="shared" si="102"/>
         <v>-169.29999999999987</v>
       </c>
       <c r="U60" s="9">
-        <f t="shared" si="104"/>
+        <f t="shared" si="102"/>
         <v>-316.89999999999998</v>
       </c>
       <c r="V60" s="9">
-        <f t="shared" si="104"/>
+        <f t="shared" si="102"/>
         <v>-316.90000000000015</v>
       </c>
       <c r="W60" s="9">
-        <f t="shared" si="104"/>
+        <f t="shared" si="102"/>
         <v>-324.2999999999999</v>
       </c>
       <c r="X60" s="9">
-        <f t="shared" si="104"/>
+        <f t="shared" si="102"/>
         <v>-327.60000000000002</v>
       </c>
       <c r="Y60" s="9">
-        <f t="shared" si="104"/>
-        <v>-366.33352800000006</v>
+        <f t="shared" si="102"/>
+        <v>-430.10000000000008</v>
       </c>
       <c r="Z60" s="9">
-        <f t="shared" si="104"/>
-        <v>-354.54277799999994</v>
+        <f t="shared" si="102"/>
+        <v>-421.90706399999988</v>
       </c>
       <c r="AA60" s="9">
-        <f t="shared" si="104"/>
-        <v>-339.100776</v>
+        <f t="shared" si="102"/>
+        <v>-383.21211099999999</v>
       </c>
       <c r="AB60" s="9">
-        <f t="shared" si="104"/>
-        <v>-348.53039100000007</v>
+        <f t="shared" si="102"/>
+        <v>-415.64811600000007</v>
       </c>
       <c r="AI60" s="9">
         <f>AI16</f>
@@ -6059,48 +6053,48 @@
         <v>-1285.7000000000003</v>
       </c>
       <c r="AK60" s="9">
-        <f t="shared" ref="AK60:AU60" si="105">AK16</f>
-        <v>-1452.0242729999995</v>
+        <f t="shared" ref="AK60:AU60" si="103">AK16</f>
+        <v>-1689.9536909999993</v>
       </c>
       <c r="AL60" s="9">
-        <f t="shared" si="105"/>
-        <v>-1182.9990407399987</v>
+        <f t="shared" si="103"/>
+        <v>-1177.9325395199996</v>
       </c>
       <c r="AM60" s="9">
-        <f t="shared" si="105"/>
-        <v>-710.08120966799959</v>
+        <f t="shared" si="103"/>
+        <v>-606.02661039999919</v>
       </c>
       <c r="AN60" s="9">
-        <f t="shared" si="105"/>
-        <v>-240.01066769136114</v>
+        <f t="shared" si="103"/>
+        <v>-104.65711413616123</v>
       </c>
       <c r="AO60" s="9">
-        <f t="shared" si="105"/>
-        <v>198.13126283928906</v>
+        <f t="shared" si="103"/>
+        <v>355.93835647866615</v>
       </c>
       <c r="AP60" s="9">
-        <f t="shared" si="105"/>
-        <v>506.19203596408926</v>
+        <f t="shared" si="103"/>
+        <v>670.48578238868038</v>
       </c>
       <c r="AQ60" s="9">
-        <f t="shared" si="105"/>
-        <v>771.45115546614261</v>
+        <f t="shared" si="103"/>
+        <v>940.00566118122208</v>
       </c>
       <c r="AR60" s="9">
-        <f t="shared" si="105"/>
-        <v>946.1797826811702</v>
+        <f t="shared" si="103"/>
+        <v>1112.4269691830461</v>
       </c>
       <c r="AS60" s="9">
-        <f t="shared" si="105"/>
-        <v>1083.9496841654684</v>
+        <f t="shared" si="103"/>
+        <v>1254.8234300804945</v>
       </c>
       <c r="AT60" s="9">
-        <f t="shared" si="105"/>
-        <v>1230.4172989709855</v>
+        <f t="shared" si="103"/>
+        <v>1406.0752162715817</v>
       </c>
       <c r="AU60" s="9">
-        <f t="shared" si="105"/>
-        <v>1386.0536971287252</v>
+        <f t="shared" si="103"/>
+        <v>1566.6598040659644</v>
       </c>
     </row>
     <row r="61" spans="2:47" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -6132,6 +6126,9 @@
         <v>-327.9</v>
       </c>
       <c r="X61" s="9">
+        <v>-325.7</v>
+      </c>
+      <c r="Y61" s="9">
         <v>-325.7</v>
       </c>
       <c r="AI61" s="9">
@@ -6186,7 +6183,7 @@
         <v>50.1</v>
       </c>
       <c r="Y62" s="6">
-        <v>53</v>
+        <v>48.8</v>
       </c>
       <c r="Z62" s="6">
         <v>56</v>
@@ -6207,47 +6204,47 @@
       </c>
       <c r="AK62" s="6">
         <f>SUM(Y62:AB62)</f>
-        <v>232</v>
+        <v>227.8</v>
       </c>
       <c r="AL62" s="6">
-        <f t="shared" ref="AL62:AU62" si="106">AK62*1.03</f>
-        <v>238.96</v>
+        <f t="shared" ref="AL62:AU62" si="104">AK62*1.03</f>
+        <v>234.63400000000001</v>
       </c>
       <c r="AM62" s="6">
-        <f t="shared" si="106"/>
-        <v>246.12880000000001</v>
+        <f t="shared" si="104"/>
+        <v>241.67302000000001</v>
       </c>
       <c r="AN62" s="6">
-        <f t="shared" si="106"/>
-        <v>253.51266400000003</v>
+        <f t="shared" si="104"/>
+        <v>248.9232106</v>
       </c>
       <c r="AO62" s="6">
-        <f t="shared" si="106"/>
-        <v>261.11804392000005</v>
+        <f t="shared" si="104"/>
+        <v>256.39090691799998</v>
       </c>
       <c r="AP62" s="6">
-        <f t="shared" si="106"/>
-        <v>268.95158523760006</v>
+        <f t="shared" si="104"/>
+        <v>264.08263412553998</v>
       </c>
       <c r="AQ62" s="6">
-        <f t="shared" si="106"/>
-        <v>277.02013279472806</v>
+        <f t="shared" si="104"/>
+        <v>272.00511314930617</v>
       </c>
       <c r="AR62" s="6">
-        <f t="shared" si="106"/>
-        <v>285.33073677856993</v>
+        <f t="shared" si="104"/>
+        <v>280.16526654378538</v>
       </c>
       <c r="AS62" s="6">
-        <f t="shared" si="106"/>
-        <v>293.89065888192704</v>
+        <f t="shared" si="104"/>
+        <v>288.57022454009893</v>
       </c>
       <c r="AT62" s="6">
-        <f t="shared" si="106"/>
-        <v>302.70737864838486</v>
+        <f t="shared" si="104"/>
+        <v>297.22733127630192</v>
       </c>
       <c r="AU62" s="6">
-        <f t="shared" si="106"/>
-        <v>311.78860000783641</v>
+        <f t="shared" si="104"/>
+        <v>306.14415121459098</v>
       </c>
     </row>
     <row r="63" spans="2:47" x14ac:dyDescent="0.3">
@@ -6282,7 +6279,7 @@
         <v>17.600000000000001</v>
       </c>
       <c r="Y63" s="6">
-        <v>20</v>
+        <v>17.8</v>
       </c>
       <c r="Z63" s="6">
         <v>21</v>
@@ -6294,56 +6291,56 @@
         <v>25</v>
       </c>
       <c r="AI63" s="6">
-        <f t="shared" ref="AI63:AI77" si="107">SUM(Q63:T63)</f>
+        <f t="shared" ref="AI63:AI77" si="105">SUM(Q63:T63)</f>
         <v>53</v>
       </c>
       <c r="AJ63" s="6">
-        <f t="shared" ref="AJ63:AJ77" si="108">SUM(U63:X63)</f>
+        <f t="shared" ref="AJ63:AJ77" si="106">SUM(U63:X63)</f>
         <v>59.9</v>
       </c>
       <c r="AK63" s="6">
-        <f t="shared" ref="AK63:AK77" si="109">SUM(Y63:AB63)</f>
-        <v>88</v>
+        <f t="shared" ref="AK63:AK77" si="107">SUM(Y63:AB63)</f>
+        <v>85.8</v>
       </c>
       <c r="AL63" s="6">
-        <f t="shared" ref="AL63:AU63" si="110">AK63*1.03</f>
-        <v>90.64</v>
+        <f t="shared" ref="AL63:AU63" si="108">AK63*1.03</f>
+        <v>88.373999999999995</v>
       </c>
       <c r="AM63" s="6">
-        <f t="shared" si="110"/>
-        <v>93.359200000000001</v>
+        <f t="shared" si="108"/>
+        <v>91.025220000000004</v>
       </c>
       <c r="AN63" s="6">
-        <f t="shared" si="110"/>
-        <v>96.159976</v>
+        <f t="shared" si="108"/>
+        <v>93.755976600000011</v>
       </c>
       <c r="AO63" s="6">
-        <f t="shared" si="110"/>
-        <v>99.044775279999996</v>
+        <f t="shared" si="108"/>
+        <v>96.568655898000017</v>
       </c>
       <c r="AP63" s="6">
-        <f t="shared" si="110"/>
-        <v>102.01611853839999</v>
+        <f t="shared" si="108"/>
+        <v>99.46571557494002</v>
       </c>
       <c r="AQ63" s="6">
-        <f t="shared" si="110"/>
-        <v>105.076602094552</v>
+        <f t="shared" si="108"/>
+        <v>102.44968704218823</v>
       </c>
       <c r="AR63" s="6">
-        <f t="shared" si="110"/>
-        <v>108.22890015738857</v>
+        <f t="shared" si="108"/>
+        <v>105.52317765345389</v>
       </c>
       <c r="AS63" s="6">
-        <f t="shared" si="110"/>
-        <v>111.47576716211023</v>
+        <f t="shared" si="108"/>
+        <v>108.68887298305751</v>
       </c>
       <c r="AT63" s="6">
-        <f t="shared" si="110"/>
-        <v>114.82004017697354</v>
+        <f t="shared" si="108"/>
+        <v>111.94953917254924</v>
       </c>
       <c r="AU63" s="6">
-        <f t="shared" si="110"/>
-        <v>118.26464138228275</v>
+        <f t="shared" si="108"/>
+        <v>115.30802534772572</v>
       </c>
     </row>
     <row r="64" spans="2:47" x14ac:dyDescent="0.3">
@@ -6378,7 +6375,7 @@
         <v>24.3</v>
       </c>
       <c r="Y64" s="6">
-        <v>24</v>
+        <v>25.8</v>
       </c>
       <c r="Z64" s="6">
         <v>25</v>
@@ -6390,56 +6387,56 @@
         <v>26</v>
       </c>
       <c r="AI64" s="6">
+        <f t="shared" si="105"/>
+        <v>74.900000000000006</v>
+      </c>
+      <c r="AJ64" s="6">
+        <f t="shared" si="106"/>
+        <v>93.1</v>
+      </c>
+      <c r="AK64" s="6">
         <f t="shared" si="107"/>
-        <v>74.900000000000006</v>
-      </c>
-      <c r="AJ64" s="6">
-        <f t="shared" si="108"/>
-        <v>93.1</v>
-      </c>
-      <c r="AK64" s="6">
+        <v>101.8</v>
+      </c>
+      <c r="AL64" s="6">
+        <f t="shared" ref="AL64:AU64" si="109">AK64*1.01</f>
+        <v>102.818</v>
+      </c>
+      <c r="AM64" s="6">
         <f t="shared" si="109"/>
-        <v>100</v>
-      </c>
-      <c r="AL64" s="6">
-        <f t="shared" ref="AL64:AU64" si="111">AK64*1.01</f>
-        <v>101</v>
-      </c>
-      <c r="AM64" s="6">
-        <f t="shared" si="111"/>
-        <v>102.01</v>
+        <v>103.84618</v>
       </c>
       <c r="AN64" s="6">
-        <f t="shared" si="111"/>
-        <v>103.0301</v>
+        <f t="shared" si="109"/>
+        <v>104.88464180000001</v>
       </c>
       <c r="AO64" s="6">
-        <f t="shared" si="111"/>
-        <v>104.060401</v>
+        <f t="shared" si="109"/>
+        <v>105.93348821800001</v>
       </c>
       <c r="AP64" s="6">
-        <f t="shared" si="111"/>
-        <v>105.10100500999999</v>
+        <f t="shared" si="109"/>
+        <v>106.99282310018</v>
       </c>
       <c r="AQ64" s="6">
-        <f t="shared" si="111"/>
-        <v>106.1520150601</v>
+        <f t="shared" si="109"/>
+        <v>108.0627513311818</v>
       </c>
       <c r="AR64" s="6">
-        <f t="shared" si="111"/>
-        <v>107.213535210701</v>
+        <f t="shared" si="109"/>
+        <v>109.14337884449363</v>
       </c>
       <c r="AS64" s="6">
-        <f t="shared" si="111"/>
-        <v>108.28567056280801</v>
+        <f t="shared" si="109"/>
+        <v>110.23481263293856</v>
       </c>
       <c r="AT64" s="6">
-        <f t="shared" si="111"/>
-        <v>109.36852726843608</v>
+        <f t="shared" si="109"/>
+        <v>111.33716075926795</v>
       </c>
       <c r="AU64" s="6">
-        <f t="shared" si="111"/>
-        <v>110.46221254112045</v>
+        <f t="shared" si="109"/>
+        <v>112.45053236686063</v>
       </c>
     </row>
     <row r="65" spans="2:47" x14ac:dyDescent="0.3">
@@ -6474,72 +6471,71 @@
         <v>428.1</v>
       </c>
       <c r="Y65" s="6">
-        <f>U65*1.3</f>
-        <v>431.46999999999997</v>
+        <v>379.5</v>
       </c>
       <c r="Z65" s="6">
-        <f t="shared" ref="Z65:AA65" si="112">V65*1.3</f>
-        <v>462.8</v>
+        <f>V65*1.1</f>
+        <v>391.6</v>
       </c>
       <c r="AA65" s="6">
-        <f t="shared" si="112"/>
-        <v>472.29</v>
+        <f>W65*1.1</f>
+        <v>399.63000000000005</v>
       </c>
       <c r="AB65" s="6">
-        <f>X65*1.2</f>
-        <v>513.72</v>
+        <f>X65*1.1</f>
+        <v>470.91000000000008</v>
       </c>
       <c r="AI65" s="6">
+        <f t="shared" si="105"/>
+        <v>1168</v>
+      </c>
+      <c r="AJ65" s="6">
+        <f t="shared" si="106"/>
+        <v>1479.3000000000002</v>
+      </c>
+      <c r="AK65" s="6">
         <f t="shared" si="107"/>
-        <v>1168</v>
-      </c>
-      <c r="AJ65" s="6">
-        <f t="shared" si="108"/>
-        <v>1479.3000000000002</v>
-      </c>
-      <c r="AK65" s="6">
-        <f t="shared" si="109"/>
-        <v>1880.28</v>
+        <v>1641.64</v>
       </c>
       <c r="AL65" s="6">
         <f>AK65*1.05</f>
-        <v>1974.2940000000001</v>
+        <v>1723.7220000000002</v>
       </c>
       <c r="AM65" s="6">
-        <f>AL65*0.8</f>
-        <v>1579.4352000000001</v>
+        <f>AL65*0.9</f>
+        <v>1551.3498000000002</v>
       </c>
       <c r="AN65" s="6">
-        <f>AM65*0.8</f>
-        <v>1263.5481600000003</v>
+        <f t="shared" ref="AN65:AU65" si="110">AM65*0.9</f>
+        <v>1396.2148200000001</v>
       </c>
       <c r="AO65" s="6">
-        <f t="shared" ref="AO65:AU65" si="113">AN65*0.8</f>
-        <v>1010.8385280000002</v>
+        <f t="shared" si="110"/>
+        <v>1256.5933380000001</v>
       </c>
       <c r="AP65" s="6">
-        <f t="shared" si="113"/>
-        <v>808.67082240000025</v>
+        <f t="shared" si="110"/>
+        <v>1130.9340042000001</v>
       </c>
       <c r="AQ65" s="6">
-        <f t="shared" si="113"/>
-        <v>646.93665792000024</v>
+        <f t="shared" si="110"/>
+        <v>1017.8406037800002</v>
       </c>
       <c r="AR65" s="6">
-        <f t="shared" si="113"/>
-        <v>517.54932633600026</v>
+        <f t="shared" si="110"/>
+        <v>916.0565434020001</v>
       </c>
       <c r="AS65" s="6">
-        <f t="shared" si="113"/>
-        <v>414.03946106880022</v>
+        <f t="shared" si="110"/>
+        <v>824.45088906180013</v>
       </c>
       <c r="AT65" s="6">
-        <f t="shared" si="113"/>
-        <v>331.23156885504022</v>
+        <f t="shared" si="110"/>
+        <v>742.00580015562014</v>
       </c>
       <c r="AU65" s="6">
-        <f t="shared" si="113"/>
-        <v>264.98525508403219</v>
+        <f t="shared" si="110"/>
+        <v>667.80522014005817</v>
       </c>
     </row>
     <row r="66" spans="2:47" x14ac:dyDescent="0.3">
@@ -6574,7 +6570,7 @@
         <v>-9.6</v>
       </c>
       <c r="Y66" s="6">
-        <v>-10</v>
+        <v>-7.7</v>
       </c>
       <c r="Z66" s="6">
         <v>-10</v>
@@ -6586,56 +6582,56 @@
         <v>-10</v>
       </c>
       <c r="AI66" s="6">
+        <f t="shared" si="105"/>
+        <v>-61.5</v>
+      </c>
+      <c r="AJ66" s="6">
+        <f t="shared" si="106"/>
+        <v>-43.5</v>
+      </c>
+      <c r="AK66" s="6">
         <f t="shared" si="107"/>
-        <v>-61.5</v>
-      </c>
-      <c r="AJ66" s="6">
-        <f t="shared" si="108"/>
-        <v>-43.5</v>
-      </c>
-      <c r="AK66" s="6">
-        <f t="shared" si="109"/>
-        <v>-40</v>
+        <v>-37.700000000000003</v>
       </c>
       <c r="AL66" s="6">
         <f>AK66*1.02</f>
-        <v>-40.799999999999997</v>
+        <v>-38.454000000000001</v>
       </c>
       <c r="AM66" s="6">
-        <f t="shared" ref="AM66:AU66" si="114">AL66*1.02</f>
-        <v>-41.616</v>
+        <f t="shared" ref="AM66:AU66" si="111">AL66*1.02</f>
+        <v>-39.223080000000003</v>
       </c>
       <c r="AN66" s="6">
-        <f t="shared" si="114"/>
-        <v>-42.448320000000002</v>
+        <f t="shared" si="111"/>
+        <v>-40.007541600000003</v>
       </c>
       <c r="AO66" s="6">
-        <f t="shared" si="114"/>
-        <v>-43.297286400000004</v>
+        <f t="shared" si="111"/>
+        <v>-40.807692432000003</v>
       </c>
       <c r="AP66" s="6">
-        <f t="shared" si="114"/>
-        <v>-44.163232128000004</v>
+        <f t="shared" si="111"/>
+        <v>-41.623846280640002</v>
       </c>
       <c r="AQ66" s="6">
-        <f t="shared" si="114"/>
-        <v>-45.046496770560005</v>
+        <f t="shared" si="111"/>
+        <v>-42.456323206252804</v>
       </c>
       <c r="AR66" s="6">
-        <f t="shared" si="114"/>
-        <v>-45.947426705971203</v>
+        <f t="shared" si="111"/>
+        <v>-43.305449670377861</v>
       </c>
       <c r="AS66" s="6">
-        <f t="shared" si="114"/>
-        <v>-46.866375240090626</v>
+        <f t="shared" si="111"/>
+        <v>-44.171558663785419</v>
       </c>
       <c r="AT66" s="6">
-        <f t="shared" si="114"/>
-        <v>-47.803702744892441</v>
+        <f t="shared" si="111"/>
+        <v>-45.054989837061129</v>
       </c>
       <c r="AU66" s="6">
-        <f t="shared" si="114"/>
-        <v>-48.759776799790288</v>
+        <f t="shared" si="111"/>
+        <v>-45.95608963380235</v>
       </c>
     </row>
     <row r="67" spans="2:47" x14ac:dyDescent="0.3">
@@ -6670,7 +6666,7 @@
         <v>-4.4000000000000004</v>
       </c>
       <c r="Y67" s="6">
-        <v>0</v>
+        <v>29.7</v>
       </c>
       <c r="Z67" s="6">
         <v>0</v>
@@ -6682,16 +6678,16 @@
         <v>0</v>
       </c>
       <c r="AI67" s="6">
+        <f t="shared" si="105"/>
+        <v>-46.800000000000004</v>
+      </c>
+      <c r="AJ67" s="6">
+        <f t="shared" si="106"/>
+        <v>31.4</v>
+      </c>
+      <c r="AK67" s="6">
         <f t="shared" si="107"/>
-        <v>-46.800000000000004</v>
-      </c>
-      <c r="AJ67" s="6">
-        <f t="shared" si="108"/>
-        <v>31.4</v>
-      </c>
-      <c r="AK67" s="6">
-        <f t="shared" si="109"/>
-        <v>0</v>
+        <v>29.7</v>
       </c>
       <c r="AL67" s="6">
         <f>0</f>
@@ -6766,7 +6762,7 @@
         <v>2.1</v>
       </c>
       <c r="Y68" s="6">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z68" s="6">
         <v>0</v>
@@ -6778,56 +6774,56 @@
         <v>0</v>
       </c>
       <c r="AI68" s="6">
+        <f t="shared" si="105"/>
+        <v>0</v>
+      </c>
+      <c r="AJ68" s="6">
+        <f t="shared" si="106"/>
+        <v>2.8</v>
+      </c>
+      <c r="AK68" s="6">
         <f t="shared" si="107"/>
-        <v>0</v>
-      </c>
-      <c r="AJ68" s="6">
-        <f t="shared" si="108"/>
-        <v>2.8</v>
-      </c>
-      <c r="AK68" s="6">
-        <f t="shared" si="109"/>
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL68" s="6">
-        <f t="shared" ref="AL68:AU68" si="115">AK68*1.2</f>
-        <v>0</v>
+        <f t="shared" ref="AL68:AU68" si="112">AK68*1.2</f>
+        <v>2.52</v>
       </c>
       <c r="AM68" s="6">
-        <f t="shared" si="115"/>
-        <v>0</v>
+        <f t="shared" si="112"/>
+        <v>3.024</v>
       </c>
       <c r="AN68" s="6">
-        <f t="shared" si="115"/>
-        <v>0</v>
+        <f t="shared" si="112"/>
+        <v>3.6288</v>
       </c>
       <c r="AO68" s="6">
-        <f t="shared" si="115"/>
-        <v>0</v>
+        <f t="shared" si="112"/>
+        <v>4.3545600000000002</v>
       </c>
       <c r="AP68" s="6">
-        <f t="shared" si="115"/>
-        <v>0</v>
+        <f t="shared" si="112"/>
+        <v>5.2254719999999999</v>
       </c>
       <c r="AQ68" s="6">
-        <f t="shared" si="115"/>
-        <v>0</v>
+        <f t="shared" si="112"/>
+        <v>6.2705663999999999</v>
       </c>
       <c r="AR68" s="6">
-        <f t="shared" si="115"/>
-        <v>0</v>
+        <f t="shared" si="112"/>
+        <v>7.5246796799999993</v>
       </c>
       <c r="AS68" s="6">
-        <f t="shared" si="115"/>
-        <v>0</v>
+        <f t="shared" si="112"/>
+        <v>9.0296156159999992</v>
       </c>
       <c r="AT68" s="6">
-        <f t="shared" si="115"/>
-        <v>0</v>
+        <f t="shared" si="112"/>
+        <v>10.835538739199999</v>
       </c>
       <c r="AU68" s="6">
-        <f t="shared" si="115"/>
-        <v>0</v>
+        <f t="shared" si="112"/>
+        <v>13.002646487039998</v>
       </c>
     </row>
     <row r="69" spans="2:47" x14ac:dyDescent="0.3">
@@ -6862,7 +6858,7 @@
         <v>-7.1</v>
       </c>
       <c r="Y69" s="6">
-        <v>0</v>
+        <v>106.5</v>
       </c>
       <c r="Z69" s="6">
         <v>0</v>
@@ -6874,56 +6870,56 @@
         <v>0</v>
       </c>
       <c r="AI69" s="6">
+        <f t="shared" si="105"/>
+        <v>-26.799999999999997</v>
+      </c>
+      <c r="AJ69" s="6">
+        <f t="shared" si="106"/>
+        <v>-7.6</v>
+      </c>
+      <c r="AK69" s="6">
         <f t="shared" si="107"/>
-        <v>-26.799999999999997</v>
-      </c>
-      <c r="AJ69" s="6">
-        <f t="shared" si="108"/>
-        <v>-7.6</v>
-      </c>
-      <c r="AK69" s="6">
-        <f t="shared" si="109"/>
-        <v>0</v>
+        <v>106.5</v>
       </c>
       <c r="AL69" s="6">
-        <f t="shared" ref="AL69:AR69" si="116">AK69*1.5</f>
-        <v>0</v>
+        <f t="shared" ref="AL69:AR69" si="113">AK69*1.5</f>
+        <v>159.75</v>
       </c>
       <c r="AM69" s="6">
-        <f t="shared" si="116"/>
-        <v>0</v>
+        <f t="shared" si="113"/>
+        <v>239.625</v>
       </c>
       <c r="AN69" s="6">
-        <f t="shared" si="116"/>
-        <v>0</v>
+        <f>AM69*1.02</f>
+        <v>244.41750000000002</v>
       </c>
       <c r="AO69" s="6">
-        <f t="shared" si="116"/>
-        <v>0</v>
+        <f t="shared" ref="AO69:AU69" si="114">AN69*1.02</f>
+        <v>249.30585000000002</v>
       </c>
       <c r="AP69" s="6">
-        <f t="shared" si="116"/>
-        <v>0</v>
+        <f t="shared" si="114"/>
+        <v>254.29196700000003</v>
       </c>
       <c r="AQ69" s="6">
-        <f t="shared" si="116"/>
-        <v>0</v>
+        <f t="shared" si="114"/>
+        <v>259.37780634000001</v>
       </c>
       <c r="AR69" s="6">
-        <f t="shared" si="116"/>
-        <v>0</v>
+        <f t="shared" si="114"/>
+        <v>264.56536246680002</v>
       </c>
       <c r="AS69" s="6">
-        <f>AR69*1.2</f>
-        <v>0</v>
+        <f t="shared" si="114"/>
+        <v>269.85666971613603</v>
       </c>
       <c r="AT69" s="6">
-        <f t="shared" ref="AT69:AU69" si="117">AS69*1.2</f>
-        <v>0</v>
+        <f t="shared" si="114"/>
+        <v>275.25380311045876</v>
       </c>
       <c r="AU69" s="6">
-        <f t="shared" si="117"/>
-        <v>0</v>
+        <f t="shared" si="114"/>
+        <v>280.75887917266795</v>
       </c>
     </row>
     <row r="70" spans="2:47" x14ac:dyDescent="0.3">
@@ -6958,7 +6954,7 @@
         <v>2.5</v>
       </c>
       <c r="Y70" s="6">
-        <v>0</v>
+        <v>-5.2</v>
       </c>
       <c r="Z70" s="6">
         <v>0</v>
@@ -6970,16 +6966,16 @@
         <v>0</v>
       </c>
       <c r="AI70" s="6">
+        <f t="shared" si="105"/>
+        <v>14.9</v>
+      </c>
+      <c r="AJ70" s="6">
+        <f t="shared" si="106"/>
+        <v>7.4</v>
+      </c>
+      <c r="AK70" s="6">
         <f t="shared" si="107"/>
-        <v>14.9</v>
-      </c>
-      <c r="AJ70" s="6">
-        <f t="shared" si="108"/>
-        <v>7.4</v>
-      </c>
-      <c r="AK70" s="6">
-        <f t="shared" si="109"/>
-        <v>0</v>
+        <v>-5.2</v>
       </c>
       <c r="AL70" s="6">
         <v>0</v>
@@ -7044,7 +7040,7 @@
         <v>-328.2</v>
       </c>
       <c r="Y71" s="6">
-        <v>0</v>
+        <v>393.7</v>
       </c>
       <c r="Z71" s="6">
         <v>0</v>
@@ -7056,16 +7052,16 @@
         <v>0</v>
       </c>
       <c r="AI71" s="6">
+        <f t="shared" si="105"/>
+        <v>-212.10000000000002</v>
+      </c>
+      <c r="AJ71" s="6">
+        <f t="shared" si="106"/>
+        <v>0.49999999999994316</v>
+      </c>
+      <c r="AK71" s="6">
         <f t="shared" si="107"/>
-        <v>-212.10000000000002</v>
-      </c>
-      <c r="AJ71" s="6">
-        <f t="shared" si="108"/>
-        <v>0.49999999999994316</v>
-      </c>
-      <c r="AK71" s="6">
-        <f t="shared" si="109"/>
-        <v>0</v>
+        <v>393.7</v>
       </c>
       <c r="AL71" s="6">
         <v>0</v>
@@ -7130,7 +7126,7 @@
         <v>-38.799999999999997</v>
       </c>
       <c r="Y72" s="6">
-        <v>0</v>
+        <v>-31.1</v>
       </c>
       <c r="Z72" s="6">
         <v>0</v>
@@ -7142,16 +7138,16 @@
         <v>0</v>
       </c>
       <c r="AI72" s="6">
+        <f t="shared" si="105"/>
+        <v>-134.80000000000001</v>
+      </c>
+      <c r="AJ72" s="6">
+        <f t="shared" si="106"/>
+        <v>-101.5</v>
+      </c>
+      <c r="AK72" s="6">
         <f t="shared" si="107"/>
-        <v>-134.80000000000001</v>
-      </c>
-      <c r="AJ72" s="6">
-        <f t="shared" si="108"/>
-        <v>-101.5</v>
-      </c>
-      <c r="AK72" s="6">
-        <f t="shared" si="109"/>
-        <v>0</v>
+        <v>-31.1</v>
       </c>
       <c r="AL72" s="6">
         <v>0</v>
@@ -7216,7 +7212,7 @@
         <v>-12.6</v>
       </c>
       <c r="Y73" s="6">
-        <v>0</v>
+        <v>-17.899999999999999</v>
       </c>
       <c r="Z73" s="6">
         <v>0</v>
@@ -7228,16 +7224,16 @@
         <v>0</v>
       </c>
       <c r="AI73" s="6">
+        <f t="shared" si="105"/>
+        <v>59.8</v>
+      </c>
+      <c r="AJ73" s="6">
+        <f t="shared" si="106"/>
+        <v>29.9</v>
+      </c>
+      <c r="AK73" s="6">
         <f t="shared" si="107"/>
-        <v>59.8</v>
-      </c>
-      <c r="AJ73" s="6">
-        <f t="shared" si="108"/>
-        <v>29.9</v>
-      </c>
-      <c r="AK73" s="6">
-        <f t="shared" si="109"/>
-        <v>0</v>
+        <v>-17.899999999999999</v>
       </c>
       <c r="AL73" s="6">
         <v>0</v>
@@ -7302,7 +7298,7 @@
         <v>6.1</v>
       </c>
       <c r="Y74" s="6">
-        <v>0</v>
+        <v>-4.4000000000000004</v>
       </c>
       <c r="Z74" s="6">
         <v>0</v>
@@ -7314,16 +7310,16 @@
         <v>0</v>
       </c>
       <c r="AI74" s="6">
+        <f t="shared" si="105"/>
+        <v>19.200000000000003</v>
+      </c>
+      <c r="AJ74" s="6">
+        <f t="shared" si="106"/>
+        <v>108.8</v>
+      </c>
+      <c r="AK74" s="6">
         <f t="shared" si="107"/>
-        <v>19.200000000000003</v>
-      </c>
-      <c r="AJ74" s="6">
-        <f t="shared" si="108"/>
-        <v>108.8</v>
-      </c>
-      <c r="AK74" s="6">
-        <f t="shared" si="109"/>
-        <v>0</v>
+        <v>-4.4000000000000004</v>
       </c>
       <c r="AL74" s="6">
         <v>0</v>
@@ -7388,7 +7384,7 @@
         <v>32.200000000000003</v>
       </c>
       <c r="Y75" s="6">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Z75" s="6">
         <v>0</v>
@@ -7400,16 +7396,16 @@
         <v>0</v>
       </c>
       <c r="AI75" s="6">
+        <f t="shared" si="105"/>
+        <v>171</v>
+      </c>
+      <c r="AJ75" s="6">
+        <f t="shared" si="106"/>
+        <v>70.900000000000006</v>
+      </c>
+      <c r="AK75" s="6">
         <f t="shared" si="107"/>
-        <v>171</v>
-      </c>
-      <c r="AJ75" s="6">
-        <f t="shared" si="108"/>
-        <v>70.900000000000006</v>
-      </c>
-      <c r="AK75" s="6">
-        <f t="shared" si="109"/>
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AL75" s="6">
         <v>0</v>
@@ -7474,7 +7470,7 @@
         <v>-12.4</v>
       </c>
       <c r="Y76" s="6">
-        <v>0</v>
+        <v>-11.8</v>
       </c>
       <c r="Z76" s="6">
         <v>0</v>
@@ -7486,55 +7482,54 @@
         <v>0</v>
       </c>
       <c r="AI76" s="6">
+        <f t="shared" si="105"/>
+        <v>-40.6</v>
+      </c>
+      <c r="AJ76" s="6">
+        <f t="shared" si="106"/>
+        <v>-46.8</v>
+      </c>
+      <c r="AK76" s="6">
         <f t="shared" si="107"/>
-        <v>-40.6</v>
-      </c>
-      <c r="AJ76" s="6">
-        <f t="shared" si="108"/>
-        <v>-46.8</v>
-      </c>
-      <c r="AK76" s="6">
-        <f t="shared" si="109"/>
-        <v>0</v>
+        <v>-11.8</v>
       </c>
       <c r="AL76" s="6">
-        <f t="shared" ref="AL76:AU76" si="118">AK76*1.05</f>
         <v>0</v>
       </c>
       <c r="AM76" s="6">
-        <f t="shared" si="118"/>
+        <f t="shared" ref="AL76:AU76" si="115">AL76*1.05</f>
         <v>0</v>
       </c>
       <c r="AN76" s="6">
-        <f t="shared" si="118"/>
+        <f t="shared" si="115"/>
         <v>0</v>
       </c>
       <c r="AO76" s="6">
-        <f t="shared" si="118"/>
+        <f t="shared" si="115"/>
         <v>0</v>
       </c>
       <c r="AP76" s="6">
-        <f t="shared" si="118"/>
+        <f t="shared" si="115"/>
         <v>0</v>
       </c>
       <c r="AQ76" s="6">
-        <f t="shared" si="118"/>
+        <f t="shared" si="115"/>
         <v>0</v>
       </c>
       <c r="AR76" s="6">
-        <f t="shared" si="118"/>
+        <f t="shared" si="115"/>
         <v>0</v>
       </c>
       <c r="AS76" s="6">
-        <f t="shared" si="118"/>
+        <f t="shared" si="115"/>
         <v>0</v>
       </c>
       <c r="AT76" s="6">
-        <f t="shared" si="118"/>
+        <f t="shared" si="115"/>
         <v>0</v>
       </c>
       <c r="AU76" s="6">
-        <f t="shared" si="118"/>
+        <f t="shared" si="115"/>
         <v>0</v>
       </c>
     </row>
@@ -7570,7 +7565,7 @@
         <v>609.4</v>
       </c>
       <c r="Y77" s="6">
-        <v>0</v>
+        <v>-271.39999999999998</v>
       </c>
       <c r="Z77" s="6">
         <v>0</v>
@@ -7582,16 +7577,16 @@
         <v>0</v>
       </c>
       <c r="AI77" s="6">
+        <f t="shared" si="105"/>
+        <v>528</v>
+      </c>
+      <c r="AJ77" s="6">
+        <f t="shared" si="106"/>
+        <v>382.7</v>
+      </c>
+      <c r="AK77" s="6">
         <f t="shared" si="107"/>
-        <v>528</v>
-      </c>
-      <c r="AJ77" s="6">
-        <f t="shared" si="108"/>
-        <v>382.7</v>
-      </c>
-      <c r="AK77" s="6">
-        <f t="shared" si="109"/>
-        <v>0</v>
+        <v>-271.39999999999998</v>
       </c>
       <c r="AL77" s="6">
         <v>0</v>
@@ -7629,56 +7624,56 @@
         <v>93</v>
       </c>
       <c r="P78" s="9">
-        <f t="shared" ref="P78:X78" si="119">P60+SUM(P62:P77)</f>
+        <f t="shared" ref="P78:X78" si="116">P60+SUM(P62:P77)</f>
         <v>217.1</v>
       </c>
       <c r="Q78" s="9">
-        <f t="shared" si="119"/>
+        <f t="shared" si="116"/>
         <v>299.80000000000007</v>
       </c>
       <c r="R78" s="9">
-        <f t="shared" si="119"/>
+        <f t="shared" si="116"/>
         <v>83.6</v>
       </c>
       <c r="S78" s="9">
-        <f t="shared" si="119"/>
+        <f t="shared" si="116"/>
         <v>121.50000000000011</v>
       </c>
       <c r="T78" s="9">
-        <f t="shared" si="119"/>
+        <f t="shared" si="116"/>
         <v>345.10000000000014</v>
       </c>
       <c r="U78" s="9">
-        <f t="shared" si="119"/>
+        <f t="shared" si="116"/>
         <v>356.30000000000007</v>
       </c>
       <c r="V78" s="9">
-        <f t="shared" si="119"/>
+        <f t="shared" si="116"/>
         <v>70.699999999999875</v>
       </c>
       <c r="W78" s="9">
-        <f t="shared" si="119"/>
+        <f t="shared" si="116"/>
         <v>105.30000000000013</v>
       </c>
       <c r="X78" s="9">
-        <f t="shared" si="119"/>
+        <f t="shared" si="116"/>
         <v>431.69999999999993</v>
       </c>
       <c r="Y78" s="9">
-        <f t="shared" ref="Y78:AB78" si="120">Y60+SUM(Y62:Y77)</f>
-        <v>152.13647199999997</v>
+        <f t="shared" ref="Y78:AB78" si="117">Y60+SUM(Y62:Y77)</f>
+        <v>228.2</v>
       </c>
       <c r="Z78" s="9">
-        <f t="shared" si="120"/>
-        <v>200.25722200000001</v>
+        <f t="shared" si="117"/>
+        <v>61.692936000000145</v>
       </c>
       <c r="AA78" s="9">
-        <f t="shared" si="120"/>
-        <v>230.18922399999997</v>
+        <f t="shared" si="117"/>
+        <v>113.41788900000006</v>
       </c>
       <c r="AB78" s="9">
-        <f t="shared" si="120"/>
-        <v>269.18960899999996</v>
+        <f t="shared" si="117"/>
+        <v>159.26188400000001</v>
       </c>
       <c r="AI78" s="9">
         <f>AI60+SUM(AI62:AI77)</f>
@@ -7689,48 +7684,48 @@
         <v>964.00000000000045</v>
       </c>
       <c r="AK78" s="9">
-        <f t="shared" ref="AK78:AU78" si="121">AK60+SUM(AK62:AK77)</f>
-        <v>808.25572700000021</v>
+        <f t="shared" ref="AK78:AU78" si="118">AK60+SUM(AK62:AK77)</f>
+        <v>523.48630900000035</v>
       </c>
       <c r="AL78" s="9">
-        <f t="shared" si="121"/>
-        <v>1181.0949592600014</v>
+        <f t="shared" si="118"/>
+        <v>1095.4314604800004</v>
       </c>
       <c r="AM78" s="9">
-        <f t="shared" si="121"/>
-        <v>1269.2359903320007</v>
+        <f t="shared" si="118"/>
+        <v>1585.2935296000005</v>
       </c>
       <c r="AN78" s="9">
-        <f t="shared" si="121"/>
-        <v>1433.7919123086392</v>
+        <f t="shared" si="118"/>
+        <v>1947.1602932638386</v>
       </c>
       <c r="AO78" s="9">
-        <f t="shared" si="121"/>
-        <v>1629.8957246392893</v>
+        <f t="shared" si="118"/>
+        <v>2284.2774630806662</v>
       </c>
       <c r="AP78" s="9">
-        <f t="shared" si="121"/>
-        <v>1746.7683350220893</v>
+        <f t="shared" si="118"/>
+        <v>2489.8545521087008</v>
       </c>
       <c r="AQ78" s="9">
-        <f t="shared" si="121"/>
-        <v>1861.5900665649629</v>
+        <f t="shared" si="118"/>
+        <v>2663.5558660176457</v>
       </c>
       <c r="AR78" s="9">
-        <f t="shared" si="121"/>
-        <v>1918.5548544578587</v>
+        <f t="shared" si="118"/>
+        <v>2752.0999281032014</v>
       </c>
       <c r="AS78" s="9">
-        <f t="shared" si="121"/>
-        <v>1964.7748666010234</v>
+        <f t="shared" si="118"/>
+        <v>2821.4829559667405</v>
       </c>
       <c r="AT78" s="9">
-        <f t="shared" si="121"/>
-        <v>2040.7411111749277</v>
+        <f t="shared" si="118"/>
+        <v>2909.6293996479185</v>
       </c>
       <c r="AU78" s="9">
-        <f t="shared" si="121"/>
-        <v>2142.7946293442069</v>
+        <f t="shared" si="118"/>
+        <v>3016.1731691611058</v>
       </c>
     </row>
     <row r="79" spans="2:47" x14ac:dyDescent="0.3">
@@ -7765,7 +7760,7 @@
         <v>11.3</v>
       </c>
       <c r="Y79" s="6">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="Z79" s="6">
         <v>16</v>
@@ -7777,16 +7772,16 @@
         <v>16</v>
       </c>
       <c r="AI79" s="6">
-        <f t="shared" ref="AI79:AI80" si="122">SUM(Q79:T79)</f>
+        <f t="shared" ref="AI79:AI80" si="119">SUM(Q79:T79)</f>
         <v>35.1</v>
       </c>
       <c r="AJ79" s="6">
-        <f t="shared" ref="AJ79:AJ80" si="123">SUM(U79:X79)</f>
+        <f t="shared" ref="AJ79:AJ80" si="120">SUM(U79:X79)</f>
         <v>46.2</v>
       </c>
       <c r="AK79" s="6">
-        <f t="shared" ref="AK79:AK80" si="124">SUM(Y79:AB79)</f>
-        <v>64</v>
+        <f t="shared" ref="AK79:AK80" si="121">SUM(Y79:AB79)</f>
+        <v>93</v>
       </c>
       <c r="AL79" s="6"/>
       <c r="AM79" s="6"/>
@@ -7831,7 +7826,7 @@
         <v>6</v>
       </c>
       <c r="Y80" s="6">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Z80" s="6">
         <v>7</v>
@@ -7843,16 +7838,16 @@
         <v>7</v>
       </c>
       <c r="AI80" s="6">
-        <f t="shared" si="122"/>
+        <f t="shared" si="119"/>
         <v>34.1</v>
       </c>
       <c r="AJ80" s="6">
-        <f t="shared" si="123"/>
+        <f t="shared" si="120"/>
         <v>29.4</v>
       </c>
       <c r="AK80" s="6">
-        <f t="shared" si="124"/>
-        <v>28</v>
+        <f t="shared" si="121"/>
+        <v>21</v>
       </c>
       <c r="AL80" s="6"/>
       <c r="AM80" s="6"/>
@@ -7867,111 +7862,111 @@
     </row>
     <row r="81" spans="2:159" x14ac:dyDescent="0.3">
       <c r="B81" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="P81" s="6">
         <f>P79+P80</f>
         <v>12.100000000000001</v>
       </c>
       <c r="Q81" s="6">
-        <f t="shared" ref="Q81:X81" si="125">Q79+Q80</f>
+        <f t="shared" ref="Q81:X81" si="122">Q79+Q80</f>
         <v>16.3</v>
       </c>
       <c r="R81" s="6">
-        <f t="shared" si="125"/>
+        <f t="shared" si="122"/>
         <v>14.2</v>
       </c>
       <c r="S81" s="6">
-        <f t="shared" si="125"/>
+        <f t="shared" si="122"/>
         <v>18.600000000000001</v>
       </c>
       <c r="T81" s="6">
-        <f t="shared" si="125"/>
+        <f t="shared" si="122"/>
         <v>20.100000000000001</v>
       </c>
       <c r="U81" s="6">
-        <f t="shared" si="125"/>
+        <f t="shared" si="122"/>
         <v>23.9</v>
       </c>
       <c r="V81" s="6">
-        <f t="shared" si="125"/>
+        <f t="shared" si="122"/>
         <v>11</v>
       </c>
       <c r="W81" s="6">
-        <f t="shared" si="125"/>
+        <f t="shared" si="122"/>
         <v>23.4</v>
       </c>
       <c r="X81" s="6">
-        <f t="shared" si="125"/>
+        <f t="shared" si="122"/>
         <v>17.3</v>
       </c>
       <c r="Y81" s="6">
-        <f t="shared" ref="Y81" si="126">Y79+Y80</f>
+        <f t="shared" ref="Y81" si="123">Y79+Y80</f>
+        <v>45</v>
+      </c>
+      <c r="Z81" s="6">
+        <f t="shared" ref="Z81" si="124">Z79+Z80</f>
         <v>23</v>
       </c>
-      <c r="Z81" s="6">
-        <f t="shared" ref="Z81" si="127">Z79+Z80</f>
+      <c r="AA81" s="6">
+        <f t="shared" ref="AA81" si="125">AA79+AA80</f>
         <v>23</v>
       </c>
-      <c r="AA81" s="6">
-        <f t="shared" ref="AA81" si="128">AA79+AA80</f>
+      <c r="AB81" s="6">
+        <f t="shared" ref="AB81" si="126">AB79+AB80</f>
         <v>23</v>
       </c>
-      <c r="AB81" s="6">
-        <f t="shared" ref="AB81" si="129">AB79+AB80</f>
-        <v>23</v>
-      </c>
       <c r="AI81" s="6">
-        <f t="shared" ref="AI81" si="130">AI79+AI80</f>
+        <f t="shared" ref="AI81" si="127">AI79+AI80</f>
         <v>69.2</v>
       </c>
       <c r="AJ81" s="6">
-        <f t="shared" ref="AJ81" si="131">AJ79+AJ80</f>
+        <f t="shared" ref="AJ81" si="128">AJ79+AJ80</f>
         <v>75.599999999999994</v>
       </c>
       <c r="AK81" s="6">
-        <f t="shared" ref="AK81" si="132">AK79+AK80</f>
-        <v>92</v>
+        <f t="shared" ref="AK81" si="129">AK79+AK80</f>
+        <v>114</v>
       </c>
       <c r="AL81" s="6">
-        <f>AK81*1.14</f>
-        <v>104.88</v>
+        <f>AK81*1.5</f>
+        <v>171</v>
       </c>
       <c r="AM81" s="6">
-        <f>AL81*1.09</f>
-        <v>114.31920000000001</v>
+        <f>AL81*1.02</f>
+        <v>174.42000000000002</v>
       </c>
       <c r="AN81" s="6">
-        <f>AM81*1.05</f>
-        <v>120.03516000000002</v>
+        <f t="shared" ref="AN81:AU81" si="130">AM81*1.02</f>
+        <v>177.90840000000003</v>
       </c>
       <c r="AO81" s="6">
-        <f>AN81*1.04</f>
-        <v>124.83656640000002</v>
+        <f t="shared" si="130"/>
+        <v>181.46656800000002</v>
       </c>
       <c r="AP81" s="6">
-        <f>AO81*1.03</f>
-        <v>128.58166339200002</v>
+        <f t="shared" si="130"/>
+        <v>185.09589936000003</v>
       </c>
       <c r="AQ81" s="6">
-        <f>AP81*1.02</f>
-        <v>131.15329665984004</v>
+        <f t="shared" si="130"/>
+        <v>188.79781734720004</v>
       </c>
       <c r="AR81" s="6">
-        <f t="shared" ref="AR81:AU81" si="133">AQ81*1.02</f>
-        <v>133.77636259303685</v>
+        <f t="shared" si="130"/>
+        <v>192.57377369414405</v>
       </c>
       <c r="AS81" s="6">
-        <f t="shared" si="133"/>
-        <v>136.45188984489758</v>
+        <f t="shared" si="130"/>
+        <v>196.42524916802694</v>
       </c>
       <c r="AT81" s="6">
-        <f t="shared" si="133"/>
-        <v>139.18092764179553</v>
+        <f t="shared" si="130"/>
+        <v>200.35375415138748</v>
       </c>
       <c r="AU81" s="6">
-        <f t="shared" si="133"/>
-        <v>141.96454619463145</v>
+        <f t="shared" si="130"/>
+        <v>204.36082923441523</v>
       </c>
     </row>
     <row r="82" spans="2:159" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -7983,657 +7978,657 @@
         <v>205</v>
       </c>
       <c r="Q82" s="9">
-        <f t="shared" ref="Q82:X82" si="134">Q78-Q81</f>
+        <f t="shared" ref="Q82:X82" si="131">Q78-Q81</f>
         <v>283.50000000000006</v>
       </c>
       <c r="R82" s="9">
-        <f t="shared" si="134"/>
+        <f t="shared" si="131"/>
         <v>69.399999999999991</v>
       </c>
       <c r="S82" s="9">
-        <f t="shared" si="134"/>
+        <f t="shared" si="131"/>
         <v>102.90000000000012</v>
       </c>
       <c r="T82" s="9">
-        <f t="shared" si="134"/>
+        <f t="shared" si="131"/>
         <v>325.00000000000011</v>
       </c>
       <c r="U82" s="9">
-        <f t="shared" si="134"/>
+        <f t="shared" si="131"/>
         <v>332.40000000000009</v>
       </c>
       <c r="V82" s="9">
-        <f t="shared" si="134"/>
+        <f t="shared" si="131"/>
         <v>59.699999999999875</v>
       </c>
       <c r="W82" s="9">
-        <f t="shared" si="134"/>
+        <f t="shared" si="131"/>
         <v>81.900000000000119</v>
       </c>
       <c r="X82" s="9">
-        <f t="shared" si="134"/>
+        <f t="shared" si="131"/>
         <v>414.39999999999992</v>
       </c>
       <c r="Y82" s="9">
-        <f t="shared" ref="Y82" si="135">Y78-Y81</f>
-        <v>129.13647199999997</v>
+        <f t="shared" ref="Y82" si="132">Y78-Y81</f>
+        <v>183.2</v>
       </c>
       <c r="Z82" s="9">
-        <f t="shared" ref="Z82" si="136">Z78-Z81</f>
-        <v>177.25722200000001</v>
+        <f t="shared" ref="Z82" si="133">Z78-Z81</f>
+        <v>38.692936000000145</v>
       </c>
       <c r="AA82" s="9">
-        <f t="shared" ref="AA82" si="137">AA78-AA81</f>
-        <v>207.18922399999997</v>
+        <f t="shared" ref="AA82" si="134">AA78-AA81</f>
+        <v>90.417889000000059</v>
       </c>
       <c r="AB82" s="9">
-        <f t="shared" ref="AB82" si="138">AB78-AB81</f>
-        <v>246.18960899999996</v>
+        <f t="shared" ref="AB82" si="135">AB78-AB81</f>
+        <v>136.26188400000001</v>
       </c>
       <c r="AI82" s="9">
-        <f t="shared" ref="AI82" si="139">AI78-AI81</f>
+        <f t="shared" ref="AI82" si="136">AI78-AI81</f>
         <v>780.80000000000052</v>
       </c>
       <c r="AJ82" s="9">
-        <f t="shared" ref="AJ82" si="140">AJ78-AJ81</f>
+        <f t="shared" ref="AJ82" si="137">AJ78-AJ81</f>
         <v>888.40000000000043</v>
       </c>
       <c r="AK82" s="9">
-        <f t="shared" ref="AK82" si="141">AK78-AK81</f>
-        <v>716.25572700000021</v>
+        <f t="shared" ref="AK82" si="138">AK78-AK81</f>
+        <v>409.48630900000035</v>
       </c>
       <c r="AL82" s="9">
-        <f t="shared" ref="AL82" si="142">AL78-AL81</f>
-        <v>1076.2149592600013</v>
+        <f t="shared" ref="AL82" si="139">AL78-AL81</f>
+        <v>924.4314604800004</v>
       </c>
       <c r="AM82" s="9">
-        <f t="shared" ref="AM82" si="143">AM78-AM81</f>
-        <v>1154.9167903320008</v>
+        <f t="shared" ref="AM82" si="140">AM78-AM81</f>
+        <v>1410.8735296000004</v>
       </c>
       <c r="AN82" s="9">
-        <f t="shared" ref="AN82" si="144">AN78-AN81</f>
-        <v>1313.7567523086391</v>
+        <f t="shared" ref="AN82" si="141">AN78-AN81</f>
+        <v>1769.2518932638386</v>
       </c>
       <c r="AO82" s="9">
-        <f t="shared" ref="AO82" si="145">AO78-AO81</f>
-        <v>1505.0591582392892</v>
+        <f t="shared" ref="AO82" si="142">AO78-AO81</f>
+        <v>2102.8108950806663</v>
       </c>
       <c r="AP82" s="9">
-        <f t="shared" ref="AP82" si="146">AP78-AP81</f>
-        <v>1618.1866716300892</v>
+        <f t="shared" ref="AP82" si="143">AP78-AP81</f>
+        <v>2304.7586527487006</v>
       </c>
       <c r="AQ82" s="9">
-        <f t="shared" ref="AQ82" si="147">AQ78-AQ81</f>
-        <v>1730.4367699051229</v>
+        <f t="shared" ref="AQ82" si="144">AQ78-AQ81</f>
+        <v>2474.7580486704455</v>
       </c>
       <c r="AR82" s="9">
-        <f t="shared" ref="AR82" si="148">AR78-AR81</f>
-        <v>1784.7784918648219</v>
+        <f t="shared" ref="AR82" si="145">AR78-AR81</f>
+        <v>2559.5261544090572</v>
       </c>
       <c r="AS82" s="9">
-        <f t="shared" ref="AS82" si="149">AS78-AS81</f>
-        <v>1828.3229767561259</v>
+        <f t="shared" ref="AS82" si="146">AS78-AS81</f>
+        <v>2625.0577067987138</v>
       </c>
       <c r="AT82" s="9">
-        <f t="shared" ref="AT82" si="150">AT78-AT81</f>
-        <v>1901.5601835331322</v>
+        <f t="shared" ref="AT82" si="147">AT78-AT81</f>
+        <v>2709.2756454965311</v>
       </c>
       <c r="AU82" s="9">
-        <f t="shared" ref="AU82" si="151">AU78-AU81</f>
-        <v>2000.8300831495753</v>
+        <f t="shared" ref="AU82" si="148">AU78-AU81</f>
+        <v>2811.8123399266906</v>
       </c>
       <c r="AV82" s="1">
         <f>AU82*(1+$AX$22)</f>
-        <v>1980.8217823180796</v>
+        <v>2783.6942165274236</v>
       </c>
       <c r="AW82" s="1">
-        <f t="shared" ref="AW82:DH82" si="152">AV82*(1+$AX$22)</f>
-        <v>1961.0135644948989</v>
+        <f t="shared" ref="AW82:DH82" si="149">AV82*(1+$AX$22)</f>
+        <v>2755.8572743621494</v>
       </c>
       <c r="AX82" s="1">
-        <f t="shared" si="152"/>
-        <v>1941.4034288499499</v>
+        <f t="shared" si="149"/>
+        <v>2728.298701618528</v>
       </c>
       <c r="AY82" s="1">
-        <f t="shared" si="152"/>
-        <v>1921.9893945614504</v>
+        <f t="shared" si="149"/>
+        <v>2701.0157146023425</v>
       </c>
       <c r="AZ82" s="1">
-        <f t="shared" si="152"/>
-        <v>1902.7695006158358</v>
+        <f t="shared" si="149"/>
+        <v>2674.0055574563189</v>
       </c>
       <c r="BA82" s="1">
-        <f t="shared" si="152"/>
-        <v>1883.7418056096774</v>
+        <f t="shared" si="149"/>
+        <v>2647.2655018817559</v>
       </c>
       <c r="BB82" s="1">
-        <f t="shared" si="152"/>
-        <v>1864.9043875535806</v>
+        <f t="shared" si="149"/>
+        <v>2620.7928468629384</v>
       </c>
       <c r="BC82" s="1">
-        <f t="shared" si="152"/>
-        <v>1846.2553436780447</v>
+        <f t="shared" si="149"/>
+        <v>2594.5849183943092</v>
       </c>
       <c r="BD82" s="1">
-        <f t="shared" si="152"/>
-        <v>1827.7927902412644</v>
+        <f t="shared" si="149"/>
+        <v>2568.639069210366</v>
       </c>
       <c r="BE82" s="1">
-        <f t="shared" si="152"/>
-        <v>1809.5148623388518</v>
+        <f t="shared" si="149"/>
+        <v>2542.9526785182625</v>
       </c>
       <c r="BF82" s="1">
-        <f t="shared" si="152"/>
-        <v>1791.4197137154633</v>
+        <f t="shared" si="149"/>
+        <v>2517.5231517330799</v>
       </c>
       <c r="BG82" s="1">
-        <f t="shared" si="152"/>
-        <v>1773.5055165783087</v>
+        <f t="shared" si="149"/>
+        <v>2492.3479202157491</v>
       </c>
       <c r="BH82" s="1">
-        <f t="shared" si="152"/>
-        <v>1755.7704614125257</v>
+        <f t="shared" si="149"/>
+        <v>2467.4244410135916</v>
       </c>
       <c r="BI82" s="1">
-        <f t="shared" si="152"/>
-        <v>1738.2127567984005</v>
+        <f t="shared" si="149"/>
+        <v>2442.7501966034556</v>
       </c>
       <c r="BJ82" s="1">
-        <f t="shared" si="152"/>
-        <v>1720.8306292304164</v>
+        <f t="shared" si="149"/>
+        <v>2418.3226946374211</v>
       </c>
       <c r="BK82" s="1">
-        <f t="shared" si="152"/>
-        <v>1703.6223229381123</v>
+        <f t="shared" si="149"/>
+        <v>2394.1394676910468</v>
       </c>
       <c r="BL82" s="1">
-        <f t="shared" si="152"/>
-        <v>1686.5860997087311</v>
+        <f t="shared" si="149"/>
+        <v>2370.1980730141363</v>
       </c>
       <c r="BM82" s="1">
-        <f t="shared" si="152"/>
-        <v>1669.7202387116438</v>
+        <f t="shared" si="149"/>
+        <v>2346.496092283995</v>
       </c>
       <c r="BN82" s="1">
-        <f t="shared" si="152"/>
-        <v>1653.0230363245273</v>
+        <f t="shared" si="149"/>
+        <v>2323.0311313611551</v>
       </c>
       <c r="BO82" s="1">
-        <f t="shared" si="152"/>
-        <v>1636.4928059612821</v>
+        <f t="shared" si="149"/>
+        <v>2299.8008200475433</v>
       </c>
       <c r="BP82" s="1">
-        <f t="shared" si="152"/>
-        <v>1620.1278779016693</v>
+        <f t="shared" si="149"/>
+        <v>2276.8028118470679</v>
       </c>
       <c r="BQ82" s="1">
-        <f t="shared" si="152"/>
-        <v>1603.9265991226525</v>
+        <f t="shared" si="149"/>
+        <v>2254.0347837285972</v>
       </c>
       <c r="BR82" s="1">
-        <f t="shared" si="152"/>
-        <v>1587.887333131426</v>
+        <f t="shared" si="149"/>
+        <v>2231.4944358913112</v>
       </c>
       <c r="BS82" s="1">
-        <f t="shared" si="152"/>
-        <v>1572.0084598001117</v>
+        <f t="shared" si="149"/>
+        <v>2209.1794915323981</v>
       </c>
       <c r="BT82" s="1">
-        <f t="shared" si="152"/>
-        <v>1556.2883752021105</v>
+        <f t="shared" si="149"/>
+        <v>2187.087696617074</v>
       </c>
       <c r="BU82" s="1">
-        <f t="shared" si="152"/>
-        <v>1540.7254914500893</v>
+        <f t="shared" si="149"/>
+        <v>2165.2168196509033</v>
       </c>
       <c r="BV82" s="1">
-        <f t="shared" si="152"/>
-        <v>1525.3182365355883</v>
+        <f t="shared" si="149"/>
+        <v>2143.5646514543942</v>
       </c>
       <c r="BW82" s="1">
-        <f t="shared" si="152"/>
-        <v>1510.0650541702323</v>
+        <f t="shared" si="149"/>
+        <v>2122.1290049398503</v>
       </c>
       <c r="BX82" s="1">
-        <f t="shared" si="152"/>
-        <v>1494.9644036285299</v>
+        <f t="shared" si="149"/>
+        <v>2100.9077148904516</v>
       </c>
       <c r="BY82" s="1">
-        <f t="shared" si="152"/>
-        <v>1480.0147595922447</v>
+        <f t="shared" si="149"/>
+        <v>2079.8986377415472</v>
       </c>
       <c r="BZ82" s="1">
-        <f t="shared" si="152"/>
-        <v>1465.2146119963222</v>
+        <f t="shared" si="149"/>
+        <v>2059.0996513641317</v>
       </c>
       <c r="CA82" s="1">
-        <f t="shared" si="152"/>
-        <v>1450.5624658763591</v>
+        <f t="shared" si="149"/>
+        <v>2038.5086548504903</v>
       </c>
       <c r="CB82" s="1">
-        <f t="shared" si="152"/>
-        <v>1436.0568412175955</v>
+        <f t="shared" si="149"/>
+        <v>2018.1235683019854</v>
       </c>
       <c r="CC82" s="1">
-        <f t="shared" si="152"/>
-        <v>1421.6962728054195</v>
+        <f t="shared" si="149"/>
+        <v>1997.9423326189656</v>
       </c>
       <c r="CD82" s="1">
-        <f t="shared" si="152"/>
-        <v>1407.4793100773654</v>
+        <f t="shared" si="149"/>
+        <v>1977.962909292776</v>
       </c>
       <c r="CE82" s="1">
-        <f t="shared" si="152"/>
-        <v>1393.4045169765918</v>
+        <f t="shared" si="149"/>
+        <v>1958.1832801998482</v>
       </c>
       <c r="CF82" s="1">
-        <f t="shared" si="152"/>
-        <v>1379.4704718068258</v>
+        <f t="shared" si="149"/>
+        <v>1938.6014473978498</v>
       </c>
       <c r="CG82" s="1">
-        <f t="shared" si="152"/>
-        <v>1365.6757670887575</v>
+        <f t="shared" si="149"/>
+        <v>1919.2154329238713</v>
       </c>
       <c r="CH82" s="1">
-        <f t="shared" si="152"/>
-        <v>1352.0190094178699</v>
+        <f t="shared" si="149"/>
+        <v>1900.0232785946325</v>
       </c>
       <c r="CI82" s="1">
-        <f t="shared" si="152"/>
-        <v>1338.4988193236911</v>
+        <f t="shared" si="149"/>
+        <v>1881.0230458086862</v>
       </c>
       <c r="CJ82" s="1">
-        <f t="shared" si="152"/>
-        <v>1325.1138311304542</v>
+        <f t="shared" si="149"/>
+        <v>1862.2128153505994</v>
       </c>
       <c r="CK82" s="1">
-        <f t="shared" si="152"/>
-        <v>1311.8626928191495</v>
+        <f t="shared" si="149"/>
+        <v>1843.5906871970933</v>
       </c>
       <c r="CL82" s="1">
-        <f t="shared" si="152"/>
-        <v>1298.7440658909579</v>
+        <f t="shared" si="149"/>
+        <v>1825.1547803251224</v>
       </c>
       <c r="CM82" s="1">
-        <f t="shared" si="152"/>
-        <v>1285.7566252320482</v>
+        <f t="shared" si="149"/>
+        <v>1806.9032325218711</v>
       </c>
       <c r="CN82" s="1">
-        <f t="shared" si="152"/>
-        <v>1272.8990589797277</v>
+        <f t="shared" si="149"/>
+        <v>1788.8342001966523</v>
       </c>
       <c r="CO82" s="1">
-        <f t="shared" si="152"/>
-        <v>1260.1700683899303</v>
+        <f t="shared" si="149"/>
+        <v>1770.9458581946858</v>
       </c>
       <c r="CP82" s="1">
-        <f t="shared" si="152"/>
-        <v>1247.568367706031</v>
+        <f t="shared" si="149"/>
+        <v>1753.236399612739</v>
       </c>
       <c r="CQ82" s="1">
-        <f t="shared" si="152"/>
-        <v>1235.0926840289708</v>
+        <f t="shared" si="149"/>
+        <v>1735.7040356166115</v>
       </c>
       <c r="CR82" s="1">
-        <f t="shared" si="152"/>
-        <v>1222.741757188681</v>
+        <f t="shared" si="149"/>
+        <v>1718.3469952604453</v>
       </c>
       <c r="CS82" s="1">
-        <f t="shared" si="152"/>
-        <v>1210.5143396167941</v>
+        <f t="shared" si="149"/>
+        <v>1701.1635253078409</v>
       </c>
       <c r="CT82" s="1">
-        <f t="shared" si="152"/>
-        <v>1198.4091962206262</v>
+        <f t="shared" si="149"/>
+        <v>1684.1518900547626</v>
       </c>
       <c r="CU82" s="1">
-        <f t="shared" si="152"/>
-        <v>1186.4251042584199</v>
+        <f t="shared" si="149"/>
+        <v>1667.3103711542149</v>
       </c>
       <c r="CV82" s="1">
-        <f t="shared" si="152"/>
-        <v>1174.5608532158358</v>
+        <f t="shared" si="149"/>
+        <v>1650.6372674426727</v>
       </c>
       <c r="CW82" s="1">
-        <f t="shared" si="152"/>
-        <v>1162.8152446836775</v>
+        <f t="shared" si="149"/>
+        <v>1634.130894768246</v>
       </c>
       <c r="CX82" s="1">
-        <f t="shared" si="152"/>
-        <v>1151.1870922368407</v>
+        <f t="shared" si="149"/>
+        <v>1617.7895858205636</v>
       </c>
       <c r="CY82" s="1">
-        <f t="shared" si="152"/>
-        <v>1139.6752213144723</v>
+        <f t="shared" si="149"/>
+        <v>1601.611689962358</v>
       </c>
       <c r="CZ82" s="1">
-        <f t="shared" si="152"/>
-        <v>1128.2784691013276</v>
+        <f t="shared" si="149"/>
+        <v>1585.5955730627345</v>
       </c>
       <c r="DA82" s="1">
-        <f t="shared" si="152"/>
-        <v>1116.9956844103142</v>
+        <f t="shared" si="149"/>
+        <v>1569.7396173321072</v>
       </c>
       <c r="DB82" s="1">
-        <f t="shared" si="152"/>
-        <v>1105.8257275662111</v>
+        <f t="shared" si="149"/>
+        <v>1554.0422211587861</v>
       </c>
       <c r="DC82" s="1">
-        <f t="shared" si="152"/>
-        <v>1094.767470290549</v>
+        <f t="shared" si="149"/>
+        <v>1538.5017989471983</v>
       </c>
       <c r="DD82" s="1">
-        <f t="shared" si="152"/>
-        <v>1083.8197955876435</v>
+        <f t="shared" si="149"/>
+        <v>1523.1167809577262</v>
       </c>
       <c r="DE82" s="1">
-        <f t="shared" si="152"/>
-        <v>1072.981597631767</v>
+        <f t="shared" si="149"/>
+        <v>1507.8856131481489</v>
       </c>
       <c r="DF82" s="1">
-        <f t="shared" si="152"/>
-        <v>1062.2517816554493</v>
+        <f t="shared" si="149"/>
+        <v>1492.8067570166675</v>
       </c>
       <c r="DG82" s="1">
-        <f t="shared" si="152"/>
-        <v>1051.6292638388948</v>
+        <f t="shared" si="149"/>
+        <v>1477.8786894465009</v>
       </c>
       <c r="DH82" s="1">
-        <f t="shared" si="152"/>
-        <v>1041.1129712005059</v>
+        <f t="shared" si="149"/>
+        <v>1463.0999025520359</v>
       </c>
       <c r="DI82" s="1">
-        <f t="shared" ref="DI82:FC82" si="153">DH82*(1+$AX$22)</f>
-        <v>1030.7018414885008</v>
+        <f t="shared" ref="DI82:FC82" si="150">DH82*(1+$AX$22)</f>
+        <v>1448.4689035265155</v>
       </c>
       <c r="DJ82" s="1">
-        <f t="shared" si="153"/>
-        <v>1020.3948230736158</v>
+        <f t="shared" si="150"/>
+        <v>1433.9842144912504</v>
       </c>
       <c r="DK82" s="1">
-        <f t="shared" si="153"/>
-        <v>1010.1908748428797</v>
+        <f t="shared" si="150"/>
+        <v>1419.6443723463378</v>
       </c>
       <c r="DL82" s="1">
-        <f t="shared" si="153"/>
-        <v>1000.0889660944508</v>
+        <f t="shared" si="150"/>
+        <v>1405.4479286228745</v>
       </c>
       <c r="DM82" s="1">
-        <f t="shared" si="153"/>
-        <v>990.08807643350633</v>
+        <f t="shared" si="150"/>
+        <v>1391.3934493366457</v>
       </c>
       <c r="DN82" s="1">
-        <f t="shared" si="153"/>
-        <v>980.18719566917127</v>
+        <f t="shared" si="150"/>
+        <v>1377.4795148432793</v>
       </c>
       <c r="DO82" s="1">
-        <f t="shared" si="153"/>
-        <v>970.38532371247959</v>
+        <f t="shared" si="150"/>
+        <v>1363.7047196948465</v>
       </c>
       <c r="DP82" s="1">
-        <f t="shared" si="153"/>
-        <v>960.68147047535479</v>
+        <f t="shared" si="150"/>
+        <v>1350.067672497898</v>
       </c>
       <c r="DQ82" s="1">
-        <f t="shared" si="153"/>
-        <v>951.07465577060123</v>
+        <f t="shared" si="150"/>
+        <v>1336.566995772919</v>
       </c>
       <c r="DR82" s="1">
-        <f t="shared" si="153"/>
-        <v>941.56390921289517</v>
+        <f t="shared" si="150"/>
+        <v>1323.2013258151899</v>
       </c>
       <c r="DS82" s="1">
-        <f t="shared" si="153"/>
-        <v>932.14827012076626</v>
+        <f t="shared" si="150"/>
+        <v>1309.9693125570379</v>
       </c>
       <c r="DT82" s="1">
-        <f t="shared" si="153"/>
-        <v>922.82678741955863</v>
+        <f t="shared" si="150"/>
+        <v>1296.8696194314675</v>
       </c>
       <c r="DU82" s="1">
-        <f t="shared" si="153"/>
-        <v>913.59851954536305</v>
+        <f t="shared" si="150"/>
+        <v>1283.9009232371529</v>
       </c>
       <c r="DV82" s="1">
-        <f t="shared" si="153"/>
-        <v>904.46253434990945</v>
+        <f t="shared" si="150"/>
+        <v>1271.0619140047813</v>
       </c>
       <c r="DW82" s="1">
-        <f t="shared" si="153"/>
-        <v>895.41790900641035</v>
+        <f t="shared" si="150"/>
+        <v>1258.3512948647335</v>
       </c>
       <c r="DX82" s="1">
-        <f t="shared" si="153"/>
-        <v>886.46372991634621</v>
+        <f t="shared" si="150"/>
+        <v>1245.7677819160863</v>
       </c>
       <c r="DY82" s="1">
-        <f t="shared" si="153"/>
-        <v>877.59909261718269</v>
+        <f t="shared" si="150"/>
+        <v>1233.3101040969254</v>
       </c>
       <c r="DZ82" s="1">
-        <f t="shared" si="153"/>
-        <v>868.82310169101083</v>
+        <f t="shared" si="150"/>
+        <v>1220.9770030559562</v>
       </c>
       <c r="EA82" s="1">
-        <f t="shared" si="153"/>
-        <v>860.13487067410074</v>
+        <f t="shared" si="150"/>
+        <v>1208.7672330253965</v>
       </c>
       <c r="EB82" s="1">
-        <f t="shared" si="153"/>
-        <v>851.53352196735977</v>
+        <f t="shared" si="150"/>
+        <v>1196.6795606951425</v>
       </c>
       <c r="EC82" s="1">
-        <f t="shared" si="153"/>
-        <v>843.01818674768617</v>
+        <f t="shared" si="150"/>
+        <v>1184.7127650881912</v>
       </c>
       <c r="ED82" s="1">
-        <f t="shared" si="153"/>
-        <v>834.58800488020927</v>
+        <f t="shared" si="150"/>
+        <v>1172.8656374373093</v>
       </c>
       <c r="EE82" s="1">
-        <f t="shared" si="153"/>
-        <v>826.24212483140718</v>
+        <f t="shared" si="150"/>
+        <v>1161.1369810629362</v>
       </c>
       <c r="EF82" s="1">
-        <f t="shared" si="153"/>
-        <v>817.97970358309306</v>
+        <f t="shared" si="150"/>
+        <v>1149.5256112523068</v>
       </c>
       <c r="EG82" s="1">
-        <f t="shared" si="153"/>
-        <v>809.79990654726214</v>
+        <f t="shared" si="150"/>
+        <v>1138.0303551397838</v>
       </c>
       <c r="EH82" s="1">
-        <f t="shared" si="153"/>
-        <v>801.70190748178948</v>
+        <f t="shared" si="150"/>
+        <v>1126.6500515883858</v>
       </c>
       <c r="EI82" s="1">
-        <f t="shared" si="153"/>
-        <v>793.6848884069716</v>
+        <f t="shared" si="150"/>
+        <v>1115.3835510725021</v>
       </c>
       <c r="EJ82" s="1">
-        <f t="shared" si="153"/>
-        <v>785.74803952290188</v>
+        <f t="shared" si="150"/>
+        <v>1104.2297155617771</v>
       </c>
       <c r="EK82" s="1">
-        <f t="shared" si="153"/>
-        <v>777.89055912767287</v>
+        <f t="shared" si="150"/>
+        <v>1093.1874184061594</v>
       </c>
       <c r="EL82" s="1">
-        <f t="shared" si="153"/>
-        <v>770.11165353639615</v>
+        <f t="shared" si="150"/>
+        <v>1082.2555442220978</v>
       </c>
       <c r="EM82" s="1">
-        <f t="shared" si="153"/>
-        <v>762.41053700103214</v>
+        <f t="shared" si="150"/>
+        <v>1071.4329887798767</v>
       </c>
       <c r="EN82" s="1">
-        <f t="shared" si="153"/>
-        <v>754.78643163102186</v>
+        <f t="shared" si="150"/>
+        <v>1060.7186588920779</v>
       </c>
       <c r="EO82" s="1">
-        <f t="shared" si="153"/>
-        <v>747.23856731471164</v>
+        <f t="shared" si="150"/>
+        <v>1050.1114723031571</v>
       </c>
       <c r="EP82" s="1">
-        <f t="shared" si="153"/>
-        <v>739.76618164156457</v>
+        <f t="shared" si="150"/>
+        <v>1039.6103575801255</v>
       </c>
       <c r="EQ82" s="1">
-        <f t="shared" si="153"/>
-        <v>732.36851982514895</v>
+        <f t="shared" si="150"/>
+        <v>1029.2142540043242</v>
       </c>
       <c r="ER82" s="1">
-        <f t="shared" si="153"/>
-        <v>725.04483462689745</v>
+        <f t="shared" si="150"/>
+        <v>1018.9221114642809</v>
       </c>
       <c r="ES82" s="1">
-        <f t="shared" si="153"/>
-        <v>717.79438628062849</v>
+        <f t="shared" si="150"/>
+        <v>1008.7328903496381</v>
       </c>
       <c r="ET82" s="1">
-        <f t="shared" si="153"/>
-        <v>710.61644241782221</v>
+        <f t="shared" si="150"/>
+        <v>998.64556144614164</v>
       </c>
       <c r="EU82" s="1">
-        <f t="shared" si="153"/>
-        <v>703.51027799364397</v>
+        <f t="shared" si="150"/>
+        <v>988.65910583168022</v>
       </c>
       <c r="EV82" s="1">
-        <f t="shared" si="153"/>
-        <v>696.47517521370753</v>
+        <f t="shared" si="150"/>
+        <v>978.77251477336335</v>
       </c>
       <c r="EW82" s="1">
-        <f t="shared" si="153"/>
-        <v>689.51042346157044</v>
+        <f t="shared" si="150"/>
+        <v>968.98478962562967</v>
       </c>
       <c r="EX82" s="1">
-        <f t="shared" si="153"/>
-        <v>682.61531922695474</v>
+        <f t="shared" si="150"/>
+        <v>959.29494172937336</v>
       </c>
       <c r="EY82" s="1">
-        <f t="shared" si="153"/>
-        <v>675.78916603468519</v>
+        <f t="shared" si="150"/>
+        <v>949.7019923120796</v>
       </c>
       <c r="EZ82" s="1">
-        <f t="shared" si="153"/>
-        <v>669.0312743743383</v>
+        <f t="shared" si="150"/>
+        <v>940.20497238895882</v>
       </c>
       <c r="FA82" s="1">
-        <f t="shared" si="153"/>
-        <v>662.34096163059496</v>
+        <f t="shared" si="150"/>
+        <v>930.80292266506922</v>
       </c>
       <c r="FB82" s="1">
-        <f t="shared" si="153"/>
-        <v>655.71755201428903</v>
+        <f t="shared" si="150"/>
+        <v>921.49489343841856</v>
       </c>
       <c r="FC82" s="1">
-        <f t="shared" si="153"/>
-        <v>649.16037649414613</v>
+        <f t="shared" si="150"/>
+        <v>912.27994450403435</v>
       </c>
     </row>
     <row r="84" spans="2:159" x14ac:dyDescent="0.3">
       <c r="B84" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AJ84" s="10">
         <f>AJ62/AI62-1</f>
         <v>0.52</v>
       </c>
       <c r="AK84" s="10">
-        <f t="shared" ref="AK84:AU84" si="154">AK62/AJ62-1</f>
-        <v>0.27192982456140347</v>
+        <f t="shared" ref="AK84:AU84" si="151">AK62/AJ62-1</f>
+        <v>0.24890350877192979</v>
       </c>
       <c r="AL84" s="10">
-        <f t="shared" si="154"/>
+        <f t="shared" si="151"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AM84" s="10">
-        <f t="shared" si="154"/>
+        <f t="shared" si="151"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AN84" s="10">
-        <f t="shared" si="154"/>
+        <f t="shared" si="151"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AO84" s="10">
-        <f t="shared" si="154"/>
+        <f t="shared" si="151"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AP84" s="10">
-        <f t="shared" si="154"/>
+        <f t="shared" si="151"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AQ84" s="10">
-        <f t="shared" si="154"/>
+        <f t="shared" si="151"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AR84" s="10">
-        <f t="shared" si="154"/>
+        <f t="shared" si="151"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AS84" s="10">
-        <f t="shared" si="154"/>
+        <f t="shared" si="151"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AT84" s="10">
-        <f t="shared" si="154"/>
+        <f t="shared" si="151"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AU84" s="10">
-        <f t="shared" si="154"/>
+        <f t="shared" si="151"/>
         <v>3.0000000000000027E-2</v>
       </c>
     </row>
     <row r="85" spans="2:159" x14ac:dyDescent="0.3">
       <c r="B85" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AJ85" s="10">
         <f>AJ81/AI81-1</f>
         <v>9.2485549132947931E-2</v>
       </c>
       <c r="AK85" s="10">
-        <f t="shared" ref="AK85:AU85" si="155">AK81/AJ81-1</f>
-        <v>0.21693121693121697</v>
+        <f t="shared" ref="AK85:AU85" si="152">AK81/AJ81-1</f>
+        <v>0.50793650793650813</v>
       </c>
       <c r="AL85" s="10">
-        <f t="shared" si="155"/>
-        <v>0.1399999999999999</v>
+        <f t="shared" si="152"/>
+        <v>0.5</v>
       </c>
       <c r="AM85" s="10">
-        <f t="shared" si="155"/>
-        <v>9.000000000000008E-2</v>
+        <f t="shared" si="152"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AN85" s="10">
-        <f t="shared" si="155"/>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" si="152"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AO85" s="10">
-        <f t="shared" si="155"/>
-        <v>4.0000000000000036E-2</v>
+        <f t="shared" si="152"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AP85" s="10">
-        <f t="shared" si="155"/>
-        <v>3.0000000000000027E-2</v>
+        <f t="shared" si="152"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AQ85" s="10">
-        <f t="shared" si="155"/>
+        <f t="shared" si="152"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AR85" s="10">
-        <f t="shared" si="155"/>
+        <f t="shared" si="152"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AS85" s="10">
-        <f t="shared" si="155"/>
+        <f t="shared" si="152"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AT85" s="10">
-        <f t="shared" si="155"/>
+        <f t="shared" si="152"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AU85" s="10">
-        <f t="shared" si="155"/>
+        <f t="shared" si="152"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AW85" t="s">
@@ -8641,7 +8636,7 @@
       </c>
       <c r="AX85" s="6">
         <f>NPV(AX23,AJ82:FC82)</f>
-        <v>18950.981149940828</v>
+        <v>25212.493568578317</v>
       </c>
     </row>
     <row r="86" spans="2:159" x14ac:dyDescent="0.3">
@@ -8650,7 +8645,7 @@
       </c>
       <c r="AX86" s="6">
         <f>Main!D8</f>
-        <v>3024.7000000000007</v>
+        <v>2593.2000000000003</v>
       </c>
     </row>
     <row r="87" spans="2:159" x14ac:dyDescent="0.3">
@@ -8659,7 +8654,7 @@
       </c>
       <c r="AX87" s="6">
         <f>AX85+AX86</f>
-        <v>21975.681149940829</v>
+        <v>27805.693568578317</v>
       </c>
     </row>
     <row r="88" spans="2:159" x14ac:dyDescent="0.3">
@@ -8668,7 +8663,7 @@
       </c>
       <c r="AX88" s="5">
         <f>AX87/AU17</f>
-        <v>66.311651025771965</v>
+        <v>83.575874867984126</v>
       </c>
     </row>
     <row r="89" spans="2:159" x14ac:dyDescent="0.3">
@@ -8677,7 +8672,7 @@
       </c>
       <c r="AX89" s="5">
         <f>Main!D3</f>
-        <v>138.38999999999999</v>
+        <v>205.72</v>
       </c>
     </row>
     <row r="90" spans="2:159" x14ac:dyDescent="0.3">
@@ -8686,7 +8681,7 @@
       </c>
       <c r="AX90" s="11">
         <f>AX88/AX89-1</f>
-        <v>-0.5208349517611679</v>
+        <v>-0.59373967106754755</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/SNOW.xlsx
+++ b/Financial Analysis/SNOW.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6DEF5EF-3C8B-4753-A296-8A0ADAB558F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{950B4762-AF5B-4957-9AD5-3A9246616DC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{BC02690B-70EA-46CB-8D56-DD95DADEB9E1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{BC02690B-70EA-46CB-8D56-DD95DADEB9E1}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="105">
   <si>
     <t>SNOW</t>
   </si>
@@ -337,7 +337,10 @@
     <t>CapEx y/y</t>
   </si>
   <si>
-    <t>Q126 8K</t>
+    <t>Q226 8K</t>
+  </si>
+  <si>
+    <t>Impairment</t>
   </si>
 </sst>
 </file>
@@ -448,15 +451,15 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>24</xdr:col>
+      <xdr:col>26</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
+      <xdr:col>26</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
-      <xdr:row>86</xdr:row>
+      <xdr:row>87</xdr:row>
       <xdr:rowOff>91440</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -472,8 +475,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="17876520" y="0"/>
-          <a:ext cx="0" cy="15453360"/>
+          <a:off x="19324320" y="0"/>
+          <a:ext cx="0" cy="15819120"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -506,7 +509,7 @@
     <xdr:to>
       <xdr:col>36</xdr:col>
       <xdr:colOff>15240</xdr:colOff>
-      <xdr:row>92</xdr:row>
+      <xdr:row>93</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -872,17 +875,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="5">
-        <v>205.72</v>
+        <v>225.31</v>
       </c>
       <c r="E3" s="4">
-        <v>45805</v>
+        <v>45912</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45805</v>
+        <v>45912</v>
       </c>
       <c r="G3" s="4">
-        <v>45889</v>
+        <v>45987</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -890,8 +893,7 @@
         <v>2</v>
       </c>
       <c r="D4" s="6">
-        <f>332.7</f>
-        <v>332.7</v>
+        <v>335.2</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>103</v>
@@ -903,7 +905,7 @@
       </c>
       <c r="D5" s="6">
         <f>D3*D4</f>
-        <v>68443.043999999994</v>
+        <v>75523.911999999997</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -911,11 +913,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="6">
-        <f>2243.1+1667.6+956.1</f>
-        <v>4866.8</v>
+        <f>1880.7+1706+1012.9</f>
+        <v>4599.5999999999995</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -923,11 +925,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="6">
-        <f>2273.6</f>
-        <v>2273.6</v>
+        <f>2275.7</f>
+        <v>2275.6999999999998</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -936,7 +938,7 @@
       </c>
       <c r="D8" s="6">
         <f>D6-D7</f>
-        <v>2593.2000000000003</v>
+        <v>2323.8999999999996</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -945,7 +947,7 @@
       </c>
       <c r="D9" s="6">
         <f>D5-D8</f>
-        <v>65849.843999999997</v>
+        <v>73200.012000000002</v>
       </c>
     </row>
   </sheetData>
@@ -956,7 +958,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C98FB002-5468-451A-8BA5-9AE8409D3CEE}">
-  <dimension ref="B1:FD90"/>
+  <dimension ref="B1:FD91"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="19.21875" bestFit="1" customWidth="1"/>
@@ -1309,15 +1311,14 @@
         <v>1042.0999999999999</v>
       </c>
       <c r="Z3" s="9">
-        <f>V3*1.2</f>
-        <v>1042.56</v>
+        <v>1145</v>
       </c>
       <c r="AA3" s="9">
-        <f t="shared" ref="AA3:AB3" si="0">W3*1.2</f>
-        <v>1130.52</v>
+        <f>W3*1.24</f>
+        <v>1168.204</v>
       </c>
       <c r="AB3" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="AB3" si="0">X3*1.2</f>
         <v>1184.1599999999999</v>
       </c>
       <c r="AD3" s="9">
@@ -1347,47 +1348,47 @@
       </c>
       <c r="AK3" s="9">
         <f>SUM(Y3:AB3)</f>
-        <v>4399.34</v>
+        <v>4539.4639999999999</v>
       </c>
       <c r="AL3" s="9">
         <f>AK3*1.24</f>
-        <v>5455.1815999999999</v>
+        <v>5628.9353599999995</v>
       </c>
       <c r="AM3" s="9">
         <f>AL3*1.2</f>
-        <v>6546.21792</v>
+        <v>6754.7224319999996</v>
       </c>
       <c r="AN3" s="9">
         <f>AM3*1.14</f>
-        <v>7462.6884287999992</v>
+        <v>7700.3835724799992</v>
       </c>
       <c r="AO3" s="9">
         <f>AN3*1.11</f>
-        <v>8283.5841559679993</v>
+        <v>8547.4257654527992</v>
       </c>
       <c r="AP3" s="9">
         <f>AO3*1.09</f>
-        <v>9029.10673000512</v>
+        <v>9316.6940843435514</v>
       </c>
       <c r="AQ3" s="9">
         <f>AP3*1.07</f>
-        <v>9661.1442011054787</v>
+        <v>9968.8626702476013</v>
       </c>
       <c r="AR3" s="9">
         <f>AQ3*1.05</f>
-        <v>10144.201411160753</v>
+        <v>10467.305803759982</v>
       </c>
       <c r="AS3" s="9">
         <f t="shared" ref="AS3:AU3" si="1">AR3*1.05</f>
-        <v>10651.411481718791</v>
+        <v>10990.671093947982</v>
       </c>
       <c r="AT3" s="9">
         <f t="shared" si="1"/>
-        <v>11183.98205580473</v>
+        <v>11540.204648645382</v>
       </c>
       <c r="AU3" s="9">
         <f t="shared" si="1"/>
-        <v>11743.181158594967</v>
+        <v>12117.214881077651</v>
       </c>
       <c r="AV3" s="9"/>
     </row>
@@ -1461,12 +1462,11 @@
         <v>348.8</v>
       </c>
       <c r="Z4" s="6">
-        <f t="shared" ref="Z4:AB4" si="2">Z3-Z5</f>
-        <v>344.0447999999999</v>
+        <v>371.8</v>
       </c>
       <c r="AA4" s="6">
-        <f t="shared" si="2"/>
-        <v>373.07159999999999</v>
+        <f t="shared" ref="AA4:AB4" si="2">AA3-AA5</f>
+        <v>385.50731999999994</v>
       </c>
       <c r="AB4" s="6">
         <f t="shared" si="2"/>
@@ -1499,47 +1499,47 @@
       </c>
       <c r="AK4" s="6">
         <f>SUM(Y4:AB4)</f>
-        <v>1456.6891999999998</v>
+        <v>1496.88012</v>
       </c>
       <c r="AL4" s="6">
         <f t="shared" ref="AL4:AQ4" si="3">AL3-AL5</f>
-        <v>1800.2099279999998</v>
+        <v>1801.2593151999995</v>
       </c>
       <c r="AM4" s="6">
         <f t="shared" si="3"/>
-        <v>2094.7897343999994</v>
+        <v>2093.9639539200007</v>
       </c>
       <c r="AN4" s="6">
         <f t="shared" si="3"/>
-        <v>2313.4334129280005</v>
+        <v>2310.1150717440005</v>
       </c>
       <c r="AO4" s="6">
         <f t="shared" si="3"/>
-        <v>2485.0752467904003</v>
+        <v>2564.2277296358398</v>
       </c>
       <c r="AP4" s="6">
         <f t="shared" si="3"/>
-        <v>2708.7320190015362</v>
+        <v>2795.008225303066</v>
       </c>
       <c r="AQ4" s="6">
         <f t="shared" si="3"/>
-        <v>2898.3432603316442</v>
+        <v>2990.6588010742807</v>
       </c>
       <c r="AR4" s="6">
         <f t="shared" ref="AR4:AU4" si="4">AR3-AR5</f>
-        <v>3043.2604233482261</v>
+        <v>3140.1917411279956</v>
       </c>
       <c r="AS4" s="6">
         <f t="shared" si="4"/>
-        <v>3195.423444515638</v>
+        <v>3297.2013281843947</v>
       </c>
       <c r="AT4" s="6">
         <f t="shared" si="4"/>
-        <v>3355.1946167414198</v>
+        <v>3462.0613945936148</v>
       </c>
       <c r="AU4" s="6">
         <f t="shared" si="4"/>
-        <v>3522.9543475784903</v>
+        <v>3635.1644643232958</v>
       </c>
     </row>
     <row r="5" spans="2:160" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1557,7 +1557,7 @@
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
       <c r="G5" s="9">
-        <f t="shared" ref="G5:Y5" si="5">G3-G4</f>
+        <f t="shared" ref="G5:Z5" si="5">G3-G4</f>
         <v>92.899999999999991</v>
       </c>
       <c r="H5" s="9">
@@ -1633,12 +1633,12 @@
         <v>693.3</v>
       </c>
       <c r="Z5" s="9">
-        <f t="shared" ref="Z5:AB5" si="6">Z3*0.67</f>
-        <v>698.51520000000005</v>
+        <f t="shared" si="5"/>
+        <v>773.2</v>
       </c>
       <c r="AA5" s="9">
-        <f t="shared" si="6"/>
-        <v>757.44839999999999</v>
+        <f t="shared" ref="AA5:AB5" si="6">AA3*0.67</f>
+        <v>782.69668000000001</v>
       </c>
       <c r="AB5" s="9">
         <f t="shared" si="6"/>
@@ -1657,7 +1657,7 @@
         <v>349.4</v>
       </c>
       <c r="AG5" s="9">
-        <f t="shared" ref="AG5:AJ5" si="7">AG3-AG4</f>
+        <f t="shared" ref="AG5:AK5" si="7">AG3-AG4</f>
         <v>760.9</v>
       </c>
       <c r="AH5" s="9">
@@ -1673,48 +1673,48 @@
         <v>2411.6999999999998</v>
       </c>
       <c r="AK5" s="9">
-        <f>AK3*0.66</f>
-        <v>2903.5644000000002</v>
+        <f t="shared" si="7"/>
+        <v>3042.5838800000001</v>
       </c>
       <c r="AL5" s="9">
-        <f>AL3*0.67</f>
-        <v>3654.9716720000001</v>
+        <f>AL3*0.68</f>
+        <v>3827.6760448</v>
       </c>
       <c r="AM5" s="9">
-        <f>AM3*0.68</f>
-        <v>4451.4281856000007</v>
+        <f>AM3*0.69</f>
+        <v>4660.7584780799989</v>
       </c>
       <c r="AN5" s="9">
-        <f>AN3*0.69</f>
-        <v>5149.2550158719987</v>
+        <f>AN3*0.7</f>
+        <v>5390.2685007359987</v>
       </c>
       <c r="AO5" s="9">
         <f>AO3*0.7</f>
-        <v>5798.508909177599</v>
+        <v>5983.1980358169594</v>
       </c>
       <c r="AP5" s="9">
         <f t="shared" ref="AP5:AU5" si="8">AP3*0.7</f>
-        <v>6320.3747110035838</v>
+        <v>6521.6858590404854</v>
       </c>
       <c r="AQ5" s="9">
         <f t="shared" si="8"/>
-        <v>6762.8009407738346</v>
+        <v>6978.2038691733205</v>
       </c>
       <c r="AR5" s="9">
         <f t="shared" si="8"/>
-        <v>7100.9409878125271</v>
+        <v>7327.1140626319866</v>
       </c>
       <c r="AS5" s="9">
         <f t="shared" si="8"/>
-        <v>7455.988037203153</v>
+        <v>7693.469765763587</v>
       </c>
       <c r="AT5" s="9">
         <f t="shared" si="8"/>
-        <v>7828.7874390633106</v>
+        <v>8078.1432540517671</v>
       </c>
       <c r="AU5" s="9">
         <f t="shared" si="8"/>
-        <v>8220.2268110164769</v>
+        <v>8482.050416754355</v>
       </c>
     </row>
     <row r="6" spans="2:160" x14ac:dyDescent="0.3">
@@ -1787,16 +1787,15 @@
         <v>458.6</v>
       </c>
       <c r="Z6" s="6">
-        <f>Z3*0.44</f>
-        <v>458.72639999999996</v>
+        <v>502</v>
       </c>
       <c r="AA6" s="6">
-        <f>AA3*0.41</f>
-        <v>463.51319999999998</v>
+        <f>AA3*0.44</f>
+        <v>514.00976000000003</v>
       </c>
       <c r="AB6" s="6">
-        <f>AB3*0.4</f>
-        <v>473.66399999999999</v>
+        <f>AB3*0.44</f>
+        <v>521.03039999999999</v>
       </c>
       <c r="AD6" s="6">
         <v>125.6</v>
@@ -1825,47 +1824,47 @@
       </c>
       <c r="AK6" s="6">
         <f>SUM(Y6:AB6)</f>
-        <v>1854.5035999999998</v>
+        <v>1995.6401599999999</v>
       </c>
       <c r="AL6" s="6">
-        <f>AL3*0.35</f>
-        <v>1909.3135599999998</v>
+        <f>AL3*0.37</f>
+        <v>2082.7060831999997</v>
       </c>
       <c r="AM6" s="6">
-        <f>AM3*0.31</f>
-        <v>2029.3275552</v>
+        <f>AM3*0.32</f>
+        <v>2161.5111782399999</v>
       </c>
       <c r="AN6" s="6">
-        <f>AN3*0.28</f>
-        <v>2089.5527600639998</v>
+        <f>AN3*0.29</f>
+        <v>2233.1112360191996</v>
       </c>
       <c r="AO6" s="6">
-        <f>AO3*0.26</f>
-        <v>2153.7318805516798</v>
+        <f>AO3*0.27</f>
+        <v>2307.8049566722561</v>
       </c>
       <c r="AP6" s="6">
         <f>AP3*0.25</f>
-        <v>2257.27668250128</v>
+        <v>2329.1735210858878</v>
       </c>
       <c r="AQ6" s="6">
         <f>AQ3*0.24</f>
-        <v>2318.6746082653149</v>
+        <v>2392.5270408594242</v>
       </c>
       <c r="AR6" s="6">
         <f>AR3*0.23</f>
-        <v>2333.1663245669733</v>
+        <v>2407.4803348647961</v>
       </c>
       <c r="AS6" s="6">
         <f t="shared" ref="AS6:AU6" si="9">AS3*0.23</f>
-        <v>2449.824640795322</v>
+        <v>2527.8543516080358</v>
       </c>
       <c r="AT6" s="6">
         <f t="shared" si="9"/>
-        <v>2572.3158728350882</v>
+        <v>2654.2470691884378</v>
       </c>
       <c r="AU6" s="6">
         <f t="shared" si="9"/>
-        <v>2700.9316664768426</v>
+        <v>2786.9594226478598</v>
       </c>
     </row>
     <row r="7" spans="2:160" x14ac:dyDescent="0.3">
@@ -1938,8 +1937,7 @@
         <v>472.4</v>
       </c>
       <c r="Z7" s="6">
-        <f>V7*1.15</f>
-        <v>503.35499999999996</v>
+        <v>492</v>
       </c>
       <c r="AA7" s="6">
         <f>W7*1.17</f>
@@ -1976,47 +1974,47 @@
       </c>
       <c r="AK7" s="6">
         <f>SUM(Y7:AB7)</f>
-        <v>2059.7379999999998</v>
+        <v>2048.3829999999998</v>
       </c>
       <c r="AL7" s="6">
         <f>AK7*1.07</f>
-        <v>2203.91966</v>
+        <v>2191.7698099999998</v>
       </c>
       <c r="AM7" s="6">
         <f>AL7*1.04</f>
-        <v>2292.0764463999999</v>
+        <v>2279.4406024</v>
       </c>
       <c r="AN7" s="6">
         <f>AM7*1.03</f>
-        <v>2360.8387397920001</v>
+        <v>2347.8238204720001</v>
       </c>
       <c r="AO7" s="6">
         <f>AN7*1.02</f>
-        <v>2408.0555145878402</v>
+        <v>2394.7802968814403</v>
       </c>
       <c r="AP7" s="6">
         <f t="shared" ref="AP7:AU7" si="10">AO7*1.02</f>
-        <v>2456.216624879597</v>
+        <v>2442.6759028190691</v>
       </c>
       <c r="AQ7" s="6">
         <f t="shared" si="10"/>
-        <v>2505.3409573771892</v>
+        <v>2491.5294208754503</v>
       </c>
       <c r="AR7" s="6">
         <f t="shared" si="10"/>
-        <v>2555.4477765247329</v>
+        <v>2541.3600092929596</v>
       </c>
       <c r="AS7" s="6">
         <f t="shared" si="10"/>
-        <v>2606.5567320552277</v>
+        <v>2592.1872094788187</v>
       </c>
       <c r="AT7" s="6">
         <f t="shared" si="10"/>
-        <v>2658.6878666963321</v>
+        <v>2644.0309536683949</v>
       </c>
       <c r="AU7" s="6">
         <f t="shared" si="10"/>
-        <v>2711.861624030259</v>
+        <v>2696.9115727417629</v>
       </c>
     </row>
     <row r="8" spans="2:160" x14ac:dyDescent="0.3">
@@ -2089,16 +2087,15 @@
         <v>209.6</v>
       </c>
       <c r="Z8" s="6">
-        <f>V8*2.17</f>
-        <v>212.226</v>
+        <v>119.5</v>
       </c>
       <c r="AA8" s="6">
-        <f>W8*2</f>
-        <v>212.6</v>
+        <f>W8*1.2</f>
+        <v>127.55999999999999</v>
       </c>
       <c r="AB8" s="6">
-        <f>X8*2</f>
-        <v>230.2</v>
+        <f>X8*1.2</f>
+        <v>138.11999999999998</v>
       </c>
       <c r="AD8" s="6">
         <v>36.1</v>
@@ -2127,47 +2124,47 @@
       </c>
       <c r="AK8" s="6">
         <f>SUM(Y8:AB8)</f>
-        <v>864.62599999999998</v>
+        <v>594.78</v>
       </c>
       <c r="AL8" s="6">
-        <f>AK8*1.1</f>
-        <v>951.08860000000004</v>
+        <f>AK8*1.05</f>
+        <v>624.51900000000001</v>
       </c>
       <c r="AM8" s="6">
         <f>AL8*1.05</f>
-        <v>998.64303000000007</v>
+        <v>655.74495000000002</v>
       </c>
       <c r="AN8" s="6">
         <f>AM8*1.04</f>
-        <v>1038.5887512000002</v>
+        <v>681.97474800000009</v>
       </c>
       <c r="AO8" s="6">
         <f>AN8*1.03</f>
-        <v>1069.7464137360002</v>
+        <v>702.43399044000012</v>
       </c>
       <c r="AP8" s="6">
         <f>AO8*1.02</f>
-        <v>1091.1413420107203</v>
+        <v>716.4826702488001</v>
       </c>
       <c r="AQ8" s="6">
         <f>AP8*1.02</f>
-        <v>1112.9641688509348</v>
+        <v>730.81232365377616</v>
       </c>
       <c r="AR8" s="6">
         <f t="shared" ref="AR8:AU8" si="11">AQ8*1.02</f>
-        <v>1135.2234522279534</v>
+        <v>745.4285701268517</v>
       </c>
       <c r="AS8" s="6">
         <f t="shared" si="11"/>
-        <v>1157.9279212725125</v>
+        <v>760.33714152938876</v>
       </c>
       <c r="AT8" s="6">
         <f t="shared" si="11"/>
-        <v>1181.0864796979629</v>
+        <v>775.54388435997657</v>
       </c>
       <c r="AU8" s="6">
         <f t="shared" si="11"/>
-        <v>1204.7082092919222</v>
+        <v>791.05476204717615</v>
       </c>
     </row>
     <row r="9" spans="2:160" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2262,15 +2259,15 @@
       </c>
       <c r="Z9" s="9">
         <f t="shared" si="12"/>
-        <v>-475.79219999999987</v>
+        <v>-340.29999999999995</v>
       </c>
       <c r="AA9" s="9">
         <f t="shared" si="12"/>
-        <v>-436.27279999999996</v>
+        <v>-376.48107999999996</v>
       </c>
       <c r="AB9" s="9">
         <f t="shared" si="12"/>
-        <v>-476.85180000000008</v>
+        <v>-432.1382000000001</v>
       </c>
       <c r="AD9" s="9">
         <f>AD5-AD6-AD7-AD8</f>
@@ -2302,47 +2299,47 @@
       </c>
       <c r="AK9" s="9">
         <f t="shared" ref="AK9" si="17">AK5-AK6-AK7-AK8</f>
-        <v>-1875.3031999999994</v>
+        <v>-1596.2192799999996</v>
       </c>
       <c r="AL9" s="9">
         <f t="shared" ref="AL9" si="18">AL5-AL6-AL7-AL8</f>
-        <v>-1409.3501479999998</v>
+        <v>-1071.3188483999995</v>
       </c>
       <c r="AM9" s="9">
         <f t="shared" ref="AM9" si="19">AM5-AM6-AM7-AM8</f>
-        <v>-868.61884599999928</v>
+        <v>-435.93825256000105</v>
       </c>
       <c r="AN9" s="9">
         <f t="shared" ref="AN9" si="20">AN5-AN6-AN7-AN8</f>
-        <v>-339.72523518400135</v>
+        <v>127.35869624479892</v>
       </c>
       <c r="AO9" s="9">
         <f t="shared" ref="AO9" si="21">AO5-AO6-AO7-AO8</f>
-        <v>166.97510030207877</v>
+        <v>578.17879182326283</v>
       </c>
       <c r="AP9" s="9">
         <f t="shared" ref="AP9" si="22">AP5-AP6-AP7-AP8</f>
-        <v>515.74006161198645</v>
+        <v>1033.3537648867284</v>
       </c>
       <c r="AQ9" s="9">
         <f t="shared" ref="AQ9:AU9" si="23">AQ5-AQ6-AQ7-AQ8</f>
-        <v>825.82120628039615</v>
+        <v>1363.3350837846697</v>
       </c>
       <c r="AR9" s="9">
         <f t="shared" si="23"/>
-        <v>1077.1034344928673</v>
+        <v>1632.8451483473787</v>
       </c>
       <c r="AS9" s="9">
         <f t="shared" si="23"/>
-        <v>1241.6787430800907</v>
+        <v>1813.0910631473434</v>
       </c>
       <c r="AT9" s="9">
         <f t="shared" si="23"/>
-        <v>1416.6972198339274</v>
+        <v>2004.3213468349584</v>
       </c>
       <c r="AU9" s="9">
         <f t="shared" si="23"/>
-        <v>1602.7253112174526</v>
+        <v>2207.1246593175556</v>
       </c>
     </row>
     <row r="10" spans="2:160" x14ac:dyDescent="0.3">
@@ -2415,11 +2412,10 @@
         <v>-53.2</v>
       </c>
       <c r="Z10" s="6">
-        <f t="shared" ref="Z10:AB10" si="24">V10*1.05</f>
-        <v>-51.765000000000001</v>
+        <v>-49.5</v>
       </c>
       <c r="AA10" s="6">
-        <f t="shared" si="24"/>
+        <f t="shared" ref="AA10:AB10" si="24">W10*1.05</f>
         <v>-51.135000000000005</v>
       </c>
       <c r="AB10" s="6">
@@ -2453,47 +2449,47 @@
       </c>
       <c r="AK10" s="6">
         <f>SUM(Y10:AB10)</f>
-        <v>-215.21500000000003</v>
+        <v>-212.95000000000002</v>
       </c>
       <c r="AL10" s="6">
         <f t="shared" ref="AL10" si="25">AK10*1.02</f>
-        <v>-219.51930000000004</v>
+        <v>-217.20900000000003</v>
       </c>
       <c r="AM10" s="6">
         <f t="shared" ref="AM10" si="26">AL10*1.02</f>
-        <v>-223.90968600000005</v>
+        <v>-221.55318000000003</v>
       </c>
       <c r="AN10" s="6">
         <f t="shared" ref="AN10" si="27">AM10*1.02</f>
-        <v>-228.38787972000006</v>
+        <v>-225.98424360000004</v>
       </c>
       <c r="AO10" s="6">
         <f t="shared" ref="AO10" si="28">AN10*1.02</f>
-        <v>-232.95563731440006</v>
+        <v>-230.50392847200004</v>
       </c>
       <c r="AP10" s="6">
         <f t="shared" ref="AP10" si="29">AO10*1.02</f>
-        <v>-237.61475006068807</v>
+        <v>-235.11400704144003</v>
       </c>
       <c r="AQ10" s="6">
         <f t="shared" ref="AQ10" si="30">AP10*1.02</f>
-        <v>-242.36704506190182</v>
+        <v>-239.81628718226884</v>
       </c>
       <c r="AR10" s="6">
         <f t="shared" ref="AR10" si="31">AQ10*1.02</f>
-        <v>-247.21438596313985</v>
+        <v>-244.61261292591422</v>
       </c>
       <c r="AS10" s="6">
         <f t="shared" ref="AS10" si="32">AR10*1.02</f>
-        <v>-252.15867368240265</v>
+        <v>-249.5048651844325</v>
       </c>
       <c r="AT10" s="6">
         <f t="shared" ref="AT10" si="33">AS10*1.02</f>
-        <v>-257.20184715605069</v>
+        <v>-254.49496248812116</v>
       </c>
       <c r="AU10" s="6">
         <f t="shared" ref="AU10" si="34">AT10*1.02</f>
-        <v>-262.34588409917171</v>
+        <v>-259.58486173788361</v>
       </c>
     </row>
     <row r="11" spans="2:160" x14ac:dyDescent="0.3">
@@ -2558,7 +2554,7 @@
         <v>2.1</v>
       </c>
       <c r="Z11" s="6">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA11" s="6">
         <v>0</v>
@@ -2581,7 +2577,7 @@
       </c>
       <c r="AK11" s="6">
         <f>SUM(Y11:AB11)</f>
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="AL11" s="6"/>
       <c r="AM11" s="6"/>
@@ -2664,7 +2660,7 @@
         <v>28.1</v>
       </c>
       <c r="Z12" s="6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA12" s="6">
         <v>0</v>
@@ -2699,7 +2695,7 @@
       </c>
       <c r="AK12" s="6">
         <f>SUM(Y12:AB12)</f>
-        <v>28.1</v>
+        <v>33.1</v>
       </c>
       <c r="AL12" s="6">
         <v>0</v>
@@ -2824,15 +2820,15 @@
       </c>
       <c r="Z13" s="9">
         <f t="shared" si="35"/>
-        <v>-424.02719999999988</v>
+        <v>-297.89999999999998</v>
       </c>
       <c r="AA13" s="9">
         <f t="shared" si="35"/>
-        <v>-385.13779999999997</v>
+        <v>-325.34607999999997</v>
       </c>
       <c r="AB13" s="9">
         <f t="shared" si="35"/>
-        <v>-417.73680000000007</v>
+        <v>-373.02320000000009</v>
       </c>
       <c r="AD13" s="9">
         <f t="shared" ref="AD13:AQ13" si="36">AD9-SUM(AD10:AD12)</f>
@@ -2864,47 +2860,47 @@
       </c>
       <c r="AK13" s="9">
         <f t="shared" si="36"/>
-        <v>-1690.2881999999993</v>
+        <v>-1420.5692799999995</v>
       </c>
       <c r="AL13" s="9">
         <f t="shared" si="36"/>
-        <v>-1189.8308479999996</v>
+        <v>-854.10984839999946</v>
       </c>
       <c r="AM13" s="9">
         <f t="shared" si="36"/>
-        <v>-644.7091599999992</v>
+        <v>-214.38507256000102</v>
       </c>
       <c r="AN13" s="9">
         <f t="shared" si="36"/>
-        <v>-111.33735546400129</v>
+        <v>353.34293984479893</v>
       </c>
       <c r="AO13" s="9">
         <f t="shared" si="36"/>
-        <v>399.93073761647884</v>
+        <v>808.68272029526292</v>
       </c>
       <c r="AP13" s="9">
         <f t="shared" si="36"/>
-        <v>753.35481167267449</v>
+        <v>1268.4677719281685</v>
       </c>
       <c r="AQ13" s="9">
         <f t="shared" si="36"/>
-        <v>1068.1882513422979</v>
+        <v>1603.1513709669384</v>
       </c>
       <c r="AR13" s="9">
         <f t="shared" ref="AR13" si="37">AR9-SUM(AR10:AR12)</f>
-        <v>1324.3178204560072</v>
+        <v>1877.4577612732928</v>
       </c>
       <c r="AS13" s="9">
         <f t="shared" ref="AS13" si="38">AS9-SUM(AS10:AS12)</f>
-        <v>1493.8374167624934</v>
+        <v>2062.5959283317761</v>
       </c>
       <c r="AT13" s="9">
         <f t="shared" ref="AT13" si="39">AT9-SUM(AT10:AT12)</f>
-        <v>1673.8990669899781</v>
+        <v>2258.8163093230796</v>
       </c>
       <c r="AU13" s="9">
         <f t="shared" ref="AU13" si="40">AU9-SUM(AU10:AU12)</f>
-        <v>1865.0711953166242</v>
+        <v>2466.7095210554394</v>
       </c>
     </row>
     <row r="14" spans="2:160" x14ac:dyDescent="0.3">
@@ -2977,7 +2973,7 @@
         <v>5.7</v>
       </c>
       <c r="Z14" s="6">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AA14" s="6">
         <v>0</v>
@@ -3012,46 +3008,46 @@
       </c>
       <c r="AK14" s="6">
         <f>SUM(Y14:AB14)</f>
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AL14" s="6">
         <v>0</v>
       </c>
       <c r="AM14" s="6">
         <f>AM13*0.05</f>
-        <v>-32.235457999999959</v>
+        <v>-10.719253628000052</v>
       </c>
       <c r="AN14" s="6">
         <f>AN13*0.05</f>
-        <v>-5.5668677732000651</v>
+        <v>17.667146992239946</v>
       </c>
       <c r="AO14" s="6">
         <f>AO13*0.1</f>
-        <v>39.993073761647885</v>
+        <v>80.868272029526295</v>
       </c>
       <c r="AP14" s="6">
         <f>AP13*0.1</f>
-        <v>75.335481167267446</v>
+        <v>126.84677719281686</v>
       </c>
       <c r="AQ14" s="6">
         <f>AQ13*0.11</f>
-        <v>117.50070764765277</v>
+        <v>176.34665080636321</v>
       </c>
       <c r="AR14" s="6">
         <f t="shared" ref="AR14:AU14" si="41">AR13*0.15</f>
-        <v>198.64767306840108</v>
+        <v>281.61866419099391</v>
       </c>
       <c r="AS14" s="6">
         <f t="shared" si="41"/>
-        <v>224.075612514374</v>
+        <v>309.3893892497664</v>
       </c>
       <c r="AT14" s="6">
         <f t="shared" si="41"/>
-        <v>251.08486004849669</v>
+        <v>338.82244639846192</v>
       </c>
       <c r="AU14" s="6">
         <f t="shared" si="41"/>
-        <v>279.7606792974936</v>
+        <v>370.00642815831588</v>
       </c>
     </row>
     <row r="15" spans="2:160" x14ac:dyDescent="0.3">
@@ -3116,16 +3112,15 @@
         <v>0.1</v>
       </c>
       <c r="Z15" s="6">
-        <f t="shared" ref="Z15:AB15" si="42">Z13*0.005</f>
-        <v>-2.1201359999999996</v>
+        <v>0.1</v>
       </c>
       <c r="AA15" s="6">
-        <f t="shared" si="42"/>
-        <v>-1.925689</v>
+        <f t="shared" ref="AA15:AB15" si="42">AA13*0.005</f>
+        <v>-1.6267303999999998</v>
       </c>
       <c r="AB15" s="6">
         <f t="shared" si="42"/>
-        <v>-2.0886840000000002</v>
+        <v>-1.8651160000000004</v>
       </c>
       <c r="AD15" s="6"/>
       <c r="AE15" s="6"/>
@@ -3145,47 +3140,47 @@
       </c>
       <c r="AK15" s="6">
         <f>SUM(Y15:AB15)</f>
-        <v>-6.0345089999999999</v>
+        <v>-3.2918464000000003</v>
       </c>
       <c r="AL15" s="6">
         <f t="shared" ref="AL15:AU15" si="43">AL13*0.01</f>
-        <v>-11.898308479999995</v>
+        <v>-8.5410984839999955</v>
       </c>
       <c r="AM15" s="6">
         <f t="shared" si="43"/>
-        <v>-6.4470915999999923</v>
+        <v>-2.1438507256000103</v>
       </c>
       <c r="AN15" s="6">
         <f t="shared" si="43"/>
-        <v>-1.113373554640013</v>
+        <v>3.5334293984479892</v>
       </c>
       <c r="AO15" s="6">
         <f t="shared" si="43"/>
-        <v>3.9993073761647886</v>
+        <v>8.0868272029526302</v>
       </c>
       <c r="AP15" s="6">
         <f t="shared" si="43"/>
-        <v>7.5335481167267453</v>
+        <v>12.684677719281686</v>
       </c>
       <c r="AQ15" s="6">
         <f t="shared" si="43"/>
-        <v>10.681882513422979</v>
+        <v>16.031513709669383</v>
       </c>
       <c r="AR15" s="6">
         <f t="shared" si="43"/>
-        <v>13.243178204560072</v>
+        <v>18.77457761273293</v>
       </c>
       <c r="AS15" s="6">
         <f t="shared" si="43"/>
-        <v>14.938374167624934</v>
+        <v>20.625959283317762</v>
       </c>
       <c r="AT15" s="6">
         <f t="shared" si="43"/>
-        <v>16.738990669899781</v>
+        <v>22.588163093230797</v>
       </c>
       <c r="AU15" s="6">
         <f t="shared" si="43"/>
-        <v>18.650711953166244</v>
+        <v>24.667095210554393</v>
       </c>
     </row>
     <row r="16" spans="2:160" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3280,15 +3275,15 @@
       </c>
       <c r="Z16" s="9">
         <f t="shared" si="45"/>
-        <v>-421.90706399999988</v>
+        <v>-298.10000000000002</v>
       </c>
       <c r="AA16" s="9">
         <f t="shared" si="45"/>
-        <v>-383.21211099999999</v>
+        <v>-323.71934959999999</v>
       </c>
       <c r="AB16" s="9">
         <f t="shared" si="45"/>
-        <v>-415.64811600000007</v>
+        <v>-371.15808400000009</v>
       </c>
       <c r="AD16" s="9">
         <f t="shared" ref="AD16:AQ16" si="46">AD13-AD14-AD15</f>
@@ -3320,499 +3315,499 @@
       </c>
       <c r="AK16" s="9">
         <f t="shared" si="46"/>
-        <v>-1689.9536909999993</v>
+        <v>-1423.0774335999995</v>
       </c>
       <c r="AL16" s="9">
         <f t="shared" si="46"/>
-        <v>-1177.9325395199996</v>
+        <v>-845.56874991599943</v>
       </c>
       <c r="AM16" s="9">
         <f t="shared" si="46"/>
-        <v>-606.02661039999919</v>
+        <v>-201.52196820640097</v>
       </c>
       <c r="AN16" s="9">
         <f t="shared" si="46"/>
-        <v>-104.65711413616123</v>
+        <v>332.14236345411098</v>
       </c>
       <c r="AO16" s="9">
         <f t="shared" si="46"/>
-        <v>355.93835647866615</v>
+        <v>719.72762106278401</v>
       </c>
       <c r="AP16" s="9">
         <f t="shared" si="46"/>
-        <v>670.48578238868038</v>
+        <v>1128.93631701607</v>
       </c>
       <c r="AQ16" s="9">
         <f t="shared" si="46"/>
-        <v>940.00566118122208</v>
+        <v>1410.7732064509059</v>
       </c>
       <c r="AR16" s="9">
         <f t="shared" ref="AR16" si="47">AR13-AR14-AR15</f>
-        <v>1112.4269691830461</v>
+        <v>1577.064519469566</v>
       </c>
       <c r="AS16" s="9">
         <f t="shared" ref="AS16" si="48">AS13-AS14-AS15</f>
-        <v>1254.8234300804945</v>
+        <v>1732.580579798692</v>
       </c>
       <c r="AT16" s="9">
         <f t="shared" ref="AT16" si="49">AT13-AT14-AT15</f>
-        <v>1406.0752162715817</v>
+        <v>1897.4056998313868</v>
       </c>
       <c r="AU16" s="9">
         <f t="shared" ref="AU16" si="50">AU13-AU14-AU15</f>
-        <v>1566.6598040659644</v>
+        <v>2072.0359976865693</v>
       </c>
       <c r="AV16" s="1">
         <f>AU16*(1+$AX$22)</f>
-        <v>1550.9932060253047</v>
+        <v>2051.3156377097034</v>
       </c>
       <c r="AW16" s="1">
         <f t="shared" ref="AW16:DH16" si="51">AV16*(1+$AX$22)</f>
-        <v>1535.4832739650517</v>
+        <v>2030.8024813326065</v>
       </c>
       <c r="AX16" s="1">
         <f t="shared" si="51"/>
-        <v>1520.1284412254013</v>
+        <v>2010.4944565192804</v>
       </c>
       <c r="AY16" s="1">
         <f t="shared" si="51"/>
-        <v>1504.9271568131473</v>
+        <v>1990.3895119540875</v>
       </c>
       <c r="AZ16" s="1">
         <f t="shared" si="51"/>
-        <v>1489.8778852450159</v>
+        <v>1970.4856168345466</v>
       </c>
       <c r="BA16" s="1">
         <f t="shared" si="51"/>
-        <v>1474.9791063925657</v>
+        <v>1950.7807606662011</v>
       </c>
       <c r="BB16" s="1">
         <f t="shared" si="51"/>
-        <v>1460.22931532864</v>
+        <v>1931.2729530595391</v>
       </c>
       <c r="BC16" s="1">
         <f t="shared" si="51"/>
-        <v>1445.6270221753537</v>
+        <v>1911.9602235289437</v>
       </c>
       <c r="BD16" s="1">
         <f t="shared" si="51"/>
-        <v>1431.1707519536001</v>
+        <v>1892.8406212936543</v>
       </c>
       <c r="BE16" s="1">
         <f t="shared" si="51"/>
-        <v>1416.8590444340641</v>
+        <v>1873.9122150807177</v>
       </c>
       <c r="BF16" s="1">
         <f t="shared" si="51"/>
-        <v>1402.6904539897234</v>
+        <v>1855.1730929299106</v>
       </c>
       <c r="BG16" s="1">
         <f t="shared" si="51"/>
-        <v>1388.6635494498262</v>
+        <v>1836.6213620006115</v>
       </c>
       <c r="BH16" s="1">
         <f t="shared" si="51"/>
-        <v>1374.7769139553279</v>
+        <v>1818.2551483806053</v>
       </c>
       <c r="BI16" s="1">
         <f t="shared" si="51"/>
-        <v>1361.0291448157745</v>
+        <v>1800.0725968967993</v>
       </c>
       <c r="BJ16" s="1">
         <f t="shared" si="51"/>
-        <v>1347.4188533676167</v>
+        <v>1782.0718709278312</v>
       </c>
       <c r="BK16" s="1">
         <f t="shared" si="51"/>
-        <v>1333.9446648339406</v>
+        <v>1764.251152218553</v>
       </c>
       <c r="BL16" s="1">
         <f t="shared" si="51"/>
-        <v>1320.6052181856012</v>
+        <v>1746.6086406963675</v>
       </c>
       <c r="BM16" s="1">
         <f t="shared" si="51"/>
-        <v>1307.3991660037452</v>
+        <v>1729.1425542894037</v>
       </c>
       <c r="BN16" s="1">
         <f t="shared" si="51"/>
-        <v>1294.3251743437077</v>
+        <v>1711.8511287465096</v>
       </c>
       <c r="BO16" s="1">
         <f t="shared" si="51"/>
-        <v>1281.3819226002706</v>
+        <v>1694.7326174590446</v>
       </c>
       <c r="BP16" s="1">
         <f t="shared" si="51"/>
-        <v>1268.5681033742678</v>
+        <v>1677.7852912844542</v>
       </c>
       <c r="BQ16" s="1">
         <f t="shared" si="51"/>
-        <v>1255.8824223405252</v>
+        <v>1661.0074383716096</v>
       </c>
       <c r="BR16" s="1">
         <f t="shared" si="51"/>
-        <v>1243.3235981171199</v>
+        <v>1644.3973639878934</v>
       </c>
       <c r="BS16" s="1">
         <f t="shared" si="51"/>
-        <v>1230.8903621359486</v>
+        <v>1627.9533903480144</v>
       </c>
       <c r="BT16" s="1">
         <f t="shared" si="51"/>
-        <v>1218.581458514589</v>
+        <v>1611.6738564445343</v>
       </c>
       <c r="BU16" s="1">
         <f t="shared" si="51"/>
-        <v>1206.3956439294432</v>
+        <v>1595.557117880089</v>
       </c>
       <c r="BV16" s="1">
         <f t="shared" si="51"/>
-        <v>1194.3316874901486</v>
+        <v>1579.601546701288</v>
       </c>
       <c r="BW16" s="1">
         <f t="shared" si="51"/>
-        <v>1182.3883706152471</v>
+        <v>1563.8055312342751</v>
       </c>
       <c r="BX16" s="1">
         <f t="shared" si="51"/>
-        <v>1170.5644869090947</v>
+        <v>1548.1674759219325</v>
       </c>
       <c r="BY16" s="1">
         <f t="shared" si="51"/>
-        <v>1158.8588420400038</v>
+        <v>1532.6858011627132</v>
       </c>
       <c r="BZ16" s="1">
         <f t="shared" si="51"/>
-        <v>1147.2702536196036</v>
+        <v>1517.3589431510861</v>
       </c>
       <c r="CA16" s="1">
         <f t="shared" si="51"/>
-        <v>1135.7975510834076</v>
+        <v>1502.1853537195752</v>
       </c>
       <c r="CB16" s="1">
         <f t="shared" si="51"/>
-        <v>1124.4395755725734</v>
+        <v>1487.1635001823795</v>
       </c>
       <c r="CC16" s="1">
         <f t="shared" si="51"/>
-        <v>1113.1951798168477</v>
+        <v>1472.2918651805558</v>
       </c>
       <c r="CD16" s="1">
         <f t="shared" si="51"/>
-        <v>1102.0632280186792</v>
+        <v>1457.5689465287503</v>
       </c>
       <c r="CE16" s="1">
         <f t="shared" si="51"/>
-        <v>1091.0425957384923</v>
+        <v>1442.9932570634628</v>
       </c>
       <c r="CF16" s="1">
         <f t="shared" si="51"/>
-        <v>1080.1321697811075</v>
+        <v>1428.5633244928281</v>
       </c>
       <c r="CG16" s="1">
         <f t="shared" si="51"/>
-        <v>1069.3308480832964</v>
+        <v>1414.2776912478998</v>
       </c>
       <c r="CH16" s="1">
         <f t="shared" si="51"/>
-        <v>1058.6375396024634</v>
+        <v>1400.1349143354207</v>
       </c>
       <c r="CI16" s="1">
         <f t="shared" si="51"/>
-        <v>1048.0511642064389</v>
+        <v>1386.1335651920665</v>
       </c>
       <c r="CJ16" s="1">
         <f t="shared" si="51"/>
-        <v>1037.5706525643745</v>
+        <v>1372.2722295401459</v>
       </c>
       <c r="CK16" s="1">
         <f t="shared" si="51"/>
-        <v>1027.1949460387307</v>
+        <v>1358.5495072447443</v>
       </c>
       <c r="CL16" s="1">
         <f t="shared" si="51"/>
-        <v>1016.9229965783434</v>
+        <v>1344.9640121722969</v>
       </c>
       <c r="CM16" s="1">
         <f t="shared" si="51"/>
-        <v>1006.75376661256</v>
+        <v>1331.5143720505739</v>
       </c>
       <c r="CN16" s="1">
         <f t="shared" si="51"/>
-        <v>996.68622894643431</v>
+        <v>1318.1992283300681</v>
       </c>
       <c r="CO16" s="1">
         <f t="shared" si="51"/>
-        <v>986.71936665697001</v>
+        <v>1305.0172360467675</v>
       </c>
       <c r="CP16" s="1">
         <f t="shared" si="51"/>
-        <v>976.85217299040028</v>
+        <v>1291.9670636862998</v>
       </c>
       <c r="CQ16" s="1">
         <f t="shared" si="51"/>
-        <v>967.08365126049625</v>
+        <v>1279.0473930494368</v>
       </c>
       <c r="CR16" s="1">
         <f t="shared" si="51"/>
-        <v>957.41281474789128</v>
+        <v>1266.2569191189425</v>
       </c>
       <c r="CS16" s="1">
         <f t="shared" si="51"/>
-        <v>947.8386866004123</v>
+        <v>1253.594349927753</v>
       </c>
       <c r="CT16" s="1">
         <f t="shared" si="51"/>
-        <v>938.36029973440816</v>
+        <v>1241.0584064284756</v>
       </c>
       <c r="CU16" s="1">
         <f t="shared" si="51"/>
-        <v>928.97669673706412</v>
+        <v>1228.6478223641907</v>
       </c>
       <c r="CV16" s="1">
         <f t="shared" si="51"/>
-        <v>919.68692976969351</v>
+        <v>1216.3613441405487</v>
       </c>
       <c r="CW16" s="1">
         <f t="shared" si="51"/>
-        <v>910.49006047199657</v>
+        <v>1204.1977306991432</v>
       </c>
       <c r="CX16" s="1">
         <f t="shared" si="51"/>
-        <v>901.38515986727657</v>
+        <v>1192.1557533921518</v>
       </c>
       <c r="CY16" s="1">
         <f t="shared" si="51"/>
-        <v>892.3713082686038</v>
+        <v>1180.2341958582304</v>
       </c>
       <c r="CZ16" s="1">
         <f t="shared" si="51"/>
-        <v>883.44759518591775</v>
+        <v>1168.4318538996481</v>
       </c>
       <c r="DA16" s="1">
         <f t="shared" si="51"/>
-        <v>874.61311923405856</v>
+        <v>1156.7475353606517</v>
       </c>
       <c r="DB16" s="1">
         <f t="shared" si="51"/>
-        <v>865.86698804171795</v>
+        <v>1145.1800600070451</v>
       </c>
       <c r="DC16" s="1">
         <f t="shared" si="51"/>
-        <v>857.20831816130078</v>
+        <v>1133.7282594069745</v>
       </c>
       <c r="DD16" s="1">
         <f t="shared" si="51"/>
-        <v>848.63623497968774</v>
+        <v>1122.3909768129047</v>
       </c>
       <c r="DE16" s="1">
         <f t="shared" si="51"/>
-        <v>840.14987262989087</v>
+        <v>1111.1670670447756</v>
       </c>
       <c r="DF16" s="1">
         <f t="shared" si="51"/>
-        <v>831.74837390359198</v>
+        <v>1100.055396374328</v>
       </c>
       <c r="DG16" s="1">
         <f t="shared" si="51"/>
-        <v>823.4308901645561</v>
+        <v>1089.0548424105848</v>
       </c>
       <c r="DH16" s="1">
         <f t="shared" si="51"/>
-        <v>815.19658126291051</v>
+        <v>1078.1642939864789</v>
       </c>
       <c r="DI16" s="1">
         <f t="shared" ref="DI16:FD16" si="52">DH16*(1+$AX$22)</f>
-        <v>807.04461545028141</v>
+        <v>1067.3826510466142</v>
       </c>
       <c r="DJ16" s="1">
         <f t="shared" si="52"/>
-        <v>798.97416929577855</v>
+        <v>1056.7088245361481</v>
       </c>
       <c r="DK16" s="1">
         <f t="shared" si="52"/>
-        <v>790.9844276028208</v>
+        <v>1046.1417362907866</v>
       </c>
       <c r="DL16" s="1">
         <f t="shared" si="52"/>
-        <v>783.07458332679255</v>
+        <v>1035.6803189278787</v>
       </c>
       <c r="DM16" s="1">
         <f t="shared" si="52"/>
-        <v>775.24383749352467</v>
+        <v>1025.3235157386</v>
       </c>
       <c r="DN16" s="1">
         <f t="shared" si="52"/>
-        <v>767.49139911858936</v>
+        <v>1015.070280581214</v>
       </c>
       <c r="DO16" s="1">
         <f t="shared" si="52"/>
-        <v>759.81648512740344</v>
+        <v>1004.9195777754019</v>
       </c>
       <c r="DP16" s="1">
         <f t="shared" si="52"/>
-        <v>752.21832027612936</v>
+        <v>994.87038199764788</v>
       </c>
       <c r="DQ16" s="1">
         <f t="shared" si="52"/>
-        <v>744.69613707336805</v>
+        <v>984.92167817767142</v>
       </c>
       <c r="DR16" s="1">
         <f t="shared" si="52"/>
-        <v>737.24917570263437</v>
+        <v>975.07246139589472</v>
       </c>
       <c r="DS16" s="1">
         <f t="shared" si="52"/>
-        <v>729.87668394560808</v>
+        <v>965.32173678193578</v>
       </c>
       <c r="DT16" s="1">
         <f t="shared" si="52"/>
-        <v>722.57791710615197</v>
+        <v>955.66851941411642</v>
       </c>
       <c r="DU16" s="1">
         <f t="shared" si="52"/>
-        <v>715.35213793509047</v>
+        <v>946.11183421997521</v>
       </c>
       <c r="DV16" s="1">
         <f t="shared" si="52"/>
-        <v>708.19861655573959</v>
+        <v>936.6507158777755</v>
       </c>
       <c r="DW16" s="1">
         <f t="shared" si="52"/>
-        <v>701.11663039018219</v>
+        <v>927.28420871899777</v>
       </c>
       <c r="DX16" s="1">
         <f t="shared" si="52"/>
-        <v>694.10546408628034</v>
+        <v>918.01136663180773</v>
       </c>
       <c r="DY16" s="1">
         <f t="shared" si="52"/>
-        <v>687.1644094454175</v>
+        <v>908.83125296548963</v>
       </c>
       <c r="DZ16" s="1">
         <f t="shared" si="52"/>
-        <v>680.29276535096335</v>
+        <v>899.74294043583473</v>
       </c>
       <c r="EA16" s="1">
         <f t="shared" si="52"/>
-        <v>673.48983769745371</v>
+        <v>890.74551103147633</v>
       </c>
       <c r="EB16" s="1">
         <f t="shared" si="52"/>
-        <v>666.75493932047914</v>
+        <v>881.83805592116153</v>
       </c>
       <c r="EC16" s="1">
         <f t="shared" si="52"/>
-        <v>660.08738992727433</v>
+        <v>873.01967536194991</v>
       </c>
       <c r="ED16" s="1">
         <f t="shared" si="52"/>
-        <v>653.48651602800157</v>
+        <v>864.28947860833046</v>
       </c>
       <c r="EE16" s="1">
         <f t="shared" si="52"/>
-        <v>646.95165086772158</v>
+        <v>855.64658382224718</v>
       </c>
       <c r="EF16" s="1">
         <f t="shared" si="52"/>
-        <v>640.48213435904438</v>
+        <v>847.09011798402469</v>
       </c>
       <c r="EG16" s="1">
         <f t="shared" si="52"/>
-        <v>634.07731301545391</v>
+        <v>838.61921680418448</v>
       </c>
       <c r="EH16" s="1">
         <f t="shared" si="52"/>
-        <v>627.73653988529941</v>
+        <v>830.23302463614266</v>
       </c>
       <c r="EI16" s="1">
         <f t="shared" si="52"/>
-        <v>621.45917448644639</v>
+        <v>821.93069438978125</v>
       </c>
       <c r="EJ16" s="1">
         <f t="shared" si="52"/>
-        <v>615.24458274158189</v>
+        <v>813.71138744588347</v>
       </c>
       <c r="EK16" s="1">
         <f t="shared" si="52"/>
-        <v>609.09213691416608</v>
+        <v>805.57427357142467</v>
       </c>
       <c r="EL16" s="1">
         <f t="shared" si="52"/>
-        <v>603.00121554502437</v>
+        <v>797.51853083571041</v>
       </c>
       <c r="EM16" s="1">
         <f t="shared" si="52"/>
-        <v>596.97120338957416</v>
+        <v>789.54334552735327</v>
       </c>
       <c r="EN16" s="1">
         <f t="shared" si="52"/>
-        <v>591.00149135567835</v>
+        <v>781.64791207207975</v>
       </c>
       <c r="EO16" s="1">
         <f t="shared" si="52"/>
-        <v>585.09147644212158</v>
+        <v>773.83143295135892</v>
       </c>
       <c r="EP16" s="1">
         <f t="shared" si="52"/>
-        <v>579.24056167770038</v>
+        <v>766.09311862184529</v>
       </c>
       <c r="EQ16" s="1">
         <f t="shared" si="52"/>
-        <v>573.44815606092334</v>
+        <v>758.43218743562682</v>
       </c>
       <c r="ER16" s="1">
         <f t="shared" si="52"/>
-        <v>567.71367450031414</v>
+        <v>750.84786556127051</v>
       </c>
       <c r="ES16" s="1">
         <f t="shared" si="52"/>
-        <v>562.03653775531097</v>
+        <v>743.33938690565776</v>
       </c>
       <c r="ET16" s="1">
         <f t="shared" si="52"/>
-        <v>556.4161723777579</v>
+        <v>735.90599303660122</v>
       </c>
       <c r="EU16" s="1">
         <f t="shared" si="52"/>
-        <v>550.8520106539803</v>
+        <v>728.5469331062352</v>
       </c>
       <c r="EV16" s="1">
         <f t="shared" si="52"/>
-        <v>545.34349054744052</v>
+        <v>721.26146377517284</v>
       </c>
       <c r="EW16" s="1">
         <f t="shared" si="52"/>
-        <v>539.89005564196611</v>
+        <v>714.04884913742114</v>
       </c>
       <c r="EX16" s="1">
         <f t="shared" si="52"/>
-        <v>534.49115508554644</v>
+        <v>706.90836064604696</v>
       </c>
       <c r="EY16" s="1">
         <f t="shared" si="52"/>
-        <v>529.14624353469094</v>
+        <v>699.83927703958648</v>
       </c>
       <c r="EZ16" s="1">
         <f t="shared" si="52"/>
-        <v>523.854781099344</v>
+        <v>692.84088426919061</v>
       </c>
       <c r="FA16" s="1">
         <f t="shared" si="52"/>
-        <v>518.6162332883506</v>
+        <v>685.91247542649864</v>
       </c>
       <c r="FB16" s="1">
         <f t="shared" si="52"/>
-        <v>513.43007095546704</v>
+        <v>679.05335067223371</v>
       </c>
       <c r="FC16" s="1">
         <f t="shared" si="52"/>
-        <v>508.29577024591237</v>
+        <v>672.26281716551136</v>
       </c>
       <c r="FD16" s="1">
         <f t="shared" si="52"/>
-        <v>503.21281254345325</v>
+        <v>665.54018899385619</v>
       </c>
     </row>
     <row r="17" spans="2:50" x14ac:dyDescent="0.3">
@@ -3888,16 +3883,13 @@
         <v>332.7</v>
       </c>
       <c r="Z17" s="6">
-        <f>332.7</f>
-        <v>332.7</v>
+        <v>335.2</v>
       </c>
       <c r="AA17" s="6">
-        <f>332.7</f>
-        <v>332.7</v>
+        <v>335.2</v>
       </c>
       <c r="AB17" s="6">
-        <f>332.7</f>
-        <v>332.7</v>
+        <v>335.2</v>
       </c>
       <c r="AD17" s="6">
         <v>284.10000000000002</v>
@@ -3918,52 +3910,41 @@
         <v>289</v>
       </c>
       <c r="AJ17" s="6">
-        <f t="shared" ref="AJ17:AU17" si="53">331.4</f>
+        <f t="shared" ref="AJ17" si="53">331.4</f>
         <v>331.4</v>
       </c>
       <c r="AK17" s="6">
-        <f>332.7</f>
-        <v>332.7</v>
+        <v>335.2</v>
       </c>
       <c r="AL17" s="6">
-        <f>332.7</f>
-        <v>332.7</v>
+        <v>335.2</v>
       </c>
       <c r="AM17" s="6">
-        <f>332.7</f>
-        <v>332.7</v>
+        <v>335.2</v>
       </c>
       <c r="AN17" s="6">
-        <f>332.7</f>
-        <v>332.7</v>
+        <v>335.2</v>
       </c>
       <c r="AO17" s="6">
-        <f>332.7</f>
-        <v>332.7</v>
+        <v>335.2</v>
       </c>
       <c r="AP17" s="6">
-        <f>332.7</f>
-        <v>332.7</v>
+        <v>335.2</v>
       </c>
       <c r="AQ17" s="6">
-        <f>332.7</f>
-        <v>332.7</v>
+        <v>335.2</v>
       </c>
       <c r="AR17" s="6">
-        <f>332.7</f>
-        <v>332.7</v>
+        <v>335.2</v>
       </c>
       <c r="AS17" s="6">
-        <f>332.7</f>
-        <v>332.7</v>
+        <v>335.2</v>
       </c>
       <c r="AT17" s="6">
-        <f>332.7</f>
-        <v>332.7</v>
+        <v>335.2</v>
       </c>
       <c r="AU17" s="6">
-        <f>332.7</f>
-        <v>332.7</v>
+        <v>335.2</v>
       </c>
     </row>
     <row r="18" spans="2:50" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -4056,15 +4037,15 @@
       </c>
       <c r="Z18" s="8">
         <f t="shared" si="55"/>
-        <v>-1.2681306402164108</v>
+        <v>-0.88931980906921249</v>
       </c>
       <c r="AA18" s="8">
         <f t="shared" si="55"/>
-        <v>-1.1518248001202285</v>
+        <v>-0.96574984964200472</v>
       </c>
       <c r="AB18" s="8">
         <f t="shared" si="55"/>
-        <v>-1.249318052299369</v>
+        <v>-1.1072735202863966</v>
       </c>
       <c r="AD18" s="8">
         <f>AD16/AD17</f>
@@ -4096,47 +4077,47 @@
       </c>
       <c r="AK18" s="8">
         <f t="shared" si="56"/>
-        <v>-5.079512146077545</v>
+        <v>-4.2454577374701659</v>
       </c>
       <c r="AL18" s="8">
         <f t="shared" si="56"/>
-        <v>-3.5405246153291245</v>
+        <v>-2.522579802852027</v>
       </c>
       <c r="AM18" s="8">
         <f t="shared" si="56"/>
-        <v>-1.8215407586414163</v>
+        <v>-0.60119918915990744</v>
       </c>
       <c r="AN18" s="8">
         <f t="shared" si="56"/>
-        <v>-0.31456902355323485</v>
+        <v>0.99087817259579647</v>
       </c>
       <c r="AO18" s="8">
         <f t="shared" si="56"/>
-        <v>1.0698477802184134</v>
+        <v>2.1471587740536515</v>
       </c>
       <c r="AP18" s="8">
         <f t="shared" si="56"/>
-        <v>2.0152863913095294</v>
+        <v>3.3679484397854118</v>
       </c>
       <c r="AQ18" s="8">
         <f t="shared" si="56"/>
-        <v>2.8253852154530272</v>
+        <v>4.2087506159036572</v>
       </c>
       <c r="AR18" s="8">
         <f t="shared" ref="AR18:AU18" si="57">AR16/AR17</f>
-        <v>3.3436338117915425</v>
+        <v>4.7048464184652925</v>
       </c>
       <c r="AS18" s="8">
         <f t="shared" si="57"/>
-        <v>3.7716363994003443</v>
+        <v>5.168796479113043</v>
       </c>
       <c r="AT18" s="8">
         <f t="shared" si="57"/>
-        <v>4.2262555343299724</v>
+        <v>5.6605181975876695</v>
       </c>
       <c r="AU18" s="8">
         <f t="shared" si="57"/>
-        <v>4.7089263723052737</v>
+        <v>6.1814916398764002</v>
       </c>
     </row>
     <row r="20" spans="2:50" x14ac:dyDescent="0.3">
@@ -4221,11 +4202,11 @@
       </c>
       <c r="Z20" s="10">
         <f t="shared" ref="Z20" si="61">Z3/V3-1</f>
-        <v>0.19999999999999996</v>
+        <v>0.31790976058931864</v>
       </c>
       <c r="AA20" s="10">
         <f t="shared" ref="AA20" si="62">AA3/W3-1</f>
-        <v>0.19999999999999996</v>
+        <v>0.24</v>
       </c>
       <c r="AB20" s="10">
         <f t="shared" ref="AB20" si="63">AB3/X3-1</f>
@@ -4258,7 +4239,7 @@
       </c>
       <c r="AK20" s="10">
         <f t="shared" si="64"/>
-        <v>0.21314251047871191</v>
+        <v>0.25178248400617709</v>
       </c>
       <c r="AL20" s="10">
         <f t="shared" si="64"/>
@@ -4391,7 +4372,7 @@
       </c>
       <c r="Z21" s="10">
         <f t="shared" si="68"/>
-        <v>0.67</v>
+        <v>0.67528384279475984</v>
       </c>
       <c r="AA21" s="10">
         <f t="shared" si="68"/>
@@ -4431,19 +4412,19 @@
       </c>
       <c r="AK21" s="10">
         <f t="shared" si="69"/>
-        <v>0.66</v>
+        <v>0.67025179184150374</v>
       </c>
       <c r="AL21" s="10">
         <f t="shared" si="69"/>
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="AM21" s="10">
         <f t="shared" si="69"/>
-        <v>0.68</v>
+        <v>0.68999999999999984</v>
       </c>
       <c r="AN21" s="10">
         <f t="shared" si="69"/>
-        <v>0.69</v>
+        <v>0.7</v>
       </c>
       <c r="AO21" s="10">
         <f t="shared" si="69"/>
@@ -4564,15 +4545,15 @@
       </c>
       <c r="Z22" s="10">
         <f t="shared" si="73"/>
-        <v>-0.45636912983425404</v>
+        <v>-0.29720524017467242</v>
       </c>
       <c r="AA22" s="10">
         <f t="shared" si="73"/>
-        <v>-0.38590453950394504</v>
+        <v>-0.32227340430267315</v>
       </c>
       <c r="AB22" s="10">
         <f t="shared" si="73"/>
-        <v>-0.40269203486015415</v>
+        <v>-0.36493227266585609</v>
       </c>
       <c r="AD22" s="10">
         <f t="shared" ref="AD22:AQ22" si="74">AD9/AD3</f>
@@ -4604,47 +4585,47 @@
       </c>
       <c r="AK22" s="10">
         <f t="shared" si="74"/>
-        <v>-0.42626921310923893</v>
+        <v>-0.35163166400262225</v>
       </c>
       <c r="AL22" s="10">
         <f t="shared" si="74"/>
-        <v>-0.25835072988220958</v>
+        <v>-0.19032353009646208</v>
       </c>
       <c r="AM22" s="10">
         <f t="shared" si="74"/>
-        <v>-0.13269018181417327</v>
+        <v>-6.4538292572138223E-2</v>
       </c>
       <c r="AN22" s="10">
         <f t="shared" si="74"/>
-        <v>-4.5523170158482576E-2</v>
+        <v>1.6539266524327381E-2</v>
       </c>
       <c r="AO22" s="10">
         <f t="shared" si="74"/>
-        <v>2.0157349422445323E-2</v>
+        <v>6.7643616650074984E-2</v>
       </c>
       <c r="AP22" s="10">
         <f t="shared" si="74"/>
-        <v>5.7119721477884668E-2</v>
+        <v>0.11091421007621695</v>
       </c>
       <c r="AQ22" s="10">
         <f t="shared" si="74"/>
-        <v>8.5478612997609685E-2</v>
+        <v>0.13675934044648724</v>
       </c>
       <c r="AR22" s="10">
         <f t="shared" ref="AR22:AU22" si="75">AR9/AR3</f>
-        <v>0.10617922405482084</v>
+        <v>0.15599478786230178</v>
       </c>
       <c r="AS22" s="10">
         <f t="shared" si="75"/>
-        <v>0.11657410336754019</v>
+        <v>0.16496636535195042</v>
       </c>
       <c r="AT22" s="10">
         <f t="shared" si="75"/>
-        <v>0.12667198612846761</v>
+        <v>0.17368161205618055</v>
       </c>
       <c r="AU22" s="10">
         <f t="shared" si="75"/>
-        <v>0.13648135795336852</v>
+        <v>0.18214785171171807</v>
       </c>
       <c r="AW22" t="s">
         <v>40</v>
@@ -4743,15 +4724,15 @@
       </c>
       <c r="Z23" s="10">
         <f t="shared" si="78"/>
-        <v>0.44</v>
+        <v>0.43842794759825326</v>
       </c>
       <c r="AA23" s="10">
         <f t="shared" si="78"/>
-        <v>0.41</v>
+        <v>0.44000000000000006</v>
       </c>
       <c r="AB23" s="10">
         <f t="shared" si="78"/>
-        <v>0.4</v>
+        <v>0.44000000000000006</v>
       </c>
       <c r="AD23" s="10">
         <f t="shared" ref="AD23:AQ23" si="79">AD6/AD3</f>
@@ -4783,23 +4764,23 @@
       </c>
       <c r="AK23" s="10">
         <f t="shared" si="79"/>
-        <v>0.42154132210740697</v>
+        <v>0.43962021947965663</v>
       </c>
       <c r="AL23" s="10">
         <f t="shared" si="79"/>
-        <v>0.35</v>
+        <v>0.37</v>
       </c>
       <c r="AM23" s="10">
         <f t="shared" si="79"/>
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="AN23" s="10">
         <f t="shared" si="79"/>
-        <v>0.28000000000000003</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="AO23" s="10">
         <f t="shared" si="79"/>
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="AP23" s="10">
         <f t="shared" si="79"/>
@@ -4819,7 +4800,7 @@
       </c>
       <c r="AT23" s="10">
         <f t="shared" si="80"/>
-        <v>0.23</v>
+        <v>0.22999999999999998</v>
       </c>
       <c r="AU23" s="10">
         <f t="shared" si="80"/>
@@ -4829,7 +4810,7 @@
         <v>41</v>
       </c>
       <c r="AX23" s="10">
-        <v>0.08</v>
+        <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="24" spans="2:50" x14ac:dyDescent="0.3">
@@ -4916,7 +4897,7 @@
       </c>
       <c r="Z24" s="10">
         <f t="shared" ref="Z24:Z25" si="84">Z7/V7-1</f>
-        <v>0.14999999999999991</v>
+        <v>0.12405757368060311</v>
       </c>
       <c r="AA24" s="10">
         <f t="shared" ref="AA24:AA25" si="85">AA7/W7-1</f>
@@ -4953,7 +4934,7 @@
       </c>
       <c r="AK24" s="10">
         <f t="shared" si="87"/>
-        <v>0.15495009532353921</v>
+        <v>0.14858304362453723</v>
       </c>
       <c r="AL24" s="10">
         <f t="shared" si="87"/>
@@ -5000,7 +4981,7 @@
       </c>
       <c r="AX24" s="6">
         <f>NPV(AX23,AJ16:FD16)</f>
-        <v>6238.3937200405708</v>
+        <v>13895.376493316469</v>
       </c>
     </row>
     <row r="25" spans="2:50" x14ac:dyDescent="0.3">
@@ -5087,15 +5068,15 @@
       </c>
       <c r="Z25" s="10">
         <f t="shared" si="84"/>
-        <v>1.17</v>
+        <v>0.22188139059304701</v>
       </c>
       <c r="AA25" s="10">
         <f t="shared" si="85"/>
-        <v>1</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="AB25" s="10">
         <f t="shared" si="86"/>
-        <v>1</v>
+        <v>0.19999999999999996</v>
       </c>
       <c r="AD25" s="10"/>
       <c r="AE25" s="10">
@@ -5124,11 +5105,11 @@
       </c>
       <c r="AK25" s="10">
         <f t="shared" si="90"/>
-        <v>1.0970797962648557</v>
+        <v>0.44259034683482912</v>
       </c>
       <c r="AL25" s="10">
         <f t="shared" si="90"/>
-        <v>0.10000000000000009</v>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="AM25" s="10">
         <f t="shared" si="90"/>
@@ -5171,7 +5152,7 @@
       </c>
       <c r="AX25" s="6">
         <f>Main!D8</f>
-        <v>2593.2000000000003</v>
+        <v>2323.8999999999996</v>
       </c>
     </row>
     <row r="26" spans="2:50" x14ac:dyDescent="0.3">
@@ -5264,7 +5245,7 @@
       </c>
       <c r="Z26" s="10">
         <f t="shared" si="95"/>
-        <v>0</v>
+        <v>-3.3568311513930855E-4</v>
       </c>
       <c r="AA26" s="10">
         <f t="shared" si="95"/>
@@ -5304,7 +5285,7 @@
       </c>
       <c r="AK26" s="10">
         <f t="shared" si="96"/>
-        <v>-3.3722059942203953E-3</v>
+        <v>-4.0828702138342747E-3</v>
       </c>
       <c r="AL26" s="10">
         <f t="shared" si="96"/>
@@ -5312,11 +5293,11 @@
       </c>
       <c r="AM26" s="10">
         <f t="shared" si="96"/>
-        <v>4.9999999999999996E-2</v>
+        <v>0.05</v>
       </c>
       <c r="AN26" s="10">
         <f t="shared" si="96"/>
-        <v>0.05</v>
+        <v>4.9999999999999996E-2</v>
       </c>
       <c r="AO26" s="10">
         <f t="shared" si="96"/>
@@ -5324,11 +5305,11 @@
       </c>
       <c r="AP26" s="10">
         <f t="shared" si="96"/>
-        <v>9.9999999999999992E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AQ26" s="10">
         <f t="shared" si="96"/>
-        <v>0.11</v>
+        <v>0.10999999999999999</v>
       </c>
       <c r="AR26" s="10">
         <f t="shared" ref="AR26:AU26" si="97">AR14/AR13</f>
@@ -5351,7 +5332,7 @@
       </c>
       <c r="AX26" s="6">
         <f>AX24+AX25</f>
-        <v>8831.5937200405715</v>
+        <v>16219.276493316469</v>
       </c>
     </row>
     <row r="27" spans="2:50" x14ac:dyDescent="0.3">
@@ -5444,15 +5425,15 @@
       </c>
       <c r="Z27" s="10">
         <f t="shared" si="99"/>
-        <v>-0.40468372467771629</v>
+        <v>-0.26034934497816598</v>
       </c>
       <c r="AA27" s="10">
         <f t="shared" si="99"/>
-        <v>-0.33896977585535859</v>
+        <v>-0.27710857829625646</v>
       </c>
       <c r="AB27" s="10">
         <f t="shared" si="99"/>
-        <v>-0.35100671868666405</v>
+        <v>-0.3134357553033375</v>
       </c>
       <c r="AD27" s="10">
         <f t="shared" ref="AD27:AU27" si="100">AD16/AD3</f>
@@ -5484,54 +5465,54 @@
       </c>
       <c r="AK27" s="10">
         <f t="shared" si="100"/>
-        <v>-0.38413800501893447</v>
+        <v>-0.3134901903837104</v>
       </c>
       <c r="AL27" s="10">
         <f t="shared" si="100"/>
-        <v>-0.21592911581898569</v>
+        <v>-0.1502182377017027</v>
       </c>
       <c r="AM27" s="10">
         <f t="shared" si="100"/>
-        <v>-9.2576601910618825E-2</v>
+        <v>-2.9834233787565497E-2</v>
       </c>
       <c r="AN27" s="10">
         <f t="shared" si="100"/>
-        <v>-1.4024049795817364E-2</v>
+        <v>4.3133223212560128E-2</v>
       </c>
       <c r="AO27" s="10">
         <f t="shared" si="100"/>
-        <v>4.2969124207210045E-2</v>
+        <v>8.4204021282266908E-2</v>
       </c>
       <c r="AP27" s="10">
         <f t="shared" si="100"/>
-        <v>7.4258263019591111E-2</v>
+        <v>0.12117348780542408</v>
       </c>
       <c r="AQ27" s="10">
         <f t="shared" si="100"/>
-        <v>9.7297550022456103E-2</v>
+        <v>0.14151796981429035</v>
       </c>
       <c r="AR27" s="10">
         <f t="shared" si="100"/>
-        <v>0.10966136456627751</v>
+        <v>0.1506657538277964</v>
       </c>
       <c r="AS27" s="10">
         <f t="shared" si="100"/>
-        <v>0.11780818272152667</v>
+        <v>0.15764101800414521</v>
       </c>
       <c r="AT27" s="10">
         <f t="shared" si="100"/>
-        <v>0.12572223464376878</v>
+        <v>0.16441698891831255</v>
       </c>
       <c r="AU27" s="10">
         <f t="shared" si="100"/>
-        <v>0.13341017079680392</v>
+        <v>0.17099936066350355</v>
       </c>
       <c r="AW27" t="s">
         <v>45</v>
       </c>
       <c r="AX27" s="5">
         <f>AX26/AQ17</f>
-        <v>26.545217072559577</v>
+        <v>48.386863046886845</v>
       </c>
     </row>
     <row r="28" spans="2:50" x14ac:dyDescent="0.3">
@@ -5540,7 +5521,7 @@
       </c>
       <c r="AX28" s="5">
         <f>Main!D3</f>
-        <v>205.72</v>
+        <v>225.31</v>
       </c>
     </row>
     <row r="29" spans="2:50" x14ac:dyDescent="0.3">
@@ -5549,7 +5530,7 @@
       </c>
       <c r="AX29" s="11">
         <f>AX27/AX28-1</f>
-        <v>-0.8709643346657614</v>
+        <v>-0.78524316254544035</v>
       </c>
     </row>
     <row r="30" spans="2:50" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -6034,15 +6015,15 @@
       </c>
       <c r="Z60" s="9">
         <f t="shared" si="102"/>
-        <v>-421.90706399999988</v>
+        <v>-298.10000000000002</v>
       </c>
       <c r="AA60" s="9">
         <f t="shared" si="102"/>
-        <v>-383.21211099999999</v>
+        <v>-323.71934959999999</v>
       </c>
       <c r="AB60" s="9">
         <f t="shared" si="102"/>
-        <v>-415.64811600000007</v>
+        <v>-371.15808400000009</v>
       </c>
       <c r="AI60" s="9">
         <f>AI16</f>
@@ -6054,47 +6035,47 @@
       </c>
       <c r="AK60" s="9">
         <f t="shared" ref="AK60:AU60" si="103">AK16</f>
-        <v>-1689.9536909999993</v>
+        <v>-1423.0774335999995</v>
       </c>
       <c r="AL60" s="9">
         <f t="shared" si="103"/>
-        <v>-1177.9325395199996</v>
+        <v>-845.56874991599943</v>
       </c>
       <c r="AM60" s="9">
         <f t="shared" si="103"/>
-        <v>-606.02661039999919</v>
+        <v>-201.52196820640097</v>
       </c>
       <c r="AN60" s="9">
         <f t="shared" si="103"/>
-        <v>-104.65711413616123</v>
+        <v>332.14236345411098</v>
       </c>
       <c r="AO60" s="9">
         <f t="shared" si="103"/>
-        <v>355.93835647866615</v>
+        <v>719.72762106278401</v>
       </c>
       <c r="AP60" s="9">
         <f t="shared" si="103"/>
-        <v>670.48578238868038</v>
+        <v>1128.93631701607</v>
       </c>
       <c r="AQ60" s="9">
         <f t="shared" si="103"/>
-        <v>940.00566118122208</v>
+        <v>1410.7732064509059</v>
       </c>
       <c r="AR60" s="9">
         <f t="shared" si="103"/>
-        <v>1112.4269691830461</v>
+        <v>1577.064519469566</v>
       </c>
       <c r="AS60" s="9">
         <f t="shared" si="103"/>
-        <v>1254.8234300804945</v>
+        <v>1732.580579798692</v>
       </c>
       <c r="AT60" s="9">
         <f t="shared" si="103"/>
-        <v>1406.0752162715817</v>
+        <v>1897.4056998313868</v>
       </c>
       <c r="AU60" s="9">
         <f t="shared" si="103"/>
-        <v>1566.6598040659644</v>
+        <v>2072.0359976865693</v>
       </c>
     </row>
     <row r="61" spans="2:47" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -6130,6 +6111,9 @@
       </c>
       <c r="Y61" s="9">
         <v>-325.7</v>
+      </c>
+      <c r="Z61" s="9">
+        <v>-297.89999999999998</v>
       </c>
       <c r="AI61" s="9">
         <f>SUM(Q61:T61)</f>
@@ -6186,7 +6170,7 @@
         <v>48.8</v>
       </c>
       <c r="Z62" s="6">
-        <v>56</v>
+        <v>54.8</v>
       </c>
       <c r="AA62" s="6">
         <v>60</v>
@@ -6204,47 +6188,47 @@
       </c>
       <c r="AK62" s="6">
         <f>SUM(Y62:AB62)</f>
-        <v>227.8</v>
+        <v>226.6</v>
       </c>
       <c r="AL62" s="6">
         <f t="shared" ref="AL62:AU62" si="104">AK62*1.03</f>
-        <v>234.63400000000001</v>
+        <v>233.398</v>
       </c>
       <c r="AM62" s="6">
         <f t="shared" si="104"/>
-        <v>241.67302000000001</v>
+        <v>240.39994000000002</v>
       </c>
       <c r="AN62" s="6">
         <f t="shared" si="104"/>
-        <v>248.9232106</v>
+        <v>247.61193820000003</v>
       </c>
       <c r="AO62" s="6">
         <f t="shared" si="104"/>
-        <v>256.39090691799998</v>
+        <v>255.04029634600002</v>
       </c>
       <c r="AP62" s="6">
         <f t="shared" si="104"/>
-        <v>264.08263412553998</v>
+        <v>262.69150523638001</v>
       </c>
       <c r="AQ62" s="6">
         <f t="shared" si="104"/>
-        <v>272.00511314930617</v>
+        <v>270.57225039347139</v>
       </c>
       <c r="AR62" s="6">
         <f t="shared" si="104"/>
-        <v>280.16526654378538</v>
+        <v>278.68941790527555</v>
       </c>
       <c r="AS62" s="6">
         <f t="shared" si="104"/>
-        <v>288.57022454009893</v>
+        <v>287.0501004424338</v>
       </c>
       <c r="AT62" s="6">
         <f t="shared" si="104"/>
-        <v>297.22733127630192</v>
+        <v>295.66160345570682</v>
       </c>
       <c r="AU62" s="6">
         <f t="shared" si="104"/>
-        <v>306.14415121459098</v>
+        <v>304.53145155937801</v>
       </c>
     </row>
     <row r="63" spans="2:47" x14ac:dyDescent="0.3">
@@ -6282,65 +6266,65 @@
         <v>17.8</v>
       </c>
       <c r="Z63" s="6">
-        <v>21</v>
+        <v>16.2</v>
       </c>
       <c r="AA63" s="6">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AB63" s="6">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AI63" s="6">
-        <f t="shared" ref="AI63:AI77" si="105">SUM(Q63:T63)</f>
+        <f t="shared" ref="AI63:AI78" si="105">SUM(Q63:T63)</f>
         <v>53</v>
       </c>
       <c r="AJ63" s="6">
-        <f t="shared" ref="AJ63:AJ77" si="106">SUM(U63:X63)</f>
+        <f t="shared" ref="AJ63:AJ78" si="106">SUM(U63:X63)</f>
         <v>59.9</v>
       </c>
       <c r="AK63" s="6">
-        <f t="shared" ref="AK63:AK77" si="107">SUM(Y63:AB63)</f>
-        <v>85.8</v>
+        <f t="shared" ref="AK63:AK78" si="107">SUM(Y63:AB63)</f>
+        <v>70</v>
       </c>
       <c r="AL63" s="6">
         <f t="shared" ref="AL63:AU63" si="108">AK63*1.03</f>
-        <v>88.373999999999995</v>
+        <v>72.100000000000009</v>
       </c>
       <c r="AM63" s="6">
         <f t="shared" si="108"/>
-        <v>91.025220000000004</v>
+        <v>74.263000000000005</v>
       </c>
       <c r="AN63" s="6">
         <f t="shared" si="108"/>
-        <v>93.755976600000011</v>
+        <v>76.490890000000007</v>
       </c>
       <c r="AO63" s="6">
         <f t="shared" si="108"/>
-        <v>96.568655898000017</v>
+        <v>78.785616700000006</v>
       </c>
       <c r="AP63" s="6">
         <f t="shared" si="108"/>
-        <v>99.46571557494002</v>
+        <v>81.149185201000009</v>
       </c>
       <c r="AQ63" s="6">
         <f t="shared" si="108"/>
-        <v>102.44968704218823</v>
+        <v>83.583660757030017</v>
       </c>
       <c r="AR63" s="6">
         <f t="shared" si="108"/>
-        <v>105.52317765345389</v>
+        <v>86.091170579740918</v>
       </c>
       <c r="AS63" s="6">
         <f t="shared" si="108"/>
-        <v>108.68887298305751</v>
+        <v>88.673905697133151</v>
       </c>
       <c r="AT63" s="6">
         <f t="shared" si="108"/>
-        <v>111.94953917254924</v>
+        <v>91.334122868047146</v>
       </c>
       <c r="AU63" s="6">
         <f t="shared" si="108"/>
-        <v>115.30802534772572</v>
+        <v>94.074146554088557</v>
       </c>
     </row>
     <row r="64" spans="2:47" x14ac:dyDescent="0.3">
@@ -6378,13 +6362,13 @@
         <v>25.8</v>
       </c>
       <c r="Z64" s="6">
-        <v>25</v>
+        <v>33.200000000000003</v>
       </c>
       <c r="AA64" s="6">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="AB64" s="6">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="AI64" s="6">
         <f t="shared" si="105"/>
@@ -6396,47 +6380,47 @@
       </c>
       <c r="AK64" s="6">
         <f t="shared" si="107"/>
-        <v>101.8</v>
+        <v>125</v>
       </c>
       <c r="AL64" s="6">
         <f t="shared" ref="AL64:AU64" si="109">AK64*1.01</f>
-        <v>102.818</v>
+        <v>126.25</v>
       </c>
       <c r="AM64" s="6">
         <f t="shared" si="109"/>
-        <v>103.84618</v>
+        <v>127.5125</v>
       </c>
       <c r="AN64" s="6">
         <f t="shared" si="109"/>
-        <v>104.88464180000001</v>
+        <v>128.78762499999999</v>
       </c>
       <c r="AO64" s="6">
         <f t="shared" si="109"/>
-        <v>105.93348821800001</v>
+        <v>130.07550125</v>
       </c>
       <c r="AP64" s="6">
         <f t="shared" si="109"/>
-        <v>106.99282310018</v>
+        <v>131.37625626249999</v>
       </c>
       <c r="AQ64" s="6">
         <f t="shared" si="109"/>
-        <v>108.0627513311818</v>
+        <v>132.69001882512498</v>
       </c>
       <c r="AR64" s="6">
         <f t="shared" si="109"/>
-        <v>109.14337884449363</v>
+        <v>134.01691901337622</v>
       </c>
       <c r="AS64" s="6">
         <f t="shared" si="109"/>
-        <v>110.23481263293856</v>
+        <v>135.35708820350999</v>
       </c>
       <c r="AT64" s="6">
         <f t="shared" si="109"/>
-        <v>111.33716075926795</v>
+        <v>136.7106590855451</v>
       </c>
       <c r="AU64" s="6">
         <f t="shared" si="109"/>
-        <v>112.45053236686063</v>
+        <v>138.07776567640056</v>
       </c>
     </row>
     <row r="65" spans="2:47" x14ac:dyDescent="0.3">
@@ -6474,12 +6458,11 @@
         <v>379.5</v>
       </c>
       <c r="Z65" s="6">
-        <f>V65*1.1</f>
-        <v>391.6</v>
+        <v>404.2</v>
       </c>
       <c r="AA65" s="6">
-        <f>W65*1.1</f>
-        <v>399.63000000000005</v>
+        <f>W65*1.12</f>
+        <v>406.89600000000007</v>
       </c>
       <c r="AB65" s="6">
         <f>X65*1.1</f>
@@ -6495,47 +6478,47 @@
       </c>
       <c r="AK65" s="6">
         <f t="shared" si="107"/>
-        <v>1641.64</v>
+        <v>1661.5060000000001</v>
       </c>
       <c r="AL65" s="6">
         <f>AK65*1.05</f>
-        <v>1723.7220000000002</v>
+        <v>1744.5813000000001</v>
       </c>
       <c r="AM65" s="6">
         <f>AL65*0.9</f>
-        <v>1551.3498000000002</v>
+        <v>1570.1231700000001</v>
       </c>
       <c r="AN65" s="6">
         <f t="shared" ref="AN65:AU65" si="110">AM65*0.9</f>
-        <v>1396.2148200000001</v>
+        <v>1413.1108530000001</v>
       </c>
       <c r="AO65" s="6">
         <f t="shared" si="110"/>
-        <v>1256.5933380000001</v>
+        <v>1271.7997677000001</v>
       </c>
       <c r="AP65" s="6">
         <f t="shared" si="110"/>
-        <v>1130.9340042000001</v>
+        <v>1144.6197909300001</v>
       </c>
       <c r="AQ65" s="6">
         <f t="shared" si="110"/>
-        <v>1017.8406037800002</v>
+        <v>1030.1578118370001</v>
       </c>
       <c r="AR65" s="6">
         <f t="shared" si="110"/>
-        <v>916.0565434020001</v>
+        <v>927.14203065330003</v>
       </c>
       <c r="AS65" s="6">
         <f t="shared" si="110"/>
-        <v>824.45088906180013</v>
+        <v>834.42782758797</v>
       </c>
       <c r="AT65" s="6">
         <f t="shared" si="110"/>
-        <v>742.00580015562014</v>
+        <v>750.98504482917303</v>
       </c>
       <c r="AU65" s="6">
         <f t="shared" si="110"/>
-        <v>667.80522014005817</v>
+        <v>675.88654034625574</v>
       </c>
     </row>
     <row r="66" spans="2:47" x14ac:dyDescent="0.3">
@@ -6573,7 +6556,7 @@
         <v>-7.7</v>
       </c>
       <c r="Z66" s="6">
-        <v>-10</v>
+        <v>-5.7</v>
       </c>
       <c r="AA66" s="6">
         <v>-10</v>
@@ -6591,47 +6574,47 @@
       </c>
       <c r="AK66" s="6">
         <f t="shared" si="107"/>
-        <v>-37.700000000000003</v>
+        <v>-33.4</v>
       </c>
       <c r="AL66" s="6">
         <f>AK66*1.02</f>
-        <v>-38.454000000000001</v>
+        <v>-34.067999999999998</v>
       </c>
       <c r="AM66" s="6">
         <f t="shared" ref="AM66:AU66" si="111">AL66*1.02</f>
-        <v>-39.223080000000003</v>
+        <v>-34.749359999999996</v>
       </c>
       <c r="AN66" s="6">
         <f t="shared" si="111"/>
-        <v>-40.007541600000003</v>
+        <v>-35.444347199999996</v>
       </c>
       <c r="AO66" s="6">
         <f t="shared" si="111"/>
-        <v>-40.807692432000003</v>
+        <v>-36.153234143999995</v>
       </c>
       <c r="AP66" s="6">
         <f t="shared" si="111"/>
-        <v>-41.623846280640002</v>
+        <v>-36.876298826879996</v>
       </c>
       <c r="AQ66" s="6">
         <f t="shared" si="111"/>
-        <v>-42.456323206252804</v>
+        <v>-37.613824803417593</v>
       </c>
       <c r="AR66" s="6">
         <f t="shared" si="111"/>
-        <v>-43.305449670377861</v>
+        <v>-38.366101299485948</v>
       </c>
       <c r="AS66" s="6">
         <f t="shared" si="111"/>
-        <v>-44.171558663785419</v>
+        <v>-39.133423325475668</v>
       </c>
       <c r="AT66" s="6">
         <f t="shared" si="111"/>
-        <v>-45.054989837061129</v>
+        <v>-39.916091791985181</v>
       </c>
       <c r="AU66" s="6">
         <f t="shared" si="111"/>
-        <v>-45.95608963380235</v>
+        <v>-40.714413627824882</v>
       </c>
     </row>
     <row r="67" spans="2:47" x14ac:dyDescent="0.3">
@@ -6669,7 +6652,7 @@
         <v>29.7</v>
       </c>
       <c r="Z67" s="6">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AA67" s="6">
         <v>0</v>
@@ -6687,7 +6670,7 @@
       </c>
       <c r="AK67" s="6">
         <f t="shared" si="107"/>
-        <v>29.7</v>
+        <v>35.299999999999997</v>
       </c>
       <c r="AL67" s="6">
         <f>0</f>
@@ -6765,7 +6748,7 @@
         <v>2.1</v>
       </c>
       <c r="Z68" s="6">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA68" s="6">
         <v>0</v>
@@ -6783,1071 +6766,1028 @@
       </c>
       <c r="AK68" s="6">
         <f t="shared" si="107"/>
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="AL68" s="6">
         <f t="shared" ref="AL68:AU68" si="112">AK68*1.2</f>
-        <v>2.52</v>
+        <v>5.04</v>
       </c>
       <c r="AM68" s="6">
         <f t="shared" si="112"/>
-        <v>3.024</v>
+        <v>6.048</v>
       </c>
       <c r="AN68" s="6">
         <f t="shared" si="112"/>
-        <v>3.6288</v>
+        <v>7.2576000000000001</v>
       </c>
       <c r="AO68" s="6">
         <f t="shared" si="112"/>
-        <v>4.3545600000000002</v>
+        <v>8.7091200000000004</v>
       </c>
       <c r="AP68" s="6">
         <f t="shared" si="112"/>
-        <v>5.2254719999999999</v>
+        <v>10.450944</v>
       </c>
       <c r="AQ68" s="6">
         <f t="shared" si="112"/>
-        <v>6.2705663999999999</v>
+        <v>12.5411328</v>
       </c>
       <c r="AR68" s="6">
         <f t="shared" si="112"/>
-        <v>7.5246796799999993</v>
+        <v>15.049359359999999</v>
       </c>
       <c r="AS68" s="6">
         <f t="shared" si="112"/>
-        <v>9.0296156159999992</v>
+        <v>18.059231231999998</v>
       </c>
       <c r="AT68" s="6">
         <f t="shared" si="112"/>
-        <v>10.835538739199999</v>
+        <v>21.671077478399997</v>
       </c>
       <c r="AU68" s="6">
         <f t="shared" si="112"/>
-        <v>13.002646487039998</v>
+        <v>26.005292974079996</v>
       </c>
     </row>
     <row r="69" spans="2:47" x14ac:dyDescent="0.3">
       <c r="B69" t="s">
+        <v>104</v>
+      </c>
+      <c r="P69" s="6"/>
+      <c r="Q69" s="6"/>
+      <c r="R69" s="6"/>
+      <c r="S69" s="6"/>
+      <c r="T69" s="6"/>
+      <c r="U69" s="6"/>
+      <c r="V69" s="6"/>
+      <c r="W69" s="6"/>
+      <c r="X69" s="6"/>
+      <c r="Y69" s="6"/>
+      <c r="Z69" s="6">
+        <v>2.1</v>
+      </c>
+      <c r="AA69" s="6"/>
+      <c r="AB69" s="6"/>
+      <c r="AI69" s="6"/>
+      <c r="AJ69" s="6"/>
+      <c r="AK69" s="6"/>
+      <c r="AL69" s="6"/>
+      <c r="AM69" s="6"/>
+      <c r="AN69" s="6"/>
+      <c r="AO69" s="6"/>
+      <c r="AP69" s="6"/>
+      <c r="AQ69" s="6"/>
+      <c r="AR69" s="6"/>
+      <c r="AS69" s="6"/>
+      <c r="AT69" s="6"/>
+      <c r="AU69" s="6"/>
+    </row>
+    <row r="70" spans="2:47" x14ac:dyDescent="0.3">
+      <c r="B70" t="s">
         <v>27</v>
       </c>
-      <c r="P69" s="6">
+      <c r="P70" s="6">
         <v>-1.4</v>
       </c>
-      <c r="Q69" s="6">
+      <c r="Q70" s="6">
         <v>-8.9</v>
       </c>
-      <c r="R69" s="6">
+      <c r="R70" s="6">
         <v>-4</v>
       </c>
-      <c r="S69" s="6">
+      <c r="S70" s="6">
         <v>-0.2</v>
       </c>
-      <c r="T69" s="6">
+      <c r="T70" s="6">
         <v>-13.7</v>
       </c>
-      <c r="U69" s="6">
-        <v>0</v>
-      </c>
-      <c r="V69" s="6">
+      <c r="U70" s="6">
+        <v>0</v>
+      </c>
+      <c r="V70" s="6">
         <v>0.1</v>
       </c>
-      <c r="W69" s="6">
+      <c r="W70" s="6">
         <v>-0.6</v>
       </c>
-      <c r="X69" s="6">
+      <c r="X70" s="6">
         <v>-7.1</v>
       </c>
-      <c r="Y69" s="6">
+      <c r="Y70" s="6">
         <v>106.5</v>
       </c>
-      <c r="Z69" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA69" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB69" s="6">
-        <v>0</v>
-      </c>
-      <c r="AI69" s="6">
+      <c r="Z70" s="6">
+        <v>-3.4</v>
+      </c>
+      <c r="AA70" s="6">
+        <v>0</v>
+      </c>
+      <c r="AB70" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI70" s="6">
         <f t="shared" si="105"/>
         <v>-26.799999999999997</v>
       </c>
-      <c r="AJ69" s="6">
+      <c r="AJ70" s="6">
         <f t="shared" si="106"/>
         <v>-7.6</v>
       </c>
-      <c r="AK69" s="6">
+      <c r="AK70" s="6">
         <f t="shared" si="107"/>
-        <v>106.5</v>
-      </c>
-      <c r="AL69" s="6">
-        <f t="shared" ref="AL69:AR69" si="113">AK69*1.5</f>
-        <v>159.75</v>
-      </c>
-      <c r="AM69" s="6">
-        <f t="shared" si="113"/>
-        <v>239.625</v>
-      </c>
-      <c r="AN69" s="6">
-        <f>AM69*1.02</f>
-        <v>244.41750000000002</v>
-      </c>
-      <c r="AO69" s="6">
-        <f t="shared" ref="AO69:AU69" si="114">AN69*1.02</f>
-        <v>249.30585000000002</v>
-      </c>
-      <c r="AP69" s="6">
-        <f t="shared" si="114"/>
-        <v>254.29196700000003</v>
-      </c>
-      <c r="AQ69" s="6">
-        <f t="shared" si="114"/>
-        <v>259.37780634000001</v>
-      </c>
-      <c r="AR69" s="6">
-        <f t="shared" si="114"/>
-        <v>264.56536246680002</v>
-      </c>
-      <c r="AS69" s="6">
-        <f t="shared" si="114"/>
-        <v>269.85666971613603</v>
-      </c>
-      <c r="AT69" s="6">
-        <f t="shared" si="114"/>
-        <v>275.25380311045876</v>
-      </c>
-      <c r="AU69" s="6">
-        <f t="shared" si="114"/>
-        <v>280.75887917266795</v>
-      </c>
-    </row>
-    <row r="70" spans="2:47" x14ac:dyDescent="0.3">
-      <c r="B70" t="s">
+        <v>103.1</v>
+      </c>
+      <c r="AL70" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM70" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN70" s="6">
+        <v>0</v>
+      </c>
+      <c r="AO70" s="6">
+        <v>0</v>
+      </c>
+      <c r="AP70" s="6">
+        <v>0</v>
+      </c>
+      <c r="AQ70" s="6">
+        <v>0</v>
+      </c>
+      <c r="AR70" s="6">
+        <v>0</v>
+      </c>
+      <c r="AS70" s="6">
+        <v>0</v>
+      </c>
+      <c r="AT70" s="6">
+        <v>0</v>
+      </c>
+      <c r="AU70" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:47" x14ac:dyDescent="0.3">
+      <c r="B71" t="s">
         <v>92</v>
       </c>
-      <c r="P70" s="6">
+      <c r="P71" s="6">
         <v>0.9</v>
       </c>
-      <c r="Q70" s="6">
+      <c r="Q71" s="6">
         <v>10</v>
       </c>
-      <c r="R70" s="6">
+      <c r="R71" s="6">
         <v>1.8</v>
       </c>
-      <c r="S70" s="6">
+      <c r="S71" s="6">
         <v>2.5</v>
       </c>
-      <c r="T70" s="6">
+      <c r="T71" s="6">
         <v>0.6</v>
       </c>
-      <c r="U70" s="6">
+      <c r="U71" s="6">
         <v>0.7</v>
       </c>
-      <c r="V70" s="6">
+      <c r="V71" s="6">
         <v>1.2</v>
       </c>
-      <c r="W70" s="6">
+      <c r="W71" s="6">
         <v>3</v>
       </c>
-      <c r="X70" s="6">
+      <c r="X71" s="6">
         <v>2.5</v>
       </c>
-      <c r="Y70" s="6">
+      <c r="Y71" s="6">
         <v>-5.2</v>
       </c>
-      <c r="Z70" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA70" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB70" s="6">
-        <v>0</v>
-      </c>
-      <c r="AI70" s="6">
+      <c r="Z71" s="6">
+        <v>1.7</v>
+      </c>
+      <c r="AA71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AB71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI71" s="6">
         <f t="shared" si="105"/>
         <v>14.9</v>
       </c>
-      <c r="AJ70" s="6">
+      <c r="AJ71" s="6">
         <f t="shared" si="106"/>
         <v>7.4</v>
       </c>
-      <c r="AK70" s="6">
+      <c r="AK71" s="6">
         <f t="shared" si="107"/>
-        <v>-5.2</v>
-      </c>
-      <c r="AL70" s="6">
-        <v>0</v>
-      </c>
-      <c r="AM70" s="6">
-        <v>0</v>
-      </c>
-      <c r="AN70" s="6">
-        <v>0</v>
-      </c>
-      <c r="AO70" s="6">
-        <v>0</v>
-      </c>
-      <c r="AP70" s="6">
-        <v>0</v>
-      </c>
-      <c r="AQ70" s="6">
-        <v>0</v>
-      </c>
-      <c r="AR70" s="6">
-        <v>0</v>
-      </c>
-      <c r="AS70" s="6">
-        <v>0</v>
-      </c>
-      <c r="AT70" s="6">
-        <v>0</v>
-      </c>
-      <c r="AU70" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="2:47" x14ac:dyDescent="0.3">
-      <c r="B71" t="s">
+        <v>-3.5</v>
+      </c>
+      <c r="AL71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AO71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AP71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AQ71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AR71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AS71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AT71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AU71" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:47" x14ac:dyDescent="0.3">
+      <c r="B72" t="s">
         <v>66</v>
       </c>
-      <c r="P71" s="6">
+      <c r="P72" s="6">
         <v>-317.7</v>
       </c>
-      <c r="Q71" s="6">
+      <c r="Q72" s="6">
         <v>362.9</v>
       </c>
-      <c r="R71" s="6">
+      <c r="R72" s="6">
         <v>-53.1</v>
       </c>
-      <c r="S71" s="6">
+      <c r="S72" s="6">
         <v>-104.7</v>
       </c>
-      <c r="T71" s="6">
+      <c r="T72" s="6">
         <v>-417.2</v>
       </c>
-      <c r="U71" s="6">
+      <c r="U72" s="6">
         <v>579.29999999999995</v>
       </c>
-      <c r="V71" s="6">
+      <c r="V72" s="6">
         <v>-87.1</v>
       </c>
-      <c r="W71" s="6">
+      <c r="W72" s="6">
         <v>-163.5</v>
       </c>
-      <c r="X71" s="6">
+      <c r="X72" s="6">
         <v>-328.2</v>
       </c>
-      <c r="Y71" s="6">
+      <c r="Y72" s="6">
         <v>393.7</v>
       </c>
-      <c r="Z71" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA71" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB71" s="6">
-        <v>0</v>
-      </c>
-      <c r="AI71" s="6">
+      <c r="Z72" s="6">
+        <v>-117.6</v>
+      </c>
+      <c r="AA72" s="6">
+        <v>0</v>
+      </c>
+      <c r="AB72" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI72" s="6">
         <f t="shared" si="105"/>
         <v>-212.10000000000002</v>
       </c>
-      <c r="AJ71" s="6">
+      <c r="AJ72" s="6">
         <f t="shared" si="106"/>
         <v>0.49999999999994316</v>
       </c>
-      <c r="AK71" s="6">
+      <c r="AK72" s="6">
         <f t="shared" si="107"/>
-        <v>393.7</v>
-      </c>
-      <c r="AL71" s="6">
-        <v>0</v>
-      </c>
-      <c r="AM71" s="6">
-        <v>0</v>
-      </c>
-      <c r="AN71" s="6">
-        <v>0</v>
-      </c>
-      <c r="AO71" s="6">
-        <v>0</v>
-      </c>
-      <c r="AP71" s="6">
-        <v>0</v>
-      </c>
-      <c r="AQ71" s="6">
-        <v>0</v>
-      </c>
-      <c r="AR71" s="6">
-        <v>0</v>
-      </c>
-      <c r="AS71" s="6">
-        <v>0</v>
-      </c>
-      <c r="AT71" s="6">
-        <v>0</v>
-      </c>
-      <c r="AU71" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="2:47" x14ac:dyDescent="0.3">
-      <c r="B72" t="s">
+        <v>276.10000000000002</v>
+      </c>
+      <c r="AL72" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM72" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN72" s="6">
+        <v>0</v>
+      </c>
+      <c r="AO72" s="6">
+        <v>0</v>
+      </c>
+      <c r="AP72" s="6">
+        <v>0</v>
+      </c>
+      <c r="AQ72" s="6">
+        <v>0</v>
+      </c>
+      <c r="AR72" s="6">
+        <v>0</v>
+      </c>
+      <c r="AS72" s="6">
+        <v>0</v>
+      </c>
+      <c r="AT72" s="6">
+        <v>0</v>
+      </c>
+      <c r="AU72" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:47" x14ac:dyDescent="0.3">
+      <c r="B73" t="s">
         <v>67</v>
       </c>
-      <c r="P72" s="6">
+      <c r="P73" s="6">
         <v>-31.5</v>
       </c>
-      <c r="Q72" s="6">
+      <c r="Q73" s="6">
         <v>-16.399999999999999</v>
       </c>
-      <c r="R72" s="6">
+      <c r="R73" s="6">
         <v>-24.6</v>
       </c>
-      <c r="S72" s="6">
+      <c r="S73" s="6">
         <v>-25.5</v>
       </c>
-      <c r="T72" s="6">
+      <c r="T73" s="6">
         <v>-68.3</v>
       </c>
-      <c r="U72" s="6">
+      <c r="U73" s="6">
         <v>-14.9</v>
       </c>
-      <c r="V72" s="6">
+      <c r="V73" s="6">
         <v>-21.8</v>
       </c>
-      <c r="W72" s="6">
+      <c r="W73" s="6">
         <v>-26</v>
       </c>
-      <c r="X72" s="6">
+      <c r="X73" s="6">
         <v>-38.799999999999997</v>
       </c>
-      <c r="Y72" s="6">
+      <c r="Y73" s="6">
         <v>-31.1</v>
       </c>
-      <c r="Z72" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA72" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB72" s="6">
-        <v>0</v>
-      </c>
-      <c r="AI72" s="6">
+      <c r="Z73" s="6">
+        <v>-53.8</v>
+      </c>
+      <c r="AA73" s="6">
+        <v>0</v>
+      </c>
+      <c r="AB73" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI73" s="6">
         <f t="shared" si="105"/>
         <v>-134.80000000000001</v>
       </c>
-      <c r="AJ72" s="6">
+      <c r="AJ73" s="6">
         <f t="shared" si="106"/>
         <v>-101.5</v>
       </c>
-      <c r="AK72" s="6">
+      <c r="AK73" s="6">
         <f t="shared" si="107"/>
-        <v>-31.1</v>
-      </c>
-      <c r="AL72" s="6">
-        <v>0</v>
-      </c>
-      <c r="AM72" s="6">
-        <v>0</v>
-      </c>
-      <c r="AN72" s="6">
-        <v>0</v>
-      </c>
-      <c r="AO72" s="6">
-        <v>0</v>
-      </c>
-      <c r="AP72" s="6">
-        <v>0</v>
-      </c>
-      <c r="AQ72" s="6">
-        <v>0</v>
-      </c>
-      <c r="AR72" s="6">
-        <v>0</v>
-      </c>
-      <c r="AS72" s="6">
-        <v>0</v>
-      </c>
-      <c r="AT72" s="6">
-        <v>0</v>
-      </c>
-      <c r="AU72" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="2:47" x14ac:dyDescent="0.3">
-      <c r="B73" t="s">
+        <v>-84.9</v>
+      </c>
+      <c r="AL73" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM73" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN73" s="6">
+        <v>0</v>
+      </c>
+      <c r="AO73" s="6">
+        <v>0</v>
+      </c>
+      <c r="AP73" s="6">
+        <v>0</v>
+      </c>
+      <c r="AQ73" s="6">
+        <v>0</v>
+      </c>
+      <c r="AR73" s="6">
+        <v>0</v>
+      </c>
+      <c r="AS73" s="6">
+        <v>0</v>
+      </c>
+      <c r="AT73" s="6">
+        <v>0</v>
+      </c>
+      <c r="AU73" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:47" x14ac:dyDescent="0.3">
+      <c r="B74" t="s">
         <v>68</v>
       </c>
-      <c r="P73" s="6">
+      <c r="P74" s="6">
         <v>-16.100000000000001</v>
       </c>
-      <c r="Q73" s="6">
+      <c r="Q74" s="6">
         <v>5.5</v>
       </c>
-      <c r="R73" s="6">
+      <c r="R74" s="6">
         <v>41.4</v>
       </c>
-      <c r="S73" s="6">
+      <c r="S74" s="6">
         <v>4.7</v>
       </c>
-      <c r="T73" s="6">
+      <c r="T74" s="6">
         <v>8.1999999999999993</v>
       </c>
-      <c r="U73" s="6">
+      <c r="U74" s="6">
         <v>-1.1000000000000001</v>
       </c>
-      <c r="V73" s="6">
+      <c r="V74" s="6">
         <v>34.5</v>
       </c>
-      <c r="W73" s="6">
+      <c r="W74" s="6">
         <v>9.1</v>
       </c>
-      <c r="X73" s="6">
+      <c r="X74" s="6">
         <v>-12.6</v>
       </c>
-      <c r="Y73" s="6">
+      <c r="Y74" s="6">
         <v>-17.899999999999999</v>
       </c>
-      <c r="Z73" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA73" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB73" s="6">
-        <v>0</v>
-      </c>
-      <c r="AI73" s="6">
+      <c r="Z74" s="6">
+        <v>-4.5</v>
+      </c>
+      <c r="AA74" s="6">
+        <v>0</v>
+      </c>
+      <c r="AB74" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI74" s="6">
         <f t="shared" si="105"/>
         <v>59.8</v>
       </c>
-      <c r="AJ73" s="6">
+      <c r="AJ74" s="6">
         <f t="shared" si="106"/>
         <v>29.9</v>
       </c>
-      <c r="AK73" s="6">
+      <c r="AK74" s="6">
         <f t="shared" si="107"/>
-        <v>-17.899999999999999</v>
-      </c>
-      <c r="AL73" s="6">
-        <v>0</v>
-      </c>
-      <c r="AM73" s="6">
-        <v>0</v>
-      </c>
-      <c r="AN73" s="6">
-        <v>0</v>
-      </c>
-      <c r="AO73" s="6">
-        <v>0</v>
-      </c>
-      <c r="AP73" s="6">
-        <v>0</v>
-      </c>
-      <c r="AQ73" s="6">
-        <v>0</v>
-      </c>
-      <c r="AR73" s="6">
-        <v>0</v>
-      </c>
-      <c r="AS73" s="6">
-        <v>0</v>
-      </c>
-      <c r="AT73" s="6">
-        <v>0</v>
-      </c>
-      <c r="AU73" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="2:47" x14ac:dyDescent="0.3">
-      <c r="B74" t="s">
+        <v>-22.4</v>
+      </c>
+      <c r="AL74" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM74" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN74" s="6">
+        <v>0</v>
+      </c>
+      <c r="AO74" s="6">
+        <v>0</v>
+      </c>
+      <c r="AP74" s="6">
+        <v>0</v>
+      </c>
+      <c r="AQ74" s="6">
+        <v>0</v>
+      </c>
+      <c r="AR74" s="6">
+        <v>0</v>
+      </c>
+      <c r="AS74" s="6">
+        <v>0</v>
+      </c>
+      <c r="AT74" s="6">
+        <v>0</v>
+      </c>
+      <c r="AU74" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:47" x14ac:dyDescent="0.3">
+      <c r="B75" t="s">
         <v>78</v>
       </c>
-      <c r="P74" s="6">
+      <c r="P75" s="6">
         <v>-2.2999999999999998</v>
       </c>
-      <c r="Q74" s="6">
+      <c r="Q75" s="6">
         <v>-3.1</v>
       </c>
-      <c r="R74" s="6">
+      <c r="R75" s="6">
         <v>20.6</v>
       </c>
-      <c r="S74" s="6">
+      <c r="S75" s="6">
         <v>34.200000000000003</v>
       </c>
-      <c r="T74" s="6">
+      <c r="T75" s="6">
         <v>-32.5</v>
       </c>
-      <c r="U74" s="6">
+      <c r="U75" s="6">
         <v>21.2</v>
       </c>
-      <c r="V74" s="6">
+      <c r="V75" s="6">
         <v>70.2</v>
       </c>
-      <c r="W74" s="6">
+      <c r="W75" s="6">
         <v>11.3</v>
       </c>
-      <c r="X74" s="6">
+      <c r="X75" s="6">
         <v>6.1</v>
       </c>
-      <c r="Y74" s="6">
+      <c r="Y75" s="6">
         <v>-4.4000000000000004</v>
       </c>
-      <c r="Z74" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA74" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB74" s="6">
-        <v>0</v>
-      </c>
-      <c r="AI74" s="6">
+      <c r="Z75" s="6">
+        <v>11.8</v>
+      </c>
+      <c r="AA75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AB75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI75" s="6">
         <f t="shared" si="105"/>
         <v>19.200000000000003</v>
       </c>
-      <c r="AJ74" s="6">
+      <c r="AJ75" s="6">
         <f t="shared" si="106"/>
         <v>108.8</v>
       </c>
-      <c r="AK74" s="6">
+      <c r="AK75" s="6">
         <f t="shared" si="107"/>
-        <v>-4.4000000000000004</v>
-      </c>
-      <c r="AL74" s="6">
-        <v>0</v>
-      </c>
-      <c r="AM74" s="6">
-        <v>0</v>
-      </c>
-      <c r="AN74" s="6">
-        <v>0</v>
-      </c>
-      <c r="AO74" s="6">
-        <v>0</v>
-      </c>
-      <c r="AP74" s="6">
-        <v>0</v>
-      </c>
-      <c r="AQ74" s="6">
-        <v>0</v>
-      </c>
-      <c r="AR74" s="6">
-        <v>0</v>
-      </c>
-      <c r="AS74" s="6">
-        <v>0</v>
-      </c>
-      <c r="AT74" s="6">
-        <v>0</v>
-      </c>
-      <c r="AU74" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="2:47" x14ac:dyDescent="0.3">
-      <c r="B75" t="s">
+        <v>7.4</v>
+      </c>
+      <c r="AL75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AO75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AP75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AQ75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AR75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AS75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AT75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AU75" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:47" x14ac:dyDescent="0.3">
+      <c r="B76" t="s">
         <v>79</v>
       </c>
-      <c r="P75" s="6">
+      <c r="P76" s="6">
         <v>46.8</v>
       </c>
-      <c r="Q75" s="6">
+      <c r="Q76" s="6">
         <v>-8.5</v>
       </c>
-      <c r="R75" s="6">
+      <c r="R76" s="6">
         <v>35.6</v>
       </c>
-      <c r="S75" s="6">
+      <c r="S76" s="6">
         <v>6.6</v>
       </c>
-      <c r="T75" s="6">
+      <c r="T76" s="6">
         <v>137.30000000000001</v>
       </c>
-      <c r="U75" s="6">
+      <c r="U76" s="6">
         <v>-54.7</v>
       </c>
-      <c r="V75" s="6">
+      <c r="V76" s="6">
         <v>59.3</v>
       </c>
-      <c r="W75" s="6">
+      <c r="W76" s="6">
         <v>34.1</v>
       </c>
-      <c r="X75" s="6">
+      <c r="X76" s="6">
         <v>32.200000000000003</v>
       </c>
-      <c r="Y75" s="6">
+      <c r="Y76" s="6">
         <v>3.9</v>
       </c>
-      <c r="Z75" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA75" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB75" s="6">
-        <v>0</v>
-      </c>
-      <c r="AI75" s="6">
+      <c r="Z76" s="6">
+        <v>93.3</v>
+      </c>
+      <c r="AA76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AB76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI76" s="6">
         <f t="shared" si="105"/>
         <v>171</v>
       </c>
-      <c r="AJ75" s="6">
+      <c r="AJ76" s="6">
         <f t="shared" si="106"/>
         <v>70.900000000000006</v>
       </c>
-      <c r="AK75" s="6">
+      <c r="AK76" s="6">
         <f t="shared" si="107"/>
-        <v>3.9</v>
-      </c>
-      <c r="AL75" s="6">
-        <v>0</v>
-      </c>
-      <c r="AM75" s="6">
-        <v>0</v>
-      </c>
-      <c r="AN75" s="6">
-        <v>0</v>
-      </c>
-      <c r="AO75" s="6">
-        <v>0</v>
-      </c>
-      <c r="AP75" s="6">
-        <v>0</v>
-      </c>
-      <c r="AQ75" s="6">
-        <v>0</v>
-      </c>
-      <c r="AR75" s="6">
-        <v>0</v>
-      </c>
-      <c r="AS75" s="6">
-        <v>0</v>
-      </c>
-      <c r="AT75" s="6">
-        <v>0</v>
-      </c>
-      <c r="AU75" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="2:47" x14ac:dyDescent="0.3">
-      <c r="B76" t="s">
+        <v>97.2</v>
+      </c>
+      <c r="AL76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AO76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AP76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AQ76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AR76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AS76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AT76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AU76" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:47" x14ac:dyDescent="0.3">
+      <c r="B77" t="s">
         <v>71</v>
       </c>
-      <c r="P76" s="6">
+      <c r="P77" s="6">
         <v>-13.2</v>
       </c>
-      <c r="Q76" s="6">
+      <c r="Q77" s="6">
         <v>-10.8</v>
       </c>
-      <c r="R76" s="6">
+      <c r="R77" s="6">
         <v>-5.3</v>
       </c>
-      <c r="S76" s="6">
+      <c r="S77" s="6">
         <v>-12.7</v>
       </c>
-      <c r="T76" s="6">
+      <c r="T77" s="6">
         <v>-11.8</v>
       </c>
-      <c r="U76" s="6">
+      <c r="U77" s="6">
         <v>-13.4</v>
       </c>
-      <c r="V76" s="6">
+      <c r="V77" s="6">
         <v>-11.9</v>
       </c>
-      <c r="W76" s="6">
+      <c r="W77" s="6">
         <v>-9.1</v>
       </c>
-      <c r="X76" s="6">
+      <c r="X77" s="6">
         <v>-12.4</v>
       </c>
-      <c r="Y76" s="6">
+      <c r="Y77" s="6">
         <v>-11.8</v>
       </c>
-      <c r="Z76" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA76" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB76" s="6">
-        <v>0</v>
-      </c>
-      <c r="AI76" s="6">
+      <c r="Z77" s="6">
+        <v>-14.6</v>
+      </c>
+      <c r="AA77" s="6">
+        <v>0</v>
+      </c>
+      <c r="AB77" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI77" s="6">
         <f t="shared" si="105"/>
         <v>-40.6</v>
       </c>
-      <c r="AJ76" s="6">
+      <c r="AJ77" s="6">
         <f t="shared" si="106"/>
         <v>-46.8</v>
       </c>
-      <c r="AK76" s="6">
+      <c r="AK77" s="6">
         <f t="shared" si="107"/>
-        <v>-11.8</v>
-      </c>
-      <c r="AL76" s="6">
-        <v>0</v>
-      </c>
-      <c r="AM76" s="6">
-        <f t="shared" ref="AL76:AU76" si="115">AL76*1.05</f>
-        <v>0</v>
-      </c>
-      <c r="AN76" s="6">
-        <f t="shared" si="115"/>
-        <v>0</v>
-      </c>
-      <c r="AO76" s="6">
-        <f t="shared" si="115"/>
-        <v>0</v>
-      </c>
-      <c r="AP76" s="6">
-        <f t="shared" si="115"/>
-        <v>0</v>
-      </c>
-      <c r="AQ76" s="6">
-        <f t="shared" si="115"/>
-        <v>0</v>
-      </c>
-      <c r="AR76" s="6">
-        <f t="shared" si="115"/>
-        <v>0</v>
-      </c>
-      <c r="AS76" s="6">
-        <f t="shared" si="115"/>
-        <v>0</v>
-      </c>
-      <c r="AT76" s="6">
-        <f t="shared" si="115"/>
-        <v>0</v>
-      </c>
-      <c r="AU76" s="6">
-        <f t="shared" si="115"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="2:47" x14ac:dyDescent="0.3">
-      <c r="B77" t="s">
+        <v>-26.4</v>
+      </c>
+      <c r="AL77" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM77" s="6">
+        <f t="shared" ref="AM77:AU77" si="113">AL77*1.05</f>
+        <v>0</v>
+      </c>
+      <c r="AN77" s="6">
+        <f t="shared" si="113"/>
+        <v>0</v>
+      </c>
+      <c r="AO77" s="6">
+        <f t="shared" si="113"/>
+        <v>0</v>
+      </c>
+      <c r="AP77" s="6">
+        <f t="shared" si="113"/>
+        <v>0</v>
+      </c>
+      <c r="AQ77" s="6">
+        <f t="shared" si="113"/>
+        <v>0</v>
+      </c>
+      <c r="AR77" s="6">
+        <f t="shared" si="113"/>
+        <v>0</v>
+      </c>
+      <c r="AS77" s="6">
+        <f t="shared" si="113"/>
+        <v>0</v>
+      </c>
+      <c r="AT77" s="6">
+        <f t="shared" si="113"/>
+        <v>0</v>
+      </c>
+      <c r="AU77" s="6">
+        <f t="shared" si="113"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="2:47" x14ac:dyDescent="0.3">
+      <c r="B78" t="s">
         <v>67</v>
       </c>
-      <c r="P77" s="6">
+      <c r="P78" s="6">
         <v>467.4</v>
       </c>
-      <c r="Q77" s="6">
+      <c r="Q78" s="6">
         <v>-110.5</v>
       </c>
-      <c r="R77" s="6">
+      <c r="R78" s="6">
         <v>-39</v>
       </c>
-      <c r="S77" s="6">
+      <c r="S78" s="6">
         <v>82.1</v>
       </c>
-      <c r="T77" s="6">
+      <c r="T78" s="6">
         <v>595.4</v>
       </c>
-      <c r="U77" s="6">
+      <c r="U78" s="6">
         <v>-261.2</v>
       </c>
-      <c r="V77" s="6">
+      <c r="V78" s="6">
         <v>-88.3</v>
       </c>
-      <c r="W77" s="6">
+      <c r="W78" s="6">
         <v>122.8</v>
       </c>
-      <c r="X77" s="6">
+      <c r="X78" s="6">
         <v>609.4</v>
       </c>
-      <c r="Y77" s="6">
+      <c r="Y78" s="6">
         <v>-271.39999999999998</v>
       </c>
-      <c r="Z77" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA77" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB77" s="6">
-        <v>0</v>
-      </c>
-      <c r="AI77" s="6">
+      <c r="Z78" s="6">
+        <v>-52.5</v>
+      </c>
+      <c r="AA78" s="6">
+        <v>0</v>
+      </c>
+      <c r="AB78" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI78" s="6">
         <f t="shared" si="105"/>
         <v>528</v>
       </c>
-      <c r="AJ77" s="6">
+      <c r="AJ78" s="6">
         <f t="shared" si="106"/>
         <v>382.7</v>
       </c>
-      <c r="AK77" s="6">
+      <c r="AK78" s="6">
         <f t="shared" si="107"/>
-        <v>-271.39999999999998</v>
-      </c>
-      <c r="AL77" s="6">
-        <v>0</v>
-      </c>
-      <c r="AM77" s="6">
-        <v>0</v>
-      </c>
-      <c r="AN77" s="6">
-        <v>0</v>
-      </c>
-      <c r="AO77" s="6">
-        <v>0</v>
-      </c>
-      <c r="AP77" s="6">
-        <v>0</v>
-      </c>
-      <c r="AQ77" s="6">
-        <v>0</v>
-      </c>
-      <c r="AR77" s="6">
-        <v>0</v>
-      </c>
-      <c r="AS77" s="6">
-        <v>0</v>
-      </c>
-      <c r="AT77" s="6">
-        <v>0</v>
-      </c>
-      <c r="AU77" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="2:47" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B78" s="1" t="s">
+        <v>-323.89999999999998</v>
+      </c>
+      <c r="AL78" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM78" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN78" s="6">
+        <v>0</v>
+      </c>
+      <c r="AO78" s="6">
+        <v>0</v>
+      </c>
+      <c r="AP78" s="6">
+        <v>0</v>
+      </c>
+      <c r="AQ78" s="6">
+        <v>0</v>
+      </c>
+      <c r="AR78" s="6">
+        <v>0</v>
+      </c>
+      <c r="AS78" s="6">
+        <v>0</v>
+      </c>
+      <c r="AT78" s="6">
+        <v>0</v>
+      </c>
+      <c r="AU78" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:47" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B79" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="P78" s="9">
-        <f t="shared" ref="P78:X78" si="116">P60+SUM(P62:P77)</f>
+      <c r="P79" s="9">
+        <f t="shared" ref="P79:X79" si="114">P60+SUM(P62:P78)</f>
         <v>217.1</v>
       </c>
-      <c r="Q78" s="9">
+      <c r="Q79" s="9">
+        <f t="shared" si="114"/>
+        <v>299.80000000000007</v>
+      </c>
+      <c r="R79" s="9">
+        <f t="shared" si="114"/>
+        <v>83.6</v>
+      </c>
+      <c r="S79" s="9">
+        <f t="shared" si="114"/>
+        <v>121.50000000000011</v>
+      </c>
+      <c r="T79" s="9">
+        <f t="shared" si="114"/>
+        <v>345.10000000000014</v>
+      </c>
+      <c r="U79" s="9">
+        <f t="shared" si="114"/>
+        <v>356.30000000000007</v>
+      </c>
+      <c r="V79" s="9">
+        <f t="shared" si="114"/>
+        <v>70.699999999999875</v>
+      </c>
+      <c r="W79" s="9">
+        <f t="shared" si="114"/>
+        <v>105.30000000000013</v>
+      </c>
+      <c r="X79" s="9">
+        <f t="shared" si="114"/>
+        <v>431.69999999999993</v>
+      </c>
+      <c r="Y79" s="9">
+        <f t="shared" ref="Y79:AB79" si="115">Y60+SUM(Y62:Y78)</f>
+        <v>228.2</v>
+      </c>
+      <c r="Z79" s="9">
+        <f t="shared" si="115"/>
+        <v>74.800000000000011</v>
+      </c>
+      <c r="AA79" s="9">
+        <f t="shared" si="115"/>
+        <v>184.17665040000009</v>
+      </c>
+      <c r="AB79" s="9">
+        <f t="shared" si="115"/>
+        <v>203.75191599999999</v>
+      </c>
+      <c r="AI79" s="9">
+        <f>AI60+SUM(AI62:AI78)</f>
+        <v>850.00000000000057</v>
+      </c>
+      <c r="AJ79" s="9">
+        <f>AJ60+SUM(AJ62:AJ78)</f>
+        <v>964.00000000000045</v>
+      </c>
+      <c r="AK79" s="9">
+        <f t="shared" ref="AK79:AU79" si="116">AK60+SUM(AK62:AK78)</f>
+        <v>688.8285664</v>
+      </c>
+      <c r="AL79" s="9">
         <f t="shared" si="116"/>
-        <v>299.80000000000007</v>
-      </c>
-      <c r="R78" s="9">
+        <v>1301.7325500840002</v>
+      </c>
+      <c r="AM79" s="9">
         <f t="shared" si="116"/>
-        <v>83.6</v>
-      </c>
-      <c r="S78" s="9">
+        <v>1782.0752817935991</v>
+      </c>
+      <c r="AN79" s="9">
         <f t="shared" si="116"/>
-        <v>121.50000000000011</v>
-      </c>
-      <c r="T78" s="9">
+        <v>2169.956922454111</v>
+      </c>
+      <c r="AO79" s="9">
         <f t="shared" si="116"/>
-        <v>345.10000000000014</v>
-      </c>
-      <c r="U78" s="9">
+        <v>2427.9846889147839</v>
+      </c>
+      <c r="AP79" s="9">
         <f t="shared" si="116"/>
-        <v>356.30000000000007</v>
-      </c>
-      <c r="V78" s="9">
+        <v>2722.3476998190699</v>
+      </c>
+      <c r="AQ79" s="9">
         <f t="shared" si="116"/>
-        <v>70.699999999999875</v>
-      </c>
-      <c r="W78" s="9">
+        <v>2902.7042562601146</v>
+      </c>
+      <c r="AR79" s="9">
         <f t="shared" si="116"/>
-        <v>105.30000000000013</v>
-      </c>
-      <c r="X78" s="9">
+        <v>2979.6873156817728</v>
+      </c>
+      <c r="AS79" s="9">
         <f t="shared" si="116"/>
-        <v>431.69999999999993</v>
-      </c>
-      <c r="Y78" s="9">
-        <f t="shared" ref="Y78:AB78" si="117">Y60+SUM(Y62:Y77)</f>
-        <v>228.2</v>
-      </c>
-      <c r="Z78" s="9">
-        <f t="shared" si="117"/>
-        <v>61.692936000000145</v>
-      </c>
-      <c r="AA78" s="9">
-        <f t="shared" si="117"/>
-        <v>113.41788900000006</v>
-      </c>
-      <c r="AB78" s="9">
-        <f t="shared" si="117"/>
-        <v>159.26188400000001</v>
-      </c>
-      <c r="AI78" s="9">
-        <f>AI60+SUM(AI62:AI77)</f>
-        <v>850.00000000000057</v>
-      </c>
-      <c r="AJ78" s="9">
-        <f>AJ60+SUM(AJ62:AJ77)</f>
-        <v>964.00000000000045</v>
-      </c>
-      <c r="AK78" s="9">
-        <f t="shared" ref="AK78:AU78" si="118">AK60+SUM(AK62:AK77)</f>
-        <v>523.48630900000035</v>
-      </c>
-      <c r="AL78" s="9">
-        <f t="shared" si="118"/>
-        <v>1095.4314604800004</v>
-      </c>
-      <c r="AM78" s="9">
-        <f t="shared" si="118"/>
-        <v>1585.2935296000005</v>
-      </c>
-      <c r="AN78" s="9">
-        <f t="shared" si="118"/>
-        <v>1947.1602932638386</v>
-      </c>
-      <c r="AO78" s="9">
-        <f t="shared" si="118"/>
-        <v>2284.2774630806662</v>
-      </c>
-      <c r="AP78" s="9">
-        <f t="shared" si="118"/>
-        <v>2489.8545521087008</v>
-      </c>
-      <c r="AQ78" s="9">
-        <f t="shared" si="118"/>
-        <v>2663.5558660176457</v>
-      </c>
-      <c r="AR78" s="9">
-        <f t="shared" si="118"/>
-        <v>2752.0999281032014</v>
-      </c>
-      <c r="AS78" s="9">
-        <f t="shared" si="118"/>
-        <v>2821.4829559667405</v>
-      </c>
-      <c r="AT78" s="9">
-        <f t="shared" si="118"/>
-        <v>2909.6293996479185</v>
-      </c>
-      <c r="AU78" s="9">
-        <f t="shared" si="118"/>
-        <v>3016.1731691611058</v>
-      </c>
-    </row>
-    <row r="79" spans="2:47" x14ac:dyDescent="0.3">
-      <c r="B79" t="s">
-        <v>70</v>
-      </c>
-      <c r="P79" s="6">
-        <v>5.4</v>
-      </c>
-      <c r="Q79" s="6">
-        <v>7</v>
-      </c>
-      <c r="R79" s="6">
-        <v>6.3</v>
-      </c>
-      <c r="S79" s="6">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="T79" s="6">
-        <v>13.1</v>
-      </c>
-      <c r="U79" s="6">
-        <v>16.5</v>
-      </c>
-      <c r="V79" s="6">
-        <v>5</v>
-      </c>
-      <c r="W79" s="6">
-        <v>13.4</v>
-      </c>
-      <c r="X79" s="6">
-        <v>11.3</v>
-      </c>
-      <c r="Y79" s="6">
-        <v>45</v>
-      </c>
-      <c r="Z79" s="6">
-        <v>16</v>
-      </c>
-      <c r="AA79" s="6">
-        <v>16</v>
-      </c>
-      <c r="AB79" s="6">
-        <v>16</v>
-      </c>
-      <c r="AI79" s="6">
-        <f t="shared" ref="AI79:AI80" si="119">SUM(Q79:T79)</f>
-        <v>35.1</v>
-      </c>
-      <c r="AJ79" s="6">
-        <f t="shared" ref="AJ79:AJ80" si="120">SUM(U79:X79)</f>
-        <v>46.2</v>
-      </c>
-      <c r="AK79" s="6">
-        <f t="shared" ref="AK79:AK80" si="121">SUM(Y79:AB79)</f>
-        <v>93</v>
-      </c>
-      <c r="AL79" s="6"/>
-      <c r="AM79" s="6"/>
-      <c r="AN79" s="6"/>
-      <c r="AO79" s="6"/>
-      <c r="AP79" s="6"/>
-      <c r="AQ79" s="6"/>
-      <c r="AR79" s="6"/>
-      <c r="AS79" s="6"/>
-      <c r="AT79" s="6"/>
-      <c r="AU79" s="6"/>
+        <v>3057.0153096362633</v>
+      </c>
+      <c r="AT79" s="9">
+        <f t="shared" si="116"/>
+        <v>3153.8521157562736</v>
+      </c>
+      <c r="AU79" s="9">
+        <f t="shared" si="116"/>
+        <v>3269.8967811689472</v>
+      </c>
     </row>
     <row r="80" spans="2:47" x14ac:dyDescent="0.3">
       <c r="B80" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="P80" s="6">
-        <v>6.7</v>
+        <v>5.4</v>
       </c>
       <c r="Q80" s="6">
-        <v>9.3000000000000007</v>
+        <v>7</v>
       </c>
       <c r="R80" s="6">
-        <v>7.9</v>
+        <v>6.3</v>
       </c>
       <c r="S80" s="6">
-        <v>9.9</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="T80" s="6">
-        <v>7</v>
+        <v>13.1</v>
       </c>
       <c r="U80" s="6">
-        <v>7.4</v>
+        <v>16.5</v>
       </c>
       <c r="V80" s="6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W80" s="6">
-        <v>10</v>
+        <v>13.4</v>
       </c>
       <c r="X80" s="6">
-        <v>6</v>
+        <v>11.3</v>
       </c>
       <c r="Y80" s="6">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="Z80" s="6">
-        <v>7</v>
+        <v>16.7</v>
       </c>
       <c r="AA80" s="6">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="AB80" s="6">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="AI80" s="6">
-        <f t="shared" si="119"/>
-        <v>34.1</v>
+        <f t="shared" ref="AI80:AI81" si="117">SUM(Q80:T80)</f>
+        <v>35.1</v>
       </c>
       <c r="AJ80" s="6">
-        <f t="shared" si="120"/>
-        <v>29.4</v>
+        <f t="shared" ref="AJ80:AJ81" si="118">SUM(U80:X80)</f>
+        <v>46.2</v>
       </c>
       <c r="AK80" s="6">
-        <f t="shared" si="121"/>
-        <v>21</v>
+        <f t="shared" ref="AK80:AK81" si="119">SUM(Y80:AB80)</f>
+        <v>106.7</v>
       </c>
       <c r="AL80" s="6"/>
       <c r="AM80" s="6"/>
@@ -7862,826 +7802,892 @@
     </row>
     <row r="81" spans="2:159" x14ac:dyDescent="0.3">
       <c r="B81" t="s">
+        <v>73</v>
+      </c>
+      <c r="P81" s="6">
+        <v>6.7</v>
+      </c>
+      <c r="Q81" s="6">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="R81" s="6">
+        <v>7.9</v>
+      </c>
+      <c r="S81" s="6">
+        <v>9.9</v>
+      </c>
+      <c r="T81" s="6">
+        <v>7</v>
+      </c>
+      <c r="U81" s="6">
+        <v>7.4</v>
+      </c>
+      <c r="V81" s="6">
+        <v>6</v>
+      </c>
+      <c r="W81" s="6">
+        <v>10</v>
+      </c>
+      <c r="X81" s="6">
+        <v>6</v>
+      </c>
+      <c r="Y81" s="6">
+        <v>0</v>
+      </c>
+      <c r="Z81" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA81" s="6">
+        <v>0</v>
+      </c>
+      <c r="AB81" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI81" s="6">
+        <f t="shared" si="117"/>
+        <v>34.1</v>
+      </c>
+      <c r="AJ81" s="6">
+        <f t="shared" si="118"/>
+        <v>29.4</v>
+      </c>
+      <c r="AK81" s="6">
+        <f t="shared" si="119"/>
+        <v>0</v>
+      </c>
+      <c r="AL81" s="6"/>
+      <c r="AM81" s="6"/>
+      <c r="AN81" s="6"/>
+      <c r="AO81" s="6"/>
+      <c r="AP81" s="6"/>
+      <c r="AQ81" s="6"/>
+      <c r="AR81" s="6"/>
+      <c r="AS81" s="6"/>
+      <c r="AT81" s="6"/>
+      <c r="AU81" s="6"/>
+    </row>
+    <row r="82" spans="2:159" x14ac:dyDescent="0.3">
+      <c r="B82" t="s">
         <v>100</v>
       </c>
-      <c r="P81" s="6">
-        <f>P79+P80</f>
+      <c r="P82" s="6">
+        <f>P80+P81</f>
         <v>12.100000000000001</v>
       </c>
-      <c r="Q81" s="6">
-        <f t="shared" ref="Q81:X81" si="122">Q79+Q80</f>
+      <c r="Q82" s="6">
+        <f t="shared" ref="Q82:X82" si="120">Q80+Q81</f>
         <v>16.3</v>
       </c>
-      <c r="R81" s="6">
-        <f t="shared" si="122"/>
+      <c r="R82" s="6">
+        <f t="shared" si="120"/>
         <v>14.2</v>
       </c>
-      <c r="S81" s="6">
-        <f t="shared" si="122"/>
+      <c r="S82" s="6">
+        <f t="shared" si="120"/>
         <v>18.600000000000001</v>
       </c>
-      <c r="T81" s="6">
-        <f t="shared" si="122"/>
+      <c r="T82" s="6">
+        <f t="shared" si="120"/>
         <v>20.100000000000001</v>
       </c>
-      <c r="U81" s="6">
-        <f t="shared" si="122"/>
+      <c r="U82" s="6">
+        <f t="shared" si="120"/>
         <v>23.9</v>
       </c>
-      <c r="V81" s="6">
-        <f t="shared" si="122"/>
+      <c r="V82" s="6">
+        <f t="shared" si="120"/>
         <v>11</v>
       </c>
-      <c r="W81" s="6">
-        <f t="shared" si="122"/>
+      <c r="W82" s="6">
+        <f t="shared" si="120"/>
         <v>23.4</v>
       </c>
-      <c r="X81" s="6">
-        <f t="shared" si="122"/>
+      <c r="X82" s="6">
+        <f t="shared" si="120"/>
         <v>17.3</v>
       </c>
-      <c r="Y81" s="6">
-        <f t="shared" ref="Y81" si="123">Y79+Y80</f>
+      <c r="Y82" s="6">
+        <f t="shared" ref="Y82" si="121">Y80+Y81</f>
         <v>45</v>
       </c>
-      <c r="Z81" s="6">
-        <f t="shared" ref="Z81" si="124">Z79+Z80</f>
-        <v>23</v>
-      </c>
-      <c r="AA81" s="6">
-        <f t="shared" ref="AA81" si="125">AA79+AA80</f>
-        <v>23</v>
-      </c>
-      <c r="AB81" s="6">
-        <f t="shared" ref="AB81" si="126">AB79+AB80</f>
-        <v>23</v>
-      </c>
-      <c r="AI81" s="6">
-        <f t="shared" ref="AI81" si="127">AI79+AI80</f>
+      <c r="Z82" s="6">
+        <f t="shared" ref="Z82" si="122">Z80+Z81</f>
+        <v>16.7</v>
+      </c>
+      <c r="AA82" s="6">
+        <f t="shared" ref="AA82" si="123">AA80+AA81</f>
+        <v>20</v>
+      </c>
+      <c r="AB82" s="6">
+        <f t="shared" ref="AB82" si="124">AB80+AB81</f>
+        <v>25</v>
+      </c>
+      <c r="AI82" s="6">
+        <f t="shared" ref="AI82" si="125">AI80+AI81</f>
         <v>69.2</v>
       </c>
-      <c r="AJ81" s="6">
-        <f t="shared" ref="AJ81" si="128">AJ79+AJ80</f>
+      <c r="AJ82" s="6">
+        <f t="shared" ref="AJ82" si="126">AJ80+AJ81</f>
         <v>75.599999999999994</v>
       </c>
-      <c r="AK81" s="6">
-        <f t="shared" ref="AK81" si="129">AK79+AK80</f>
-        <v>114</v>
-      </c>
-      <c r="AL81" s="6">
-        <f>AK81*1.5</f>
-        <v>171</v>
-      </c>
-      <c r="AM81" s="6">
-        <f>AL81*1.02</f>
-        <v>174.42000000000002</v>
-      </c>
-      <c r="AN81" s="6">
-        <f t="shared" ref="AN81:AU81" si="130">AM81*1.02</f>
-        <v>177.90840000000003</v>
-      </c>
-      <c r="AO81" s="6">
-        <f t="shared" si="130"/>
-        <v>181.46656800000002</v>
-      </c>
-      <c r="AP81" s="6">
-        <f t="shared" si="130"/>
-        <v>185.09589936000003</v>
-      </c>
-      <c r="AQ81" s="6">
-        <f t="shared" si="130"/>
-        <v>188.79781734720004</v>
-      </c>
-      <c r="AR81" s="6">
-        <f t="shared" si="130"/>
-        <v>192.57377369414405</v>
-      </c>
-      <c r="AS81" s="6">
-        <f t="shared" si="130"/>
-        <v>196.42524916802694</v>
-      </c>
-      <c r="AT81" s="6">
-        <f t="shared" si="130"/>
-        <v>200.35375415138748</v>
-      </c>
-      <c r="AU81" s="6">
-        <f t="shared" si="130"/>
-        <v>204.36082923441523</v>
-      </c>
-    </row>
-    <row r="82" spans="2:159" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B82" s="1" t="s">
+      <c r="AK82" s="6">
+        <f t="shared" ref="AK82" si="127">AK80+AK81</f>
+        <v>106.7</v>
+      </c>
+      <c r="AL82" s="6">
+        <f>AK82*1.3</f>
+        <v>138.71</v>
+      </c>
+      <c r="AM82" s="6">
+        <f>AL82*1.02</f>
+        <v>141.48420000000002</v>
+      </c>
+      <c r="AN82" s="6">
+        <f t="shared" ref="AN82:AU82" si="128">AM82*1.02</f>
+        <v>144.31388400000003</v>
+      </c>
+      <c r="AO82" s="6">
+        <f t="shared" si="128"/>
+        <v>147.20016168000004</v>
+      </c>
+      <c r="AP82" s="6">
+        <f t="shared" si="128"/>
+        <v>150.14416491360004</v>
+      </c>
+      <c r="AQ82" s="6">
+        <f t="shared" si="128"/>
+        <v>153.14704821187203</v>
+      </c>
+      <c r="AR82" s="6">
+        <f t="shared" si="128"/>
+        <v>156.20998917610947</v>
+      </c>
+      <c r="AS82" s="6">
+        <f t="shared" si="128"/>
+        <v>159.33418895963166</v>
+      </c>
+      <c r="AT82" s="6">
+        <f t="shared" si="128"/>
+        <v>162.52087273882429</v>
+      </c>
+      <c r="AU82" s="6">
+        <f t="shared" si="128"/>
+        <v>165.77129019360078</v>
+      </c>
+    </row>
+    <row r="83" spans="2:159" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B83" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="P82" s="9">
-        <f>P78-P81</f>
+      <c r="P83" s="9">
+        <f>P79-P82</f>
         <v>205</v>
       </c>
-      <c r="Q82" s="9">
-        <f t="shared" ref="Q82:X82" si="131">Q78-Q81</f>
+      <c r="Q83" s="9">
+        <f t="shared" ref="Q83:X83" si="129">Q79-Q82</f>
         <v>283.50000000000006</v>
       </c>
-      <c r="R82" s="9">
-        <f t="shared" si="131"/>
+      <c r="R83" s="9">
+        <f t="shared" si="129"/>
         <v>69.399999999999991</v>
       </c>
-      <c r="S82" s="9">
-        <f t="shared" si="131"/>
+      <c r="S83" s="9">
+        <f t="shared" si="129"/>
         <v>102.90000000000012</v>
       </c>
-      <c r="T82" s="9">
-        <f t="shared" si="131"/>
+      <c r="T83" s="9">
+        <f t="shared" si="129"/>
         <v>325.00000000000011</v>
       </c>
-      <c r="U82" s="9">
-        <f t="shared" si="131"/>
+      <c r="U83" s="9">
+        <f t="shared" si="129"/>
         <v>332.40000000000009</v>
       </c>
-      <c r="V82" s="9">
-        <f t="shared" si="131"/>
+      <c r="V83" s="9">
+        <f t="shared" si="129"/>
         <v>59.699999999999875</v>
       </c>
-      <c r="W82" s="9">
-        <f t="shared" si="131"/>
+      <c r="W83" s="9">
+        <f t="shared" si="129"/>
         <v>81.900000000000119</v>
       </c>
-      <c r="X82" s="9">
-        <f t="shared" si="131"/>
+      <c r="X83" s="9">
+        <f t="shared" si="129"/>
         <v>414.39999999999992</v>
       </c>
-      <c r="Y82" s="9">
-        <f t="shared" ref="Y82" si="132">Y78-Y81</f>
+      <c r="Y83" s="9">
+        <f t="shared" ref="Y83" si="130">Y79-Y82</f>
         <v>183.2</v>
       </c>
-      <c r="Z82" s="9">
-        <f t="shared" ref="Z82" si="133">Z78-Z81</f>
-        <v>38.692936000000145</v>
-      </c>
-      <c r="AA82" s="9">
-        <f t="shared" ref="AA82" si="134">AA78-AA81</f>
-        <v>90.417889000000059</v>
-      </c>
-      <c r="AB82" s="9">
-        <f t="shared" ref="AB82" si="135">AB78-AB81</f>
-        <v>136.26188400000001</v>
-      </c>
-      <c r="AI82" s="9">
-        <f t="shared" ref="AI82" si="136">AI78-AI81</f>
+      <c r="Z83" s="9">
+        <f t="shared" ref="Z83" si="131">Z79-Z82</f>
+        <v>58.100000000000009</v>
+      </c>
+      <c r="AA83" s="9">
+        <f t="shared" ref="AA83" si="132">AA79-AA82</f>
+        <v>164.17665040000009</v>
+      </c>
+      <c r="AB83" s="9">
+        <f t="shared" ref="AB83" si="133">AB79-AB82</f>
+        <v>178.75191599999999</v>
+      </c>
+      <c r="AI83" s="9">
+        <f t="shared" ref="AI83" si="134">AI79-AI82</f>
         <v>780.80000000000052</v>
       </c>
-      <c r="AJ82" s="9">
-        <f t="shared" ref="AJ82" si="137">AJ78-AJ81</f>
+      <c r="AJ83" s="9">
+        <f t="shared" ref="AJ83" si="135">AJ79-AJ82</f>
         <v>888.40000000000043</v>
       </c>
-      <c r="AK82" s="9">
-        <f t="shared" ref="AK82" si="138">AK78-AK81</f>
-        <v>409.48630900000035</v>
-      </c>
-      <c r="AL82" s="9">
-        <f t="shared" ref="AL82" si="139">AL78-AL81</f>
-        <v>924.4314604800004</v>
-      </c>
-      <c r="AM82" s="9">
-        <f t="shared" ref="AM82" si="140">AM78-AM81</f>
-        <v>1410.8735296000004</v>
-      </c>
-      <c r="AN82" s="9">
-        <f t="shared" ref="AN82" si="141">AN78-AN81</f>
-        <v>1769.2518932638386</v>
-      </c>
-      <c r="AO82" s="9">
-        <f t="shared" ref="AO82" si="142">AO78-AO81</f>
-        <v>2102.8108950806663</v>
-      </c>
-      <c r="AP82" s="9">
-        <f t="shared" ref="AP82" si="143">AP78-AP81</f>
-        <v>2304.7586527487006</v>
-      </c>
-      <c r="AQ82" s="9">
-        <f t="shared" ref="AQ82" si="144">AQ78-AQ81</f>
-        <v>2474.7580486704455</v>
-      </c>
-      <c r="AR82" s="9">
-        <f t="shared" ref="AR82" si="145">AR78-AR81</f>
-        <v>2559.5261544090572</v>
-      </c>
-      <c r="AS82" s="9">
-        <f t="shared" ref="AS82" si="146">AS78-AS81</f>
-        <v>2625.0577067987138</v>
-      </c>
-      <c r="AT82" s="9">
-        <f t="shared" ref="AT82" si="147">AT78-AT81</f>
-        <v>2709.2756454965311</v>
-      </c>
-      <c r="AU82" s="9">
-        <f t="shared" ref="AU82" si="148">AU78-AU81</f>
-        <v>2811.8123399266906</v>
-      </c>
-      <c r="AV82" s="1">
-        <f>AU82*(1+$AX$22)</f>
-        <v>2783.6942165274236</v>
-      </c>
-      <c r="AW82" s="1">
-        <f t="shared" ref="AW82:DH82" si="149">AV82*(1+$AX$22)</f>
-        <v>2755.8572743621494</v>
-      </c>
-      <c r="AX82" s="1">
-        <f t="shared" si="149"/>
-        <v>2728.298701618528</v>
-      </c>
-      <c r="AY82" s="1">
-        <f t="shared" si="149"/>
-        <v>2701.0157146023425</v>
-      </c>
-      <c r="AZ82" s="1">
-        <f t="shared" si="149"/>
-        <v>2674.0055574563189</v>
-      </c>
-      <c r="BA82" s="1">
-        <f t="shared" si="149"/>
-        <v>2647.2655018817559</v>
-      </c>
-      <c r="BB82" s="1">
-        <f t="shared" si="149"/>
-        <v>2620.7928468629384</v>
-      </c>
-      <c r="BC82" s="1">
-        <f t="shared" si="149"/>
-        <v>2594.5849183943092</v>
-      </c>
-      <c r="BD82" s="1">
-        <f t="shared" si="149"/>
-        <v>2568.639069210366</v>
-      </c>
-      <c r="BE82" s="1">
-        <f t="shared" si="149"/>
-        <v>2542.9526785182625</v>
-      </c>
-      <c r="BF82" s="1">
-        <f t="shared" si="149"/>
-        <v>2517.5231517330799</v>
-      </c>
-      <c r="BG82" s="1">
-        <f t="shared" si="149"/>
-        <v>2492.3479202157491</v>
-      </c>
-      <c r="BH82" s="1">
-        <f t="shared" si="149"/>
-        <v>2467.4244410135916</v>
-      </c>
-      <c r="BI82" s="1">
-        <f t="shared" si="149"/>
-        <v>2442.7501966034556</v>
-      </c>
-      <c r="BJ82" s="1">
-        <f t="shared" si="149"/>
-        <v>2418.3226946374211</v>
-      </c>
-      <c r="BK82" s="1">
-        <f t="shared" si="149"/>
-        <v>2394.1394676910468</v>
-      </c>
-      <c r="BL82" s="1">
-        <f t="shared" si="149"/>
-        <v>2370.1980730141363</v>
-      </c>
-      <c r="BM82" s="1">
-        <f t="shared" si="149"/>
-        <v>2346.496092283995</v>
-      </c>
-      <c r="BN82" s="1">
-        <f t="shared" si="149"/>
-        <v>2323.0311313611551</v>
-      </c>
-      <c r="BO82" s="1">
-        <f t="shared" si="149"/>
-        <v>2299.8008200475433</v>
-      </c>
-      <c r="BP82" s="1">
-        <f t="shared" si="149"/>
-        <v>2276.8028118470679</v>
-      </c>
-      <c r="BQ82" s="1">
-        <f t="shared" si="149"/>
-        <v>2254.0347837285972</v>
-      </c>
-      <c r="BR82" s="1">
-        <f t="shared" si="149"/>
-        <v>2231.4944358913112</v>
-      </c>
-      <c r="BS82" s="1">
-        <f t="shared" si="149"/>
-        <v>2209.1794915323981</v>
-      </c>
-      <c r="BT82" s="1">
-        <f t="shared" si="149"/>
-        <v>2187.087696617074</v>
-      </c>
-      <c r="BU82" s="1">
-        <f t="shared" si="149"/>
-        <v>2165.2168196509033</v>
-      </c>
-      <c r="BV82" s="1">
-        <f t="shared" si="149"/>
-        <v>2143.5646514543942</v>
-      </c>
-      <c r="BW82" s="1">
-        <f t="shared" si="149"/>
-        <v>2122.1290049398503</v>
-      </c>
-      <c r="BX82" s="1">
-        <f t="shared" si="149"/>
-        <v>2100.9077148904516</v>
-      </c>
-      <c r="BY82" s="1">
-        <f t="shared" si="149"/>
-        <v>2079.8986377415472</v>
-      </c>
-      <c r="BZ82" s="1">
-        <f t="shared" si="149"/>
-        <v>2059.0996513641317</v>
-      </c>
-      <c r="CA82" s="1">
-        <f t="shared" si="149"/>
-        <v>2038.5086548504903</v>
-      </c>
-      <c r="CB82" s="1">
-        <f t="shared" si="149"/>
-        <v>2018.1235683019854</v>
-      </c>
-      <c r="CC82" s="1">
-        <f t="shared" si="149"/>
-        <v>1997.9423326189656</v>
-      </c>
-      <c r="CD82" s="1">
-        <f t="shared" si="149"/>
-        <v>1977.962909292776</v>
-      </c>
-      <c r="CE82" s="1">
-        <f t="shared" si="149"/>
-        <v>1958.1832801998482</v>
-      </c>
-      <c r="CF82" s="1">
-        <f t="shared" si="149"/>
-        <v>1938.6014473978498</v>
-      </c>
-      <c r="CG82" s="1">
-        <f t="shared" si="149"/>
-        <v>1919.2154329238713</v>
-      </c>
-      <c r="CH82" s="1">
-        <f t="shared" si="149"/>
-        <v>1900.0232785946325</v>
-      </c>
-      <c r="CI82" s="1">
-        <f t="shared" si="149"/>
-        <v>1881.0230458086862</v>
-      </c>
-      <c r="CJ82" s="1">
-        <f t="shared" si="149"/>
-        <v>1862.2128153505994</v>
-      </c>
-      <c r="CK82" s="1">
-        <f t="shared" si="149"/>
-        <v>1843.5906871970933</v>
-      </c>
-      <c r="CL82" s="1">
-        <f t="shared" si="149"/>
-        <v>1825.1547803251224</v>
-      </c>
-      <c r="CM82" s="1">
-        <f t="shared" si="149"/>
-        <v>1806.9032325218711</v>
-      </c>
-      <c r="CN82" s="1">
-        <f t="shared" si="149"/>
-        <v>1788.8342001966523</v>
-      </c>
-      <c r="CO82" s="1">
-        <f t="shared" si="149"/>
-        <v>1770.9458581946858</v>
-      </c>
-      <c r="CP82" s="1">
-        <f t="shared" si="149"/>
-        <v>1753.236399612739</v>
-      </c>
-      <c r="CQ82" s="1">
-        <f t="shared" si="149"/>
-        <v>1735.7040356166115</v>
-      </c>
-      <c r="CR82" s="1">
-        <f t="shared" si="149"/>
-        <v>1718.3469952604453</v>
-      </c>
-      <c r="CS82" s="1">
-        <f t="shared" si="149"/>
-        <v>1701.1635253078409</v>
-      </c>
-      <c r="CT82" s="1">
-        <f t="shared" si="149"/>
-        <v>1684.1518900547626</v>
-      </c>
-      <c r="CU82" s="1">
-        <f t="shared" si="149"/>
-        <v>1667.3103711542149</v>
-      </c>
-      <c r="CV82" s="1">
-        <f t="shared" si="149"/>
-        <v>1650.6372674426727</v>
-      </c>
-      <c r="CW82" s="1">
-        <f t="shared" si="149"/>
-        <v>1634.130894768246</v>
-      </c>
-      <c r="CX82" s="1">
-        <f t="shared" si="149"/>
-        <v>1617.7895858205636</v>
-      </c>
-      <c r="CY82" s="1">
-        <f t="shared" si="149"/>
-        <v>1601.611689962358</v>
-      </c>
-      <c r="CZ82" s="1">
-        <f t="shared" si="149"/>
-        <v>1585.5955730627345</v>
-      </c>
-      <c r="DA82" s="1">
-        <f t="shared" si="149"/>
-        <v>1569.7396173321072</v>
-      </c>
-      <c r="DB82" s="1">
-        <f t="shared" si="149"/>
-        <v>1554.0422211587861</v>
-      </c>
-      <c r="DC82" s="1">
-        <f t="shared" si="149"/>
-        <v>1538.5017989471983</v>
-      </c>
-      <c r="DD82" s="1">
-        <f t="shared" si="149"/>
-        <v>1523.1167809577262</v>
-      </c>
-      <c r="DE82" s="1">
-        <f t="shared" si="149"/>
-        <v>1507.8856131481489</v>
-      </c>
-      <c r="DF82" s="1">
-        <f t="shared" si="149"/>
-        <v>1492.8067570166675</v>
-      </c>
-      <c r="DG82" s="1">
-        <f t="shared" si="149"/>
-        <v>1477.8786894465009</v>
-      </c>
-      <c r="DH82" s="1">
-        <f t="shared" si="149"/>
-        <v>1463.0999025520359</v>
-      </c>
-      <c r="DI82" s="1">
-        <f t="shared" ref="DI82:FC82" si="150">DH82*(1+$AX$22)</f>
-        <v>1448.4689035265155</v>
-      </c>
-      <c r="DJ82" s="1">
-        <f t="shared" si="150"/>
-        <v>1433.9842144912504</v>
-      </c>
-      <c r="DK82" s="1">
-        <f t="shared" si="150"/>
-        <v>1419.6443723463378</v>
-      </c>
-      <c r="DL82" s="1">
-        <f t="shared" si="150"/>
-        <v>1405.4479286228745</v>
-      </c>
-      <c r="DM82" s="1">
-        <f t="shared" si="150"/>
-        <v>1391.3934493366457</v>
-      </c>
-      <c r="DN82" s="1">
-        <f t="shared" si="150"/>
-        <v>1377.4795148432793</v>
-      </c>
-      <c r="DO82" s="1">
-        <f t="shared" si="150"/>
-        <v>1363.7047196948465</v>
-      </c>
-      <c r="DP82" s="1">
-        <f t="shared" si="150"/>
-        <v>1350.067672497898</v>
-      </c>
-      <c r="DQ82" s="1">
-        <f t="shared" si="150"/>
-        <v>1336.566995772919</v>
-      </c>
-      <c r="DR82" s="1">
-        <f t="shared" si="150"/>
-        <v>1323.2013258151899</v>
-      </c>
-      <c r="DS82" s="1">
-        <f t="shared" si="150"/>
-        <v>1309.9693125570379</v>
-      </c>
-      <c r="DT82" s="1">
-        <f t="shared" si="150"/>
-        <v>1296.8696194314675</v>
-      </c>
-      <c r="DU82" s="1">
-        <f t="shared" si="150"/>
-        <v>1283.9009232371529</v>
-      </c>
-      <c r="DV82" s="1">
-        <f t="shared" si="150"/>
-        <v>1271.0619140047813</v>
-      </c>
-      <c r="DW82" s="1">
-        <f t="shared" si="150"/>
-        <v>1258.3512948647335</v>
-      </c>
-      <c r="DX82" s="1">
-        <f t="shared" si="150"/>
-        <v>1245.7677819160863</v>
-      </c>
-      <c r="DY82" s="1">
-        <f t="shared" si="150"/>
-        <v>1233.3101040969254</v>
-      </c>
-      <c r="DZ82" s="1">
-        <f t="shared" si="150"/>
-        <v>1220.9770030559562</v>
-      </c>
-      <c r="EA82" s="1">
-        <f t="shared" si="150"/>
-        <v>1208.7672330253965</v>
-      </c>
-      <c r="EB82" s="1">
-        <f t="shared" si="150"/>
-        <v>1196.6795606951425</v>
-      </c>
-      <c r="EC82" s="1">
-        <f t="shared" si="150"/>
-        <v>1184.7127650881912</v>
-      </c>
-      <c r="ED82" s="1">
-        <f t="shared" si="150"/>
-        <v>1172.8656374373093</v>
-      </c>
-      <c r="EE82" s="1">
-        <f t="shared" si="150"/>
-        <v>1161.1369810629362</v>
-      </c>
-      <c r="EF82" s="1">
-        <f t="shared" si="150"/>
-        <v>1149.5256112523068</v>
-      </c>
-      <c r="EG82" s="1">
-        <f t="shared" si="150"/>
-        <v>1138.0303551397838</v>
-      </c>
-      <c r="EH82" s="1">
-        <f t="shared" si="150"/>
-        <v>1126.6500515883858</v>
-      </c>
-      <c r="EI82" s="1">
-        <f t="shared" si="150"/>
-        <v>1115.3835510725021</v>
-      </c>
-      <c r="EJ82" s="1">
-        <f t="shared" si="150"/>
-        <v>1104.2297155617771</v>
-      </c>
-      <c r="EK82" s="1">
-        <f t="shared" si="150"/>
-        <v>1093.1874184061594</v>
-      </c>
-      <c r="EL82" s="1">
-        <f t="shared" si="150"/>
-        <v>1082.2555442220978</v>
-      </c>
-      <c r="EM82" s="1">
-        <f t="shared" si="150"/>
-        <v>1071.4329887798767</v>
-      </c>
-      <c r="EN82" s="1">
-        <f t="shared" si="150"/>
-        <v>1060.7186588920779</v>
-      </c>
-      <c r="EO82" s="1">
-        <f t="shared" si="150"/>
-        <v>1050.1114723031571</v>
-      </c>
-      <c r="EP82" s="1">
-        <f t="shared" si="150"/>
-        <v>1039.6103575801255</v>
-      </c>
-      <c r="EQ82" s="1">
-        <f t="shared" si="150"/>
-        <v>1029.2142540043242</v>
-      </c>
-      <c r="ER82" s="1">
-        <f t="shared" si="150"/>
-        <v>1018.9221114642809</v>
-      </c>
-      <c r="ES82" s="1">
-        <f t="shared" si="150"/>
-        <v>1008.7328903496381</v>
-      </c>
-      <c r="ET82" s="1">
-        <f t="shared" si="150"/>
-        <v>998.64556144614164</v>
-      </c>
-      <c r="EU82" s="1">
-        <f t="shared" si="150"/>
-        <v>988.65910583168022</v>
-      </c>
-      <c r="EV82" s="1">
-        <f t="shared" si="150"/>
-        <v>978.77251477336335</v>
-      </c>
-      <c r="EW82" s="1">
-        <f t="shared" si="150"/>
-        <v>968.98478962562967</v>
-      </c>
-      <c r="EX82" s="1">
-        <f t="shared" si="150"/>
-        <v>959.29494172937336</v>
-      </c>
-      <c r="EY82" s="1">
-        <f t="shared" si="150"/>
-        <v>949.7019923120796</v>
-      </c>
-      <c r="EZ82" s="1">
-        <f t="shared" si="150"/>
-        <v>940.20497238895882</v>
-      </c>
-      <c r="FA82" s="1">
-        <f t="shared" si="150"/>
-        <v>930.80292266506922</v>
-      </c>
-      <c r="FB82" s="1">
-        <f t="shared" si="150"/>
-        <v>921.49489343841856</v>
-      </c>
-      <c r="FC82" s="1">
-        <f t="shared" si="150"/>
-        <v>912.27994450403435</v>
-      </c>
-    </row>
-    <row r="84" spans="2:159" x14ac:dyDescent="0.3">
-      <c r="B84" t="s">
+      <c r="AK83" s="9">
+        <f t="shared" ref="AK83" si="136">AK79-AK82</f>
+        <v>582.12856639999995</v>
+      </c>
+      <c r="AL83" s="9">
+        <f t="shared" ref="AL83" si="137">AL79-AL82</f>
+        <v>1163.0225500840002</v>
+      </c>
+      <c r="AM83" s="9">
+        <f t="shared" ref="AM83" si="138">AM79-AM82</f>
+        <v>1640.591081793599</v>
+      </c>
+      <c r="AN83" s="9">
+        <f t="shared" ref="AN83" si="139">AN79-AN82</f>
+        <v>2025.6430384541109</v>
+      </c>
+      <c r="AO83" s="9">
+        <f t="shared" ref="AO83" si="140">AO79-AO82</f>
+        <v>2280.784527234784</v>
+      </c>
+      <c r="AP83" s="9">
+        <f t="shared" ref="AP83" si="141">AP79-AP82</f>
+        <v>2572.20353490547</v>
+      </c>
+      <c r="AQ83" s="9">
+        <f t="shared" ref="AQ83" si="142">AQ79-AQ82</f>
+        <v>2749.5572080482425</v>
+      </c>
+      <c r="AR83" s="9">
+        <f t="shared" ref="AR83" si="143">AR79-AR82</f>
+        <v>2823.4773265056633</v>
+      </c>
+      <c r="AS83" s="9">
+        <f t="shared" ref="AS83" si="144">AS79-AS82</f>
+        <v>2897.6811206766315</v>
+      </c>
+      <c r="AT83" s="9">
+        <f t="shared" ref="AT83" si="145">AT79-AT82</f>
+        <v>2991.3312430174492</v>
+      </c>
+      <c r="AU83" s="9">
+        <f t="shared" ref="AU83" si="146">AU79-AU82</f>
+        <v>3104.1254909753466</v>
+      </c>
+      <c r="AV83" s="1">
+        <f>AU83*(1+$AX$22)</f>
+        <v>3073.0842360655929</v>
+      </c>
+      <c r="AW83" s="1">
+        <f t="shared" ref="AW83:DH83" si="147">AV83*(1+$AX$22)</f>
+        <v>3042.3533937049369</v>
+      </c>
+      <c r="AX83" s="1">
+        <f t="shared" si="147"/>
+        <v>3011.9298597678876</v>
+      </c>
+      <c r="AY83" s="1">
+        <f t="shared" si="147"/>
+        <v>2981.8105611702085</v>
+      </c>
+      <c r="AZ83" s="1">
+        <f t="shared" si="147"/>
+        <v>2951.9924555585062</v>
+      </c>
+      <c r="BA83" s="1">
+        <f t="shared" si="147"/>
+        <v>2922.4725310029212</v>
+      </c>
+      <c r="BB83" s="1">
+        <f t="shared" si="147"/>
+        <v>2893.2478056928921</v>
+      </c>
+      <c r="BC83" s="1">
+        <f t="shared" si="147"/>
+        <v>2864.3153276359631</v>
+      </c>
+      <c r="BD83" s="1">
+        <f t="shared" si="147"/>
+        <v>2835.6721743596036</v>
+      </c>
+      <c r="BE83" s="1">
+        <f t="shared" si="147"/>
+        <v>2807.3154526160074</v>
+      </c>
+      <c r="BF83" s="1">
+        <f t="shared" si="147"/>
+        <v>2779.2422980898473</v>
+      </c>
+      <c r="BG83" s="1">
+        <f t="shared" si="147"/>
+        <v>2751.4498751089486</v>
+      </c>
+      <c r="BH83" s="1">
+        <f t="shared" si="147"/>
+        <v>2723.9353763578592</v>
+      </c>
+      <c r="BI83" s="1">
+        <f t="shared" si="147"/>
+        <v>2696.6960225942807</v>
+      </c>
+      <c r="BJ83" s="1">
+        <f t="shared" si="147"/>
+        <v>2669.729062368338</v>
+      </c>
+      <c r="BK83" s="1">
+        <f t="shared" si="147"/>
+        <v>2643.0317717446546</v>
+      </c>
+      <c r="BL83" s="1">
+        <f t="shared" si="147"/>
+        <v>2616.6014540272081</v>
+      </c>
+      <c r="BM83" s="1">
+        <f t="shared" si="147"/>
+        <v>2590.435439486936</v>
+      </c>
+      <c r="BN83" s="1">
+        <f t="shared" si="147"/>
+        <v>2564.5310850920669</v>
+      </c>
+      <c r="BO83" s="1">
+        <f t="shared" si="147"/>
+        <v>2538.885774241146</v>
+      </c>
+      <c r="BP83" s="1">
+        <f t="shared" si="147"/>
+        <v>2513.4969164987347</v>
+      </c>
+      <c r="BQ83" s="1">
+        <f t="shared" si="147"/>
+        <v>2488.3619473337471</v>
+      </c>
+      <c r="BR83" s="1">
+        <f t="shared" si="147"/>
+        <v>2463.4783278604095</v>
+      </c>
+      <c r="BS83" s="1">
+        <f t="shared" si="147"/>
+        <v>2438.8435445818054</v>
+      </c>
+      <c r="BT83" s="1">
+        <f t="shared" si="147"/>
+        <v>2414.4551091359872</v>
+      </c>
+      <c r="BU83" s="1">
+        <f t="shared" si="147"/>
+        <v>2390.3105580446272</v>
+      </c>
+      <c r="BV83" s="1">
+        <f t="shared" si="147"/>
+        <v>2366.407452464181</v>
+      </c>
+      <c r="BW83" s="1">
+        <f t="shared" si="147"/>
+        <v>2342.7433779395392</v>
+      </c>
+      <c r="BX83" s="1">
+        <f t="shared" si="147"/>
+        <v>2319.3159441601438</v>
+      </c>
+      <c r="BY83" s="1">
+        <f t="shared" si="147"/>
+        <v>2296.1227847185423</v>
+      </c>
+      <c r="BZ83" s="1">
+        <f t="shared" si="147"/>
+        <v>2273.1615568713569</v>
+      </c>
+      <c r="CA83" s="1">
+        <f t="shared" si="147"/>
+        <v>2250.4299413026433</v>
+      </c>
+      <c r="CB83" s="1">
+        <f t="shared" si="147"/>
+        <v>2227.9256418896171</v>
+      </c>
+      <c r="CC83" s="1">
+        <f t="shared" si="147"/>
+        <v>2205.6463854707208</v>
+      </c>
+      <c r="CD83" s="1">
+        <f t="shared" si="147"/>
+        <v>2183.5899216160137</v>
+      </c>
+      <c r="CE83" s="1">
+        <f t="shared" si="147"/>
+        <v>2161.7540223998535</v>
+      </c>
+      <c r="CF83" s="1">
+        <f t="shared" si="147"/>
+        <v>2140.1364821758548</v>
+      </c>
+      <c r="CG83" s="1">
+        <f t="shared" si="147"/>
+        <v>2118.735117354096</v>
+      </c>
+      <c r="CH83" s="1">
+        <f t="shared" si="147"/>
+        <v>2097.5477661805548</v>
+      </c>
+      <c r="CI83" s="1">
+        <f t="shared" si="147"/>
+        <v>2076.5722885187492</v>
+      </c>
+      <c r="CJ83" s="1">
+        <f t="shared" si="147"/>
+        <v>2055.8065656335616</v>
+      </c>
+      <c r="CK83" s="1">
+        <f t="shared" si="147"/>
+        <v>2035.2484999772259</v>
+      </c>
+      <c r="CL83" s="1">
+        <f t="shared" si="147"/>
+        <v>2014.8960149774537</v>
+      </c>
+      <c r="CM83" s="1">
+        <f t="shared" si="147"/>
+        <v>1994.747054827679</v>
+      </c>
+      <c r="CN83" s="1">
+        <f t="shared" si="147"/>
+        <v>1974.7995842794021</v>
+      </c>
+      <c r="CO83" s="1">
+        <f t="shared" si="147"/>
+        <v>1955.051588436608</v>
+      </c>
+      <c r="CP83" s="1">
+        <f t="shared" si="147"/>
+        <v>1935.5010725522418</v>
+      </c>
+      <c r="CQ83" s="1">
+        <f t="shared" si="147"/>
+        <v>1916.1460618267195</v>
+      </c>
+      <c r="CR83" s="1">
+        <f t="shared" si="147"/>
+        <v>1896.9846012084522</v>
+      </c>
+      <c r="CS83" s="1">
+        <f t="shared" si="147"/>
+        <v>1878.0147551963676</v>
+      </c>
+      <c r="CT83" s="1">
+        <f t="shared" si="147"/>
+        <v>1859.2346076444039</v>
+      </c>
+      <c r="CU83" s="1">
+        <f t="shared" si="147"/>
+        <v>1840.6422615679598</v>
+      </c>
+      <c r="CV83" s="1">
+        <f t="shared" si="147"/>
+        <v>1822.2358389522803</v>
+      </c>
+      <c r="CW83" s="1">
+        <f t="shared" si="147"/>
+        <v>1804.0134805627574</v>
+      </c>
+      <c r="CX83" s="1">
+        <f t="shared" si="147"/>
+        <v>1785.9733457571299</v>
+      </c>
+      <c r="CY83" s="1">
+        <f t="shared" si="147"/>
+        <v>1768.1136122995586</v>
+      </c>
+      <c r="CZ83" s="1">
+        <f t="shared" si="147"/>
+        <v>1750.4324761765629</v>
+      </c>
+      <c r="DA83" s="1">
+        <f t="shared" si="147"/>
+        <v>1732.9281514147972</v>
+      </c>
+      <c r="DB83" s="1">
+        <f t="shared" si="147"/>
+        <v>1715.5988699006491</v>
+      </c>
+      <c r="DC83" s="1">
+        <f t="shared" si="147"/>
+        <v>1698.4428812016426</v>
+      </c>
+      <c r="DD83" s="1">
+        <f t="shared" si="147"/>
+        <v>1681.4584523896262</v>
+      </c>
+      <c r="DE83" s="1">
+        <f t="shared" si="147"/>
+        <v>1664.64386786573</v>
+      </c>
+      <c r="DF83" s="1">
+        <f t="shared" si="147"/>
+        <v>1647.9974291870728</v>
+      </c>
+      <c r="DG83" s="1">
+        <f t="shared" si="147"/>
+        <v>1631.517454895202</v>
+      </c>
+      <c r="DH83" s="1">
+        <f t="shared" si="147"/>
+        <v>1615.2022803462501</v>
+      </c>
+      <c r="DI83" s="1">
+        <f t="shared" ref="DI83:FC83" si="148">DH83*(1+$AX$22)</f>
+        <v>1599.0502575427874</v>
+      </c>
+      <c r="DJ83" s="1">
+        <f t="shared" si="148"/>
+        <v>1583.0597549673596</v>
+      </c>
+      <c r="DK83" s="1">
+        <f t="shared" si="148"/>
+        <v>1567.2291574176859</v>
+      </c>
+      <c r="DL83" s="1">
+        <f t="shared" si="148"/>
+        <v>1551.5568658435091</v>
+      </c>
+      <c r="DM83" s="1">
+        <f t="shared" si="148"/>
+        <v>1536.041297185074</v>
+      </c>
+      <c r="DN83" s="1">
+        <f t="shared" si="148"/>
+        <v>1520.6808842132232</v>
+      </c>
+      <c r="DO83" s="1">
+        <f t="shared" si="148"/>
+        <v>1505.474075371091</v>
+      </c>
+      <c r="DP83" s="1">
+        <f t="shared" si="148"/>
+        <v>1490.4193346173799</v>
+      </c>
+      <c r="DQ83" s="1">
+        <f t="shared" si="148"/>
+        <v>1475.5151412712062</v>
+      </c>
+      <c r="DR83" s="1">
+        <f t="shared" si="148"/>
+        <v>1460.759989858494</v>
+      </c>
+      <c r="DS83" s="1">
+        <f t="shared" si="148"/>
+        <v>1446.152389959909</v>
+      </c>
+      <c r="DT83" s="1">
+        <f t="shared" si="148"/>
+        <v>1431.6908660603099</v>
+      </c>
+      <c r="DU83" s="1">
+        <f t="shared" si="148"/>
+        <v>1417.3739573997068</v>
+      </c>
+      <c r="DV83" s="1">
+        <f t="shared" si="148"/>
+        <v>1403.2002178257096</v>
+      </c>
+      <c r="DW83" s="1">
+        <f t="shared" si="148"/>
+        <v>1389.1682156474526</v>
+      </c>
+      <c r="DX83" s="1">
+        <f t="shared" si="148"/>
+        <v>1375.276533490978</v>
+      </c>
+      <c r="DY83" s="1">
+        <f t="shared" si="148"/>
+        <v>1361.5237681560682</v>
+      </c>
+      <c r="DZ83" s="1">
+        <f t="shared" si="148"/>
+        <v>1347.9085304745074</v>
+      </c>
+      <c r="EA83" s="1">
+        <f t="shared" si="148"/>
+        <v>1334.4294451697624</v>
+      </c>
+      <c r="EB83" s="1">
+        <f t="shared" si="148"/>
+        <v>1321.0851507180648</v>
+      </c>
+      <c r="EC83" s="1">
+        <f t="shared" si="148"/>
+        <v>1307.8742992108841</v>
+      </c>
+      <c r="ED83" s="1">
+        <f t="shared" si="148"/>
+        <v>1294.7955562187753</v>
+      </c>
+      <c r="EE83" s="1">
+        <f t="shared" si="148"/>
+        <v>1281.8476006565875</v>
+      </c>
+      <c r="EF83" s="1">
+        <f t="shared" si="148"/>
+        <v>1269.0291246500217</v>
+      </c>
+      <c r="EG83" s="1">
+        <f t="shared" si="148"/>
+        <v>1256.3388334035214</v>
+      </c>
+      <c r="EH83" s="1">
+        <f t="shared" si="148"/>
+        <v>1243.7754450694863</v>
+      </c>
+      <c r="EI83" s="1">
+        <f t="shared" si="148"/>
+        <v>1231.3376906187914</v>
+      </c>
+      <c r="EJ83" s="1">
+        <f t="shared" si="148"/>
+        <v>1219.0243137126035</v>
+      </c>
+      <c r="EK83" s="1">
+        <f t="shared" si="148"/>
+        <v>1206.8340705754774</v>
+      </c>
+      <c r="EL83" s="1">
+        <f t="shared" si="148"/>
+        <v>1194.7657298697227</v>
+      </c>
+      <c r="EM83" s="1">
+        <f t="shared" si="148"/>
+        <v>1182.8180725710254</v>
+      </c>
+      <c r="EN83" s="1">
+        <f t="shared" si="148"/>
+        <v>1170.989891845315</v>
+      </c>
+      <c r="EO83" s="1">
+        <f t="shared" si="148"/>
+        <v>1159.279992926862</v>
+      </c>
+      <c r="EP83" s="1">
+        <f t="shared" si="148"/>
+        <v>1147.6871929975932</v>
+      </c>
+      <c r="EQ83" s="1">
+        <f t="shared" si="148"/>
+        <v>1136.2103210676173</v>
+      </c>
+      <c r="ER83" s="1">
+        <f t="shared" si="148"/>
+        <v>1124.8482178569411</v>
+      </c>
+      <c r="ES83" s="1">
+        <f t="shared" si="148"/>
+        <v>1113.5997356783716</v>
+      </c>
+      <c r="ET83" s="1">
+        <f t="shared" si="148"/>
+        <v>1102.4637383215879</v>
+      </c>
+      <c r="EU83" s="1">
+        <f t="shared" si="148"/>
+        <v>1091.4391009383721</v>
+      </c>
+      <c r="EV83" s="1">
+        <f t="shared" si="148"/>
+        <v>1080.5247099289884</v>
+      </c>
+      <c r="EW83" s="1">
+        <f t="shared" si="148"/>
+        <v>1069.7194628296984</v>
+      </c>
+      <c r="EX83" s="1">
+        <f t="shared" si="148"/>
+        <v>1059.0222682014014</v>
+      </c>
+      <c r="EY83" s="1">
+        <f t="shared" si="148"/>
+        <v>1048.4320455193874</v>
+      </c>
+      <c r="EZ83" s="1">
+        <f t="shared" si="148"/>
+        <v>1037.9477250641935</v>
+      </c>
+      <c r="FA83" s="1">
+        <f t="shared" si="148"/>
+        <v>1027.5682478135516</v>
+      </c>
+      <c r="FB83" s="1">
+        <f t="shared" si="148"/>
+        <v>1017.292565335416</v>
+      </c>
+      <c r="FC83" s="1">
+        <f t="shared" si="148"/>
+        <v>1007.1196396820619</v>
+      </c>
+    </row>
+    <row r="85" spans="2:159" x14ac:dyDescent="0.3">
+      <c r="B85" t="s">
         <v>101</v>
       </c>
-      <c r="AJ84" s="10">
+      <c r="AJ85" s="10">
         <f>AJ62/AI62-1</f>
         <v>0.52</v>
       </c>
-      <c r="AK84" s="10">
-        <f t="shared" ref="AK84:AU84" si="151">AK62/AJ62-1</f>
-        <v>0.24890350877192979</v>
-      </c>
-      <c r="AL84" s="10">
-        <f t="shared" si="151"/>
+      <c r="AK85" s="10">
+        <f t="shared" ref="AK85:AU85" si="149">AK62/AJ62-1</f>
+        <v>0.24232456140350878</v>
+      </c>
+      <c r="AL85" s="10">
+        <f t="shared" si="149"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AM84" s="10">
-        <f t="shared" si="151"/>
+      <c r="AM85" s="10">
+        <f t="shared" si="149"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AN84" s="10">
-        <f t="shared" si="151"/>
+      <c r="AN85" s="10">
+        <f t="shared" si="149"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AO84" s="10">
-        <f t="shared" si="151"/>
+      <c r="AO85" s="10">
+        <f t="shared" si="149"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AP84" s="10">
-        <f t="shared" si="151"/>
+      <c r="AP85" s="10">
+        <f t="shared" si="149"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AQ84" s="10">
-        <f t="shared" si="151"/>
+      <c r="AQ85" s="10">
+        <f t="shared" si="149"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AR84" s="10">
-        <f t="shared" si="151"/>
+      <c r="AR85" s="10">
+        <f t="shared" si="149"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AS84" s="10">
-        <f t="shared" si="151"/>
+      <c r="AS85" s="10">
+        <f t="shared" si="149"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AT84" s="10">
-        <f t="shared" si="151"/>
+      <c r="AT85" s="10">
+        <f t="shared" si="149"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AU84" s="10">
-        <f t="shared" si="151"/>
+      <c r="AU85" s="10">
+        <f t="shared" si="149"/>
         <v>3.0000000000000027E-2</v>
       </c>
     </row>
-    <row r="85" spans="2:159" x14ac:dyDescent="0.3">
-      <c r="B85" t="s">
+    <row r="86" spans="2:159" x14ac:dyDescent="0.3">
+      <c r="B86" t="s">
         <v>102</v>
       </c>
-      <c r="AJ85" s="10">
-        <f>AJ81/AI81-1</f>
+      <c r="AJ86" s="10">
+        <f>AJ82/AI82-1</f>
         <v>9.2485549132947931E-2</v>
       </c>
-      <c r="AK85" s="10">
-        <f t="shared" ref="AK85:AU85" si="152">AK81/AJ81-1</f>
-        <v>0.50793650793650813</v>
-      </c>
-      <c r="AL85" s="10">
-        <f t="shared" si="152"/>
-        <v>0.5</v>
-      </c>
-      <c r="AM85" s="10">
-        <f t="shared" si="152"/>
+      <c r="AK86" s="10">
+        <f t="shared" ref="AK86:AU86" si="150">AK82/AJ82-1</f>
+        <v>0.41137566137566162</v>
+      </c>
+      <c r="AL86" s="10">
+        <f t="shared" si="150"/>
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="AM86" s="10">
+        <f t="shared" si="150"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AN85" s="10">
-        <f t="shared" si="152"/>
+      <c r="AN86" s="10">
+        <f t="shared" si="150"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AO85" s="10">
-        <f t="shared" si="152"/>
+      <c r="AO86" s="10">
+        <f t="shared" si="150"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AP85" s="10">
-        <f t="shared" si="152"/>
+      <c r="AP86" s="10">
+        <f t="shared" si="150"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AQ85" s="10">
-        <f t="shared" si="152"/>
+      <c r="AQ86" s="10">
+        <f t="shared" si="150"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AR85" s="10">
-        <f t="shared" si="152"/>
+      <c r="AR86" s="10">
+        <f t="shared" si="150"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AS85" s="10">
-        <f t="shared" si="152"/>
+      <c r="AS86" s="10">
+        <f t="shared" si="150"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AT85" s="10">
-        <f t="shared" si="152"/>
+      <c r="AT86" s="10">
+        <f t="shared" si="150"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AU85" s="10">
-        <f t="shared" si="152"/>
+      <c r="AU86" s="10">
+        <f t="shared" si="150"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AW85" t="s">
+      <c r="AW86" t="s">
         <v>95</v>
       </c>
-      <c r="AX85" s="6">
-        <f>NPV(AX23,AJ82:FC82)</f>
-        <v>25212.493568578317</v>
-      </c>
-    </row>
-    <row r="86" spans="2:159" x14ac:dyDescent="0.3">
-      <c r="AW86" t="s">
-        <v>43</v>
-      </c>
       <c r="AX86" s="6">
-        <f>Main!D8</f>
-        <v>2593.2000000000003</v>
+        <f>NPV(AX23,AJ83:FC83)</f>
+        <v>32567.343639517119</v>
       </c>
     </row>
     <row r="87" spans="2:159" x14ac:dyDescent="0.3">
       <c r="AW87" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AX87" s="6">
-        <f>AX85+AX86</f>
-        <v>27805.693568578317</v>
+        <f>Main!D8</f>
+        <v>2323.8999999999996</v>
       </c>
     </row>
     <row r="88" spans="2:159" x14ac:dyDescent="0.3">
       <c r="AW88" t="s">
-        <v>45</v>
-      </c>
-      <c r="AX88" s="5">
-        <f>AX87/AU17</f>
-        <v>83.575874867984126</v>
+        <v>44</v>
+      </c>
+      <c r="AX88" s="6">
+        <f>AX86+AX87</f>
+        <v>34891.243639517117</v>
       </c>
     </row>
     <row r="89" spans="2:159" x14ac:dyDescent="0.3">
       <c r="AW89" t="s">
+        <v>45</v>
+      </c>
+      <c r="AX89" s="5">
+        <f>AX88/AU17</f>
+        <v>104.09082231359523</v>
+      </c>
+    </row>
+    <row r="90" spans="2:159" x14ac:dyDescent="0.3">
+      <c r="AW90" t="s">
         <v>46</v>
       </c>
-      <c r="AX89" s="5">
+      <c r="AX90" s="5">
         <f>Main!D3</f>
-        <v>205.72</v>
-      </c>
-    </row>
-    <row r="90" spans="2:159" x14ac:dyDescent="0.3">
-      <c r="AW90" s="1" t="s">
+        <v>225.31</v>
+      </c>
+    </row>
+    <row r="91" spans="2:159" x14ac:dyDescent="0.3">
+      <c r="AW91" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AX90" s="11">
-        <f>AX88/AX89-1</f>
-        <v>-0.59373967106754755</v>
+      <c r="AX91" s="11">
+        <f>AX89/AX90-1</f>
+        <v>-0.53801064172209301</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/SNOW.xlsx
+++ b/Financial Analysis/SNOW.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{950B4762-AF5B-4957-9AD5-3A9246616DC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F85AE0E-FFBA-43E0-9AA4-B11DA89DCB3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{BC02690B-70EA-46CB-8D56-DD95DADEB9E1}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="105">
   <si>
     <t>SNOW</t>
   </si>
@@ -337,10 +337,10 @@
     <t>CapEx y/y</t>
   </si>
   <si>
-    <t>Q226 8K</t>
-  </si>
-  <si>
     <t>Impairment</t>
+  </si>
+  <si>
+    <t>Restructuring</t>
   </si>
 </sst>
 </file>
@@ -451,15 +451,15 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
-      <xdr:row>87</xdr:row>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
+      <xdr:row>88</xdr:row>
       <xdr:rowOff>91440</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -475,8 +475,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="19324320" y="0"/>
-          <a:ext cx="0" cy="15819120"/>
+          <a:off x="20055840" y="0"/>
+          <a:ext cx="0" cy="16184880"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -509,7 +509,7 @@
     <xdr:to>
       <xdr:col>36</xdr:col>
       <xdr:colOff>15240</xdr:colOff>
-      <xdr:row>93</xdr:row>
+      <xdr:row>94</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -875,17 +875,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="5">
-        <v>225.31</v>
+        <v>198.52</v>
       </c>
       <c r="E3" s="4">
-        <v>45912</v>
+        <v>46052</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45912</v>
+        <v>46052</v>
       </c>
       <c r="G3" s="4">
-        <v>45987</v>
+        <v>46085</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -893,10 +893,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="6">
-        <v>335.2</v>
+        <f>342.2</f>
+        <v>342.2</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -905,7 +906,7 @@
       </c>
       <c r="D5" s="6">
         <f>D3*D4</f>
-        <v>75523.911999999997</v>
+        <v>67933.543999999994</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -913,11 +914,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="6">
-        <f>1880.7+1706+1012.9</f>
-        <v>4599.5999999999995</v>
+        <f>1941.7+1411.4+1041.5</f>
+        <v>4394.6000000000004</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -925,11 +926,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="6">
-        <f>2275.7</f>
-        <v>2275.6999999999998</v>
+        <f>2277.7</f>
+        <v>2277.6999999999998</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -938,7 +939,7 @@
       </c>
       <c r="D8" s="6">
         <f>D6-D7</f>
-        <v>2323.8999999999996</v>
+        <v>2116.9000000000005</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -947,7 +948,7 @@
       </c>
       <c r="D9" s="6">
         <f>D5-D8</f>
-        <v>73200.012000000002</v>
+        <v>65816.644</v>
       </c>
     </row>
   </sheetData>
@@ -958,7 +959,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C98FB002-5468-451A-8BA5-9AE8409D3CEE}">
-  <dimension ref="B1:FD91"/>
+  <dimension ref="B1:FD92"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="19.21875" bestFit="1" customWidth="1"/>
@@ -1314,8 +1315,7 @@
         <v>1145</v>
       </c>
       <c r="AA3" s="9">
-        <f>W3*1.24</f>
-        <v>1168.204</v>
+        <v>1212.9000000000001</v>
       </c>
       <c r="AB3" s="9">
         <f t="shared" ref="AB3" si="0">X3*1.2</f>
@@ -1348,47 +1348,47 @@
       </c>
       <c r="AK3" s="9">
         <f>SUM(Y3:AB3)</f>
-        <v>4539.4639999999999</v>
+        <v>4584.16</v>
       </c>
       <c r="AL3" s="9">
         <f>AK3*1.24</f>
-        <v>5628.9353599999995</v>
+        <v>5684.3584000000001</v>
       </c>
       <c r="AM3" s="9">
         <f>AL3*1.2</f>
-        <v>6754.7224319999996</v>
+        <v>6821.2300800000003</v>
       </c>
       <c r="AN3" s="9">
         <f>AM3*1.14</f>
-        <v>7700.3835724799992</v>
+        <v>7776.2022911999993</v>
       </c>
       <c r="AO3" s="9">
         <f>AN3*1.11</f>
-        <v>8547.4257654527992</v>
+        <v>8631.5845432320002</v>
       </c>
       <c r="AP3" s="9">
         <f>AO3*1.09</f>
-        <v>9316.6940843435514</v>
+        <v>9408.4271521228802</v>
       </c>
       <c r="AQ3" s="9">
         <f>AP3*1.07</f>
-        <v>9968.8626702476013</v>
+        <v>10067.017052771482</v>
       </c>
       <c r="AR3" s="9">
         <f>AQ3*1.05</f>
-        <v>10467.305803759982</v>
+        <v>10570.367905410056</v>
       </c>
       <c r="AS3" s="9">
         <f t="shared" ref="AS3:AU3" si="1">AR3*1.05</f>
-        <v>10990.671093947982</v>
+        <v>11098.886300680559</v>
       </c>
       <c r="AT3" s="9">
         <f t="shared" si="1"/>
-        <v>11540.204648645382</v>
+        <v>11653.830615714587</v>
       </c>
       <c r="AU3" s="9">
         <f t="shared" si="1"/>
-        <v>12117.214881077651</v>
+        <v>12236.522146500318</v>
       </c>
       <c r="AV3" s="9"/>
     </row>
@@ -1465,11 +1465,10 @@
         <v>371.8</v>
       </c>
       <c r="AA4" s="6">
-        <f t="shared" ref="AA4:AB4" si="2">AA3-AA5</f>
-        <v>385.50731999999994</v>
+        <v>390.9</v>
       </c>
       <c r="AB4" s="6">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="AB4" si="2">AB3-AB5</f>
         <v>390.77279999999996</v>
       </c>
       <c r="AD4" s="6">
@@ -1499,47 +1498,47 @@
       </c>
       <c r="AK4" s="6">
         <f>SUM(Y4:AB4)</f>
-        <v>1496.88012</v>
+        <v>1502.2728</v>
       </c>
       <c r="AL4" s="6">
         <f t="shared" ref="AL4:AQ4" si="3">AL3-AL5</f>
-        <v>1801.2593151999995</v>
+        <v>1818.9946879999998</v>
       </c>
       <c r="AM4" s="6">
         <f t="shared" si="3"/>
-        <v>2093.9639539200007</v>
+        <v>2114.5813248000004</v>
       </c>
       <c r="AN4" s="6">
         <f t="shared" si="3"/>
-        <v>2310.1150717440005</v>
+        <v>2332.8606873600002</v>
       </c>
       <c r="AO4" s="6">
         <f t="shared" si="3"/>
-        <v>2564.2277296358398</v>
+        <v>2589.4753629696006</v>
       </c>
       <c r="AP4" s="6">
         <f t="shared" si="3"/>
-        <v>2795.008225303066</v>
+        <v>2822.5281456368648</v>
       </c>
       <c r="AQ4" s="6">
         <f t="shared" si="3"/>
-        <v>2990.6588010742807</v>
+        <v>3020.1051158314449</v>
       </c>
       <c r="AR4" s="6">
         <f t="shared" ref="AR4:AU4" si="4">AR3-AR5</f>
-        <v>3140.1917411279956</v>
+        <v>3171.1103716230173</v>
       </c>
       <c r="AS4" s="6">
         <f t="shared" si="4"/>
-        <v>3297.2013281843947</v>
+        <v>3329.6658902041681</v>
       </c>
       <c r="AT4" s="6">
         <f t="shared" si="4"/>
-        <v>3462.0613945936148</v>
+        <v>3496.149184714377</v>
       </c>
       <c r="AU4" s="6">
         <f t="shared" si="4"/>
-        <v>3635.1644643232958</v>
+        <v>3670.9566439500959</v>
       </c>
     </row>
     <row r="5" spans="2:160" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1557,7 +1556,7 @@
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
       <c r="G5" s="9">
-        <f t="shared" ref="G5:Z5" si="5">G3-G4</f>
+        <f t="shared" ref="G5:AA5" si="5">G3-G4</f>
         <v>92.899999999999991</v>
       </c>
       <c r="H5" s="9">
@@ -1637,11 +1636,11 @@
         <v>773.2</v>
       </c>
       <c r="AA5" s="9">
-        <f t="shared" ref="AA5:AB5" si="6">AA3*0.67</f>
-        <v>782.69668000000001</v>
+        <f t="shared" si="5"/>
+        <v>822.00000000000011</v>
       </c>
       <c r="AB5" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="AB5" si="6">AB3*0.67</f>
         <v>793.38719999999989</v>
       </c>
       <c r="AD5" s="9">
@@ -1674,47 +1673,47 @@
       </c>
       <c r="AK5" s="9">
         <f t="shared" si="7"/>
-        <v>3042.5838800000001</v>
+        <v>3081.8872000000001</v>
       </c>
       <c r="AL5" s="9">
         <f>AL3*0.68</f>
-        <v>3827.6760448</v>
+        <v>3865.3637120000003</v>
       </c>
       <c r="AM5" s="9">
         <f>AM3*0.69</f>
-        <v>4660.7584780799989</v>
+        <v>4706.6487551999999</v>
       </c>
       <c r="AN5" s="9">
         <f>AN3*0.7</f>
-        <v>5390.2685007359987</v>
+        <v>5443.3416038399992</v>
       </c>
       <c r="AO5" s="9">
         <f>AO3*0.7</f>
-        <v>5983.1980358169594</v>
+        <v>6042.1091802623996</v>
       </c>
       <c r="AP5" s="9">
         <f t="shared" ref="AP5:AU5" si="8">AP3*0.7</f>
-        <v>6521.6858590404854</v>
+        <v>6585.8990064860154</v>
       </c>
       <c r="AQ5" s="9">
         <f t="shared" si="8"/>
-        <v>6978.2038691733205</v>
+        <v>7046.9119369400369</v>
       </c>
       <c r="AR5" s="9">
         <f t="shared" si="8"/>
-        <v>7327.1140626319866</v>
+        <v>7399.2575337870385</v>
       </c>
       <c r="AS5" s="9">
         <f t="shared" si="8"/>
-        <v>7693.469765763587</v>
+        <v>7769.2204104763905</v>
       </c>
       <c r="AT5" s="9">
         <f t="shared" si="8"/>
-        <v>8078.1432540517671</v>
+        <v>8157.6814310002101</v>
       </c>
       <c r="AU5" s="9">
         <f t="shared" si="8"/>
-        <v>8482.050416754355</v>
+        <v>8565.5655025502219</v>
       </c>
     </row>
     <row r="6" spans="2:160" x14ac:dyDescent="0.3">
@@ -1790,8 +1789,7 @@
         <v>502</v>
       </c>
       <c r="AA6" s="6">
-        <f>AA3*0.44</f>
-        <v>514.00976000000003</v>
+        <v>550.4</v>
       </c>
       <c r="AB6" s="6">
         <f>AB3*0.44</f>
@@ -1824,47 +1822,47 @@
       </c>
       <c r="AK6" s="6">
         <f>SUM(Y6:AB6)</f>
-        <v>1995.6401599999999</v>
+        <v>2032.0304000000001</v>
       </c>
       <c r="AL6" s="6">
-        <f>AL3*0.37</f>
-        <v>2082.7060831999997</v>
+        <f>AL3*0.38</f>
+        <v>2160.056192</v>
       </c>
       <c r="AM6" s="6">
-        <f>AM3*0.32</f>
-        <v>2161.5111782399999</v>
+        <f>AM3*0.33</f>
+        <v>2251.0059264000001</v>
       </c>
       <c r="AN6" s="6">
-        <f>AN3*0.29</f>
-        <v>2233.1112360191996</v>
+        <f>AN3*0.3</f>
+        <v>2332.8606873599997</v>
       </c>
       <c r="AO6" s="6">
-        <f>AO3*0.27</f>
-        <v>2307.8049566722561</v>
+        <f>AO3*0.28</f>
+        <v>2416.8436721049602</v>
       </c>
       <c r="AP6" s="6">
-        <f>AP3*0.25</f>
-        <v>2329.1735210858878</v>
+        <f>AP3*0.26</f>
+        <v>2446.1910595519489</v>
       </c>
       <c r="AQ6" s="6">
-        <f>AQ3*0.24</f>
-        <v>2392.5270408594242</v>
+        <f>AQ3*0.25</f>
+        <v>2516.7542631928704</v>
       </c>
       <c r="AR6" s="6">
-        <f>AR3*0.23</f>
-        <v>2407.4803348647961</v>
+        <f t="shared" ref="AR6:AU6" si="9">AR3*0.25</f>
+        <v>2642.5919763525139</v>
       </c>
       <c r="AS6" s="6">
-        <f t="shared" ref="AS6:AU6" si="9">AS3*0.23</f>
-        <v>2527.8543516080358</v>
+        <f t="shared" si="9"/>
+        <v>2774.7215751701397</v>
       </c>
       <c r="AT6" s="6">
         <f t="shared" si="9"/>
-        <v>2654.2470691884378</v>
+        <v>2913.4576539286468</v>
       </c>
       <c r="AU6" s="6">
         <f t="shared" si="9"/>
-        <v>2786.9594226478598</v>
+        <v>3059.1305366250795</v>
       </c>
     </row>
     <row r="7" spans="2:160" x14ac:dyDescent="0.3">
@@ -1940,12 +1938,11 @@
         <v>492</v>
       </c>
       <c r="AA7" s="6">
-        <f>W7*1.17</f>
-        <v>517.60799999999995</v>
+        <v>494</v>
       </c>
       <c r="AB7" s="6">
-        <f>X7*1.15</f>
-        <v>566.375</v>
+        <f>X7*1.12</f>
+        <v>551.6</v>
       </c>
       <c r="AD7" s="6">
         <v>68.7</v>
@@ -1974,47 +1971,47 @@
       </c>
       <c r="AK7" s="6">
         <f>SUM(Y7:AB7)</f>
-        <v>2048.3829999999998</v>
+        <v>2010</v>
       </c>
       <c r="AL7" s="6">
         <f>AK7*1.07</f>
-        <v>2191.7698099999998</v>
+        <v>2150.7000000000003</v>
       </c>
       <c r="AM7" s="6">
         <f>AL7*1.04</f>
-        <v>2279.4406024</v>
+        <v>2236.7280000000005</v>
       </c>
       <c r="AN7" s="6">
         <f>AM7*1.03</f>
-        <v>2347.8238204720001</v>
+        <v>2303.8298400000008</v>
       </c>
       <c r="AO7" s="6">
         <f>AN7*1.02</f>
-        <v>2394.7802968814403</v>
+        <v>2349.9064368000008</v>
       </c>
       <c r="AP7" s="6">
         <f t="shared" ref="AP7:AU7" si="10">AO7*1.02</f>
-        <v>2442.6759028190691</v>
+        <v>2396.904565536001</v>
       </c>
       <c r="AQ7" s="6">
         <f t="shared" si="10"/>
-        <v>2491.5294208754503</v>
+        <v>2444.8426568467212</v>
       </c>
       <c r="AR7" s="6">
         <f t="shared" si="10"/>
-        <v>2541.3600092929596</v>
+        <v>2493.7395099836558</v>
       </c>
       <c r="AS7" s="6">
         <f t="shared" si="10"/>
-        <v>2592.1872094788187</v>
+        <v>2543.6143001833289</v>
       </c>
       <c r="AT7" s="6">
         <f t="shared" si="10"/>
-        <v>2644.0309536683949</v>
+        <v>2594.4865861869953</v>
       </c>
       <c r="AU7" s="6">
         <f t="shared" si="10"/>
-        <v>2696.9115727417629</v>
+        <v>2646.3763179107355</v>
       </c>
     </row>
     <row r="8" spans="2:160" x14ac:dyDescent="0.3">
@@ -2090,8 +2087,7 @@
         <v>119.5</v>
       </c>
       <c r="AA8" s="6">
-        <f>W8*1.2</f>
-        <v>127.55999999999999</v>
+        <v>107.1</v>
       </c>
       <c r="AB8" s="6">
         <f>X8*1.2</f>
@@ -2124,47 +2120,47 @@
       </c>
       <c r="AK8" s="6">
         <f>SUM(Y8:AB8)</f>
-        <v>594.78</v>
+        <v>574.32000000000005</v>
       </c>
       <c r="AL8" s="6">
         <f>AK8*1.05</f>
-        <v>624.51900000000001</v>
+        <v>603.03600000000006</v>
       </c>
       <c r="AM8" s="6">
         <f>AL8*1.05</f>
-        <v>655.74495000000002</v>
+        <v>633.18780000000004</v>
       </c>
       <c r="AN8" s="6">
         <f>AM8*1.04</f>
-        <v>681.97474800000009</v>
+        <v>658.51531200000011</v>
       </c>
       <c r="AO8" s="6">
         <f>AN8*1.03</f>
-        <v>702.43399044000012</v>
+        <v>678.27077136000014</v>
       </c>
       <c r="AP8" s="6">
         <f>AO8*1.02</f>
-        <v>716.4826702488001</v>
+        <v>691.83618678720018</v>
       </c>
       <c r="AQ8" s="6">
         <f>AP8*1.02</f>
-        <v>730.81232365377616</v>
+        <v>705.67291052294422</v>
       </c>
       <c r="AR8" s="6">
         <f t="shared" ref="AR8:AU8" si="11">AQ8*1.02</f>
-        <v>745.4285701268517</v>
+        <v>719.78636873340315</v>
       </c>
       <c r="AS8" s="6">
         <f t="shared" si="11"/>
-        <v>760.33714152938876</v>
+        <v>734.18209610807128</v>
       </c>
       <c r="AT8" s="6">
         <f t="shared" si="11"/>
-        <v>775.54388435997657</v>
+        <v>748.86573803023271</v>
       </c>
       <c r="AU8" s="6">
         <f t="shared" si="11"/>
-        <v>791.05476204717615</v>
+        <v>763.84305279083742</v>
       </c>
     </row>
     <row r="9" spans="2:160" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2263,11 +2259,11 @@
       </c>
       <c r="AA9" s="9">
         <f t="shared" si="12"/>
-        <v>-376.48107999999996</v>
+        <v>-329.49999999999989</v>
       </c>
       <c r="AB9" s="9">
         <f t="shared" si="12"/>
-        <v>-432.1382000000001</v>
+        <v>-417.36320000000012</v>
       </c>
       <c r="AD9" s="9">
         <f>AD5-AD6-AD7-AD8</f>
@@ -2299,47 +2295,47 @@
       </c>
       <c r="AK9" s="9">
         <f t="shared" ref="AK9" si="17">AK5-AK6-AK7-AK8</f>
-        <v>-1596.2192799999996</v>
+        <v>-1534.4632000000001</v>
       </c>
       <c r="AL9" s="9">
         <f t="shared" ref="AL9" si="18">AL5-AL6-AL7-AL8</f>
-        <v>-1071.3188483999995</v>
+        <v>-1048.42848</v>
       </c>
       <c r="AM9" s="9">
         <f t="shared" ref="AM9" si="19">AM5-AM6-AM7-AM8</f>
-        <v>-435.93825256000105</v>
+        <v>-414.27297120000082</v>
       </c>
       <c r="AN9" s="9">
         <f t="shared" ref="AN9" si="20">AN5-AN6-AN7-AN8</f>
-        <v>127.35869624479892</v>
+        <v>148.13576447999856</v>
       </c>
       <c r="AO9" s="9">
         <f t="shared" ref="AO9" si="21">AO5-AO6-AO7-AO8</f>
-        <v>578.17879182326283</v>
+        <v>597.08829999743841</v>
       </c>
       <c r="AP9" s="9">
         <f t="shared" ref="AP9" si="22">AP5-AP6-AP7-AP8</f>
-        <v>1033.3537648867284</v>
+        <v>1050.9671946108649</v>
       </c>
       <c r="AQ9" s="9">
         <f t="shared" ref="AQ9:AU9" si="23">AQ5-AQ6-AQ7-AQ8</f>
-        <v>1363.3350837846697</v>
+        <v>1379.6421063775006</v>
       </c>
       <c r="AR9" s="9">
         <f t="shared" si="23"/>
-        <v>1632.8451483473787</v>
+        <v>1543.1396787174651</v>
       </c>
       <c r="AS9" s="9">
         <f t="shared" si="23"/>
-        <v>1813.0910631473434</v>
+        <v>1716.7024390148508</v>
       </c>
       <c r="AT9" s="9">
         <f t="shared" si="23"/>
-        <v>2004.3213468349584</v>
+        <v>1900.8714528543358</v>
       </c>
       <c r="AU9" s="9">
         <f t="shared" si="23"/>
-        <v>2207.1246593175556</v>
+        <v>2096.2155952235689</v>
       </c>
     </row>
     <row r="10" spans="2:160" x14ac:dyDescent="0.3">
@@ -2415,12 +2411,11 @@
         <v>-49.5</v>
       </c>
       <c r="AA10" s="6">
-        <f t="shared" ref="AA10:AB10" si="24">W10*1.05</f>
-        <v>-51.135000000000005</v>
+        <v>-45.5</v>
       </c>
       <c r="AB10" s="6">
-        <f t="shared" si="24"/>
-        <v>-59.115000000000002</v>
+        <f>X10*1.02</f>
+        <v>-57.425999999999995</v>
       </c>
       <c r="AD10" s="6">
         <v>-8.8000000000000007</v>
@@ -2449,47 +2444,47 @@
       </c>
       <c r="AK10" s="6">
         <f>SUM(Y10:AB10)</f>
-        <v>-212.95000000000002</v>
+        <v>-205.62599999999998</v>
       </c>
       <c r="AL10" s="6">
-        <f t="shared" ref="AL10" si="25">AK10*1.02</f>
-        <v>-217.20900000000003</v>
+        <f t="shared" ref="AL10" si="24">AK10*1.02</f>
+        <v>-209.73851999999997</v>
       </c>
       <c r="AM10" s="6">
-        <f t="shared" ref="AM10" si="26">AL10*1.02</f>
-        <v>-221.55318000000003</v>
+        <f t="shared" ref="AM10" si="25">AL10*1.02</f>
+        <v>-213.93329039999998</v>
       </c>
       <c r="AN10" s="6">
-        <f t="shared" ref="AN10" si="27">AM10*1.02</f>
-        <v>-225.98424360000004</v>
+        <f t="shared" ref="AN10" si="26">AM10*1.02</f>
+        <v>-218.21195620799998</v>
       </c>
       <c r="AO10" s="6">
-        <f t="shared" ref="AO10" si="28">AN10*1.02</f>
-        <v>-230.50392847200004</v>
+        <f t="shared" ref="AO10" si="27">AN10*1.02</f>
+        <v>-222.57619533215998</v>
       </c>
       <c r="AP10" s="6">
-        <f t="shared" ref="AP10" si="29">AO10*1.02</f>
-        <v>-235.11400704144003</v>
+        <f t="shared" ref="AP10" si="28">AO10*1.02</f>
+        <v>-227.0277192388032</v>
       </c>
       <c r="AQ10" s="6">
-        <f t="shared" ref="AQ10" si="30">AP10*1.02</f>
-        <v>-239.81628718226884</v>
+        <f t="shared" ref="AQ10" si="29">AP10*1.02</f>
+        <v>-231.56827362357927</v>
       </c>
       <c r="AR10" s="6">
-        <f t="shared" ref="AR10" si="31">AQ10*1.02</f>
-        <v>-244.61261292591422</v>
+        <f t="shared" ref="AR10" si="30">AQ10*1.02</f>
+        <v>-236.19963909605087</v>
       </c>
       <c r="AS10" s="6">
-        <f t="shared" ref="AS10" si="32">AR10*1.02</f>
-        <v>-249.5048651844325</v>
+        <f t="shared" ref="AS10" si="31">AR10*1.02</f>
+        <v>-240.9236318779719</v>
       </c>
       <c r="AT10" s="6">
-        <f t="shared" ref="AT10" si="33">AS10*1.02</f>
-        <v>-254.49496248812116</v>
+        <f t="shared" ref="AT10" si="32">AS10*1.02</f>
+        <v>-245.74210451553134</v>
       </c>
       <c r="AU10" s="6">
-        <f t="shared" ref="AU10" si="34">AT10*1.02</f>
-        <v>-259.58486173788361</v>
+        <f t="shared" ref="AU10" si="33">AT10*1.02</f>
+        <v>-250.65694660584197</v>
       </c>
     </row>
     <row r="11" spans="2:160" x14ac:dyDescent="0.3">
@@ -2557,7 +2552,7 @@
         <v>2.1</v>
       </c>
       <c r="AA11" s="6">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB11" s="6">
         <v>0</v>
@@ -2577,7 +2572,7 @@
       </c>
       <c r="AK11" s="6">
         <f>SUM(Y11:AB11)</f>
-        <v>4.2</v>
+        <v>6.3000000000000007</v>
       </c>
       <c r="AL11" s="6"/>
       <c r="AM11" s="6"/>
@@ -2663,7 +2658,7 @@
         <v>5</v>
       </c>
       <c r="AA12" s="6">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB12" s="6">
         <v>0</v>
@@ -2695,7 +2690,7 @@
       </c>
       <c r="AK12" s="6">
         <f>SUM(Y12:AB12)</f>
-        <v>33.1</v>
+        <v>35</v>
       </c>
       <c r="AL12" s="6">
         <v>0</v>
@@ -2751,156 +2746,156 @@
         <v>-197.5</v>
       </c>
       <c r="I13" s="9">
-        <f t="shared" ref="I13:AB13" si="35">I9-SUM(I10:I12)</f>
+        <f t="shared" ref="I13:AB13" si="34">I9-SUM(I10:I12)</f>
         <v>-203.5</v>
       </c>
       <c r="J13" s="9">
+        <f t="shared" si="34"/>
+        <v>-189.20000000000002</v>
+      </c>
+      <c r="K13" s="9">
+        <f t="shared" si="34"/>
+        <v>-153.80000000000004</v>
+      </c>
+      <c r="L13" s="9">
+        <f t="shared" si="34"/>
+        <v>-130.6</v>
+      </c>
+      <c r="M13" s="9">
+        <f t="shared" si="34"/>
+        <v>-192.4</v>
+      </c>
+      <c r="N13" s="9">
+        <f t="shared" si="34"/>
+        <v>-218.9</v>
+      </c>
+      <c r="O13" s="9">
+        <f t="shared" si="34"/>
+        <v>-197.5</v>
+      </c>
+      <c r="P13" s="9">
+        <f t="shared" si="34"/>
+        <v>-207.2</v>
+      </c>
+      <c r="Q13" s="9">
+        <f t="shared" si="34"/>
+        <v>-232.79999999999995</v>
+      </c>
+      <c r="R13" s="9">
+        <f t="shared" si="34"/>
+        <v>-230.99999999999997</v>
+      </c>
+      <c r="S13" s="9">
+        <f t="shared" si="34"/>
+        <v>-211.29999999999995</v>
+      </c>
+      <c r="T13" s="9">
+        <f t="shared" si="34"/>
+        <v>-174.19999999999987</v>
+      </c>
+      <c r="U13" s="9">
+        <f t="shared" si="34"/>
+        <v>-315</v>
+      </c>
+      <c r="V13" s="9">
+        <f t="shared" si="34"/>
+        <v>-314.00000000000011</v>
+      </c>
+      <c r="W13" s="9">
+        <f t="shared" si="34"/>
+        <v>-325.99999999999994</v>
+      </c>
+      <c r="X13" s="9">
+        <f t="shared" si="34"/>
+        <v>-330.1</v>
+      </c>
+      <c r="Y13" s="9">
+        <f t="shared" si="34"/>
+        <v>-424.30000000000007</v>
+      </c>
+      <c r="Z13" s="9">
+        <f t="shared" si="34"/>
+        <v>-297.89999999999998</v>
+      </c>
+      <c r="AA13" s="9">
+        <f t="shared" si="34"/>
+        <v>-287.99999999999989</v>
+      </c>
+      <c r="AB13" s="9">
+        <f t="shared" si="34"/>
+        <v>-359.93720000000013</v>
+      </c>
+      <c r="AD13" s="9">
+        <f t="shared" ref="AD13:AQ13" si="35">AD9-SUM(AD10:AD12)</f>
+        <v>-177.1</v>
+      </c>
+      <c r="AE13" s="9">
         <f t="shared" si="35"/>
-        <v>-189.20000000000002</v>
-      </c>
-      <c r="K13" s="9">
+        <v>-347.5</v>
+      </c>
+      <c r="AF13" s="9">
         <f t="shared" si="35"/>
-        <v>-153.80000000000004</v>
-      </c>
-      <c r="L13" s="9">
+        <v>-537.00000000000011</v>
+      </c>
+      <c r="AG13" s="9">
         <f t="shared" si="35"/>
-        <v>-130.6</v>
-      </c>
-      <c r="M13" s="9">
+        <v>-677.1</v>
+      </c>
+      <c r="AH13" s="9">
         <f t="shared" si="35"/>
-        <v>-192.4</v>
-      </c>
-      <c r="N13" s="9">
+        <v>-816.00000000000011</v>
+      </c>
+      <c r="AI13" s="9">
         <f t="shared" si="35"/>
-        <v>-218.9</v>
-      </c>
-      <c r="O13" s="9">
+        <v>-849.3</v>
+      </c>
+      <c r="AJ13" s="9">
         <f t="shared" si="35"/>
-        <v>-197.5</v>
-      </c>
-      <c r="P13" s="9">
+        <v>-1285.1000000000004</v>
+      </c>
+      <c r="AK13" s="9">
         <f t="shared" si="35"/>
-        <v>-207.2</v>
-      </c>
-      <c r="Q13" s="9">
+        <v>-1370.1372000000001</v>
+      </c>
+      <c r="AL13" s="9">
         <f t="shared" si="35"/>
-        <v>-232.79999999999995</v>
-      </c>
-      <c r="R13" s="9">
+        <v>-838.68996000000004</v>
+      </c>
+      <c r="AM13" s="9">
         <f t="shared" si="35"/>
-        <v>-230.99999999999997</v>
-      </c>
-      <c r="S13" s="9">
+        <v>-200.33968080000085</v>
+      </c>
+      <c r="AN13" s="9">
         <f t="shared" si="35"/>
-        <v>-211.29999999999995</v>
-      </c>
-      <c r="T13" s="9">
+        <v>366.3477206879985</v>
+      </c>
+      <c r="AO13" s="9">
         <f t="shared" si="35"/>
-        <v>-174.19999999999987</v>
-      </c>
-      <c r="U13" s="9">
+        <v>819.66449532959837</v>
+      </c>
+      <c r="AP13" s="9">
         <f t="shared" si="35"/>
-        <v>-315</v>
-      </c>
-      <c r="V13" s="9">
+        <v>1277.9949138496681</v>
+      </c>
+      <c r="AQ13" s="9">
         <f t="shared" si="35"/>
-        <v>-314.00000000000011</v>
-      </c>
-      <c r="W13" s="9">
-        <f t="shared" si="35"/>
-        <v>-325.99999999999994</v>
-      </c>
-      <c r="X13" s="9">
-        <f t="shared" si="35"/>
-        <v>-330.1</v>
-      </c>
-      <c r="Y13" s="9">
-        <f t="shared" si="35"/>
-        <v>-424.30000000000007</v>
-      </c>
-      <c r="Z13" s="9">
-        <f t="shared" si="35"/>
-        <v>-297.89999999999998</v>
-      </c>
-      <c r="AA13" s="9">
-        <f t="shared" si="35"/>
-        <v>-325.34607999999997</v>
-      </c>
-      <c r="AB13" s="9">
-        <f t="shared" si="35"/>
-        <v>-373.02320000000009</v>
-      </c>
-      <c r="AD13" s="9">
-        <f t="shared" ref="AD13:AQ13" si="36">AD9-SUM(AD10:AD12)</f>
-        <v>-177.1</v>
-      </c>
-      <c r="AE13" s="9">
-        <f t="shared" si="36"/>
-        <v>-347.5</v>
-      </c>
-      <c r="AF13" s="9">
-        <f t="shared" si="36"/>
-        <v>-537.00000000000011</v>
-      </c>
-      <c r="AG13" s="9">
-        <f t="shared" si="36"/>
-        <v>-677.1</v>
-      </c>
-      <c r="AH13" s="9">
-        <f t="shared" si="36"/>
-        <v>-816.00000000000011</v>
-      </c>
-      <c r="AI13" s="9">
-        <f t="shared" si="36"/>
-        <v>-849.3</v>
-      </c>
-      <c r="AJ13" s="9">
-        <f t="shared" si="36"/>
-        <v>-1285.1000000000004</v>
-      </c>
-      <c r="AK13" s="9">
-        <f t="shared" si="36"/>
-        <v>-1420.5692799999995</v>
-      </c>
-      <c r="AL13" s="9">
-        <f t="shared" si="36"/>
-        <v>-854.10984839999946</v>
-      </c>
-      <c r="AM13" s="9">
-        <f t="shared" si="36"/>
-        <v>-214.38507256000102</v>
-      </c>
-      <c r="AN13" s="9">
-        <f t="shared" si="36"/>
-        <v>353.34293984479893</v>
-      </c>
-      <c r="AO13" s="9">
-        <f t="shared" si="36"/>
-        <v>808.68272029526292</v>
-      </c>
-      <c r="AP13" s="9">
-        <f t="shared" si="36"/>
-        <v>1268.4677719281685</v>
-      </c>
-      <c r="AQ13" s="9">
-        <f t="shared" si="36"/>
-        <v>1603.1513709669384</v>
+        <v>1611.2103800010798</v>
       </c>
       <c r="AR13" s="9">
-        <f t="shared" ref="AR13" si="37">AR9-SUM(AR10:AR12)</f>
-        <v>1877.4577612732928</v>
+        <f t="shared" ref="AR13" si="36">AR9-SUM(AR10:AR12)</f>
+        <v>1779.3393178135161</v>
       </c>
       <c r="AS13" s="9">
-        <f t="shared" ref="AS13" si="38">AS9-SUM(AS10:AS12)</f>
-        <v>2062.5959283317761</v>
+        <f t="shared" ref="AS13" si="37">AS9-SUM(AS10:AS12)</f>
+        <v>1957.6260708928228</v>
       </c>
       <c r="AT13" s="9">
-        <f t="shared" ref="AT13" si="39">AT9-SUM(AT10:AT12)</f>
-        <v>2258.8163093230796</v>
+        <f t="shared" ref="AT13" si="38">AT9-SUM(AT10:AT12)</f>
+        <v>2146.6135573698671</v>
       </c>
       <c r="AU13" s="9">
-        <f t="shared" ref="AU13" si="40">AU9-SUM(AU10:AU12)</f>
-        <v>2466.7095210554394</v>
+        <f t="shared" ref="AU13" si="39">AU9-SUM(AU10:AU12)</f>
+        <v>2346.8725418294107</v>
       </c>
     </row>
     <row r="14" spans="2:160" x14ac:dyDescent="0.3">
@@ -2976,7 +2971,7 @@
         <v>0.1</v>
       </c>
       <c r="AA14" s="6">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AB14" s="6">
         <v>0</v>
@@ -3008,46 +3003,46 @@
       </c>
       <c r="AK14" s="6">
         <f>SUM(Y14:AB14)</f>
-        <v>5.8</v>
+        <v>9.5</v>
       </c>
       <c r="AL14" s="6">
         <v>0</v>
       </c>
       <c r="AM14" s="6">
         <f>AM13*0.05</f>
-        <v>-10.719253628000052</v>
+        <v>-10.016984040000043</v>
       </c>
       <c r="AN14" s="6">
         <f>AN13*0.05</f>
-        <v>17.667146992239946</v>
+        <v>18.317386034399927</v>
       </c>
       <c r="AO14" s="6">
         <f>AO13*0.1</f>
-        <v>80.868272029526295</v>
+        <v>81.966449532959842</v>
       </c>
       <c r="AP14" s="6">
         <f>AP13*0.1</f>
-        <v>126.84677719281686</v>
+        <v>127.79949138496681</v>
       </c>
       <c r="AQ14" s="6">
         <f>AQ13*0.11</f>
-        <v>176.34665080636321</v>
+        <v>177.23314180011877</v>
       </c>
       <c r="AR14" s="6">
-        <f t="shared" ref="AR14:AU14" si="41">AR13*0.15</f>
-        <v>281.61866419099391</v>
+        <f t="shared" ref="AR14:AU14" si="40">AR13*0.15</f>
+        <v>266.90089767202738</v>
       </c>
       <c r="AS14" s="6">
-        <f t="shared" si="41"/>
-        <v>309.3893892497664</v>
+        <f t="shared" si="40"/>
+        <v>293.64391063392338</v>
       </c>
       <c r="AT14" s="6">
-        <f t="shared" si="41"/>
-        <v>338.82244639846192</v>
+        <f t="shared" si="40"/>
+        <v>321.99203360548006</v>
       </c>
       <c r="AU14" s="6">
-        <f t="shared" si="41"/>
-        <v>370.00642815831588</v>
+        <f t="shared" si="40"/>
+        <v>352.03088127441157</v>
       </c>
     </row>
     <row r="15" spans="2:160" x14ac:dyDescent="0.3">
@@ -3115,12 +3110,11 @@
         <v>0.1</v>
       </c>
       <c r="AA15" s="6">
-        <f t="shared" ref="AA15:AB15" si="42">AA13*0.005</f>
-        <v>-1.6267303999999998</v>
+        <v>2.4</v>
       </c>
       <c r="AB15" s="6">
-        <f t="shared" si="42"/>
-        <v>-1.8651160000000004</v>
+        <f t="shared" ref="AB15" si="41">AB13*0.005</f>
+        <v>-1.7996860000000008</v>
       </c>
       <c r="AD15" s="6"/>
       <c r="AE15" s="6"/>
@@ -3140,47 +3134,47 @@
       </c>
       <c r="AK15" s="6">
         <f>SUM(Y15:AB15)</f>
-        <v>-3.2918464000000003</v>
+        <v>0.8003139999999993</v>
       </c>
       <c r="AL15" s="6">
-        <f t="shared" ref="AL15:AU15" si="43">AL13*0.01</f>
-        <v>-8.5410984839999955</v>
+        <f t="shared" ref="AL15:AU15" si="42">AL13*0.01</f>
+        <v>-8.3868996000000013</v>
       </c>
       <c r="AM15" s="6">
-        <f t="shared" si="43"/>
-        <v>-2.1438507256000103</v>
+        <f t="shared" si="42"/>
+        <v>-2.0033968080000086</v>
       </c>
       <c r="AN15" s="6">
-        <f t="shared" si="43"/>
-        <v>3.5334293984479892</v>
+        <f t="shared" si="42"/>
+        <v>3.663477206879985</v>
       </c>
       <c r="AO15" s="6">
-        <f t="shared" si="43"/>
-        <v>8.0868272029526302</v>
+        <f t="shared" si="42"/>
+        <v>8.1966449532959835</v>
       </c>
       <c r="AP15" s="6">
-        <f t="shared" si="43"/>
-        <v>12.684677719281686</v>
+        <f t="shared" si="42"/>
+        <v>12.779949138496681</v>
       </c>
       <c r="AQ15" s="6">
-        <f t="shared" si="43"/>
-        <v>16.031513709669383</v>
+        <f t="shared" si="42"/>
+        <v>16.112103800010797</v>
       </c>
       <c r="AR15" s="6">
-        <f t="shared" si="43"/>
-        <v>18.77457761273293</v>
+        <f t="shared" si="42"/>
+        <v>17.793393178135162</v>
       </c>
       <c r="AS15" s="6">
-        <f t="shared" si="43"/>
-        <v>20.625959283317762</v>
+        <f t="shared" si="42"/>
+        <v>19.576260708928228</v>
       </c>
       <c r="AT15" s="6">
-        <f t="shared" si="43"/>
-        <v>22.588163093230797</v>
+        <f t="shared" si="42"/>
+        <v>21.466135573698672</v>
       </c>
       <c r="AU15" s="6">
-        <f t="shared" si="43"/>
-        <v>24.667095210554393</v>
+        <f t="shared" si="42"/>
+        <v>23.468725418294106</v>
       </c>
     </row>
     <row r="16" spans="2:160" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3206,608 +3200,608 @@
         <v>-198.8</v>
       </c>
       <c r="I16" s="9">
-        <f t="shared" ref="I16:X16" si="44">I13-I14-I15</f>
+        <f t="shared" ref="I16:X16" si="43">I13-I14-I15</f>
         <v>-203.2</v>
       </c>
       <c r="J16" s="9">
+        <f t="shared" si="43"/>
+        <v>-189.70000000000002</v>
+      </c>
+      <c r="K16" s="9">
+        <f t="shared" si="43"/>
+        <v>-155.00000000000003</v>
+      </c>
+      <c r="L16" s="9">
+        <f t="shared" si="43"/>
+        <v>-132.1</v>
+      </c>
+      <c r="M16" s="9">
+        <f t="shared" si="43"/>
+        <v>-165.70000000000002</v>
+      </c>
+      <c r="N16" s="9">
+        <f t="shared" si="43"/>
+        <v>-222.70000000000002</v>
+      </c>
+      <c r="O16" s="9">
+        <f t="shared" si="43"/>
+        <v>-201</v>
+      </c>
+      <c r="P16" s="9">
+        <f t="shared" si="43"/>
+        <v>-207.29999999999998</v>
+      </c>
+      <c r="Q16" s="9">
+        <f t="shared" si="43"/>
+        <v>-225.79999999999995</v>
+      </c>
+      <c r="R16" s="9">
+        <f t="shared" si="43"/>
+        <v>-226.79999999999998</v>
+      </c>
+      <c r="S16" s="9">
+        <f t="shared" si="43"/>
+        <v>-214.29999999999995</v>
+      </c>
+      <c r="T16" s="9">
+        <f t="shared" si="43"/>
+        <v>-169.29999999999987</v>
+      </c>
+      <c r="U16" s="9">
+        <f t="shared" si="43"/>
+        <v>-316.89999999999998</v>
+      </c>
+      <c r="V16" s="9">
+        <f t="shared" si="43"/>
+        <v>-316.90000000000015</v>
+      </c>
+      <c r="W16" s="9">
+        <f t="shared" si="43"/>
+        <v>-324.2999999999999</v>
+      </c>
+      <c r="X16" s="9">
+        <f t="shared" si="43"/>
+        <v>-327.60000000000002</v>
+      </c>
+      <c r="Y16" s="9">
+        <f t="shared" ref="Y16:AB16" si="44">Y13-Y14-Y15</f>
+        <v>-430.10000000000008</v>
+      </c>
+      <c r="Z16" s="9">
         <f t="shared" si="44"/>
-        <v>-189.70000000000002</v>
-      </c>
-      <c r="K16" s="9">
+        <v>-298.10000000000002</v>
+      </c>
+      <c r="AA16" s="9">
         <f t="shared" si="44"/>
-        <v>-155.00000000000003</v>
-      </c>
-      <c r="L16" s="9">
+        <v>-294.09999999999985</v>
+      </c>
+      <c r="AB16" s="9">
         <f t="shared" si="44"/>
-        <v>-132.1</v>
-      </c>
-      <c r="M16" s="9">
-        <f t="shared" si="44"/>
-        <v>-165.70000000000002</v>
-      </c>
-      <c r="N16" s="9">
-        <f t="shared" si="44"/>
-        <v>-222.70000000000002</v>
-      </c>
-      <c r="O16" s="9">
-        <f t="shared" si="44"/>
-        <v>-201</v>
-      </c>
-      <c r="P16" s="9">
-        <f t="shared" si="44"/>
-        <v>-207.29999999999998</v>
-      </c>
-      <c r="Q16" s="9">
-        <f t="shared" si="44"/>
-        <v>-225.79999999999995</v>
-      </c>
-      <c r="R16" s="9">
-        <f t="shared" si="44"/>
-        <v>-226.79999999999998</v>
-      </c>
-      <c r="S16" s="9">
-        <f t="shared" si="44"/>
-        <v>-214.29999999999995</v>
-      </c>
-      <c r="T16" s="9">
-        <f t="shared" si="44"/>
-        <v>-169.29999999999987</v>
-      </c>
-      <c r="U16" s="9">
-        <f t="shared" si="44"/>
-        <v>-316.89999999999998</v>
-      </c>
-      <c r="V16" s="9">
-        <f t="shared" si="44"/>
-        <v>-316.90000000000015</v>
-      </c>
-      <c r="W16" s="9">
-        <f t="shared" si="44"/>
-        <v>-324.2999999999999</v>
-      </c>
-      <c r="X16" s="9">
-        <f t="shared" si="44"/>
-        <v>-327.60000000000002</v>
-      </c>
-      <c r="Y16" s="9">
-        <f t="shared" ref="Y16:AB16" si="45">Y13-Y14-Y15</f>
-        <v>-430.10000000000008</v>
-      </c>
-      <c r="Z16" s="9">
+        <v>-358.13751400000012</v>
+      </c>
+      <c r="AD16" s="9">
+        <f t="shared" ref="AD16:AQ16" si="45">AD13-AD14-AD15</f>
+        <v>-177.9</v>
+      </c>
+      <c r="AE16" s="9">
         <f t="shared" si="45"/>
-        <v>-298.10000000000002</v>
-      </c>
-      <c r="AA16" s="9">
+        <v>-348.5</v>
+      </c>
+      <c r="AF16" s="9">
         <f t="shared" si="45"/>
-        <v>-323.71934959999999</v>
-      </c>
-      <c r="AB16" s="9">
+        <v>-539.10000000000014</v>
+      </c>
+      <c r="AG16" s="9">
         <f t="shared" si="45"/>
-        <v>-371.15808400000009</v>
-      </c>
-      <c r="AD16" s="9">
-        <f t="shared" ref="AD16:AQ16" si="46">AD13-AD14-AD15</f>
-        <v>-177.9</v>
-      </c>
-      <c r="AE16" s="9">
-        <f t="shared" si="46"/>
-        <v>-348.5</v>
-      </c>
-      <c r="AF16" s="9">
-        <f t="shared" si="46"/>
-        <v>-539.10000000000014</v>
-      </c>
-      <c r="AG16" s="9">
-        <f t="shared" si="46"/>
         <v>-680</v>
       </c>
       <c r="AH16" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="45"/>
         <v>-796.70000000000016</v>
       </c>
       <c r="AI16" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="45"/>
         <v>-836.19999999999993</v>
       </c>
       <c r="AJ16" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="45"/>
         <v>-1285.7000000000003</v>
       </c>
       <c r="AK16" s="9">
-        <f t="shared" si="46"/>
-        <v>-1423.0774335999995</v>
+        <f t="shared" si="45"/>
+        <v>-1380.4375140000002</v>
       </c>
       <c r="AL16" s="9">
-        <f t="shared" si="46"/>
-        <v>-845.56874991599943</v>
+        <f t="shared" si="45"/>
+        <v>-830.30306040000005</v>
       </c>
       <c r="AM16" s="9">
-        <f t="shared" si="46"/>
-        <v>-201.52196820640097</v>
+        <f t="shared" si="45"/>
+        <v>-188.31929995200079</v>
       </c>
       <c r="AN16" s="9">
-        <f t="shared" si="46"/>
-        <v>332.14236345411098</v>
+        <f t="shared" si="45"/>
+        <v>344.3668574467186</v>
       </c>
       <c r="AO16" s="9">
-        <f t="shared" si="46"/>
-        <v>719.72762106278401</v>
+        <f t="shared" si="45"/>
+        <v>729.50140084334259</v>
       </c>
       <c r="AP16" s="9">
-        <f t="shared" si="46"/>
-        <v>1128.93631701607</v>
+        <f t="shared" si="45"/>
+        <v>1137.4154733262046</v>
       </c>
       <c r="AQ16" s="9">
-        <f t="shared" si="46"/>
-        <v>1410.7732064509059</v>
+        <f t="shared" si="45"/>
+        <v>1417.8651344009502</v>
       </c>
       <c r="AR16" s="9">
-        <f t="shared" ref="AR16" si="47">AR13-AR14-AR15</f>
-        <v>1577.064519469566</v>
+        <f t="shared" ref="AR16" si="46">AR13-AR14-AR15</f>
+        <v>1494.6450269633535</v>
       </c>
       <c r="AS16" s="9">
-        <f t="shared" ref="AS16" si="48">AS13-AS14-AS15</f>
-        <v>1732.580579798692</v>
+        <f t="shared" ref="AS16" si="47">AS13-AS14-AS15</f>
+        <v>1644.4058995499713</v>
       </c>
       <c r="AT16" s="9">
-        <f t="shared" ref="AT16" si="49">AT13-AT14-AT15</f>
-        <v>1897.4056998313868</v>
+        <f t="shared" ref="AT16" si="48">AT13-AT14-AT15</f>
+        <v>1803.1553881906882</v>
       </c>
       <c r="AU16" s="9">
-        <f t="shared" ref="AU16" si="50">AU13-AU14-AU15</f>
-        <v>2072.0359976865693</v>
+        <f t="shared" ref="AU16" si="49">AU13-AU14-AU15</f>
+        <v>1971.3729351367051</v>
       </c>
       <c r="AV16" s="1">
         <f>AU16*(1+$AX$22)</f>
-        <v>2051.3156377097034</v>
+        <v>1951.6592057853381</v>
       </c>
       <c r="AW16" s="1">
-        <f t="shared" ref="AW16:DH16" si="51">AV16*(1+$AX$22)</f>
-        <v>2030.8024813326065</v>
+        <f t="shared" ref="AW16:DH16" si="50">AV16*(1+$AX$22)</f>
+        <v>1932.1426137274848</v>
       </c>
       <c r="AX16" s="1">
+        <f t="shared" si="50"/>
+        <v>1912.82118759021</v>
+      </c>
+      <c r="AY16" s="1">
+        <f t="shared" si="50"/>
+        <v>1893.692975714308</v>
+      </c>
+      <c r="AZ16" s="1">
+        <f t="shared" si="50"/>
+        <v>1874.7560459571648</v>
+      </c>
+      <c r="BA16" s="1">
+        <f t="shared" si="50"/>
+        <v>1856.0084854975933</v>
+      </c>
+      <c r="BB16" s="1">
+        <f t="shared" si="50"/>
+        <v>1837.4484006426173</v>
+      </c>
+      <c r="BC16" s="1">
+        <f t="shared" si="50"/>
+        <v>1819.0739166361911</v>
+      </c>
+      <c r="BD16" s="1">
+        <f t="shared" si="50"/>
+        <v>1800.8831774698292</v>
+      </c>
+      <c r="BE16" s="1">
+        <f t="shared" si="50"/>
+        <v>1782.8743456951308</v>
+      </c>
+      <c r="BF16" s="1">
+        <f t="shared" si="50"/>
+        <v>1765.0456022381795</v>
+      </c>
+      <c r="BG16" s="1">
+        <f t="shared" si="50"/>
+        <v>1747.3951462157977</v>
+      </c>
+      <c r="BH16" s="1">
+        <f t="shared" si="50"/>
+        <v>1729.9211947536396</v>
+      </c>
+      <c r="BI16" s="1">
+        <f t="shared" si="50"/>
+        <v>1712.6219828061032</v>
+      </c>
+      <c r="BJ16" s="1">
+        <f t="shared" si="50"/>
+        <v>1695.4957629780422</v>
+      </c>
+      <c r="BK16" s="1">
+        <f t="shared" si="50"/>
+        <v>1678.5408053482618</v>
+      </c>
+      <c r="BL16" s="1">
+        <f t="shared" si="50"/>
+        <v>1661.7553972947792</v>
+      </c>
+      <c r="BM16" s="1">
+        <f t="shared" si="50"/>
+        <v>1645.1378433218313</v>
+      </c>
+      <c r="BN16" s="1">
+        <f t="shared" si="50"/>
+        <v>1628.686464888613</v>
+      </c>
+      <c r="BO16" s="1">
+        <f t="shared" si="50"/>
+        <v>1612.3996002397269</v>
+      </c>
+      <c r="BP16" s="1">
+        <f t="shared" si="50"/>
+        <v>1596.2756042373296</v>
+      </c>
+      <c r="BQ16" s="1">
+        <f t="shared" si="50"/>
+        <v>1580.3128481949564</v>
+      </c>
+      <c r="BR16" s="1">
+        <f t="shared" si="50"/>
+        <v>1564.5097197130067</v>
+      </c>
+      <c r="BS16" s="1">
+        <f t="shared" si="50"/>
+        <v>1548.8646225158766</v>
+      </c>
+      <c r="BT16" s="1">
+        <f t="shared" si="50"/>
+        <v>1533.3759762907177</v>
+      </c>
+      <c r="BU16" s="1">
+        <f t="shared" si="50"/>
+        <v>1518.0422165278105</v>
+      </c>
+      <c r="BV16" s="1">
+        <f t="shared" si="50"/>
+        <v>1502.8617943625325</v>
+      </c>
+      <c r="BW16" s="1">
+        <f t="shared" si="50"/>
+        <v>1487.8331764189072</v>
+      </c>
+      <c r="BX16" s="1">
+        <f t="shared" si="50"/>
+        <v>1472.954844654718</v>
+      </c>
+      <c r="BY16" s="1">
+        <f t="shared" si="50"/>
+        <v>1458.2252962081709</v>
+      </c>
+      <c r="BZ16" s="1">
+        <f t="shared" si="50"/>
+        <v>1443.6430432460893</v>
+      </c>
+      <c r="CA16" s="1">
+        <f t="shared" si="50"/>
+        <v>1429.2066128136285</v>
+      </c>
+      <c r="CB16" s="1">
+        <f t="shared" si="50"/>
+        <v>1414.9145466854923</v>
+      </c>
+      <c r="CC16" s="1">
+        <f t="shared" si="50"/>
+        <v>1400.7654012186374</v>
+      </c>
+      <c r="CD16" s="1">
+        <f t="shared" si="50"/>
+        <v>1386.7577472064511</v>
+      </c>
+      <c r="CE16" s="1">
+        <f t="shared" si="50"/>
+        <v>1372.8901697343865</v>
+      </c>
+      <c r="CF16" s="1">
+        <f t="shared" si="50"/>
+        <v>1359.1612680370426</v>
+      </c>
+      <c r="CG16" s="1">
+        <f t="shared" si="50"/>
+        <v>1345.5696553566722</v>
+      </c>
+      <c r="CH16" s="1">
+        <f t="shared" si="50"/>
+        <v>1332.1139588031056</v>
+      </c>
+      <c r="CI16" s="1">
+        <f t="shared" si="50"/>
+        <v>1318.7928192150746</v>
+      </c>
+      <c r="CJ16" s="1">
+        <f t="shared" si="50"/>
+        <v>1305.6048910229238</v>
+      </c>
+      <c r="CK16" s="1">
+        <f t="shared" si="50"/>
+        <v>1292.5488421126945</v>
+      </c>
+      <c r="CL16" s="1">
+        <f t="shared" si="50"/>
+        <v>1279.6233536915674</v>
+      </c>
+      <c r="CM16" s="1">
+        <f t="shared" si="50"/>
+        <v>1266.8271201546518</v>
+      </c>
+      <c r="CN16" s="1">
+        <f t="shared" si="50"/>
+        <v>1254.1588489531052</v>
+      </c>
+      <c r="CO16" s="1">
+        <f t="shared" si="50"/>
+        <v>1241.6172604635742</v>
+      </c>
+      <c r="CP16" s="1">
+        <f t="shared" si="50"/>
+        <v>1229.2010878589385</v>
+      </c>
+      <c r="CQ16" s="1">
+        <f t="shared" si="50"/>
+        <v>1216.909076980349</v>
+      </c>
+      <c r="CR16" s="1">
+        <f t="shared" si="50"/>
+        <v>1204.7399862105456</v>
+      </c>
+      <c r="CS16" s="1">
+        <f t="shared" si="50"/>
+        <v>1192.69258634844</v>
+      </c>
+      <c r="CT16" s="1">
+        <f t="shared" si="50"/>
+        <v>1180.7656604849556</v>
+      </c>
+      <c r="CU16" s="1">
+        <f t="shared" si="50"/>
+        <v>1168.9580038801059</v>
+      </c>
+      <c r="CV16" s="1">
+        <f t="shared" si="50"/>
+        <v>1157.2684238413049</v>
+      </c>
+      <c r="CW16" s="1">
+        <f t="shared" si="50"/>
+        <v>1145.6957396028918</v>
+      </c>
+      <c r="CX16" s="1">
+        <f t="shared" si="50"/>
+        <v>1134.2387822068629</v>
+      </c>
+      <c r="CY16" s="1">
+        <f t="shared" si="50"/>
+        <v>1122.8963943847943</v>
+      </c>
+      <c r="CZ16" s="1">
+        <f t="shared" si="50"/>
+        <v>1111.6674304409464</v>
+      </c>
+      <c r="DA16" s="1">
+        <f t="shared" si="50"/>
+        <v>1100.5507561365368</v>
+      </c>
+      <c r="DB16" s="1">
+        <f t="shared" si="50"/>
+        <v>1089.5452485751714</v>
+      </c>
+      <c r="DC16" s="1">
+        <f t="shared" si="50"/>
+        <v>1078.6497960894196</v>
+      </c>
+      <c r="DD16" s="1">
+        <f t="shared" si="50"/>
+        <v>1067.8632981285255</v>
+      </c>
+      <c r="DE16" s="1">
+        <f t="shared" si="50"/>
+        <v>1057.1846651472401</v>
+      </c>
+      <c r="DF16" s="1">
+        <f t="shared" si="50"/>
+        <v>1046.6128184957677</v>
+      </c>
+      <c r="DG16" s="1">
+        <f t="shared" si="50"/>
+        <v>1036.1466903108101</v>
+      </c>
+      <c r="DH16" s="1">
+        <f t="shared" si="50"/>
+        <v>1025.785223407702</v>
+      </c>
+      <c r="DI16" s="1">
+        <f t="shared" ref="DI16:FD16" si="51">DH16*(1+$AX$22)</f>
+        <v>1015.5273711736249</v>
+      </c>
+      <c r="DJ16" s="1">
         <f t="shared" si="51"/>
-        <v>2010.4944565192804</v>
-      </c>
-      <c r="AY16" s="1">
+        <v>1005.3720974618886</v>
+      </c>
+      <c r="DK16" s="1">
         <f t="shared" si="51"/>
-        <v>1990.3895119540875</v>
-      </c>
-      <c r="AZ16" s="1">
+        <v>995.3183764872698</v>
+      </c>
+      <c r="DL16" s="1">
         <f t="shared" si="51"/>
-        <v>1970.4856168345466</v>
-      </c>
-      <c r="BA16" s="1">
+        <v>985.36519272239707</v>
+      </c>
+      <c r="DM16" s="1">
         <f t="shared" si="51"/>
-        <v>1950.7807606662011</v>
-      </c>
-      <c r="BB16" s="1">
+        <v>975.51154079517312</v>
+      </c>
+      <c r="DN16" s="1">
         <f t="shared" si="51"/>
-        <v>1931.2729530595391</v>
-      </c>
-      <c r="BC16" s="1">
+        <v>965.75642538722138</v>
+      </c>
+      <c r="DO16" s="1">
         <f t="shared" si="51"/>
-        <v>1911.9602235289437</v>
-      </c>
-      <c r="BD16" s="1">
+        <v>956.09886113334915</v>
+      </c>
+      <c r="DP16" s="1">
         <f t="shared" si="51"/>
-        <v>1892.8406212936543</v>
-      </c>
-      <c r="BE16" s="1">
+        <v>946.53787252201562</v>
+      </c>
+      <c r="DQ16" s="1">
         <f t="shared" si="51"/>
-        <v>1873.9122150807177</v>
-      </c>
-      <c r="BF16" s="1">
+        <v>937.07249379679547</v>
+      </c>
+      <c r="DR16" s="1">
         <f t="shared" si="51"/>
-        <v>1855.1730929299106</v>
-      </c>
-      <c r="BG16" s="1">
+        <v>927.70176885882756</v>
+      </c>
+      <c r="DS16" s="1">
         <f t="shared" si="51"/>
-        <v>1836.6213620006115</v>
-      </c>
-      <c r="BH16" s="1">
+        <v>918.42475117023923</v>
+      </c>
+      <c r="DT16" s="1">
         <f t="shared" si="51"/>
-        <v>1818.2551483806053</v>
-      </c>
-      <c r="BI16" s="1">
+        <v>909.2405036585368</v>
+      </c>
+      <c r="DU16" s="1">
         <f t="shared" si="51"/>
-        <v>1800.0725968967993</v>
-      </c>
-      <c r="BJ16" s="1">
+        <v>900.14809862195136</v>
+      </c>
+      <c r="DV16" s="1">
         <f t="shared" si="51"/>
-        <v>1782.0718709278312</v>
-      </c>
-      <c r="BK16" s="1">
+        <v>891.14661763573179</v>
+      </c>
+      <c r="DW16" s="1">
         <f t="shared" si="51"/>
-        <v>1764.251152218553</v>
-      </c>
-      <c r="BL16" s="1">
+        <v>882.23515145937449</v>
+      </c>
+      <c r="DX16" s="1">
         <f t="shared" si="51"/>
-        <v>1746.6086406963675</v>
-      </c>
-      <c r="BM16" s="1">
+        <v>873.41279994478077</v>
+      </c>
+      <c r="DY16" s="1">
         <f t="shared" si="51"/>
-        <v>1729.1425542894037</v>
-      </c>
-      <c r="BN16" s="1">
+        <v>864.67867194533301</v>
+      </c>
+      <c r="DZ16" s="1">
         <f t="shared" si="51"/>
-        <v>1711.8511287465096</v>
-      </c>
-      <c r="BO16" s="1">
+        <v>856.03188522587971</v>
+      </c>
+      <c r="EA16" s="1">
         <f t="shared" si="51"/>
-        <v>1694.7326174590446</v>
-      </c>
-      <c r="BP16" s="1">
+        <v>847.47156637362093</v>
+      </c>
+      <c r="EB16" s="1">
         <f t="shared" si="51"/>
-        <v>1677.7852912844542</v>
-      </c>
-      <c r="BQ16" s="1">
+        <v>838.99685070988471</v>
+      </c>
+      <c r="EC16" s="1">
         <f t="shared" si="51"/>
-        <v>1661.0074383716096</v>
-      </c>
-      <c r="BR16" s="1">
+        <v>830.60688220278587</v>
+      </c>
+      <c r="ED16" s="1">
         <f t="shared" si="51"/>
-        <v>1644.3973639878934</v>
-      </c>
-      <c r="BS16" s="1">
+        <v>822.30081338075797</v>
+      </c>
+      <c r="EE16" s="1">
         <f t="shared" si="51"/>
-        <v>1627.9533903480144</v>
-      </c>
-      <c r="BT16" s="1">
+        <v>814.07780524695033</v>
+      </c>
+      <c r="EF16" s="1">
         <f t="shared" si="51"/>
-        <v>1611.6738564445343</v>
-      </c>
-      <c r="BU16" s="1">
+        <v>805.93702719448083</v>
+      </c>
+      <c r="EG16" s="1">
         <f t="shared" si="51"/>
-        <v>1595.557117880089</v>
-      </c>
-      <c r="BV16" s="1">
+        <v>797.87765692253606</v>
+      </c>
+      <c r="EH16" s="1">
         <f t="shared" si="51"/>
-        <v>1579.601546701288</v>
-      </c>
-      <c r="BW16" s="1">
+        <v>789.89888035331069</v>
+      </c>
+      <c r="EI16" s="1">
         <f t="shared" si="51"/>
-        <v>1563.8055312342751</v>
-      </c>
-      <c r="BX16" s="1">
+        <v>781.99989154977754</v>
+      </c>
+      <c r="EJ16" s="1">
         <f t="shared" si="51"/>
-        <v>1548.1674759219325</v>
-      </c>
-      <c r="BY16" s="1">
+        <v>774.17989263427978</v>
+      </c>
+      <c r="EK16" s="1">
         <f t="shared" si="51"/>
-        <v>1532.6858011627132</v>
-      </c>
-      <c r="BZ16" s="1">
+        <v>766.43809370793701</v>
+      </c>
+      <c r="EL16" s="1">
         <f t="shared" si="51"/>
-        <v>1517.3589431510861</v>
-      </c>
-      <c r="CA16" s="1">
+        <v>758.77371277085763</v>
+      </c>
+      <c r="EM16" s="1">
         <f t="shared" si="51"/>
-        <v>1502.1853537195752</v>
-      </c>
-      <c r="CB16" s="1">
+        <v>751.18597564314905</v>
+      </c>
+      <c r="EN16" s="1">
         <f t="shared" si="51"/>
-        <v>1487.1635001823795</v>
-      </c>
-      <c r="CC16" s="1">
+        <v>743.67411588671757</v>
+      </c>
+      <c r="EO16" s="1">
         <f t="shared" si="51"/>
-        <v>1472.2918651805558</v>
-      </c>
-      <c r="CD16" s="1">
+        <v>736.23737472785035</v>
+      </c>
+      <c r="EP16" s="1">
         <f t="shared" si="51"/>
-        <v>1457.5689465287503</v>
-      </c>
-      <c r="CE16" s="1">
+        <v>728.87500098057183</v>
+      </c>
+      <c r="EQ16" s="1">
         <f t="shared" si="51"/>
-        <v>1442.9932570634628</v>
-      </c>
-      <c r="CF16" s="1">
+        <v>721.58625097076606</v>
+      </c>
+      <c r="ER16" s="1">
         <f t="shared" si="51"/>
-        <v>1428.5633244928281</v>
-      </c>
-      <c r="CG16" s="1">
+        <v>714.37038846105838</v>
+      </c>
+      <c r="ES16" s="1">
         <f t="shared" si="51"/>
-        <v>1414.2776912478998</v>
-      </c>
-      <c r="CH16" s="1">
+        <v>707.22668457644784</v>
+      </c>
+      <c r="ET16" s="1">
         <f t="shared" si="51"/>
-        <v>1400.1349143354207</v>
-      </c>
-      <c r="CI16" s="1">
+        <v>700.15441773068335</v>
+      </c>
+      <c r="EU16" s="1">
         <f t="shared" si="51"/>
-        <v>1386.1335651920665</v>
-      </c>
-      <c r="CJ16" s="1">
+        <v>693.15287355337648</v>
+      </c>
+      <c r="EV16" s="1">
         <f t="shared" si="51"/>
-        <v>1372.2722295401459</v>
-      </c>
-      <c r="CK16" s="1">
+        <v>686.22134481784269</v>
+      </c>
+      <c r="EW16" s="1">
         <f t="shared" si="51"/>
-        <v>1358.5495072447443</v>
-      </c>
-      <c r="CL16" s="1">
+        <v>679.35913136966428</v>
+      </c>
+      <c r="EX16" s="1">
         <f t="shared" si="51"/>
-        <v>1344.9640121722969</v>
-      </c>
-      <c r="CM16" s="1">
+        <v>672.56554005596763</v>
+      </c>
+      <c r="EY16" s="1">
         <f t="shared" si="51"/>
-        <v>1331.5143720505739</v>
-      </c>
-      <c r="CN16" s="1">
+        <v>665.8398846554079</v>
+      </c>
+      <c r="EZ16" s="1">
         <f t="shared" si="51"/>
-        <v>1318.1992283300681</v>
-      </c>
-      <c r="CO16" s="1">
+        <v>659.18148580885384</v>
+      </c>
+      <c r="FA16" s="1">
         <f t="shared" si="51"/>
-        <v>1305.0172360467675</v>
-      </c>
-      <c r="CP16" s="1">
+        <v>652.58967095076525</v>
+      </c>
+      <c r="FB16" s="1">
         <f t="shared" si="51"/>
-        <v>1291.9670636862998</v>
-      </c>
-      <c r="CQ16" s="1">
+        <v>646.06377424125765</v>
+      </c>
+      <c r="FC16" s="1">
         <f t="shared" si="51"/>
-        <v>1279.0473930494368</v>
-      </c>
-      <c r="CR16" s="1">
+        <v>639.60313649884506</v>
+      </c>
+      <c r="FD16" s="1">
         <f t="shared" si="51"/>
-        <v>1266.2569191189425</v>
-      </c>
-      <c r="CS16" s="1">
-        <f t="shared" si="51"/>
-        <v>1253.594349927753</v>
-      </c>
-      <c r="CT16" s="1">
-        <f t="shared" si="51"/>
-        <v>1241.0584064284756</v>
-      </c>
-      <c r="CU16" s="1">
-        <f t="shared" si="51"/>
-        <v>1228.6478223641907</v>
-      </c>
-      <c r="CV16" s="1">
-        <f t="shared" si="51"/>
-        <v>1216.3613441405487</v>
-      </c>
-      <c r="CW16" s="1">
-        <f t="shared" si="51"/>
-        <v>1204.1977306991432</v>
-      </c>
-      <c r="CX16" s="1">
-        <f t="shared" si="51"/>
-        <v>1192.1557533921518</v>
-      </c>
-      <c r="CY16" s="1">
-        <f t="shared" si="51"/>
-        <v>1180.2341958582304</v>
-      </c>
-      <c r="CZ16" s="1">
-        <f t="shared" si="51"/>
-        <v>1168.4318538996481</v>
-      </c>
-      <c r="DA16" s="1">
-        <f t="shared" si="51"/>
-        <v>1156.7475353606517</v>
-      </c>
-      <c r="DB16" s="1">
-        <f t="shared" si="51"/>
-        <v>1145.1800600070451</v>
-      </c>
-      <c r="DC16" s="1">
-        <f t="shared" si="51"/>
-        <v>1133.7282594069745</v>
-      </c>
-      <c r="DD16" s="1">
-        <f t="shared" si="51"/>
-        <v>1122.3909768129047</v>
-      </c>
-      <c r="DE16" s="1">
-        <f t="shared" si="51"/>
-        <v>1111.1670670447756</v>
-      </c>
-      <c r="DF16" s="1">
-        <f t="shared" si="51"/>
-        <v>1100.055396374328</v>
-      </c>
-      <c r="DG16" s="1">
-        <f t="shared" si="51"/>
-        <v>1089.0548424105848</v>
-      </c>
-      <c r="DH16" s="1">
-        <f t="shared" si="51"/>
-        <v>1078.1642939864789</v>
-      </c>
-      <c r="DI16" s="1">
-        <f t="shared" ref="DI16:FD16" si="52">DH16*(1+$AX$22)</f>
-        <v>1067.3826510466142</v>
-      </c>
-      <c r="DJ16" s="1">
-        <f t="shared" si="52"/>
-        <v>1056.7088245361481</v>
-      </c>
-      <c r="DK16" s="1">
-        <f t="shared" si="52"/>
-        <v>1046.1417362907866</v>
-      </c>
-      <c r="DL16" s="1">
-        <f t="shared" si="52"/>
-        <v>1035.6803189278787</v>
-      </c>
-      <c r="DM16" s="1">
-        <f t="shared" si="52"/>
-        <v>1025.3235157386</v>
-      </c>
-      <c r="DN16" s="1">
-        <f t="shared" si="52"/>
-        <v>1015.070280581214</v>
-      </c>
-      <c r="DO16" s="1">
-        <f t="shared" si="52"/>
-        <v>1004.9195777754019</v>
-      </c>
-      <c r="DP16" s="1">
-        <f t="shared" si="52"/>
-        <v>994.87038199764788</v>
-      </c>
-      <c r="DQ16" s="1">
-        <f t="shared" si="52"/>
-        <v>984.92167817767142</v>
-      </c>
-      <c r="DR16" s="1">
-        <f t="shared" si="52"/>
-        <v>975.07246139589472</v>
-      </c>
-      <c r="DS16" s="1">
-        <f t="shared" si="52"/>
-        <v>965.32173678193578</v>
-      </c>
-      <c r="DT16" s="1">
-        <f t="shared" si="52"/>
-        <v>955.66851941411642</v>
-      </c>
-      <c r="DU16" s="1">
-        <f t="shared" si="52"/>
-        <v>946.11183421997521</v>
-      </c>
-      <c r="DV16" s="1">
-        <f t="shared" si="52"/>
-        <v>936.6507158777755</v>
-      </c>
-      <c r="DW16" s="1">
-        <f t="shared" si="52"/>
-        <v>927.28420871899777</v>
-      </c>
-      <c r="DX16" s="1">
-        <f t="shared" si="52"/>
-        <v>918.01136663180773</v>
-      </c>
-      <c r="DY16" s="1">
-        <f t="shared" si="52"/>
-        <v>908.83125296548963</v>
-      </c>
-      <c r="DZ16" s="1">
-        <f t="shared" si="52"/>
-        <v>899.74294043583473</v>
-      </c>
-      <c r="EA16" s="1">
-        <f t="shared" si="52"/>
-        <v>890.74551103147633</v>
-      </c>
-      <c r="EB16" s="1">
-        <f t="shared" si="52"/>
-        <v>881.83805592116153</v>
-      </c>
-      <c r="EC16" s="1">
-        <f t="shared" si="52"/>
-        <v>873.01967536194991</v>
-      </c>
-      <c r="ED16" s="1">
-        <f t="shared" si="52"/>
-        <v>864.28947860833046</v>
-      </c>
-      <c r="EE16" s="1">
-        <f t="shared" si="52"/>
-        <v>855.64658382224718</v>
-      </c>
-      <c r="EF16" s="1">
-        <f t="shared" si="52"/>
-        <v>847.09011798402469</v>
-      </c>
-      <c r="EG16" s="1">
-        <f t="shared" si="52"/>
-        <v>838.61921680418448</v>
-      </c>
-      <c r="EH16" s="1">
-        <f t="shared" si="52"/>
-        <v>830.23302463614266</v>
-      </c>
-      <c r="EI16" s="1">
-        <f t="shared" si="52"/>
-        <v>821.93069438978125</v>
-      </c>
-      <c r="EJ16" s="1">
-        <f t="shared" si="52"/>
-        <v>813.71138744588347</v>
-      </c>
-      <c r="EK16" s="1">
-        <f t="shared" si="52"/>
-        <v>805.57427357142467</v>
-      </c>
-      <c r="EL16" s="1">
-        <f t="shared" si="52"/>
-        <v>797.51853083571041</v>
-      </c>
-      <c r="EM16" s="1">
-        <f t="shared" si="52"/>
-        <v>789.54334552735327</v>
-      </c>
-      <c r="EN16" s="1">
-        <f t="shared" si="52"/>
-        <v>781.64791207207975</v>
-      </c>
-      <c r="EO16" s="1">
-        <f t="shared" si="52"/>
-        <v>773.83143295135892</v>
-      </c>
-      <c r="EP16" s="1">
-        <f t="shared" si="52"/>
-        <v>766.09311862184529</v>
-      </c>
-      <c r="EQ16" s="1">
-        <f t="shared" si="52"/>
-        <v>758.43218743562682</v>
-      </c>
-      <c r="ER16" s="1">
-        <f t="shared" si="52"/>
-        <v>750.84786556127051</v>
-      </c>
-      <c r="ES16" s="1">
-        <f t="shared" si="52"/>
-        <v>743.33938690565776</v>
-      </c>
-      <c r="ET16" s="1">
-        <f t="shared" si="52"/>
-        <v>735.90599303660122</v>
-      </c>
-      <c r="EU16" s="1">
-        <f t="shared" si="52"/>
-        <v>728.5469331062352</v>
-      </c>
-      <c r="EV16" s="1">
-        <f t="shared" si="52"/>
-        <v>721.26146377517284</v>
-      </c>
-      <c r="EW16" s="1">
-        <f t="shared" si="52"/>
-        <v>714.04884913742114</v>
-      </c>
-      <c r="EX16" s="1">
-        <f t="shared" si="52"/>
-        <v>706.90836064604696</v>
-      </c>
-      <c r="EY16" s="1">
-        <f t="shared" si="52"/>
-        <v>699.83927703958648</v>
-      </c>
-      <c r="EZ16" s="1">
-        <f t="shared" si="52"/>
-        <v>692.84088426919061</v>
-      </c>
-      <c r="FA16" s="1">
-        <f t="shared" si="52"/>
-        <v>685.91247542649864</v>
-      </c>
-      <c r="FB16" s="1">
-        <f t="shared" si="52"/>
-        <v>679.05335067223371</v>
-      </c>
-      <c r="FC16" s="1">
-        <f t="shared" si="52"/>
-        <v>672.26281716551136</v>
-      </c>
-      <c r="FD16" s="1">
-        <f t="shared" si="52"/>
-        <v>665.54018899385619</v>
+        <v>633.20710513385666</v>
       </c>
     </row>
     <row r="17" spans="2:50" x14ac:dyDescent="0.3">
@@ -3886,10 +3880,12 @@
         <v>335.2</v>
       </c>
       <c r="AA17" s="6">
-        <v>335.2</v>
+        <f>342.2</f>
+        <v>342.2</v>
       </c>
       <c r="AB17" s="6">
-        <v>335.2</v>
+        <f>342.2</f>
+        <v>342.2</v>
       </c>
       <c r="AD17" s="6">
         <v>284.10000000000002</v>
@@ -3910,41 +3906,52 @@
         <v>289</v>
       </c>
       <c r="AJ17" s="6">
-        <f t="shared" ref="AJ17" si="53">331.4</f>
+        <f t="shared" ref="AJ17" si="52">331.4</f>
         <v>331.4</v>
       </c>
       <c r="AK17" s="6">
-        <v>335.2</v>
+        <f t="shared" ref="AK17:AU17" si="53">342.2</f>
+        <v>342.2</v>
       </c>
       <c r="AL17" s="6">
-        <v>335.2</v>
+        <f t="shared" si="53"/>
+        <v>342.2</v>
       </c>
       <c r="AM17" s="6">
-        <v>335.2</v>
+        <f t="shared" si="53"/>
+        <v>342.2</v>
       </c>
       <c r="AN17" s="6">
-        <v>335.2</v>
+        <f t="shared" si="53"/>
+        <v>342.2</v>
       </c>
       <c r="AO17" s="6">
-        <v>335.2</v>
+        <f t="shared" si="53"/>
+        <v>342.2</v>
       </c>
       <c r="AP17" s="6">
-        <v>335.2</v>
+        <f t="shared" si="53"/>
+        <v>342.2</v>
       </c>
       <c r="AQ17" s="6">
-        <v>335.2</v>
+        <f t="shared" si="53"/>
+        <v>342.2</v>
       </c>
       <c r="AR17" s="6">
-        <v>335.2</v>
+        <f t="shared" si="53"/>
+        <v>342.2</v>
       </c>
       <c r="AS17" s="6">
-        <v>335.2</v>
+        <f t="shared" si="53"/>
+        <v>342.2</v>
       </c>
       <c r="AT17" s="6">
-        <v>335.2</v>
+        <f t="shared" si="53"/>
+        <v>342.2</v>
       </c>
       <c r="AU17" s="6">
-        <v>335.2</v>
+        <f t="shared" si="53"/>
+        <v>342.2</v>
       </c>
     </row>
     <row r="18" spans="2:50" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -4041,11 +4048,11 @@
       </c>
       <c r="AA18" s="8">
         <f t="shared" si="55"/>
-        <v>-0.96574984964200472</v>
+        <v>-0.85943892460549343</v>
       </c>
       <c r="AB18" s="8">
         <f t="shared" si="55"/>
-        <v>-1.1072735202863966</v>
+        <v>-1.0465736820572769</v>
       </c>
       <c r="AD18" s="8">
         <f>AD16/AD17</f>
@@ -4077,47 +4084,47 @@
       </c>
       <c r="AK18" s="8">
         <f t="shared" si="56"/>
-        <v>-4.2454577374701659</v>
+        <v>-4.0340079310344832</v>
       </c>
       <c r="AL18" s="8">
         <f t="shared" si="56"/>
-        <v>-2.522579802852027</v>
+        <v>-2.426367797779077</v>
       </c>
       <c r="AM18" s="8">
         <f t="shared" si="56"/>
-        <v>-0.60119918915990744</v>
+        <v>-0.55031940371712684</v>
       </c>
       <c r="AN18" s="8">
         <f t="shared" si="56"/>
-        <v>0.99087817259579647</v>
+        <v>1.0063321374831051</v>
       </c>
       <c r="AO18" s="8">
         <f t="shared" si="56"/>
-        <v>2.1471587740536515</v>
+        <v>2.1317983659945723</v>
       </c>
       <c r="AP18" s="8">
         <f t="shared" si="56"/>
-        <v>3.3679484397854118</v>
+        <v>3.3238324761139819</v>
       </c>
       <c r="AQ18" s="8">
         <f t="shared" si="56"/>
-        <v>4.2087506159036572</v>
+        <v>4.1433814564609888</v>
       </c>
       <c r="AR18" s="8">
         <f t="shared" ref="AR18:AU18" si="57">AR16/AR17</f>
-        <v>4.7048464184652925</v>
+        <v>4.3677528549484324</v>
       </c>
       <c r="AS18" s="8">
         <f t="shared" si="57"/>
-        <v>5.168796479113043</v>
+        <v>4.8053942125948899</v>
       </c>
       <c r="AT18" s="8">
         <f t="shared" si="57"/>
-        <v>5.6605181975876695</v>
+        <v>5.2693027124216485</v>
       </c>
       <c r="AU18" s="8">
         <f t="shared" si="57"/>
-        <v>6.1814916398764002</v>
+        <v>5.7608794130236856</v>
       </c>
     </row>
     <row r="20" spans="2:50" x14ac:dyDescent="0.3">
@@ -4206,7 +4213,7 @@
       </c>
       <c r="AA20" s="10">
         <f t="shared" ref="AA20" si="62">AA3/W3-1</f>
-        <v>0.24</v>
+        <v>0.28744294660864034</v>
       </c>
       <c r="AB20" s="10">
         <f t="shared" ref="AB20" si="63">AB3/X3-1</f>
@@ -4239,7 +4246,7 @@
       </c>
       <c r="AK20" s="10">
         <f t="shared" si="64"/>
-        <v>0.25178248400617709</v>
+        <v>0.26410765497463062</v>
       </c>
       <c r="AL20" s="10">
         <f t="shared" si="64"/>
@@ -4376,7 +4383,7 @@
       </c>
       <c r="AA21" s="10">
         <f t="shared" si="68"/>
-        <v>0.67</v>
+        <v>0.67771456838980959</v>
       </c>
       <c r="AB21" s="10">
         <f t="shared" si="68"/>
@@ -4412,7 +4419,7 @@
       </c>
       <c r="AK21" s="10">
         <f t="shared" si="69"/>
-        <v>0.67025179184150374</v>
+        <v>0.67229049596872714</v>
       </c>
       <c r="AL21" s="10">
         <f t="shared" si="69"/>
@@ -4420,7 +4427,7 @@
       </c>
       <c r="AM21" s="10">
         <f t="shared" si="69"/>
-        <v>0.68999999999999984</v>
+        <v>0.69</v>
       </c>
       <c r="AN21" s="10">
         <f t="shared" si="69"/>
@@ -4549,11 +4556,11 @@
       </c>
       <c r="AA22" s="10">
         <f t="shared" si="73"/>
-        <v>-0.32227340430267315</v>
+        <v>-0.27166295655041622</v>
       </c>
       <c r="AB22" s="10">
         <f t="shared" si="73"/>
-        <v>-0.36493227266585609</v>
+        <v>-0.3524550736386976</v>
       </c>
       <c r="AD22" s="10">
         <f t="shared" ref="AD22:AQ22" si="74">AD9/AD3</f>
@@ -4585,47 +4592,47 @@
       </c>
       <c r="AK22" s="10">
         <f t="shared" si="74"/>
-        <v>-0.35163166400262225</v>
+        <v>-0.33473159750095988</v>
       </c>
       <c r="AL22" s="10">
         <f t="shared" si="74"/>
-        <v>-0.19032353009646208</v>
+        <v>-0.1844409529138768</v>
       </c>
       <c r="AM22" s="10">
         <f t="shared" si="74"/>
-        <v>-6.4538292572138223E-2</v>
+        <v>-6.0732883415655262E-2</v>
       </c>
       <c r="AN22" s="10">
         <f t="shared" si="74"/>
-        <v>1.6539266524327381E-2</v>
+        <v>1.9049885655320151E-2</v>
       </c>
       <c r="AO22" s="10">
         <f t="shared" si="74"/>
-        <v>6.7643616650074984E-2</v>
+        <v>6.917481917797047E-2</v>
       </c>
       <c r="AP22" s="10">
         <f t="shared" si="74"/>
-        <v>0.11091421007621695</v>
+        <v>0.11170487666195394</v>
       </c>
       <c r="AQ22" s="10">
         <f t="shared" si="74"/>
-        <v>0.13675934044648724</v>
+        <v>0.13704577027588136</v>
       </c>
       <c r="AR22" s="10">
         <f t="shared" ref="AR22:AU22" si="75">AR9/AR3</f>
-        <v>0.15599478786230178</v>
+        <v>0.14598731969657042</v>
       </c>
       <c r="AS22" s="10">
         <f t="shared" si="75"/>
-        <v>0.16496636535195042</v>
+        <v>0.15467339627666846</v>
       </c>
       <c r="AT22" s="10">
         <f t="shared" si="75"/>
-        <v>0.17368161205618055</v>
+        <v>0.16311129924019224</v>
       </c>
       <c r="AU22" s="10">
         <f t="shared" si="75"/>
-        <v>0.18214785171171807</v>
+        <v>0.17130811926190098</v>
       </c>
       <c r="AW22" t="s">
         <v>40</v>
@@ -4728,7 +4735,7 @@
       </c>
       <c r="AA23" s="10">
         <f t="shared" si="78"/>
-        <v>0.44000000000000006</v>
+        <v>0.45378844092670456</v>
       </c>
       <c r="AB23" s="10">
         <f t="shared" si="78"/>
@@ -4764,47 +4771,47 @@
       </c>
       <c r="AK23" s="10">
         <f t="shared" si="79"/>
-        <v>0.43962021947965663</v>
+        <v>0.44327213709818158</v>
       </c>
       <c r="AL23" s="10">
         <f t="shared" si="79"/>
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="AM23" s="10">
         <f t="shared" si="79"/>
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="AN23" s="10">
         <f t="shared" si="79"/>
-        <v>0.28999999999999998</v>
+        <v>0.3</v>
       </c>
       <c r="AO23" s="10">
         <f t="shared" si="79"/>
-        <v>0.27</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="AP23" s="10">
         <f t="shared" si="79"/>
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="AQ23" s="10">
         <f t="shared" si="79"/>
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="AR23" s="10">
         <f t="shared" ref="AR23:AU23" si="80">AR6/AR3</f>
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="AS23" s="10">
         <f t="shared" si="80"/>
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="AT23" s="10">
         <f t="shared" si="80"/>
-        <v>0.22999999999999998</v>
+        <v>0.25</v>
       </c>
       <c r="AU23" s="10">
         <f t="shared" si="80"/>
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="AW23" t="s">
         <v>41</v>
@@ -4901,11 +4908,11 @@
       </c>
       <c r="AA24" s="10">
         <f t="shared" ref="AA24:AA25" si="85">AA7/W7-1</f>
-        <v>0.16999999999999993</v>
+        <v>0.11663652802893321</v>
       </c>
       <c r="AB24" s="10">
         <f t="shared" ref="AB24:AB25" si="86">AB7/X7-1</f>
-        <v>0.14999999999999991</v>
+        <v>0.12000000000000011</v>
       </c>
       <c r="AD24" s="10"/>
       <c r="AE24" s="10">
@@ -4934,7 +4941,7 @@
       </c>
       <c r="AK24" s="10">
         <f t="shared" si="87"/>
-        <v>0.14858304362453723</v>
+        <v>0.12706067062913529</v>
       </c>
       <c r="AL24" s="10">
         <f t="shared" si="87"/>
@@ -4981,7 +4988,7 @@
       </c>
       <c r="AX24" s="6">
         <f>NPV(AX23,AJ16:FD16)</f>
-        <v>13895.376493316469</v>
+        <v>13247.639328441321</v>
       </c>
     </row>
     <row r="25" spans="2:50" x14ac:dyDescent="0.3">
@@ -5072,7 +5079,7 @@
       </c>
       <c r="AA25" s="10">
         <f t="shared" si="85"/>
-        <v>0.19999999999999996</v>
+        <v>7.5258701787392912E-3</v>
       </c>
       <c r="AB25" s="10">
         <f t="shared" si="86"/>
@@ -5105,7 +5112,7 @@
       </c>
       <c r="AK25" s="10">
         <f t="shared" si="90"/>
-        <v>0.44259034683482912</v>
+        <v>0.39296628668445344</v>
       </c>
       <c r="AL25" s="10">
         <f t="shared" si="90"/>
@@ -5152,7 +5159,7 @@
       </c>
       <c r="AX25" s="6">
         <f>Main!D8</f>
-        <v>2323.8999999999996</v>
+        <v>2116.9000000000005</v>
       </c>
     </row>
     <row r="26" spans="2:50" x14ac:dyDescent="0.3">
@@ -5249,7 +5256,7 @@
       </c>
       <c r="AA26" s="10">
         <f t="shared" si="95"/>
-        <v>0</v>
+        <v>-1.2847222222222229E-2</v>
       </c>
       <c r="AB26" s="10">
         <f t="shared" si="95"/>
@@ -5285,7 +5292,7 @@
       </c>
       <c r="AK26" s="10">
         <f t="shared" si="96"/>
-        <v>-4.0828702138342747E-3</v>
+        <v>-6.9336121959173132E-3</v>
       </c>
       <c r="AL26" s="10">
         <f t="shared" si="96"/>
@@ -5297,7 +5304,7 @@
       </c>
       <c r="AN26" s="10">
         <f t="shared" si="96"/>
-        <v>4.9999999999999996E-2</v>
+        <v>0.05</v>
       </c>
       <c r="AO26" s="10">
         <f t="shared" si="96"/>
@@ -5309,7 +5316,7 @@
       </c>
       <c r="AQ26" s="10">
         <f t="shared" si="96"/>
-        <v>0.10999999999999999</v>
+        <v>0.11</v>
       </c>
       <c r="AR26" s="10">
         <f t="shared" ref="AR26:AU26" si="97">AR14/AR13</f>
@@ -5332,7 +5339,7 @@
       </c>
       <c r="AX26" s="6">
         <f>AX24+AX25</f>
-        <v>16219.276493316469</v>
+        <v>15364.539328441322</v>
       </c>
     </row>
     <row r="27" spans="2:50" x14ac:dyDescent="0.3">
@@ -5429,11 +5436,11 @@
       </c>
       <c r="AA27" s="10">
         <f t="shared" si="99"/>
-        <v>-0.27710857829625646</v>
+        <v>-0.24247670871465068</v>
       </c>
       <c r="AB27" s="10">
         <f t="shared" si="99"/>
-        <v>-0.3134357553033375</v>
+        <v>-0.30244013815700593</v>
       </c>
       <c r="AD27" s="10">
         <f t="shared" ref="AD27:AU27" si="100">AD16/AD3</f>
@@ -5465,54 +5472,54 @@
       </c>
       <c r="AK27" s="10">
         <f t="shared" si="100"/>
-        <v>-0.3134901903837104</v>
+        <v>-0.3011320534187289</v>
       </c>
       <c r="AL27" s="10">
         <f t="shared" si="100"/>
-        <v>-0.1502182377017027</v>
+        <v>-0.14606803476712518</v>
       </c>
       <c r="AM27" s="10">
         <f t="shared" si="100"/>
-        <v>-2.9834233787565497E-2</v>
+        <v>-2.7607821132460728E-2</v>
       </c>
       <c r="AN27" s="10">
         <f t="shared" si="100"/>
-        <v>4.3133223212560128E-2</v>
+        <v>4.4284709238650348E-2</v>
       </c>
       <c r="AO27" s="10">
         <f t="shared" si="100"/>
-        <v>8.4204021282266908E-2</v>
+        <v>8.4515351403855798E-2</v>
       </c>
       <c r="AP27" s="10">
         <f t="shared" si="100"/>
-        <v>0.12117348780542408</v>
+        <v>0.12089326461645214</v>
       </c>
       <c r="AQ27" s="10">
         <f t="shared" si="100"/>
-        <v>0.14151796981429035</v>
+        <v>0.14084262765906486</v>
       </c>
       <c r="AR27" s="10">
         <f t="shared" si="100"/>
-        <v>0.1506657538277964</v>
+        <v>0.1413995274656783</v>
       </c>
       <c r="AS27" s="10">
         <f t="shared" si="100"/>
-        <v>0.15764101800414521</v>
+        <v>0.14815954096665898</v>
       </c>
       <c r="AT27" s="10">
         <f t="shared" si="100"/>
-        <v>0.16441698891831255</v>
+        <v>0.15472641122475442</v>
       </c>
       <c r="AU27" s="10">
         <f t="shared" si="100"/>
-        <v>0.17099936066350355</v>
+        <v>0.16110565661833282</v>
       </c>
       <c r="AW27" t="s">
         <v>45</v>
       </c>
       <c r="AX27" s="5">
         <f>AX26/AQ17</f>
-        <v>48.386863046886845</v>
+        <v>44.89929669328265</v>
       </c>
     </row>
     <row r="28" spans="2:50" x14ac:dyDescent="0.3">
@@ -5521,7 +5528,7 @@
       </c>
       <c r="AX28" s="5">
         <f>Main!D3</f>
-        <v>225.31</v>
+        <v>198.52</v>
       </c>
     </row>
     <row r="29" spans="2:50" x14ac:dyDescent="0.3">
@@ -5530,7 +5537,7 @@
       </c>
       <c r="AX29" s="11">
         <f>AX27/AX28-1</f>
-        <v>-0.78524316254544035</v>
+        <v>-0.77382985747893085</v>
       </c>
     </row>
     <row r="30" spans="2:50" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -6019,11 +6026,11 @@
       </c>
       <c r="AA60" s="9">
         <f t="shared" si="102"/>
-        <v>-323.71934959999999</v>
+        <v>-294.09999999999985</v>
       </c>
       <c r="AB60" s="9">
         <f t="shared" si="102"/>
-        <v>-371.15808400000009</v>
+        <v>-358.13751400000012</v>
       </c>
       <c r="AI60" s="9">
         <f>AI16</f>
@@ -6035,47 +6042,47 @@
       </c>
       <c r="AK60" s="9">
         <f t="shared" ref="AK60:AU60" si="103">AK16</f>
-        <v>-1423.0774335999995</v>
+        <v>-1380.4375140000002</v>
       </c>
       <c r="AL60" s="9">
         <f t="shared" si="103"/>
-        <v>-845.56874991599943</v>
+        <v>-830.30306040000005</v>
       </c>
       <c r="AM60" s="9">
         <f t="shared" si="103"/>
-        <v>-201.52196820640097</v>
+        <v>-188.31929995200079</v>
       </c>
       <c r="AN60" s="9">
         <f t="shared" si="103"/>
-        <v>332.14236345411098</v>
+        <v>344.3668574467186</v>
       </c>
       <c r="AO60" s="9">
         <f t="shared" si="103"/>
-        <v>719.72762106278401</v>
+        <v>729.50140084334259</v>
       </c>
       <c r="AP60" s="9">
         <f t="shared" si="103"/>
-        <v>1128.93631701607</v>
+        <v>1137.4154733262046</v>
       </c>
       <c r="AQ60" s="9">
         <f t="shared" si="103"/>
-        <v>1410.7732064509059</v>
+        <v>1417.8651344009502</v>
       </c>
       <c r="AR60" s="9">
         <f t="shared" si="103"/>
-        <v>1577.064519469566</v>
+        <v>1494.6450269633535</v>
       </c>
       <c r="AS60" s="9">
         <f t="shared" si="103"/>
-        <v>1732.580579798692</v>
+        <v>1644.4058995499713</v>
       </c>
       <c r="AT60" s="9">
         <f t="shared" si="103"/>
-        <v>1897.4056998313868</v>
+        <v>1803.1553881906882</v>
       </c>
       <c r="AU60" s="9">
         <f t="shared" si="103"/>
-        <v>2072.0359976865693</v>
+        <v>1971.3729351367051</v>
       </c>
     </row>
     <row r="61" spans="2:47" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -6114,6 +6121,9 @@
       </c>
       <c r="Z61" s="9">
         <v>-297.89999999999998</v>
+      </c>
+      <c r="AA61" s="9">
+        <v>-291.60000000000002</v>
       </c>
       <c r="AI61" s="9">
         <f>SUM(Q61:T61)</f>
@@ -6173,7 +6183,7 @@
         <v>54.8</v>
       </c>
       <c r="AA62" s="6">
-        <v>60</v>
+        <v>57.9</v>
       </c>
       <c r="AB62" s="6">
         <v>63</v>
@@ -6188,47 +6198,47 @@
       </c>
       <c r="AK62" s="6">
         <f>SUM(Y62:AB62)</f>
-        <v>226.6</v>
+        <v>224.5</v>
       </c>
       <c r="AL62" s="6">
         <f t="shared" ref="AL62:AU62" si="104">AK62*1.03</f>
-        <v>233.398</v>
+        <v>231.23500000000001</v>
       </c>
       <c r="AM62" s="6">
         <f t="shared" si="104"/>
-        <v>240.39994000000002</v>
+        <v>238.17205000000001</v>
       </c>
       <c r="AN62" s="6">
         <f t="shared" si="104"/>
-        <v>247.61193820000003</v>
+        <v>245.31721150000001</v>
       </c>
       <c r="AO62" s="6">
         <f t="shared" si="104"/>
-        <v>255.04029634600002</v>
+        <v>252.67672784500002</v>
       </c>
       <c r="AP62" s="6">
         <f t="shared" si="104"/>
-        <v>262.69150523638001</v>
+        <v>260.25702968035</v>
       </c>
       <c r="AQ62" s="6">
         <f t="shared" si="104"/>
-        <v>270.57225039347139</v>
+        <v>268.06474057076053</v>
       </c>
       <c r="AR62" s="6">
         <f t="shared" si="104"/>
-        <v>278.68941790527555</v>
+        <v>276.10668278788336</v>
       </c>
       <c r="AS62" s="6">
         <f t="shared" si="104"/>
-        <v>287.0501004424338</v>
+        <v>284.38988327151986</v>
       </c>
       <c r="AT62" s="6">
         <f t="shared" si="104"/>
-        <v>295.66160345570682</v>
+        <v>292.92157976966547</v>
       </c>
       <c r="AU62" s="6">
         <f t="shared" si="104"/>
-        <v>304.53145155937801</v>
+        <v>301.70922716275544</v>
       </c>
     </row>
     <row r="63" spans="2:47" x14ac:dyDescent="0.3">
@@ -6269,62 +6279,62 @@
         <v>16.2</v>
       </c>
       <c r="AA63" s="6">
-        <v>18</v>
+        <v>15.8</v>
       </c>
       <c r="AB63" s="6">
         <v>18</v>
       </c>
       <c r="AI63" s="6">
-        <f t="shared" ref="AI63:AI78" si="105">SUM(Q63:T63)</f>
+        <f t="shared" ref="AI63:AI79" si="105">SUM(Q63:T63)</f>
         <v>53</v>
       </c>
       <c r="AJ63" s="6">
-        <f t="shared" ref="AJ63:AJ78" si="106">SUM(U63:X63)</f>
+        <f t="shared" ref="AJ63:AJ79" si="106">SUM(U63:X63)</f>
         <v>59.9</v>
       </c>
       <c r="AK63" s="6">
-        <f t="shared" ref="AK63:AK78" si="107">SUM(Y63:AB63)</f>
-        <v>70</v>
+        <f t="shared" ref="AK63:AK79" si="107">SUM(Y63:AB63)</f>
+        <v>67.8</v>
       </c>
       <c r="AL63" s="6">
         <f t="shared" ref="AL63:AU63" si="108">AK63*1.03</f>
-        <v>72.100000000000009</v>
+        <v>69.834000000000003</v>
       </c>
       <c r="AM63" s="6">
         <f t="shared" si="108"/>
-        <v>74.263000000000005</v>
+        <v>71.929020000000008</v>
       </c>
       <c r="AN63" s="6">
         <f t="shared" si="108"/>
-        <v>76.490890000000007</v>
+        <v>74.086890600000004</v>
       </c>
       <c r="AO63" s="6">
         <f t="shared" si="108"/>
-        <v>78.785616700000006</v>
+        <v>76.309497318000012</v>
       </c>
       <c r="AP63" s="6">
         <f t="shared" si="108"/>
-        <v>81.149185201000009</v>
+        <v>78.598782237540021</v>
       </c>
       <c r="AQ63" s="6">
         <f t="shared" si="108"/>
-        <v>83.583660757030017</v>
+        <v>80.956745704666218</v>
       </c>
       <c r="AR63" s="6">
         <f t="shared" si="108"/>
-        <v>86.091170579740918</v>
+        <v>83.38544807580621</v>
       </c>
       <c r="AS63" s="6">
         <f t="shared" si="108"/>
-        <v>88.673905697133151</v>
+        <v>85.887011518080399</v>
       </c>
       <c r="AT63" s="6">
         <f t="shared" si="108"/>
-        <v>91.334122868047146</v>
+        <v>88.463621863622819</v>
       </c>
       <c r="AU63" s="6">
         <f t="shared" si="108"/>
-        <v>94.074146554088557</v>
+        <v>91.117530519531513</v>
       </c>
     </row>
     <row r="64" spans="2:47" x14ac:dyDescent="0.3">
@@ -6365,10 +6375,10 @@
         <v>33.200000000000003</v>
       </c>
       <c r="AA64" s="6">
-        <v>33</v>
+        <v>36.5</v>
       </c>
       <c r="AB64" s="6">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="AI64" s="6">
         <f t="shared" si="105"/>
@@ -6380,47 +6390,47 @@
       </c>
       <c r="AK64" s="6">
         <f t="shared" si="107"/>
-        <v>125</v>
+        <v>135.5</v>
       </c>
       <c r="AL64" s="6">
         <f t="shared" ref="AL64:AU64" si="109">AK64*1.01</f>
-        <v>126.25</v>
+        <v>136.85499999999999</v>
       </c>
       <c r="AM64" s="6">
         <f t="shared" si="109"/>
-        <v>127.5125</v>
+        <v>138.22354999999999</v>
       </c>
       <c r="AN64" s="6">
         <f t="shared" si="109"/>
-        <v>128.78762499999999</v>
+        <v>139.6057855</v>
       </c>
       <c r="AO64" s="6">
         <f t="shared" si="109"/>
-        <v>130.07550125</v>
+        <v>141.00184335500001</v>
       </c>
       <c r="AP64" s="6">
         <f t="shared" si="109"/>
-        <v>131.37625626249999</v>
+        <v>142.41186178855</v>
       </c>
       <c r="AQ64" s="6">
         <f t="shared" si="109"/>
-        <v>132.69001882512498</v>
+        <v>143.83598040643551</v>
       </c>
       <c r="AR64" s="6">
         <f t="shared" si="109"/>
-        <v>134.01691901337622</v>
+        <v>145.27434021049987</v>
       </c>
       <c r="AS64" s="6">
         <f t="shared" si="109"/>
-        <v>135.35708820350999</v>
+        <v>146.72708361260487</v>
       </c>
       <c r="AT64" s="6">
         <f t="shared" si="109"/>
-        <v>136.7106590855451</v>
+        <v>148.19435444873093</v>
       </c>
       <c r="AU64" s="6">
         <f t="shared" si="109"/>
-        <v>138.07776567640056</v>
+        <v>149.67629799321824</v>
       </c>
     </row>
     <row r="65" spans="2:47" x14ac:dyDescent="0.3">
@@ -6461,8 +6471,7 @@
         <v>404.2</v>
       </c>
       <c r="AA65" s="6">
-        <f>W65*1.12</f>
-        <v>406.89600000000007</v>
+        <v>412.3</v>
       </c>
       <c r="AB65" s="6">
         <f>X65*1.1</f>
@@ -6478,47 +6487,47 @@
       </c>
       <c r="AK65" s="6">
         <f t="shared" si="107"/>
-        <v>1661.5060000000001</v>
+        <v>1666.91</v>
       </c>
       <c r="AL65" s="6">
         <f>AK65*1.05</f>
-        <v>1744.5813000000001</v>
+        <v>1750.2555000000002</v>
       </c>
       <c r="AM65" s="6">
         <f>AL65*0.9</f>
-        <v>1570.1231700000001</v>
+        <v>1575.2299500000001</v>
       </c>
       <c r="AN65" s="6">
         <f t="shared" ref="AN65:AU65" si="110">AM65*0.9</f>
-        <v>1413.1108530000001</v>
+        <v>1417.7069550000001</v>
       </c>
       <c r="AO65" s="6">
         <f t="shared" si="110"/>
-        <v>1271.7997677000001</v>
+        <v>1275.9362595000002</v>
       </c>
       <c r="AP65" s="6">
         <f t="shared" si="110"/>
-        <v>1144.6197909300001</v>
+        <v>1148.3426335500003</v>
       </c>
       <c r="AQ65" s="6">
         <f t="shared" si="110"/>
-        <v>1030.1578118370001</v>
+        <v>1033.5083701950002</v>
       </c>
       <c r="AR65" s="6">
         <f t="shared" si="110"/>
-        <v>927.14203065330003</v>
+        <v>930.15753317550025</v>
       </c>
       <c r="AS65" s="6">
         <f t="shared" si="110"/>
-        <v>834.42782758797</v>
+        <v>837.14177985795027</v>
       </c>
       <c r="AT65" s="6">
         <f t="shared" si="110"/>
-        <v>750.98504482917303</v>
+        <v>753.42760187215526</v>
       </c>
       <c r="AU65" s="6">
         <f t="shared" si="110"/>
-        <v>675.88654034625574</v>
+        <v>678.08484168493976</v>
       </c>
     </row>
     <row r="66" spans="2:47" x14ac:dyDescent="0.3">
@@ -6559,7 +6568,7 @@
         <v>-5.7</v>
       </c>
       <c r="AA66" s="6">
-        <v>-10</v>
+        <v>-5.0999999999999996</v>
       </c>
       <c r="AB66" s="6">
         <v>-10</v>
@@ -6574,47 +6583,47 @@
       </c>
       <c r="AK66" s="6">
         <f t="shared" si="107"/>
-        <v>-33.4</v>
+        <v>-28.5</v>
       </c>
       <c r="AL66" s="6">
         <f>AK66*1.02</f>
-        <v>-34.067999999999998</v>
+        <v>-29.07</v>
       </c>
       <c r="AM66" s="6">
         <f t="shared" ref="AM66:AU66" si="111">AL66*1.02</f>
-        <v>-34.749359999999996</v>
+        <v>-29.651400000000002</v>
       </c>
       <c r="AN66" s="6">
         <f t="shared" si="111"/>
-        <v>-35.444347199999996</v>
+        <v>-30.244428000000003</v>
       </c>
       <c r="AO66" s="6">
         <f t="shared" si="111"/>
-        <v>-36.153234143999995</v>
+        <v>-30.849316560000002</v>
       </c>
       <c r="AP66" s="6">
         <f t="shared" si="111"/>
-        <v>-36.876298826879996</v>
+        <v>-31.466302891200002</v>
       </c>
       <c r="AQ66" s="6">
         <f t="shared" si="111"/>
-        <v>-37.613824803417593</v>
+        <v>-32.095628949024004</v>
       </c>
       <c r="AR66" s="6">
         <f t="shared" si="111"/>
-        <v>-38.366101299485948</v>
+        <v>-32.737541528004485</v>
       </c>
       <c r="AS66" s="6">
         <f t="shared" si="111"/>
-        <v>-39.133423325475668</v>
+        <v>-33.392292358564575</v>
       </c>
       <c r="AT66" s="6">
         <f t="shared" si="111"/>
-        <v>-39.916091791985181</v>
+        <v>-34.060138205735868</v>
       </c>
       <c r="AU66" s="6">
         <f t="shared" si="111"/>
-        <v>-40.714413627824882</v>
+        <v>-34.741340969850583</v>
       </c>
     </row>
     <row r="67" spans="2:47" x14ac:dyDescent="0.3">
@@ -6655,7 +6664,7 @@
         <v>5.6</v>
       </c>
       <c r="AA67" s="6">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="AB67" s="6">
         <v>0</v>
@@ -6670,7 +6679,7 @@
       </c>
       <c r="AK67" s="6">
         <f t="shared" si="107"/>
-        <v>35.299999999999997</v>
+        <v>35.599999999999994</v>
       </c>
       <c r="AL67" s="6">
         <f>0</f>
@@ -6751,7 +6760,7 @@
         <v>2.1</v>
       </c>
       <c r="AA68" s="6">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB68" s="6">
         <v>0</v>
@@ -6766,52 +6775,52 @@
       </c>
       <c r="AK68" s="6">
         <f t="shared" si="107"/>
-        <v>4.2</v>
+        <v>6.3000000000000007</v>
       </c>
       <c r="AL68" s="6">
         <f t="shared" ref="AL68:AU68" si="112">AK68*1.2</f>
-        <v>5.04</v>
+        <v>7.5600000000000005</v>
       </c>
       <c r="AM68" s="6">
         <f t="shared" si="112"/>
-        <v>6.048</v>
+        <v>9.072000000000001</v>
       </c>
       <c r="AN68" s="6">
         <f t="shared" si="112"/>
-        <v>7.2576000000000001</v>
+        <v>10.8864</v>
       </c>
       <c r="AO68" s="6">
         <f t="shared" si="112"/>
-        <v>8.7091200000000004</v>
+        <v>13.06368</v>
       </c>
       <c r="AP68" s="6">
         <f t="shared" si="112"/>
-        <v>10.450944</v>
+        <v>15.676416</v>
       </c>
       <c r="AQ68" s="6">
         <f t="shared" si="112"/>
-        <v>12.5411328</v>
+        <v>18.8116992</v>
       </c>
       <c r="AR68" s="6">
         <f t="shared" si="112"/>
-        <v>15.049359359999999</v>
+        <v>22.574039039999999</v>
       </c>
       <c r="AS68" s="6">
         <f t="shared" si="112"/>
-        <v>18.059231231999998</v>
+        <v>27.088846847999999</v>
       </c>
       <c r="AT68" s="6">
         <f t="shared" si="112"/>
-        <v>21.671077478399997</v>
+        <v>32.506616217599998</v>
       </c>
       <c r="AU68" s="6">
         <f t="shared" si="112"/>
-        <v>26.005292974079996</v>
+        <v>39.007939461119996</v>
       </c>
     </row>
     <row r="69" spans="2:47" x14ac:dyDescent="0.3">
       <c r="B69" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="P69" s="6"/>
       <c r="Q69" s="6"/>
@@ -6826,11 +6835,16 @@
       <c r="Z69" s="6">
         <v>2.1</v>
       </c>
-      <c r="AA69" s="6"/>
+      <c r="AA69" s="6">
+        <v>0.1</v>
+      </c>
       <c r="AB69" s="6"/>
       <c r="AI69" s="6"/>
       <c r="AJ69" s="6"/>
-      <c r="AK69" s="6"/>
+      <c r="AK69" s="6">
+        <f t="shared" si="107"/>
+        <v>2.2000000000000002</v>
+      </c>
       <c r="AL69" s="6"/>
       <c r="AM69" s="6"/>
       <c r="AN69" s="6"/>
@@ -6930,930 +6944,902 @@
     </row>
     <row r="71" spans="2:47" x14ac:dyDescent="0.3">
       <c r="B71" t="s">
+        <v>104</v>
+      </c>
+      <c r="P71" s="6"/>
+      <c r="Q71" s="6"/>
+      <c r="R71" s="6"/>
+      <c r="S71" s="6"/>
+      <c r="T71" s="6"/>
+      <c r="U71" s="6"/>
+      <c r="V71" s="6"/>
+      <c r="W71" s="6">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="X71" s="6"/>
+      <c r="Y71" s="6"/>
+      <c r="Z71" s="6"/>
+      <c r="AA71" s="6">
+        <v>-11.2</v>
+      </c>
+      <c r="AB71" s="6"/>
+      <c r="AI71" s="6"/>
+      <c r="AJ71" s="6"/>
+      <c r="AK71" s="6">
+        <f t="shared" si="107"/>
+        <v>-11.2</v>
+      </c>
+      <c r="AL71" s="6"/>
+      <c r="AM71" s="6"/>
+      <c r="AN71" s="6"/>
+      <c r="AO71" s="6"/>
+      <c r="AP71" s="6"/>
+      <c r="AQ71" s="6"/>
+      <c r="AR71" s="6"/>
+      <c r="AS71" s="6"/>
+      <c r="AT71" s="6"/>
+      <c r="AU71" s="6"/>
+    </row>
+    <row r="72" spans="2:47" x14ac:dyDescent="0.3">
+      <c r="B72" t="s">
         <v>92</v>
       </c>
-      <c r="P71" s="6">
+      <c r="P72" s="6">
         <v>0.9</v>
       </c>
-      <c r="Q71" s="6">
+      <c r="Q72" s="6">
         <v>10</v>
       </c>
-      <c r="R71" s="6">
+      <c r="R72" s="6">
         <v>1.8</v>
       </c>
-      <c r="S71" s="6">
+      <c r="S72" s="6">
         <v>2.5</v>
       </c>
-      <c r="T71" s="6">
+      <c r="T72" s="6">
         <v>0.6</v>
       </c>
-      <c r="U71" s="6">
+      <c r="U72" s="6">
         <v>0.7</v>
       </c>
-      <c r="V71" s="6">
+      <c r="V72" s="6">
         <v>1.2</v>
       </c>
-      <c r="W71" s="6">
-        <v>3</v>
-      </c>
-      <c r="X71" s="6">
+      <c r="W72" s="6">
+        <v>1.8</v>
+      </c>
+      <c r="X72" s="6">
         <v>2.5</v>
       </c>
-      <c r="Y71" s="6">
+      <c r="Y72" s="6">
         <v>-5.2</v>
       </c>
-      <c r="Z71" s="6">
+      <c r="Z72" s="6">
         <v>1.7</v>
       </c>
-      <c r="AA71" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB71" s="6">
-        <v>0</v>
-      </c>
-      <c r="AI71" s="6">
+      <c r="AA72" s="6">
+        <v>1.2</v>
+      </c>
+      <c r="AB72" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI72" s="6">
         <f t="shared" si="105"/>
         <v>14.9</v>
       </c>
-      <c r="AJ71" s="6">
+      <c r="AJ72" s="6">
         <f t="shared" si="106"/>
-        <v>7.4</v>
-      </c>
-      <c r="AK71" s="6">
+        <v>6.2</v>
+      </c>
+      <c r="AK72" s="6">
         <f t="shared" si="107"/>
-        <v>-3.5</v>
-      </c>
-      <c r="AL71" s="6">
-        <v>0</v>
-      </c>
-      <c r="AM71" s="6">
-        <v>0</v>
-      </c>
-      <c r="AN71" s="6">
-        <v>0</v>
-      </c>
-      <c r="AO71" s="6">
-        <v>0</v>
-      </c>
-      <c r="AP71" s="6">
-        <v>0</v>
-      </c>
-      <c r="AQ71" s="6">
-        <v>0</v>
-      </c>
-      <c r="AR71" s="6">
-        <v>0</v>
-      </c>
-      <c r="AS71" s="6">
-        <v>0</v>
-      </c>
-      <c r="AT71" s="6">
-        <v>0</v>
-      </c>
-      <c r="AU71" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="2:47" x14ac:dyDescent="0.3">
-      <c r="B72" t="s">
+        <v>-2.2999999999999998</v>
+      </c>
+      <c r="AL72" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM72" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN72" s="6">
+        <v>0</v>
+      </c>
+      <c r="AO72" s="6">
+        <v>0</v>
+      </c>
+      <c r="AP72" s="6">
+        <v>0</v>
+      </c>
+      <c r="AQ72" s="6">
+        <v>0</v>
+      </c>
+      <c r="AR72" s="6">
+        <v>0</v>
+      </c>
+      <c r="AS72" s="6">
+        <v>0</v>
+      </c>
+      <c r="AT72" s="6">
+        <v>0</v>
+      </c>
+      <c r="AU72" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:47" x14ac:dyDescent="0.3">
+      <c r="B73" t="s">
         <v>66</v>
       </c>
-      <c r="P72" s="6">
+      <c r="P73" s="6">
         <v>-317.7</v>
       </c>
-      <c r="Q72" s="6">
+      <c r="Q73" s="6">
         <v>362.9</v>
       </c>
-      <c r="R72" s="6">
+      <c r="R73" s="6">
         <v>-53.1</v>
       </c>
-      <c r="S72" s="6">
+      <c r="S73" s="6">
         <v>-104.7</v>
       </c>
-      <c r="T72" s="6">
+      <c r="T73" s="6">
         <v>-417.2</v>
       </c>
-      <c r="U72" s="6">
+      <c r="U73" s="6">
         <v>579.29999999999995</v>
       </c>
-      <c r="V72" s="6">
+      <c r="V73" s="6">
         <v>-87.1</v>
       </c>
-      <c r="W72" s="6">
+      <c r="W73" s="6">
         <v>-163.5</v>
       </c>
-      <c r="X72" s="6">
+      <c r="X73" s="6">
         <v>-328.2</v>
       </c>
-      <c r="Y72" s="6">
+      <c r="Y73" s="6">
         <v>393.7</v>
       </c>
-      <c r="Z72" s="6">
+      <c r="Z73" s="6">
         <v>-117.6</v>
       </c>
-      <c r="AA72" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB72" s="6">
-        <v>0</v>
-      </c>
-      <c r="AI72" s="6">
+      <c r="AA73" s="6">
+        <v>-288.7</v>
+      </c>
+      <c r="AB73" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI73" s="6">
         <f t="shared" si="105"/>
         <v>-212.10000000000002</v>
       </c>
-      <c r="AJ72" s="6">
+      <c r="AJ73" s="6">
         <f t="shared" si="106"/>
         <v>0.49999999999994316</v>
       </c>
-      <c r="AK72" s="6">
+      <c r="AK73" s="6">
         <f t="shared" si="107"/>
-        <v>276.10000000000002</v>
-      </c>
-      <c r="AL72" s="6">
-        <v>0</v>
-      </c>
-      <c r="AM72" s="6">
-        <v>0</v>
-      </c>
-      <c r="AN72" s="6">
-        <v>0</v>
-      </c>
-      <c r="AO72" s="6">
-        <v>0</v>
-      </c>
-      <c r="AP72" s="6">
-        <v>0</v>
-      </c>
-      <c r="AQ72" s="6">
-        <v>0</v>
-      </c>
-      <c r="AR72" s="6">
-        <v>0</v>
-      </c>
-      <c r="AS72" s="6">
-        <v>0</v>
-      </c>
-      <c r="AT72" s="6">
-        <v>0</v>
-      </c>
-      <c r="AU72" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="2:47" x14ac:dyDescent="0.3">
-      <c r="B73" t="s">
+        <v>-12.599999999999966</v>
+      </c>
+      <c r="AL73" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM73" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN73" s="6">
+        <v>0</v>
+      </c>
+      <c r="AO73" s="6">
+        <v>0</v>
+      </c>
+      <c r="AP73" s="6">
+        <v>0</v>
+      </c>
+      <c r="AQ73" s="6">
+        <v>0</v>
+      </c>
+      <c r="AR73" s="6">
+        <v>0</v>
+      </c>
+      <c r="AS73" s="6">
+        <v>0</v>
+      </c>
+      <c r="AT73" s="6">
+        <v>0</v>
+      </c>
+      <c r="AU73" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:47" x14ac:dyDescent="0.3">
+      <c r="B74" t="s">
         <v>67</v>
       </c>
-      <c r="P73" s="6">
+      <c r="P74" s="6">
         <v>-31.5</v>
       </c>
-      <c r="Q73" s="6">
+      <c r="Q74" s="6">
         <v>-16.399999999999999</v>
       </c>
-      <c r="R73" s="6">
+      <c r="R74" s="6">
         <v>-24.6</v>
       </c>
-      <c r="S73" s="6">
+      <c r="S74" s="6">
         <v>-25.5</v>
       </c>
-      <c r="T73" s="6">
+      <c r="T74" s="6">
         <v>-68.3</v>
       </c>
-      <c r="U73" s="6">
+      <c r="U74" s="6">
         <v>-14.9</v>
       </c>
-      <c r="V73" s="6">
+      <c r="V74" s="6">
         <v>-21.8</v>
       </c>
-      <c r="W73" s="6">
+      <c r="W74" s="6">
         <v>-26</v>
       </c>
-      <c r="X73" s="6">
+      <c r="X74" s="6">
         <v>-38.799999999999997</v>
       </c>
-      <c r="Y73" s="6">
+      <c r="Y74" s="6">
         <v>-31.1</v>
       </c>
-      <c r="Z73" s="6">
+      <c r="Z74" s="6">
         <v>-53.8</v>
       </c>
-      <c r="AA73" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB73" s="6">
-        <v>0</v>
-      </c>
-      <c r="AI73" s="6">
+      <c r="AA74" s="6">
+        <v>-96.8</v>
+      </c>
+      <c r="AB74" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI74" s="6">
         <f t="shared" si="105"/>
         <v>-134.80000000000001</v>
       </c>
-      <c r="AJ73" s="6">
+      <c r="AJ74" s="6">
         <f t="shared" si="106"/>
         <v>-101.5</v>
       </c>
-      <c r="AK73" s="6">
+      <c r="AK74" s="6">
         <f t="shared" si="107"/>
-        <v>-84.9</v>
-      </c>
-      <c r="AL73" s="6">
-        <v>0</v>
-      </c>
-      <c r="AM73" s="6">
-        <v>0</v>
-      </c>
-      <c r="AN73" s="6">
-        <v>0</v>
-      </c>
-      <c r="AO73" s="6">
-        <v>0</v>
-      </c>
-      <c r="AP73" s="6">
-        <v>0</v>
-      </c>
-      <c r="AQ73" s="6">
-        <v>0</v>
-      </c>
-      <c r="AR73" s="6">
-        <v>0</v>
-      </c>
-      <c r="AS73" s="6">
-        <v>0</v>
-      </c>
-      <c r="AT73" s="6">
-        <v>0</v>
-      </c>
-      <c r="AU73" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="2:47" x14ac:dyDescent="0.3">
-      <c r="B74" t="s">
+        <v>-181.7</v>
+      </c>
+      <c r="AL74" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM74" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN74" s="6">
+        <v>0</v>
+      </c>
+      <c r="AO74" s="6">
+        <v>0</v>
+      </c>
+      <c r="AP74" s="6">
+        <v>0</v>
+      </c>
+      <c r="AQ74" s="6">
+        <v>0</v>
+      </c>
+      <c r="AR74" s="6">
+        <v>0</v>
+      </c>
+      <c r="AS74" s="6">
+        <v>0</v>
+      </c>
+      <c r="AT74" s="6">
+        <v>0</v>
+      </c>
+      <c r="AU74" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:47" x14ac:dyDescent="0.3">
+      <c r="B75" t="s">
         <v>68</v>
       </c>
-      <c r="P74" s="6">
+      <c r="P75" s="6">
         <v>-16.100000000000001</v>
       </c>
-      <c r="Q74" s="6">
+      <c r="Q75" s="6">
         <v>5.5</v>
       </c>
-      <c r="R74" s="6">
+      <c r="R75" s="6">
         <v>41.4</v>
       </c>
-      <c r="S74" s="6">
+      <c r="S75" s="6">
         <v>4.7</v>
       </c>
-      <c r="T74" s="6">
+      <c r="T75" s="6">
         <v>8.1999999999999993</v>
       </c>
-      <c r="U74" s="6">
+      <c r="U75" s="6">
         <v>-1.1000000000000001</v>
       </c>
-      <c r="V74" s="6">
+      <c r="V75" s="6">
         <v>34.5</v>
       </c>
-      <c r="W74" s="6">
+      <c r="W75" s="6">
         <v>9.1</v>
       </c>
-      <c r="X74" s="6">
+      <c r="X75" s="6">
         <v>-12.6</v>
       </c>
-      <c r="Y74" s="6">
+      <c r="Y75" s="6">
         <v>-17.899999999999999</v>
       </c>
-      <c r="Z74" s="6">
+      <c r="Z75" s="6">
         <v>-4.5</v>
       </c>
-      <c r="AA74" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB74" s="6">
-        <v>0</v>
-      </c>
-      <c r="AI74" s="6">
+      <c r="AA75" s="6">
+        <v>19.8</v>
+      </c>
+      <c r="AB75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI75" s="6">
         <f t="shared" si="105"/>
         <v>59.8</v>
       </c>
-      <c r="AJ74" s="6">
+      <c r="AJ75" s="6">
         <f t="shared" si="106"/>
         <v>29.9</v>
       </c>
-      <c r="AK74" s="6">
+      <c r="AK75" s="6">
         <f t="shared" si="107"/>
-        <v>-22.4</v>
-      </c>
-      <c r="AL74" s="6">
-        <v>0</v>
-      </c>
-      <c r="AM74" s="6">
-        <v>0</v>
-      </c>
-      <c r="AN74" s="6">
-        <v>0</v>
-      </c>
-      <c r="AO74" s="6">
-        <v>0</v>
-      </c>
-      <c r="AP74" s="6">
-        <v>0</v>
-      </c>
-      <c r="AQ74" s="6">
-        <v>0</v>
-      </c>
-      <c r="AR74" s="6">
-        <v>0</v>
-      </c>
-      <c r="AS74" s="6">
-        <v>0</v>
-      </c>
-      <c r="AT74" s="6">
-        <v>0</v>
-      </c>
-      <c r="AU74" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="2:47" x14ac:dyDescent="0.3">
-      <c r="B75" t="s">
+        <v>-2.5999999999999979</v>
+      </c>
+      <c r="AL75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AO75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AP75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AQ75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AR75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AS75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AT75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AU75" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:47" x14ac:dyDescent="0.3">
+      <c r="B76" t="s">
         <v>78</v>
       </c>
-      <c r="P75" s="6">
+      <c r="P76" s="6">
         <v>-2.2999999999999998</v>
       </c>
-      <c r="Q75" s="6">
+      <c r="Q76" s="6">
         <v>-3.1</v>
       </c>
-      <c r="R75" s="6">
+      <c r="R76" s="6">
         <v>20.6</v>
       </c>
-      <c r="S75" s="6">
+      <c r="S76" s="6">
         <v>34.200000000000003</v>
       </c>
-      <c r="T75" s="6">
+      <c r="T76" s="6">
         <v>-32.5</v>
       </c>
-      <c r="U75" s="6">
+      <c r="U76" s="6">
         <v>21.2</v>
       </c>
-      <c r="V75" s="6">
+      <c r="V76" s="6">
         <v>70.2</v>
       </c>
-      <c r="W75" s="6">
+      <c r="W76" s="6">
         <v>11.3</v>
       </c>
-      <c r="X75" s="6">
+      <c r="X76" s="6">
         <v>6.1</v>
       </c>
-      <c r="Y75" s="6">
+      <c r="Y76" s="6">
         <v>-4.4000000000000004</v>
       </c>
-      <c r="Z75" s="6">
+      <c r="Z76" s="6">
         <v>11.8</v>
       </c>
-      <c r="AA75" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB75" s="6">
-        <v>0</v>
-      </c>
-      <c r="AI75" s="6">
+      <c r="AA76" s="6">
+        <v>28.9</v>
+      </c>
+      <c r="AB76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI76" s="6">
         <f t="shared" si="105"/>
         <v>19.200000000000003</v>
       </c>
-      <c r="AJ75" s="6">
+      <c r="AJ76" s="6">
         <f t="shared" si="106"/>
         <v>108.8</v>
       </c>
-      <c r="AK75" s="6">
+      <c r="AK76" s="6">
         <f t="shared" si="107"/>
-        <v>7.4</v>
-      </c>
-      <c r="AL75" s="6">
-        <v>0</v>
-      </c>
-      <c r="AM75" s="6">
-        <v>0</v>
-      </c>
-      <c r="AN75" s="6">
-        <v>0</v>
-      </c>
-      <c r="AO75" s="6">
-        <v>0</v>
-      </c>
-      <c r="AP75" s="6">
-        <v>0</v>
-      </c>
-      <c r="AQ75" s="6">
-        <v>0</v>
-      </c>
-      <c r="AR75" s="6">
-        <v>0</v>
-      </c>
-      <c r="AS75" s="6">
-        <v>0</v>
-      </c>
-      <c r="AT75" s="6">
-        <v>0</v>
-      </c>
-      <c r="AU75" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="2:47" x14ac:dyDescent="0.3">
-      <c r="B76" t="s">
+        <v>36.299999999999997</v>
+      </c>
+      <c r="AL76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AO76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AP76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AQ76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AR76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AS76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AT76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AU76" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:47" x14ac:dyDescent="0.3">
+      <c r="B77" t="s">
         <v>79</v>
       </c>
-      <c r="P76" s="6">
+      <c r="P77" s="6">
         <v>46.8</v>
       </c>
-      <c r="Q76" s="6">
+      <c r="Q77" s="6">
         <v>-8.5</v>
       </c>
-      <c r="R76" s="6">
+      <c r="R77" s="6">
         <v>35.6</v>
       </c>
-      <c r="S76" s="6">
+      <c r="S77" s="6">
         <v>6.6</v>
       </c>
-      <c r="T76" s="6">
+      <c r="T77" s="6">
         <v>137.30000000000001</v>
       </c>
-      <c r="U76" s="6">
+      <c r="U77" s="6">
         <v>-54.7</v>
       </c>
-      <c r="V76" s="6">
+      <c r="V77" s="6">
         <v>59.3</v>
       </c>
-      <c r="W76" s="6">
+      <c r="W77" s="6">
         <v>34.1</v>
       </c>
-      <c r="X76" s="6">
+      <c r="X77" s="6">
         <v>32.200000000000003</v>
       </c>
-      <c r="Y76" s="6">
+      <c r="Y77" s="6">
         <v>3.9</v>
       </c>
-      <c r="Z76" s="6">
+      <c r="Z77" s="6">
         <v>93.3</v>
       </c>
-      <c r="AA76" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB76" s="6">
-        <v>0</v>
-      </c>
-      <c r="AI76" s="6">
+      <c r="AA77" s="6">
+        <v>120.6</v>
+      </c>
+      <c r="AB77" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI77" s="6">
         <f t="shared" si="105"/>
         <v>171</v>
       </c>
-      <c r="AJ76" s="6">
+      <c r="AJ77" s="6">
         <f t="shared" si="106"/>
         <v>70.900000000000006</v>
       </c>
-      <c r="AK76" s="6">
+      <c r="AK77" s="6">
         <f t="shared" si="107"/>
-        <v>97.2</v>
-      </c>
-      <c r="AL76" s="6">
-        <v>0</v>
-      </c>
-      <c r="AM76" s="6">
-        <v>0</v>
-      </c>
-      <c r="AN76" s="6">
-        <v>0</v>
-      </c>
-      <c r="AO76" s="6">
-        <v>0</v>
-      </c>
-      <c r="AP76" s="6">
-        <v>0</v>
-      </c>
-      <c r="AQ76" s="6">
-        <v>0</v>
-      </c>
-      <c r="AR76" s="6">
-        <v>0</v>
-      </c>
-      <c r="AS76" s="6">
-        <v>0</v>
-      </c>
-      <c r="AT76" s="6">
-        <v>0</v>
-      </c>
-      <c r="AU76" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="2:47" x14ac:dyDescent="0.3">
-      <c r="B77" t="s">
+        <v>217.8</v>
+      </c>
+      <c r="AL77" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM77" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN77" s="6">
+        <v>0</v>
+      </c>
+      <c r="AO77" s="6">
+        <v>0</v>
+      </c>
+      <c r="AP77" s="6">
+        <v>0</v>
+      </c>
+      <c r="AQ77" s="6">
+        <v>0</v>
+      </c>
+      <c r="AR77" s="6">
+        <v>0</v>
+      </c>
+      <c r="AS77" s="6">
+        <v>0</v>
+      </c>
+      <c r="AT77" s="6">
+        <v>0</v>
+      </c>
+      <c r="AU77" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="2:47" x14ac:dyDescent="0.3">
+      <c r="B78" t="s">
         <v>71</v>
       </c>
-      <c r="P77" s="6">
+      <c r="P78" s="6">
         <v>-13.2</v>
       </c>
-      <c r="Q77" s="6">
+      <c r="Q78" s="6">
         <v>-10.8</v>
       </c>
-      <c r="R77" s="6">
+      <c r="R78" s="6">
         <v>-5.3</v>
       </c>
-      <c r="S77" s="6">
+      <c r="S78" s="6">
         <v>-12.7</v>
       </c>
-      <c r="T77" s="6">
+      <c r="T78" s="6">
         <v>-11.8</v>
       </c>
-      <c r="U77" s="6">
+      <c r="U78" s="6">
         <v>-13.4</v>
       </c>
-      <c r="V77" s="6">
+      <c r="V78" s="6">
         <v>-11.9</v>
       </c>
-      <c r="W77" s="6">
+      <c r="W78" s="6">
         <v>-9.1</v>
       </c>
-      <c r="X77" s="6">
+      <c r="X78" s="6">
         <v>-12.4</v>
       </c>
-      <c r="Y77" s="6">
+      <c r="Y78" s="6">
         <v>-11.8</v>
       </c>
-      <c r="Z77" s="6">
+      <c r="Z78" s="6">
         <v>-14.6</v>
       </c>
-      <c r="AA77" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB77" s="6">
-        <v>0</v>
-      </c>
-      <c r="AI77" s="6">
+      <c r="AA78" s="6">
+        <v>-16</v>
+      </c>
+      <c r="AB78" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI78" s="6">
         <f t="shared" si="105"/>
         <v>-40.6</v>
       </c>
-      <c r="AJ77" s="6">
+      <c r="AJ78" s="6">
         <f t="shared" si="106"/>
         <v>-46.8</v>
       </c>
-      <c r="AK77" s="6">
+      <c r="AK78" s="6">
         <f t="shared" si="107"/>
-        <v>-26.4</v>
-      </c>
-      <c r="AL77" s="6">
-        <v>0</v>
-      </c>
-      <c r="AM77" s="6">
-        <f t="shared" ref="AM77:AU77" si="113">AL77*1.05</f>
-        <v>0</v>
-      </c>
-      <c r="AN77" s="6">
+        <v>-42.4</v>
+      </c>
+      <c r="AL78" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM78" s="6">
+        <f t="shared" ref="AM78:AU78" si="113">AL78*1.05</f>
+        <v>0</v>
+      </c>
+      <c r="AN78" s="6">
         <f t="shared" si="113"/>
         <v>0</v>
       </c>
-      <c r="AO77" s="6">
+      <c r="AO78" s="6">
         <f t="shared" si="113"/>
         <v>0</v>
       </c>
-      <c r="AP77" s="6">
+      <c r="AP78" s="6">
         <f t="shared" si="113"/>
         <v>0</v>
       </c>
-      <c r="AQ77" s="6">
+      <c r="AQ78" s="6">
         <f t="shared" si="113"/>
         <v>0</v>
       </c>
-      <c r="AR77" s="6">
+      <c r="AR78" s="6">
         <f t="shared" si="113"/>
         <v>0</v>
       </c>
-      <c r="AS77" s="6">
+      <c r="AS78" s="6">
         <f t="shared" si="113"/>
         <v>0</v>
       </c>
-      <c r="AT77" s="6">
+      <c r="AT78" s="6">
         <f t="shared" si="113"/>
         <v>0</v>
       </c>
-      <c r="AU77" s="6">
+      <c r="AU78" s="6">
         <f t="shared" si="113"/>
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="2:47" x14ac:dyDescent="0.3">
-      <c r="B78" t="s">
+    <row r="79" spans="2:47" x14ac:dyDescent="0.3">
+      <c r="B79" t="s">
         <v>67</v>
       </c>
-      <c r="P78" s="6">
+      <c r="P79" s="6">
         <v>467.4</v>
       </c>
-      <c r="Q78" s="6">
+      <c r="Q79" s="6">
         <v>-110.5</v>
       </c>
-      <c r="R78" s="6">
+      <c r="R79" s="6">
         <v>-39</v>
       </c>
-      <c r="S78" s="6">
+      <c r="S79" s="6">
         <v>82.1</v>
       </c>
-      <c r="T78" s="6">
+      <c r="T79" s="6">
         <v>595.4</v>
       </c>
-      <c r="U78" s="6">
+      <c r="U79" s="6">
         <v>-261.2</v>
       </c>
-      <c r="V78" s="6">
+      <c r="V79" s="6">
         <v>-88.3</v>
       </c>
-      <c r="W78" s="6">
+      <c r="W79" s="6">
         <v>122.8</v>
       </c>
-      <c r="X78" s="6">
+      <c r="X79" s="6">
         <v>609.4</v>
       </c>
-      <c r="Y78" s="6">
+      <c r="Y79" s="6">
         <v>-271.39999999999998</v>
       </c>
-      <c r="Z78" s="6">
+      <c r="Z79" s="6">
         <v>-52.5</v>
       </c>
-      <c r="AA78" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB78" s="6">
-        <v>0</v>
-      </c>
-      <c r="AI78" s="6">
+      <c r="AA79" s="6">
+        <v>151.5</v>
+      </c>
+      <c r="AB79" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI79" s="6">
         <f t="shared" si="105"/>
         <v>528</v>
       </c>
-      <c r="AJ78" s="6">
+      <c r="AJ79" s="6">
         <f t="shared" si="106"/>
         <v>382.7</v>
       </c>
-      <c r="AK78" s="6">
+      <c r="AK79" s="6">
         <f t="shared" si="107"/>
-        <v>-323.89999999999998</v>
-      </c>
-      <c r="AL78" s="6">
-        <v>0</v>
-      </c>
-      <c r="AM78" s="6">
-        <v>0</v>
-      </c>
-      <c r="AN78" s="6">
-        <v>0</v>
-      </c>
-      <c r="AO78" s="6">
-        <v>0</v>
-      </c>
-      <c r="AP78" s="6">
-        <v>0</v>
-      </c>
-      <c r="AQ78" s="6">
-        <v>0</v>
-      </c>
-      <c r="AR78" s="6">
-        <v>0</v>
-      </c>
-      <c r="AS78" s="6">
-        <v>0</v>
-      </c>
-      <c r="AT78" s="6">
-        <v>0</v>
-      </c>
-      <c r="AU78" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="2:47" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B79" s="1" t="s">
+        <v>-172.39999999999998</v>
+      </c>
+      <c r="AL79" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM79" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN79" s="6">
+        <v>0</v>
+      </c>
+      <c r="AO79" s="6">
+        <v>0</v>
+      </c>
+      <c r="AP79" s="6">
+        <v>0</v>
+      </c>
+      <c r="AQ79" s="6">
+        <v>0</v>
+      </c>
+      <c r="AR79" s="6">
+        <v>0</v>
+      </c>
+      <c r="AS79" s="6">
+        <v>0</v>
+      </c>
+      <c r="AT79" s="6">
+        <v>0</v>
+      </c>
+      <c r="AU79" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="2:47" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B80" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="P79" s="9">
-        <f t="shared" ref="P79:X79" si="114">P60+SUM(P62:P78)</f>
+      <c r="P80" s="9">
+        <f t="shared" ref="P80:X80" si="114">P60+SUM(P62:P79)</f>
         <v>217.1</v>
       </c>
-      <c r="Q79" s="9">
+      <c r="Q80" s="9">
         <f t="shared" si="114"/>
         <v>299.80000000000007</v>
       </c>
-      <c r="R79" s="9">
+      <c r="R80" s="9">
         <f t="shared" si="114"/>
         <v>83.6</v>
       </c>
-      <c r="S79" s="9">
+      <c r="S80" s="9">
         <f t="shared" si="114"/>
         <v>121.50000000000011</v>
       </c>
-      <c r="T79" s="9">
+      <c r="T80" s="9">
         <f t="shared" si="114"/>
         <v>345.10000000000014</v>
       </c>
-      <c r="U79" s="9">
+      <c r="U80" s="9">
         <f t="shared" si="114"/>
         <v>356.30000000000007</v>
       </c>
-      <c r="V79" s="9">
+      <c r="V80" s="9">
         <f t="shared" si="114"/>
         <v>70.699999999999875</v>
       </c>
-      <c r="W79" s="9">
+      <c r="W80" s="9">
         <f t="shared" si="114"/>
-        <v>105.30000000000013</v>
-      </c>
-      <c r="X79" s="9">
+        <v>105.20000000000016</v>
+      </c>
+      <c r="X80" s="9">
         <f t="shared" si="114"/>
         <v>431.69999999999993</v>
       </c>
-      <c r="Y79" s="9">
-        <f t="shared" ref="Y79:AB79" si="115">Y60+SUM(Y62:Y78)</f>
+      <c r="Y80" s="9">
+        <f t="shared" ref="Y80:AB80" si="115">Y60+SUM(Y62:Y79)</f>
         <v>228.2</v>
       </c>
-      <c r="Z79" s="9">
+      <c r="Z80" s="9">
         <f t="shared" si="115"/>
         <v>74.800000000000011</v>
       </c>
-      <c r="AA79" s="9">
+      <c r="AA80" s="9">
         <f t="shared" si="115"/>
-        <v>184.17665040000009</v>
-      </c>
-      <c r="AB79" s="9">
+        <v>135.10000000000014</v>
+      </c>
+      <c r="AB80" s="9">
         <f t="shared" si="115"/>
-        <v>203.75191599999999</v>
-      </c>
-      <c r="AI79" s="9">
-        <f>AI60+SUM(AI62:AI78)</f>
+        <v>223.77248599999996</v>
+      </c>
+      <c r="AI80" s="9">
+        <f>AI60+SUM(AI62:AI79)</f>
         <v>850.00000000000057</v>
       </c>
-      <c r="AJ79" s="9">
-        <f>AJ60+SUM(AJ62:AJ78)</f>
-        <v>964.00000000000045</v>
-      </c>
-      <c r="AK79" s="9">
-        <f t="shared" ref="AK79:AU79" si="116">AK60+SUM(AK62:AK78)</f>
-        <v>688.8285664</v>
-      </c>
-      <c r="AL79" s="9">
+      <c r="AJ80" s="9">
+        <f>AJ60+SUM(AJ62:AJ79)</f>
+        <v>962.80000000000018</v>
+      </c>
+      <c r="AK80" s="9">
+        <f t="shared" ref="AK80:AU80" si="116">AK60+SUM(AK62:AK79)</f>
+        <v>661.87248599999975</v>
+      </c>
+      <c r="AL80" s="9">
         <f t="shared" si="116"/>
-        <v>1301.7325500840002</v>
-      </c>
-      <c r="AM79" s="9">
+        <v>1336.3664395999999</v>
+      </c>
+      <c r="AM80" s="9">
         <f t="shared" si="116"/>
-        <v>1782.0752817935991</v>
-      </c>
-      <c r="AN79" s="9">
+        <v>1814.6558700479993</v>
+      </c>
+      <c r="AN80" s="9">
         <f t="shared" si="116"/>
-        <v>2169.956922454111</v>
-      </c>
-      <c r="AO79" s="9">
+        <v>2201.725672046719</v>
+      </c>
+      <c r="AO80" s="9">
         <f t="shared" si="116"/>
-        <v>2427.9846889147839</v>
-      </c>
-      <c r="AP79" s="9">
+        <v>2457.640092301343</v>
+      </c>
+      <c r="AP80" s="9">
         <f t="shared" si="116"/>
-        <v>2722.3476998190699</v>
-      </c>
-      <c r="AQ79" s="9">
+        <v>2751.2358936914452</v>
+      </c>
+      <c r="AQ80" s="9">
         <f t="shared" si="116"/>
-        <v>2902.7042562601146</v>
-      </c>
-      <c r="AR79" s="9">
+        <v>2930.9470415287888</v>
+      </c>
+      <c r="AR80" s="9">
         <f t="shared" si="116"/>
-        <v>2979.6873156817728</v>
-      </c>
-      <c r="AS79" s="9">
+        <v>2919.4055287250385</v>
+      </c>
+      <c r="AS80" s="9">
         <f t="shared" si="116"/>
-        <v>3057.0153096362633</v>
-      </c>
-      <c r="AT79" s="9">
+        <v>2992.2482122995621</v>
+      </c>
+      <c r="AT80" s="9">
         <f t="shared" si="116"/>
-        <v>3153.8521157562736</v>
-      </c>
-      <c r="AU79" s="9">
+        <v>3084.6090241567267</v>
+      </c>
+      <c r="AU80" s="9">
         <f t="shared" si="116"/>
-        <v>3269.8967811689472</v>
-      </c>
-    </row>
-    <row r="80" spans="2:47" x14ac:dyDescent="0.3">
-      <c r="B80" t="s">
-        <v>70</v>
-      </c>
-      <c r="P80" s="6">
-        <v>5.4</v>
-      </c>
-      <c r="Q80" s="6">
-        <v>7</v>
-      </c>
-      <c r="R80" s="6">
-        <v>6.3</v>
-      </c>
-      <c r="S80" s="6">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="T80" s="6">
-        <v>13.1</v>
-      </c>
-      <c r="U80" s="6">
-        <v>16.5</v>
-      </c>
-      <c r="V80" s="6">
-        <v>5</v>
-      </c>
-      <c r="W80" s="6">
-        <v>13.4</v>
-      </c>
-      <c r="X80" s="6">
-        <v>11.3</v>
-      </c>
-      <c r="Y80" s="6">
-        <v>45</v>
-      </c>
-      <c r="Z80" s="6">
-        <v>16.7</v>
-      </c>
-      <c r="AA80" s="6">
-        <v>20</v>
-      </c>
-      <c r="AB80" s="6">
-        <v>25</v>
-      </c>
-      <c r="AI80" s="6">
-        <f t="shared" ref="AI80:AI81" si="117">SUM(Q80:T80)</f>
-        <v>35.1</v>
-      </c>
-      <c r="AJ80" s="6">
-        <f t="shared" ref="AJ80:AJ81" si="118">SUM(U80:X80)</f>
-        <v>46.2</v>
-      </c>
-      <c r="AK80" s="6">
-        <f t="shared" ref="AK80:AK81" si="119">SUM(Y80:AB80)</f>
-        <v>106.7</v>
-      </c>
-      <c r="AL80" s="6"/>
-      <c r="AM80" s="6"/>
-      <c r="AN80" s="6"/>
-      <c r="AO80" s="6"/>
-      <c r="AP80" s="6"/>
-      <c r="AQ80" s="6"/>
-      <c r="AR80" s="6"/>
-      <c r="AS80" s="6"/>
-      <c r="AT80" s="6"/>
-      <c r="AU80" s="6"/>
+        <v>3196.2274309884197</v>
+      </c>
     </row>
     <row r="81" spans="2:159" x14ac:dyDescent="0.3">
       <c r="B81" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="P81" s="6">
-        <v>6.7</v>
+        <v>5.4</v>
       </c>
       <c r="Q81" s="6">
-        <v>9.3000000000000007</v>
+        <v>7</v>
       </c>
       <c r="R81" s="6">
-        <v>7.9</v>
+        <v>6.3</v>
       </c>
       <c r="S81" s="6">
-        <v>9.9</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="T81" s="6">
-        <v>7</v>
+        <v>13.1</v>
       </c>
       <c r="U81" s="6">
-        <v>7.4</v>
+        <v>16.5</v>
       </c>
       <c r="V81" s="6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W81" s="6">
-        <v>10</v>
+        <v>13.4</v>
       </c>
       <c r="X81" s="6">
-        <v>6</v>
+        <v>11.3</v>
       </c>
       <c r="Y81" s="6">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="Z81" s="6">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="AA81" s="6">
-        <v>0</v>
+        <v>23.9</v>
       </c>
       <c r="AB81" s="6">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AI81" s="6">
-        <f t="shared" si="117"/>
-        <v>34.1</v>
+        <f t="shared" ref="AI81:AI82" si="117">SUM(Q81:T81)</f>
+        <v>35.1</v>
       </c>
       <c r="AJ81" s="6">
-        <f t="shared" si="118"/>
-        <v>29.4</v>
+        <f t="shared" ref="AJ81:AJ82" si="118">SUM(U81:X81)</f>
+        <v>46.2</v>
       </c>
       <c r="AK81" s="6">
-        <f t="shared" si="119"/>
-        <v>0</v>
+        <f t="shared" ref="AK81:AK82" si="119">SUM(Y81:AB81)</f>
+        <v>110.6</v>
       </c>
       <c r="AL81" s="6"/>
       <c r="AM81" s="6"/>
@@ -7868,826 +7854,892 @@
     </row>
     <row r="82" spans="2:159" x14ac:dyDescent="0.3">
       <c r="B82" t="s">
+        <v>73</v>
+      </c>
+      <c r="P82" s="6">
+        <v>6.7</v>
+      </c>
+      <c r="Q82" s="6">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="R82" s="6">
+        <v>7.9</v>
+      </c>
+      <c r="S82" s="6">
+        <v>9.9</v>
+      </c>
+      <c r="T82" s="6">
+        <v>7</v>
+      </c>
+      <c r="U82" s="6">
+        <v>7.4</v>
+      </c>
+      <c r="V82" s="6">
+        <v>6</v>
+      </c>
+      <c r="W82" s="6">
+        <v>10</v>
+      </c>
+      <c r="X82" s="6">
+        <v>6</v>
+      </c>
+      <c r="Y82" s="6">
+        <v>0</v>
+      </c>
+      <c r="Z82" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA82" s="6">
+        <v>0</v>
+      </c>
+      <c r="AB82" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI82" s="6">
+        <f t="shared" si="117"/>
+        <v>34.1</v>
+      </c>
+      <c r="AJ82" s="6">
+        <f t="shared" si="118"/>
+        <v>29.4</v>
+      </c>
+      <c r="AK82" s="6">
+        <f t="shared" si="119"/>
+        <v>0</v>
+      </c>
+      <c r="AL82" s="6"/>
+      <c r="AM82" s="6"/>
+      <c r="AN82" s="6"/>
+      <c r="AO82" s="6"/>
+      <c r="AP82" s="6"/>
+      <c r="AQ82" s="6"/>
+      <c r="AR82" s="6"/>
+      <c r="AS82" s="6"/>
+      <c r="AT82" s="6"/>
+      <c r="AU82" s="6"/>
+    </row>
+    <row r="83" spans="2:159" x14ac:dyDescent="0.3">
+      <c r="B83" t="s">
         <v>100</v>
       </c>
-      <c r="P82" s="6">
-        <f>P80+P81</f>
+      <c r="P83" s="6">
+        <f>P81+P82</f>
         <v>12.100000000000001</v>
       </c>
-      <c r="Q82" s="6">
-        <f t="shared" ref="Q82:X82" si="120">Q80+Q81</f>
+      <c r="Q83" s="6">
+        <f t="shared" ref="Q83:X83" si="120">Q81+Q82</f>
         <v>16.3</v>
       </c>
-      <c r="R82" s="6">
+      <c r="R83" s="6">
         <f t="shared" si="120"/>
         <v>14.2</v>
       </c>
-      <c r="S82" s="6">
+      <c r="S83" s="6">
         <f t="shared" si="120"/>
         <v>18.600000000000001</v>
       </c>
-      <c r="T82" s="6">
+      <c r="T83" s="6">
         <f t="shared" si="120"/>
         <v>20.100000000000001</v>
       </c>
-      <c r="U82" s="6">
+      <c r="U83" s="6">
         <f t="shared" si="120"/>
         <v>23.9</v>
       </c>
-      <c r="V82" s="6">
+      <c r="V83" s="6">
         <f t="shared" si="120"/>
         <v>11</v>
       </c>
-      <c r="W82" s="6">
+      <c r="W83" s="6">
         <f t="shared" si="120"/>
         <v>23.4</v>
       </c>
-      <c r="X82" s="6">
+      <c r="X83" s="6">
         <f t="shared" si="120"/>
         <v>17.3</v>
       </c>
-      <c r="Y82" s="6">
-        <f t="shared" ref="Y82" si="121">Y80+Y81</f>
+      <c r="Y83" s="6">
+        <f t="shared" ref="Y83" si="121">Y81+Y82</f>
         <v>45</v>
       </c>
-      <c r="Z82" s="6">
-        <f t="shared" ref="Z82" si="122">Z80+Z81</f>
+      <c r="Z83" s="6">
+        <f t="shared" ref="Z83" si="122">Z81+Z82</f>
         <v>16.7</v>
       </c>
-      <c r="AA82" s="6">
-        <f t="shared" ref="AA82" si="123">AA80+AA81</f>
-        <v>20</v>
-      </c>
-      <c r="AB82" s="6">
-        <f t="shared" ref="AB82" si="124">AB80+AB81</f>
+      <c r="AA83" s="6">
+        <f t="shared" ref="AA83" si="123">AA81+AA82</f>
+        <v>23.9</v>
+      </c>
+      <c r="AB83" s="6">
+        <f t="shared" ref="AB83" si="124">AB81+AB82</f>
         <v>25</v>
       </c>
-      <c r="AI82" s="6">
-        <f t="shared" ref="AI82" si="125">AI80+AI81</f>
+      <c r="AI83" s="6">
+        <f t="shared" ref="AI83" si="125">AI81+AI82</f>
         <v>69.2</v>
       </c>
-      <c r="AJ82" s="6">
-        <f t="shared" ref="AJ82" si="126">AJ80+AJ81</f>
+      <c r="AJ83" s="6">
+        <f t="shared" ref="AJ83" si="126">AJ81+AJ82</f>
         <v>75.599999999999994</v>
       </c>
-      <c r="AK82" s="6">
-        <f t="shared" ref="AK82" si="127">AK80+AK81</f>
-        <v>106.7</v>
-      </c>
-      <c r="AL82" s="6">
-        <f>AK82*1.3</f>
-        <v>138.71</v>
-      </c>
-      <c r="AM82" s="6">
-        <f>AL82*1.02</f>
-        <v>141.48420000000002</v>
-      </c>
-      <c r="AN82" s="6">
-        <f t="shared" ref="AN82:AU82" si="128">AM82*1.02</f>
-        <v>144.31388400000003</v>
-      </c>
-      <c r="AO82" s="6">
+      <c r="AK83" s="6">
+        <f t="shared" ref="AK83" si="127">AK81+AK82</f>
+        <v>110.6</v>
+      </c>
+      <c r="AL83" s="6">
+        <f>AK83*1.3</f>
+        <v>143.78</v>
+      </c>
+      <c r="AM83" s="6">
+        <f>AL83*1.15</f>
+        <v>165.34699999999998</v>
+      </c>
+      <c r="AN83" s="6">
+        <f>AM83*1.1</f>
+        <v>181.8817</v>
+      </c>
+      <c r="AO83" s="6">
+        <f>AN83*1.07</f>
+        <v>194.61341899999999</v>
+      </c>
+      <c r="AP83" s="6">
+        <f>AO83*1.06</f>
+        <v>206.29022413999999</v>
+      </c>
+      <c r="AQ83" s="6">
+        <f>AP83*1.05</f>
+        <v>216.604735347</v>
+      </c>
+      <c r="AR83" s="6">
+        <f t="shared" ref="AR83:AU83" si="128">AQ83*1.05</f>
+        <v>227.43497211435002</v>
+      </c>
+      <c r="AS83" s="6">
         <f t="shared" si="128"/>
-        <v>147.20016168000004</v>
-      </c>
-      <c r="AP82" s="6">
+        <v>238.80672072006752</v>
+      </c>
+      <c r="AT83" s="6">
         <f t="shared" si="128"/>
-        <v>150.14416491360004</v>
-      </c>
-      <c r="AQ82" s="6">
+        <v>250.74705675607089</v>
+      </c>
+      <c r="AU83" s="6">
         <f t="shared" si="128"/>
-        <v>153.14704821187203</v>
-      </c>
-      <c r="AR82" s="6">
-        <f t="shared" si="128"/>
-        <v>156.20998917610947</v>
-      </c>
-      <c r="AS82" s="6">
-        <f t="shared" si="128"/>
-        <v>159.33418895963166</v>
-      </c>
-      <c r="AT82" s="6">
-        <f t="shared" si="128"/>
-        <v>162.52087273882429</v>
-      </c>
-      <c r="AU82" s="6">
-        <f t="shared" si="128"/>
-        <v>165.77129019360078</v>
-      </c>
-    </row>
-    <row r="83" spans="2:159" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B83" s="1" t="s">
+        <v>263.28440959387444</v>
+      </c>
+    </row>
+    <row r="84" spans="2:159" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B84" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="P83" s="9">
-        <f>P79-P82</f>
+      <c r="P84" s="9">
+        <f>P80-P83</f>
         <v>205</v>
       </c>
-      <c r="Q83" s="9">
-        <f t="shared" ref="Q83:X83" si="129">Q79-Q82</f>
+      <c r="Q84" s="9">
+        <f t="shared" ref="Q84:X84" si="129">Q80-Q83</f>
         <v>283.50000000000006</v>
       </c>
-      <c r="R83" s="9">
+      <c r="R84" s="9">
         <f t="shared" si="129"/>
         <v>69.399999999999991</v>
       </c>
-      <c r="S83" s="9">
+      <c r="S84" s="9">
         <f t="shared" si="129"/>
         <v>102.90000000000012</v>
       </c>
-      <c r="T83" s="9">
+      <c r="T84" s="9">
         <f t="shared" si="129"/>
         <v>325.00000000000011</v>
       </c>
-      <c r="U83" s="9">
+      <c r="U84" s="9">
         <f t="shared" si="129"/>
         <v>332.40000000000009</v>
       </c>
-      <c r="V83" s="9">
+      <c r="V84" s="9">
         <f t="shared" si="129"/>
         <v>59.699999999999875</v>
       </c>
-      <c r="W83" s="9">
+      <c r="W84" s="9">
         <f t="shared" si="129"/>
-        <v>81.900000000000119</v>
-      </c>
-      <c r="X83" s="9">
+        <v>81.800000000000153</v>
+      </c>
+      <c r="X84" s="9">
         <f t="shared" si="129"/>
         <v>414.39999999999992</v>
       </c>
-      <c r="Y83" s="9">
-        <f t="shared" ref="Y83" si="130">Y79-Y82</f>
+      <c r="Y84" s="9">
+        <f t="shared" ref="Y84" si="130">Y80-Y83</f>
         <v>183.2</v>
       </c>
-      <c r="Z83" s="9">
-        <f t="shared" ref="Z83" si="131">Z79-Z82</f>
+      <c r="Z84" s="9">
+        <f t="shared" ref="Z84" si="131">Z80-Z83</f>
         <v>58.100000000000009</v>
       </c>
-      <c r="AA83" s="9">
-        <f t="shared" ref="AA83" si="132">AA79-AA82</f>
-        <v>164.17665040000009</v>
-      </c>
-      <c r="AB83" s="9">
-        <f t="shared" ref="AB83" si="133">AB79-AB82</f>
-        <v>178.75191599999999</v>
-      </c>
-      <c r="AI83" s="9">
-        <f t="shared" ref="AI83" si="134">AI79-AI82</f>
+      <c r="AA84" s="9">
+        <f t="shared" ref="AA84" si="132">AA80-AA83</f>
+        <v>111.20000000000013</v>
+      </c>
+      <c r="AB84" s="9">
+        <f t="shared" ref="AB84" si="133">AB80-AB83</f>
+        <v>198.77248599999996</v>
+      </c>
+      <c r="AI84" s="9">
+        <f t="shared" ref="AI84" si="134">AI80-AI83</f>
         <v>780.80000000000052</v>
       </c>
-      <c r="AJ83" s="9">
-        <f t="shared" ref="AJ83" si="135">AJ79-AJ82</f>
-        <v>888.40000000000043</v>
-      </c>
-      <c r="AK83" s="9">
-        <f t="shared" ref="AK83" si="136">AK79-AK82</f>
-        <v>582.12856639999995</v>
-      </c>
-      <c r="AL83" s="9">
-        <f t="shared" ref="AL83" si="137">AL79-AL82</f>
-        <v>1163.0225500840002</v>
-      </c>
-      <c r="AM83" s="9">
-        <f t="shared" ref="AM83" si="138">AM79-AM82</f>
-        <v>1640.591081793599</v>
-      </c>
-      <c r="AN83" s="9">
-        <f t="shared" ref="AN83" si="139">AN79-AN82</f>
-        <v>2025.6430384541109</v>
-      </c>
-      <c r="AO83" s="9">
-        <f t="shared" ref="AO83" si="140">AO79-AO82</f>
-        <v>2280.784527234784</v>
-      </c>
-      <c r="AP83" s="9">
-        <f t="shared" ref="AP83" si="141">AP79-AP82</f>
-        <v>2572.20353490547</v>
-      </c>
-      <c r="AQ83" s="9">
-        <f t="shared" ref="AQ83" si="142">AQ79-AQ82</f>
-        <v>2749.5572080482425</v>
-      </c>
-      <c r="AR83" s="9">
-        <f t="shared" ref="AR83" si="143">AR79-AR82</f>
-        <v>2823.4773265056633</v>
-      </c>
-      <c r="AS83" s="9">
-        <f t="shared" ref="AS83" si="144">AS79-AS82</f>
-        <v>2897.6811206766315</v>
-      </c>
-      <c r="AT83" s="9">
-        <f t="shared" ref="AT83" si="145">AT79-AT82</f>
-        <v>2991.3312430174492</v>
-      </c>
-      <c r="AU83" s="9">
-        <f t="shared" ref="AU83" si="146">AU79-AU82</f>
-        <v>3104.1254909753466</v>
-      </c>
-      <c r="AV83" s="1">
-        <f>AU83*(1+$AX$22)</f>
-        <v>3073.0842360655929</v>
-      </c>
-      <c r="AW83" s="1">
-        <f t="shared" ref="AW83:DH83" si="147">AV83*(1+$AX$22)</f>
-        <v>3042.3533937049369</v>
-      </c>
-      <c r="AX83" s="1">
+      <c r="AJ84" s="9">
+        <f t="shared" ref="AJ84" si="135">AJ80-AJ83</f>
+        <v>887.20000000000016</v>
+      </c>
+      <c r="AK84" s="9">
+        <f t="shared" ref="AK84" si="136">AK80-AK83</f>
+        <v>551.27248599999973</v>
+      </c>
+      <c r="AL84" s="9">
+        <f t="shared" ref="AL84" si="137">AL80-AL83</f>
+        <v>1192.5864395999999</v>
+      </c>
+      <c r="AM84" s="9">
+        <f t="shared" ref="AM84" si="138">AM80-AM83</f>
+        <v>1649.3088700479993</v>
+      </c>
+      <c r="AN84" s="9">
+        <f t="shared" ref="AN84" si="139">AN80-AN83</f>
+        <v>2019.843972046719</v>
+      </c>
+      <c r="AO84" s="9">
+        <f t="shared" ref="AO84" si="140">AO80-AO83</f>
+        <v>2263.0266733013432</v>
+      </c>
+      <c r="AP84" s="9">
+        <f t="shared" ref="AP84" si="141">AP80-AP83</f>
+        <v>2544.945669551445</v>
+      </c>
+      <c r="AQ84" s="9">
+        <f t="shared" ref="AQ84" si="142">AQ80-AQ83</f>
+        <v>2714.3423061817889</v>
+      </c>
+      <c r="AR84" s="9">
+        <f t="shared" ref="AR84" si="143">AR80-AR83</f>
+        <v>2691.9705566106886</v>
+      </c>
+      <c r="AS84" s="9">
+        <f t="shared" ref="AS84" si="144">AS80-AS83</f>
+        <v>2753.4414915794946</v>
+      </c>
+      <c r="AT84" s="9">
+        <f t="shared" ref="AT84" si="145">AT80-AT83</f>
+        <v>2833.8619674006559</v>
+      </c>
+      <c r="AU84" s="9">
+        <f t="shared" ref="AU84" si="146">AU80-AU83</f>
+        <v>2932.9430213945452</v>
+      </c>
+      <c r="AV84" s="1">
+        <f>AU84*(1+$AX$22)</f>
+        <v>2903.6135911805995</v>
+      </c>
+      <c r="AW84" s="1">
+        <f t="shared" ref="AW84:DH84" si="147">AV84*(1+$AX$22)</f>
+        <v>2874.5774552687935</v>
+      </c>
+      <c r="AX84" s="1">
         <f t="shared" si="147"/>
-        <v>3011.9298597678876</v>
-      </c>
-      <c r="AY83" s="1">
+        <v>2845.8316807161054</v>
+      </c>
+      <c r="AY84" s="1">
         <f t="shared" si="147"/>
-        <v>2981.8105611702085</v>
-      </c>
-      <c r="AZ83" s="1">
+        <v>2817.3733639089442</v>
+      </c>
+      <c r="AZ84" s="1">
         <f t="shared" si="147"/>
-        <v>2951.9924555585062</v>
-      </c>
-      <c r="BA83" s="1">
+        <v>2789.1996302698549</v>
+      </c>
+      <c r="BA84" s="1">
         <f t="shared" si="147"/>
-        <v>2922.4725310029212</v>
-      </c>
-      <c r="BB83" s="1">
+        <v>2761.3076339671561</v>
+      </c>
+      <c r="BB84" s="1">
         <f t="shared" si="147"/>
-        <v>2893.2478056928921</v>
-      </c>
-      <c r="BC83" s="1">
+        <v>2733.6945576274843</v>
+      </c>
+      <c r="BC84" s="1">
         <f t="shared" si="147"/>
-        <v>2864.3153276359631</v>
-      </c>
-      <c r="BD83" s="1">
+        <v>2706.3576120512093</v>
+      </c>
+      <c r="BD84" s="1">
         <f t="shared" si="147"/>
-        <v>2835.6721743596036</v>
-      </c>
-      <c r="BE83" s="1">
+        <v>2679.2940359306972</v>
+      </c>
+      <c r="BE84" s="1">
         <f t="shared" si="147"/>
-        <v>2807.3154526160074</v>
-      </c>
-      <c r="BF83" s="1">
+        <v>2652.5010955713901</v>
+      </c>
+      <c r="BF84" s="1">
         <f t="shared" si="147"/>
-        <v>2779.2422980898473</v>
-      </c>
-      <c r="BG83" s="1">
+        <v>2625.976084615676</v>
+      </c>
+      <c r="BG84" s="1">
         <f t="shared" si="147"/>
-        <v>2751.4498751089486</v>
-      </c>
-      <c r="BH83" s="1">
+        <v>2599.716323769519</v>
+      </c>
+      <c r="BH84" s="1">
         <f t="shared" si="147"/>
-        <v>2723.9353763578592</v>
-      </c>
-      <c r="BI83" s="1">
+        <v>2573.7191605318239</v>
+      </c>
+      <c r="BI84" s="1">
         <f t="shared" si="147"/>
-        <v>2696.6960225942807</v>
-      </c>
-      <c r="BJ83" s="1">
+        <v>2547.9819689265055</v>
+      </c>
+      <c r="BJ84" s="1">
         <f t="shared" si="147"/>
-        <v>2669.729062368338</v>
-      </c>
-      <c r="BK83" s="1">
+        <v>2522.5021492372402</v>
+      </c>
+      <c r="BK84" s="1">
         <f t="shared" si="147"/>
-        <v>2643.0317717446546</v>
-      </c>
-      <c r="BL83" s="1">
+        <v>2497.2771277448678</v>
+      </c>
+      <c r="BL84" s="1">
         <f t="shared" si="147"/>
-        <v>2616.6014540272081</v>
-      </c>
-      <c r="BM83" s="1">
+        <v>2472.304356467419</v>
+      </c>
+      <c r="BM84" s="1">
         <f t="shared" si="147"/>
-        <v>2590.435439486936</v>
-      </c>
-      <c r="BN83" s="1">
+        <v>2447.5813129027447</v>
+      </c>
+      <c r="BN84" s="1">
         <f t="shared" si="147"/>
-        <v>2564.5310850920669</v>
-      </c>
-      <c r="BO83" s="1">
+        <v>2423.1054997737174</v>
+      </c>
+      <c r="BO84" s="1">
         <f t="shared" si="147"/>
-        <v>2538.885774241146</v>
-      </c>
-      <c r="BP83" s="1">
+        <v>2398.87444477598</v>
+      </c>
+      <c r="BP84" s="1">
         <f t="shared" si="147"/>
-        <v>2513.4969164987347</v>
-      </c>
-      <c r="BQ83" s="1">
+        <v>2374.8857003282201</v>
+      </c>
+      <c r="BQ84" s="1">
         <f t="shared" si="147"/>
-        <v>2488.3619473337471</v>
-      </c>
-      <c r="BR83" s="1">
+        <v>2351.1368433249377</v>
+      </c>
+      <c r="BR84" s="1">
         <f t="shared" si="147"/>
-        <v>2463.4783278604095</v>
-      </c>
-      <c r="BS83" s="1">
+        <v>2327.6254748916881</v>
+      </c>
+      <c r="BS84" s="1">
         <f t="shared" si="147"/>
-        <v>2438.8435445818054</v>
-      </c>
-      <c r="BT83" s="1">
+        <v>2304.3492201427712</v>
+      </c>
+      <c r="BT84" s="1">
         <f t="shared" si="147"/>
-        <v>2414.4551091359872</v>
-      </c>
-      <c r="BU83" s="1">
+        <v>2281.3057279413433</v>
+      </c>
+      <c r="BU84" s="1">
         <f t="shared" si="147"/>
-        <v>2390.3105580446272</v>
-      </c>
-      <c r="BV83" s="1">
+        <v>2258.4926706619299</v>
+      </c>
+      <c r="BV84" s="1">
         <f t="shared" si="147"/>
-        <v>2366.407452464181</v>
-      </c>
-      <c r="BW83" s="1">
+        <v>2235.9077439553107</v>
+      </c>
+      <c r="BW84" s="1">
         <f t="shared" si="147"/>
-        <v>2342.7433779395392</v>
-      </c>
-      <c r="BX83" s="1">
+        <v>2213.5486665157578</v>
+      </c>
+      <c r="BX84" s="1">
         <f t="shared" si="147"/>
-        <v>2319.3159441601438</v>
-      </c>
-      <c r="BY83" s="1">
+        <v>2191.4131798506</v>
+      </c>
+      <c r="BY84" s="1">
         <f t="shared" si="147"/>
-        <v>2296.1227847185423</v>
-      </c>
-      <c r="BZ83" s="1">
+        <v>2169.4990480520942</v>
+      </c>
+      <c r="BZ84" s="1">
         <f t="shared" si="147"/>
-        <v>2273.1615568713569</v>
-      </c>
-      <c r="CA83" s="1">
+        <v>2147.8040575715731</v>
+      </c>
+      <c r="CA84" s="1">
         <f t="shared" si="147"/>
-        <v>2250.4299413026433</v>
-      </c>
-      <c r="CB83" s="1">
+        <v>2126.3260169958576</v>
+      </c>
+      <c r="CB84" s="1">
         <f t="shared" si="147"/>
-        <v>2227.9256418896171</v>
-      </c>
-      <c r="CC83" s="1">
+        <v>2105.0627568258988</v>
+      </c>
+      <c r="CC84" s="1">
         <f t="shared" si="147"/>
-        <v>2205.6463854707208</v>
-      </c>
-      <c r="CD83" s="1">
+        <v>2084.0121292576396</v>
+      </c>
+      <c r="CD84" s="1">
         <f t="shared" si="147"/>
-        <v>2183.5899216160137</v>
-      </c>
-      <c r="CE83" s="1">
+        <v>2063.1720079650631</v>
+      </c>
+      <c r="CE84" s="1">
         <f t="shared" si="147"/>
-        <v>2161.7540223998535</v>
-      </c>
-      <c r="CF83" s="1">
+        <v>2042.5402878854125</v>
+      </c>
+      <c r="CF84" s="1">
         <f t="shared" si="147"/>
-        <v>2140.1364821758548</v>
-      </c>
-      <c r="CG83" s="1">
+        <v>2022.1148850065583</v>
+      </c>
+      <c r="CG84" s="1">
         <f t="shared" si="147"/>
-        <v>2118.735117354096</v>
-      </c>
-      <c r="CH83" s="1">
+        <v>2001.8937361564927</v>
+      </c>
+      <c r="CH84" s="1">
         <f t="shared" si="147"/>
-        <v>2097.5477661805548</v>
-      </c>
-      <c r="CI83" s="1">
+        <v>1981.8747987949278</v>
+      </c>
+      <c r="CI84" s="1">
         <f t="shared" si="147"/>
-        <v>2076.5722885187492</v>
-      </c>
-      <c r="CJ83" s="1">
+        <v>1962.0560508069784</v>
+      </c>
+      <c r="CJ84" s="1">
         <f t="shared" si="147"/>
-        <v>2055.8065656335616</v>
-      </c>
-      <c r="CK83" s="1">
+        <v>1942.4354902989087</v>
+      </c>
+      <c r="CK84" s="1">
         <f t="shared" si="147"/>
-        <v>2035.2484999772259</v>
-      </c>
-      <c r="CL83" s="1">
+        <v>1923.0111353959196</v>
+      </c>
+      <c r="CL84" s="1">
         <f t="shared" si="147"/>
-        <v>2014.8960149774537</v>
-      </c>
-      <c r="CM83" s="1">
+        <v>1903.7810240419603</v>
+      </c>
+      <c r="CM84" s="1">
         <f t="shared" si="147"/>
-        <v>1994.747054827679</v>
-      </c>
-      <c r="CN83" s="1">
+        <v>1884.7432138015406</v>
+      </c>
+      <c r="CN84" s="1">
         <f t="shared" si="147"/>
-        <v>1974.7995842794021</v>
-      </c>
-      <c r="CO83" s="1">
+        <v>1865.8957816635252</v>
+      </c>
+      <c r="CO84" s="1">
         <f t="shared" si="147"/>
-        <v>1955.051588436608</v>
-      </c>
-      <c r="CP83" s="1">
+        <v>1847.23682384689</v>
+      </c>
+      <c r="CP84" s="1">
         <f t="shared" si="147"/>
-        <v>1935.5010725522418</v>
-      </c>
-      <c r="CQ83" s="1">
+        <v>1828.764455608421</v>
+      </c>
+      <c r="CQ84" s="1">
         <f t="shared" si="147"/>
-        <v>1916.1460618267195</v>
-      </c>
-      <c r="CR83" s="1">
+        <v>1810.4768110523369</v>
+      </c>
+      <c r="CR84" s="1">
         <f t="shared" si="147"/>
-        <v>1896.9846012084522</v>
-      </c>
-      <c r="CS83" s="1">
+        <v>1792.3720429418136</v>
+      </c>
+      <c r="CS84" s="1">
         <f t="shared" si="147"/>
-        <v>1878.0147551963676</v>
-      </c>
-      <c r="CT83" s="1">
+        <v>1774.4483225123954</v>
+      </c>
+      <c r="CT84" s="1">
         <f t="shared" si="147"/>
-        <v>1859.2346076444039</v>
-      </c>
-      <c r="CU83" s="1">
+        <v>1756.7038392872714</v>
+      </c>
+      <c r="CU84" s="1">
         <f t="shared" si="147"/>
-        <v>1840.6422615679598</v>
-      </c>
-      <c r="CV83" s="1">
+        <v>1739.1368008943987</v>
+      </c>
+      <c r="CV84" s="1">
         <f t="shared" si="147"/>
-        <v>1822.2358389522803</v>
-      </c>
-      <c r="CW83" s="1">
+        <v>1721.7454328854546</v>
+      </c>
+      <c r="CW84" s="1">
         <f t="shared" si="147"/>
-        <v>1804.0134805627574</v>
-      </c>
-      <c r="CX83" s="1">
+        <v>1704.5279785566001</v>
+      </c>
+      <c r="CX84" s="1">
         <f t="shared" si="147"/>
-        <v>1785.9733457571299</v>
-      </c>
-      <c r="CY83" s="1">
+        <v>1687.4826987710342</v>
+      </c>
+      <c r="CY84" s="1">
         <f t="shared" si="147"/>
-        <v>1768.1136122995586</v>
-      </c>
-      <c r="CZ83" s="1">
+        <v>1670.6078717833238</v>
+      </c>
+      <c r="CZ84" s="1">
         <f t="shared" si="147"/>
-        <v>1750.4324761765629</v>
-      </c>
-      <c r="DA83" s="1">
+        <v>1653.9017930654907</v>
+      </c>
+      <c r="DA84" s="1">
         <f t="shared" si="147"/>
-        <v>1732.9281514147972</v>
-      </c>
-      <c r="DB83" s="1">
+        <v>1637.3627751348358</v>
+      </c>
+      <c r="DB84" s="1">
         <f t="shared" si="147"/>
-        <v>1715.5988699006491</v>
-      </c>
-      <c r="DC83" s="1">
+        <v>1620.9891473834875</v>
+      </c>
+      <c r="DC84" s="1">
         <f t="shared" si="147"/>
-        <v>1698.4428812016426</v>
-      </c>
-      <c r="DD83" s="1">
+        <v>1604.7792559096526</v>
+      </c>
+      <c r="DD84" s="1">
         <f t="shared" si="147"/>
-        <v>1681.4584523896262</v>
-      </c>
-      <c r="DE83" s="1">
+        <v>1588.7314633505562</v>
+      </c>
+      <c r="DE84" s="1">
         <f t="shared" si="147"/>
-        <v>1664.64386786573</v>
-      </c>
-      <c r="DF83" s="1">
+        <v>1572.8441487170505</v>
+      </c>
+      <c r="DF84" s="1">
         <f t="shared" si="147"/>
-        <v>1647.9974291870728</v>
-      </c>
-      <c r="DG83" s="1">
+        <v>1557.1157072298799</v>
+      </c>
+      <c r="DG84" s="1">
         <f t="shared" si="147"/>
-        <v>1631.517454895202</v>
-      </c>
-      <c r="DH83" s="1">
+        <v>1541.5445501575812</v>
+      </c>
+      <c r="DH84" s="1">
         <f t="shared" si="147"/>
-        <v>1615.2022803462501</v>
-      </c>
-      <c r="DI83" s="1">
-        <f t="shared" ref="DI83:FC83" si="148">DH83*(1+$AX$22)</f>
-        <v>1599.0502575427874</v>
-      </c>
-      <c r="DJ83" s="1">
+        <v>1526.1291046560054</v>
+      </c>
+      <c r="DI84" s="1">
+        <f t="shared" ref="DI84:FC84" si="148">DH84*(1+$AX$22)</f>
+        <v>1510.8678136094454</v>
+      </c>
+      <c r="DJ84" s="1">
         <f t="shared" si="148"/>
-        <v>1583.0597549673596</v>
-      </c>
-      <c r="DK83" s="1">
+        <v>1495.7591354733509</v>
+      </c>
+      <c r="DK84" s="1">
         <f t="shared" si="148"/>
-        <v>1567.2291574176859</v>
-      </c>
-      <c r="DL83" s="1">
+        <v>1480.8015441186174</v>
+      </c>
+      <c r="DL84" s="1">
         <f t="shared" si="148"/>
-        <v>1551.5568658435091</v>
-      </c>
-      <c r="DM83" s="1">
+        <v>1465.9935286774312</v>
+      </c>
+      <c r="DM84" s="1">
         <f t="shared" si="148"/>
-        <v>1536.041297185074</v>
-      </c>
-      <c r="DN83" s="1">
+        <v>1451.3335933906569</v>
+      </c>
+      <c r="DN84" s="1">
         <f t="shared" si="148"/>
-        <v>1520.6808842132232</v>
-      </c>
-      <c r="DO83" s="1">
+        <v>1436.8202574567504</v>
+      </c>
+      <c r="DO84" s="1">
         <f t="shared" si="148"/>
-        <v>1505.474075371091</v>
-      </c>
-      <c r="DP83" s="1">
+        <v>1422.4520548821829</v>
+      </c>
+      <c r="DP84" s="1">
         <f t="shared" si="148"/>
-        <v>1490.4193346173799</v>
-      </c>
-      <c r="DQ83" s="1">
+        <v>1408.2275343333611</v>
+      </c>
+      <c r="DQ84" s="1">
         <f t="shared" si="148"/>
-        <v>1475.5151412712062</v>
-      </c>
-      <c r="DR83" s="1">
+        <v>1394.1452589900275</v>
+      </c>
+      <c r="DR84" s="1">
         <f t="shared" si="148"/>
-        <v>1460.759989858494</v>
-      </c>
-      <c r="DS83" s="1">
+        <v>1380.2038064001272</v>
+      </c>
+      <c r="DS84" s="1">
         <f t="shared" si="148"/>
-        <v>1446.152389959909</v>
-      </c>
-      <c r="DT83" s="1">
+        <v>1366.401768336126</v>
+      </c>
+      <c r="DT84" s="1">
         <f t="shared" si="148"/>
-        <v>1431.6908660603099</v>
-      </c>
-      <c r="DU83" s="1">
+        <v>1352.7377506527648</v>
+      </c>
+      <c r="DU84" s="1">
         <f t="shared" si="148"/>
-        <v>1417.3739573997068</v>
-      </c>
-      <c r="DV83" s="1">
+        <v>1339.2103731462371</v>
+      </c>
+      <c r="DV84" s="1">
         <f t="shared" si="148"/>
-        <v>1403.2002178257096</v>
-      </c>
-      <c r="DW83" s="1">
+        <v>1325.8182694147747</v>
+      </c>
+      <c r="DW84" s="1">
         <f t="shared" si="148"/>
-        <v>1389.1682156474526</v>
-      </c>
-      <c r="DX83" s="1">
+        <v>1312.5600867206269</v>
+      </c>
+      <c r="DX84" s="1">
         <f t="shared" si="148"/>
-        <v>1375.276533490978</v>
-      </c>
-      <c r="DY83" s="1">
+        <v>1299.4344858534207</v>
+      </c>
+      <c r="DY84" s="1">
         <f t="shared" si="148"/>
-        <v>1361.5237681560682</v>
-      </c>
-      <c r="DZ83" s="1">
+        <v>1286.4401409948864</v>
+      </c>
+      <c r="DZ84" s="1">
         <f t="shared" si="148"/>
-        <v>1347.9085304745074</v>
-      </c>
-      <c r="EA83" s="1">
+        <v>1273.5757395849375</v>
+      </c>
+      <c r="EA84" s="1">
         <f t="shared" si="148"/>
-        <v>1334.4294451697624</v>
-      </c>
-      <c r="EB83" s="1">
+        <v>1260.8399821890882</v>
+      </c>
+      <c r="EB84" s="1">
         <f t="shared" si="148"/>
-        <v>1321.0851507180648</v>
-      </c>
-      <c r="EC83" s="1">
+        <v>1248.2315823671972</v>
+      </c>
+      <c r="EC84" s="1">
         <f t="shared" si="148"/>
-        <v>1307.8742992108841</v>
-      </c>
-      <c r="ED83" s="1">
+        <v>1235.7492665435252</v>
+      </c>
+      <c r="ED84" s="1">
         <f t="shared" si="148"/>
-        <v>1294.7955562187753</v>
-      </c>
-      <c r="EE83" s="1">
+        <v>1223.3917738780899</v>
+      </c>
+      <c r="EE84" s="1">
         <f t="shared" si="148"/>
-        <v>1281.8476006565875</v>
-      </c>
-      <c r="EF83" s="1">
+        <v>1211.1578561393089</v>
+      </c>
+      <c r="EF84" s="1">
         <f t="shared" si="148"/>
-        <v>1269.0291246500217</v>
-      </c>
-      <c r="EG83" s="1">
+        <v>1199.0462775779158</v>
+      </c>
+      <c r="EG84" s="1">
         <f t="shared" si="148"/>
-        <v>1256.3388334035214</v>
-      </c>
-      <c r="EH83" s="1">
+        <v>1187.0558148021366</v>
+      </c>
+      <c r="EH84" s="1">
         <f t="shared" si="148"/>
-        <v>1243.7754450694863</v>
-      </c>
-      <c r="EI83" s="1">
+        <v>1175.1852566541152</v>
+      </c>
+      <c r="EI84" s="1">
         <f t="shared" si="148"/>
-        <v>1231.3376906187914</v>
-      </c>
-      <c r="EJ83" s="1">
+        <v>1163.433404087574</v>
+      </c>
+      <c r="EJ84" s="1">
         <f t="shared" si="148"/>
-        <v>1219.0243137126035</v>
-      </c>
-      <c r="EK83" s="1">
+        <v>1151.7990700466983</v>
+      </c>
+      <c r="EK84" s="1">
         <f t="shared" si="148"/>
-        <v>1206.8340705754774</v>
-      </c>
-      <c r="EL83" s="1">
+        <v>1140.2810793462313</v>
+      </c>
+      <c r="EL84" s="1">
         <f t="shared" si="148"/>
-        <v>1194.7657298697227</v>
-      </c>
-      <c r="EM83" s="1">
+        <v>1128.878268552769</v>
+      </c>
+      <c r="EM84" s="1">
         <f t="shared" si="148"/>
-        <v>1182.8180725710254</v>
-      </c>
-      <c r="EN83" s="1">
+        <v>1117.5894858672414</v>
+      </c>
+      <c r="EN84" s="1">
         <f t="shared" si="148"/>
-        <v>1170.989891845315</v>
-      </c>
-      <c r="EO83" s="1">
+        <v>1106.413591008569</v>
+      </c>
+      <c r="EO84" s="1">
         <f t="shared" si="148"/>
-        <v>1159.279992926862</v>
-      </c>
-      <c r="EP83" s="1">
+        <v>1095.3494550984833</v>
+      </c>
+      <c r="EP84" s="1">
         <f t="shared" si="148"/>
-        <v>1147.6871929975932</v>
-      </c>
-      <c r="EQ83" s="1">
+        <v>1084.3959605474984</v>
+      </c>
+      <c r="EQ84" s="1">
         <f t="shared" si="148"/>
-        <v>1136.2103210676173</v>
-      </c>
-      <c r="ER83" s="1">
+        <v>1073.5520009420234</v>
+      </c>
+      <c r="ER84" s="1">
         <f t="shared" si="148"/>
-        <v>1124.8482178569411</v>
-      </c>
-      <c r="ES83" s="1">
+        <v>1062.8164809326031</v>
+      </c>
+      <c r="ES84" s="1">
         <f t="shared" si="148"/>
-        <v>1113.5997356783716</v>
-      </c>
-      <c r="ET83" s="1">
+        <v>1052.188316123277</v>
+      </c>
+      <c r="ET84" s="1">
         <f t="shared" si="148"/>
-        <v>1102.4637383215879</v>
-      </c>
-      <c r="EU83" s="1">
+        <v>1041.6664329620442</v>
+      </c>
+      <c r="EU84" s="1">
         <f t="shared" si="148"/>
-        <v>1091.4391009383721</v>
-      </c>
-      <c r="EV83" s="1">
+        <v>1031.2497686324236</v>
+      </c>
+      <c r="EV84" s="1">
         <f t="shared" si="148"/>
-        <v>1080.5247099289884</v>
-      </c>
-      <c r="EW83" s="1">
+        <v>1020.9372709460994</v>
+      </c>
+      <c r="EW84" s="1">
         <f t="shared" si="148"/>
-        <v>1069.7194628296984</v>
-      </c>
-      <c r="EX83" s="1">
+        <v>1010.7278982366383</v>
+      </c>
+      <c r="EX84" s="1">
         <f t="shared" si="148"/>
-        <v>1059.0222682014014</v>
-      </c>
-      <c r="EY83" s="1">
+        <v>1000.6206192542719</v>
+      </c>
+      <c r="EY84" s="1">
         <f t="shared" si="148"/>
-        <v>1048.4320455193874</v>
-      </c>
-      <c r="EZ83" s="1">
+        <v>990.61441306172912</v>
+      </c>
+      <c r="EZ84" s="1">
         <f t="shared" si="148"/>
-        <v>1037.9477250641935</v>
-      </c>
-      <c r="FA83" s="1">
+        <v>980.70826893111177</v>
+      </c>
+      <c r="FA84" s="1">
         <f t="shared" si="148"/>
-        <v>1027.5682478135516</v>
-      </c>
-      <c r="FB83" s="1">
+        <v>970.9011862418007</v>
+      </c>
+      <c r="FB84" s="1">
         <f t="shared" si="148"/>
-        <v>1017.292565335416</v>
-      </c>
-      <c r="FC83" s="1">
+        <v>961.19217437938266</v>
+      </c>
+      <c r="FC84" s="1">
         <f t="shared" si="148"/>
-        <v>1007.1196396820619</v>
-      </c>
-    </row>
-    <row r="85" spans="2:159" x14ac:dyDescent="0.3">
-      <c r="B85" t="s">
+        <v>951.58025263558886</v>
+      </c>
+    </row>
+    <row r="86" spans="2:159" x14ac:dyDescent="0.3">
+      <c r="B86" t="s">
         <v>101</v>
       </c>
-      <c r="AJ85" s="10">
+      <c r="AJ86" s="10">
         <f>AJ62/AI62-1</f>
         <v>0.52</v>
       </c>
-      <c r="AK85" s="10">
-        <f t="shared" ref="AK85:AU85" si="149">AK62/AJ62-1</f>
-        <v>0.24232456140350878</v>
-      </c>
-      <c r="AL85" s="10">
+      <c r="AK86" s="10">
+        <f t="shared" ref="AK86:AU86" si="149">AK62/AJ62-1</f>
+        <v>0.23081140350877183</v>
+      </c>
+      <c r="AL86" s="10">
         <f t="shared" si="149"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AM85" s="10">
+      <c r="AM86" s="10">
         <f t="shared" si="149"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AN85" s="10">
+      <c r="AN86" s="10">
         <f t="shared" si="149"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AO85" s="10">
+      <c r="AO86" s="10">
         <f t="shared" si="149"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AP85" s="10">
+      <c r="AP86" s="10">
         <f t="shared" si="149"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AQ85" s="10">
+      <c r="AQ86" s="10">
         <f t="shared" si="149"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AR85" s="10">
+      <c r="AR86" s="10">
         <f t="shared" si="149"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AS85" s="10">
+      <c r="AS86" s="10">
         <f t="shared" si="149"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AT85" s="10">
+      <c r="AT86" s="10">
         <f t="shared" si="149"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AU85" s="10">
+      <c r="AU86" s="10">
         <f t="shared" si="149"/>
         <v>3.0000000000000027E-2</v>
       </c>
     </row>
-    <row r="86" spans="2:159" x14ac:dyDescent="0.3">
-      <c r="B86" t="s">
+    <row r="87" spans="2:159" x14ac:dyDescent="0.3">
+      <c r="B87" t="s">
         <v>102</v>
       </c>
-      <c r="AJ86" s="10">
-        <f>AJ82/AI82-1</f>
+      <c r="AJ87" s="10">
+        <f>AJ83/AI83-1</f>
         <v>9.2485549132947931E-2</v>
       </c>
-      <c r="AK86" s="10">
-        <f t="shared" ref="AK86:AU86" si="150">AK82/AJ82-1</f>
-        <v>0.41137566137566162</v>
-      </c>
-      <c r="AL86" s="10">
+      <c r="AK87" s="10">
+        <f t="shared" ref="AK87:AU87" si="150">AK83/AJ83-1</f>
+        <v>0.46296296296296302</v>
+      </c>
+      <c r="AL87" s="10">
         <f t="shared" si="150"/>
         <v>0.30000000000000004</v>
       </c>
-      <c r="AM86" s="10">
+      <c r="AM87" s="10">
         <f t="shared" si="150"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AN86" s="10">
+        <v>0.14999999999999991</v>
+      </c>
+      <c r="AN87" s="10">
         <f t="shared" si="150"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AO86" s="10">
+        <v>0.10000000000000009</v>
+      </c>
+      <c r="AO87" s="10">
         <f t="shared" si="150"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AP86" s="10">
+        <v>7.0000000000000062E-2</v>
+      </c>
+      <c r="AP87" s="10">
         <f t="shared" si="150"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AQ86" s="10">
+        <v>6.0000000000000053E-2</v>
+      </c>
+      <c r="AQ87" s="10">
         <f t="shared" si="150"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AR86" s="10">
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="AR87" s="10">
         <f t="shared" si="150"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AS86" s="10">
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="AS87" s="10">
         <f t="shared" si="150"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AT86" s="10">
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="AT87" s="10">
         <f t="shared" si="150"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AU86" s="10">
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="AU87" s="10">
         <f t="shared" si="150"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AW86" t="s">
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="AW87" t="s">
         <v>95</v>
       </c>
-      <c r="AX86" s="6">
-        <f>NPV(AX23,AJ83:FC83)</f>
-        <v>32567.343639517119</v>
-      </c>
-    </row>
-    <row r="87" spans="2:159" x14ac:dyDescent="0.3">
-      <c r="AW87" t="s">
-        <v>43</v>
-      </c>
       <c r="AX87" s="6">
-        <f>Main!D8</f>
-        <v>2323.8999999999996</v>
+        <f>NPV(AX23,AJ84:FC84)</f>
+        <v>31280.511340793932</v>
       </c>
     </row>
     <row r="88" spans="2:159" x14ac:dyDescent="0.3">
       <c r="AW88" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AX88" s="6">
-        <f>AX86+AX87</f>
-        <v>34891.243639517117</v>
+        <f>Main!D8</f>
+        <v>2116.9000000000005</v>
       </c>
     </row>
     <row r="89" spans="2:159" x14ac:dyDescent="0.3">
       <c r="AW89" t="s">
-        <v>45</v>
-      </c>
-      <c r="AX89" s="5">
-        <f>AX88/AU17</f>
-        <v>104.09082231359523</v>
+        <v>44</v>
+      </c>
+      <c r="AX89" s="6">
+        <f>AX87+AX88</f>
+        <v>33397.411340793929</v>
       </c>
     </row>
     <row r="90" spans="2:159" x14ac:dyDescent="0.3">
       <c r="AW90" t="s">
+        <v>45</v>
+      </c>
+      <c r="AX90" s="5">
+        <f>AX89/AU17</f>
+        <v>97.596175747498336</v>
+      </c>
+    </row>
+    <row r="91" spans="2:159" x14ac:dyDescent="0.3">
+      <c r="AW91" t="s">
         <v>46</v>
       </c>
-      <c r="AX90" s="5">
+      <c r="AX91" s="5">
         <f>Main!D3</f>
-        <v>225.31</v>
-      </c>
-    </row>
-    <row r="91" spans="2:159" x14ac:dyDescent="0.3">
-      <c r="AW91" s="1" t="s">
+        <v>198.52</v>
+      </c>
+    </row>
+    <row r="92" spans="2:159" x14ac:dyDescent="0.3">
+      <c r="AW92" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AX91" s="11">
-        <f>AX89/AX90-1</f>
-        <v>-0.53801064172209301</v>
+      <c r="AX92" s="11">
+        <f>AX90/AX91-1</f>
+        <v>-0.50838114171117099</v>
       </c>
     </row>
   </sheetData>
